--- a/Results/Phase 2/Ammonia/ammonia eutrophication marine results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia eutrophication marine results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008526485002888336</v>
+        <v>0.0008526485002888309</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009024653104807752</v>
+        <v>0.0009024653104807751</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000845605047283964</v>
+        <v>0.0008456050472839616</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008337502026067178</v>
+        <v>0.0008337502026067168</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000839381416620382</v>
+        <v>0.0008393814166203795</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008729592442491227</v>
+        <v>0.0008729592442491216</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008422652297619751</v>
+        <v>0.0008422652297619724</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008483548701617395</v>
+        <v>0.00084835487016174</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008539364125510784</v>
+        <v>0.0008539364125510783</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008625173429668862</v>
+        <v>0.0008625173429668845</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008629694360990163</v>
+        <v>0.0008629694360990177</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008744750027090964</v>
+        <v>0.000874475002709096</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008518582131704815</v>
+        <v>0.0008518582131704801</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001201559148296636</v>
+        <v>0.001201559148296635</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008545538387561252</v>
+        <v>0.0008545538387561246</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.000838015611219056</v>
+        <v>0.0008380156112190542</v>
       </c>
       <c r="R2" t="n">
-        <v>0.000838207727918613</v>
+        <v>0.0008382077279186104</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008488002071268536</v>
+        <v>0.0008488002071268515</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008490949315460754</v>
+        <v>0.0008490949315460741</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001094081543554181</v>
+        <v>0.001094081543554183</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008361016529817402</v>
+        <v>0.0008361016529817393</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001031752158034924</v>
+        <v>0.001031752158034927</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008473877013727455</v>
+        <v>0.0008473877013727463</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.000850818267439753</v>
+        <v>0.0008508182674397506</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009932310506495286</v>
+        <v>0.0009932310506495276</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008509192366693643</v>
+        <v>0.0008509192366693664</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.000876538470051419</v>
+        <v>0.0008765384700514183</v>
       </c>
     </row>
     <row r="3">
@@ -674,82 +674,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0009844044445347093</v>
+        <v>0.0009844044445347108</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009318304059817164</v>
+        <v>0.0009318304059817162</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009354703603034432</v>
+        <v>0.0009354703603034424</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008502894260445161</v>
+        <v>0.0008502894260445176</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008910898486940443</v>
+        <v>0.0008910898486940448</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00112930196823968</v>
+        <v>0.001129301968239678</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0009119192812979812</v>
+        <v>0.000911919281297985</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0009552829669371688</v>
+        <v>0.0009552829669371693</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009941881366239697</v>
+        <v>0.0009941881366239708</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001056402415188634</v>
+        <v>0.001056402415188632</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001058842332570696</v>
+        <v>0.001058842332570695</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001142491056823973</v>
+        <v>0.001142491056823972</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0009798745113633967</v>
+        <v>0.0009798745113633951</v>
       </c>
       <c r="O3" t="n">
         <v>0.001545369485840165</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0009981323992155758</v>
+        <v>0.0009981323992155765</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008810038897506329</v>
+        <v>0.0008810038897506338</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008826816439438602</v>
+        <v>0.000882681643943861</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009573454050562965</v>
+        <v>0.0009573454050562967</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0009604978911943846</v>
+        <v>0.0009604978911943853</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001423708224561262</v>
+        <v>0.001423708224561261</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008668340878038404</v>
+        <v>0.0008668340878038435</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001212941932841404</v>
+        <v>0.001212941932841405</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0009480954974041592</v>
+        <v>0.0009480954974041586</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009722424049608579</v>
+        <v>0.0009722424049608577</v>
       </c>
       <c r="Z3" t="n">
         <v>0.001141899114380424</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0009730281743950529</v>
+        <v>0.0009730281743950532</v>
       </c>
       <c r="AB3" t="n">
         <v>0.001156119823705701</v>
@@ -765,16 +765,16 @@
         <v>0.00112776772270603</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0008480033471139882</v>
+        <v>0.0008480033471139881</v>
       </c>
       <c r="D4" t="n">
         <v>0.001048208680867558</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000914302756740084</v>
+        <v>0.0009143027567400838</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0009779099095108504</v>
+        <v>0.0009779099095108506</v>
       </c>
       <c r="G4" t="n">
         <v>0.001357186919141336</v>
@@ -783,7 +783,7 @@
         <v>0.001010483905564735</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001079269195253073</v>
+        <v>0.001079269195253072</v>
       </c>
       <c r="J4" t="n">
         <v>0.001141906483674203</v>
@@ -795,52 +795,52 @@
         <v>0.001244347440547114</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001374452612374492</v>
+        <v>0.001374452612374491</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001118841066154214</v>
+        <v>0.001118841066154215</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001097232574185379</v>
+        <v>0.001097232574185378</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001149289397193109</v>
+        <v>0.00114928939719311</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0009624825092013477</v>
+        <v>0.0009624825092013475</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0009646525557008875</v>
+        <v>0.0009646525557008874</v>
       </c>
       <c r="S4" t="n">
         <v>0.001084299481139145</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001087628529034194</v>
+        <v>0.001087628529034193</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001204451277297963</v>
+        <v>0.001204451277297961</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0009381823934979842</v>
+        <v>0.0009381823934979839</v>
       </c>
       <c r="W4" t="n">
         <v>0.0009878200773720601</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001068344578861773</v>
+        <v>0.001068344578861772</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001100850289425391</v>
+        <v>0.00110085028942539</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0009731313625709385</v>
+        <v>0.0009731313625709377</v>
       </c>
       <c r="AA4" t="n">
         <v>0.001108234894623593</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0013943399265298</v>
+        <v>0.001394339926529799</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007143700060979637</v>
+        <v>0.007143700060979638</v>
       </c>
       <c r="C5" t="n">
         <v>0.002061320871580145</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006335241335606767</v>
+        <v>0.006335241335606773</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003298507718521663</v>
+        <v>0.003298507718521659</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004942071840186409</v>
+        <v>0.004942071840186399</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01172729431084703</v>
+        <v>0.01172729431084702</v>
       </c>
       <c r="H5" t="n">
         <v>0.005745152196399195</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007071866976302514</v>
+        <v>0.007071866976302513</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007787982867722695</v>
+        <v>0.007787982867722694</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01031782346814854</v>
+        <v>0.01031782346814856</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009953088150898229</v>
+        <v>0.009953088150898235</v>
       </c>
       <c r="M5" t="n">
         <v>0.0134375544946488</v>
       </c>
       <c r="N5" t="n">
-        <v>0.009022239518681271</v>
+        <v>0.009022239518681261</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00644290482608379</v>
+        <v>0.006442904826083793</v>
       </c>
       <c r="P5" t="n">
-        <v>0.007654044244838573</v>
+        <v>0.007654044244838565</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.004430425134075026</v>
+        <v>0.00443042513407502</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004656357418873849</v>
+        <v>0.004656357418873847</v>
       </c>
       <c r="S5" t="n">
-        <v>0.006509899177198558</v>
+        <v>0.006509899177198544</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007200425714470175</v>
+        <v>0.007200425714470165</v>
       </c>
       <c r="U5" t="n">
-        <v>0.009114093841126582</v>
+        <v>0.009114093841126564</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003689391606355642</v>
+        <v>0.003689391606355641</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004841760731992541</v>
+        <v>0.004841760731992534</v>
       </c>
       <c r="X5" t="n">
-        <v>0.006682634948560349</v>
+        <v>0.006682634948560339</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.007262550275752312</v>
+        <v>0.007262550275752293</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004354486256830507</v>
+        <v>0.004354486256830496</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.007324237475524178</v>
+        <v>0.007324237475524176</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01428982117509026</v>
+        <v>0.01428982117509024</v>
       </c>
     </row>
     <row r="6">
@@ -938,43 +938,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001285564881273551</v>
+        <v>0.001452390225326869</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001172625849734829</v>
+        <v>0.001172625849734828</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00120600583943508</v>
+        <v>0.001206005839435076</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001238925259360925</v>
+        <v>0.001072099915307602</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001135707068078371</v>
+        <v>0.00130253241213169</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001514984077708857</v>
+        <v>0.001681809421762176</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001335106408185576</v>
+        <v>0.001335106408185575</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001403891697873913</v>
+        <v>0.00123706635382059</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00129970364224172</v>
+        <v>0.001466528986295043</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001397037999214081</v>
+        <v>0.00139703799921408</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001568969943167956</v>
+        <v>0.001402144599114632</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001532249770942011</v>
+        <v>0.001532249770942009</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001277427058008942</v>
+        <v>0.001277427058008948</v>
       </c>
       <c r="O6" t="n">
         <v>0.001422704203139344</v>
@@ -983,37 +983,37 @@
         <v>0.001474761238914924</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001120279667768868</v>
+        <v>0.001120279667768864</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001289275058321728</v>
+        <v>0.001122449714268405</v>
       </c>
       <c r="S6" t="n">
         <v>0.001408921983759985</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001245425687601715</v>
+        <v>0.001245425687601711</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001368492547167051</v>
+        <v>0.001368492547167047</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001262804896118825</v>
+        <v>0.001262804896118824</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001157015547409234</v>
+        <v>0.00131329180364717</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001392967081482613</v>
+        <v>0.001392967081482612</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001274294120723601</v>
+        <v>0.001274294120723605</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001130928521138459</v>
+        <v>0.001130928521138456</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001432857397244433</v>
+        <v>0.001266032053191111</v>
       </c>
       <c r="AB6" t="n">
         <v>0.001555187684752818</v>
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001246734210045121</v>
+        <v>0.00124673421004512</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0009669698344530799</v>
+        <v>0.0009669698344530793</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00116717516820665</v>
+        <v>0.001167175168206649</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001033269244079175</v>
+        <v>0.001033269244079174</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001096876396849942</v>
+        <v>0.001096876396849941</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001476153406480427</v>
+        <v>0.001476153406480426</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001129450392903826</v>
+        <v>0.001129450392903825</v>
       </c>
       <c r="I7" t="n">
         <v>0.001198235682592164</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001260872971013294</v>
+        <v>0.001260872971013293</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001358207327985654</v>
+        <v>0.001358207327985653</v>
       </c>
       <c r="L7" t="n">
         <v>0.001363313927886205</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001493419099713582</v>
+        <v>0.001493419099713581</v>
       </c>
       <c r="N7" t="n">
         <v>0.001237807553493305</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001216188485838513</v>
+        <v>0.001216188485838512</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001268245308846244</v>
+        <v>0.001268245308846243</v>
       </c>
       <c r="Q7" t="n">
         <v>0.001081448996540438</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001083619043039979</v>
+        <v>0.001083619043039978</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001203265968478236</v>
+        <v>0.001203265968478234</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001206595016373285</v>
+        <v>0.001206595016373284</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00132950596091328</v>
+        <v>0.001329505960913279</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001057148880837076</v>
+        <v>0.001057148880837075</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001106786564711152</v>
+        <v>0.001106786564711151</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001187311066200864</v>
+        <v>0.001187311066200862</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001226060888066049</v>
+        <v>0.001226060888066048</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00109209784991003</v>
+        <v>0.001092097849910029</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001227201381962684</v>
+        <v>0.001227201381962683</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001513306413868891</v>
+        <v>0.001513306413868889</v>
       </c>
     </row>
     <row r="8">
@@ -1123,37 +1123,37 @@
         <v>0.001447161747417377</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001313255823289902</v>
+        <v>0.001217778130599945</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001225486733119057</v>
+        <v>0.001225486733119056</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001756139985691154</v>
+        <v>0.001793321240784315</v>
       </c>
       <c r="H8" t="n">
         <v>0.001409436972114553</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001478222261802891</v>
+        <v>0.001478222261802892</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001540859550224022</v>
+        <v>0.001540859550224021</v>
       </c>
       <c r="K8" t="n">
         <v>0.001638193907196381</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001643300507096934</v>
+        <v>0.001643300507096933</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001773405678924309</v>
+        <v>0.001773405678924307</v>
       </c>
       <c r="N8" t="n">
         <v>0.001378798292265494</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001395387064115926</v>
+        <v>0.001395387064115925</v>
       </c>
       <c r="P8" t="n">
         <v>0.001438080814787722</v>
@@ -1162,22 +1162,22 @@
         <v>0.001146886153609908</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001363605622250705</v>
+        <v>0.001363605622250706</v>
       </c>
       <c r="S8" t="n">
         <v>0.001483252547688963</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001486581595584011</v>
+        <v>0.001486581595584012</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001499204185006366</v>
+        <v>0.001522016629853239</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001337135460047802</v>
+        <v>0.001288002891978744</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001386808383597652</v>
+        <v>0.001386808383597651</v>
       </c>
       <c r="X8" t="n">
         <v>0.001269182411104945</v>
@@ -1186,13 +1186,13 @@
         <v>0.001684139394192592</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001372084429120755</v>
+        <v>0.00118944287523687</v>
       </c>
       <c r="AA8" t="n">
         <v>0.001507187961173411</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.00198059808017103</v>
+        <v>0.001980598080171027</v>
       </c>
     </row>
     <row r="9">
@@ -1208,22 +1208,22 @@
         <v>0.001478725079241106</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001678930412994676</v>
+        <v>0.001678930412994677</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001545024488867201</v>
+        <v>0.001510360201721816</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001608631641637968</v>
+        <v>0.001262391980437009</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001987908651268455</v>
+        <v>0.001987908679645648</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001641205637691853</v>
+        <v>0.001641205637691852</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001709990927380191</v>
+        <v>0.00170999092738019</v>
       </c>
       <c r="J9" t="n">
         <v>0.00177262821580132</v>
@@ -1232,7 +1232,7 @@
         <v>0.00186996257277368</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001875069172674232</v>
+        <v>0.00187506917267423</v>
       </c>
       <c r="M9" t="n">
         <v>0.002005174344501608</v>
@@ -1241,13 +1241,13 @@
         <v>0.001749562798281333</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001777728649251891</v>
+        <v>0.001777728649251889</v>
       </c>
       <c r="P9" t="n">
         <v>0.001840610531693017</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001593204269705658</v>
+        <v>0.001593204269705657</v>
       </c>
       <c r="R9" t="n">
         <v>0.001595374287828004</v>
@@ -1259,10 +1259,10 @@
         <v>0.00171835026116131</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001841417120726647</v>
+        <v>0.001841417120726646</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001568904125625102</v>
+        <v>0.00174222538232633</v>
       </c>
       <c r="W9" t="n">
         <v>0.001618541809499178</v>
@@ -1271,16 +1271,16 @@
         <v>0.00169906631098889</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001737816132854075</v>
+        <v>0.001737816132854074</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001603853094698056</v>
+        <v>0.001513299097286771</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.00173895662675071</v>
+        <v>0.001738956626750709</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002025061658656918</v>
+        <v>0.002025061658656916</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007635455992532496</v>
+        <v>0.000763545599253249</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008197371866976495</v>
+        <v>0.0008197371866976492</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007650611057453328</v>
+        <v>0.0007650611057453321</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000764325287328473</v>
+        <v>0.0007643252873284722</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007658323322207798</v>
+        <v>0.000765832332220779</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007665995629165226</v>
+        <v>0.0007665995629165216</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007653534024949582</v>
+        <v>0.0007653534024949574</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007653194387578793</v>
+        <v>0.0007653194387578786</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007668353206452569</v>
+        <v>0.0007668353206452567</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007669680229525518</v>
+        <v>0.0007669680229525512</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007684241503812301</v>
+        <v>0.0007684241503812294</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007650341934511759</v>
+        <v>0.0007650341934511756</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007662409865791292</v>
+        <v>0.0007662409865791284</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001085677255385883</v>
+        <v>0.001085677255385884</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007671865244713649</v>
+        <v>0.0007671865244713642</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007647574709812427</v>
+        <v>0.0007647574709812419</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007685633534906061</v>
+        <v>0.0007685633534906053</v>
       </c>
       <c r="S2" t="n">
         <v>0.000767489222876068</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007658385874528723</v>
+        <v>0.0007658385874528715</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009250609974273882</v>
+        <v>0.0009250609974273886</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007673397245664856</v>
+        <v>0.0007673397245664847</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0008969573941823853</v>
+        <v>0.0008969573941823841</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0007827402918047803</v>
+        <v>0.0007827402918047801</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0007743056571487949</v>
+        <v>0.000774305657148794</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009128364620264476</v>
+        <v>0.0009128364620264471</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0007729913997843244</v>
+        <v>0.0007729913997843236</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0007640567454095878</v>
+        <v>0.0007640567454095875</v>
       </c>
     </row>
     <row r="3">
@@ -1534,22 +1534,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000733012279350961</v>
+        <v>0.0007330122793509612</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008322055344252563</v>
+        <v>0.0008322055344252565</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007438837145392019</v>
+        <v>0.0007438837145392017</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007385230893343228</v>
+        <v>0.0007385230893343224</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007494149312004078</v>
+        <v>0.0007494149312004077</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007546787728259987</v>
+        <v>0.0007546787728259983</v>
       </c>
       <c r="H3" t="n">
         <v>0.0007460561097329492</v>
@@ -1558,61 +1558,61 @@
         <v>0.0007457612556148819</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007564377710794681</v>
+        <v>0.0007564377710794673</v>
       </c>
       <c r="K3" t="n">
         <v>0.0007573809893121478</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007676801667393099</v>
+        <v>0.0007676801667393107</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0007452483078057123</v>
+        <v>0.0007452483078057126</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0007523196923732473</v>
+        <v>0.0007523196923732475</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001294940607402644</v>
+        <v>0.001294940607402645</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0007588408733068362</v>
+        <v>0.0007588408733068366</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007416763902396661</v>
+        <v>0.0007416763902396664</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007690262402070941</v>
+        <v>0.0007690262402070944</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007610021063782811</v>
+        <v>0.0007610021063782818</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007494774176286826</v>
+        <v>0.0007494774176286824</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001021943527370768</v>
+        <v>0.001021943527370769</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007599429687555819</v>
+        <v>0.000759942968755582</v>
       </c>
       <c r="W3" t="n">
-        <v>0.000989669918037594</v>
+        <v>0.0009896699180375944</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008698604766982475</v>
+        <v>0.0008698604766982468</v>
       </c>
       <c r="Y3" t="n">
         <v>0.000809912457382025</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0009952180748716538</v>
+        <v>0.0009952180748716549</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008005028699367624</v>
+        <v>0.0008005028699367627</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0007373493017168907</v>
+        <v>0.0007373493017168913</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007026304120847873</v>
+        <v>0.0007026304120847876</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007158115069057098</v>
+        <v>0.0007158115069057097</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007197487550802981</v>
+        <v>0.0007197487550802985</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007114373475686722</v>
+        <v>0.0007114373475686728</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007284601129021751</v>
+        <v>0.0007284601129021752</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007371263365541495</v>
+        <v>0.0007371263365541503</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007230503813304647</v>
+        <v>0.0007230503813304651</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00072266674529607</v>
+        <v>0.0007226667452960706</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0007395064718647121</v>
+        <v>0.0007395064718647124</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007412882621610897</v>
+        <v>0.0007412882621610904</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007577358913197268</v>
+        <v>0.0007577358913197274</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007222641957004231</v>
+        <v>0.0007222641957004234</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001521316262528358</v>
+        <v>0.001521316262528355</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0007653133730703684</v>
+        <v>0.000765313373070369</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0007437563373317558</v>
+        <v>0.0007437563373317561</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0007163190607410085</v>
+        <v>0.0007163190607410083</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0007593082544767204</v>
+        <v>0.0007593082544767209</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0007471754550610252</v>
+        <v>0.0007471754550610254</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007285307686262156</v>
+        <v>0.0007285307686262155</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0007449942585629405</v>
+        <v>0.0007449942585629407</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007436548745028864</v>
+        <v>0.0007436548745028868</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0007776017228010849</v>
+        <v>0.0007776017228010852</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0009194432944491506</v>
+        <v>0.0009194432944491516</v>
       </c>
       <c r="Y4" t="n">
         <v>0.0008202458009004766</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0007354494425352424</v>
+        <v>0.0007354494425352428</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0008093250743662017</v>
+        <v>0.0008093250743662024</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0007094785550354668</v>
+        <v>0.0007094785550354678</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009464040478411968</v>
+        <v>0.0009464040478411972</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001202920708125604</v>
+        <v>0.001202920708125605</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001277770909246163</v>
+        <v>0.001277770909246164</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001074256265258151</v>
+        <v>0.001074256265258152</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001445803955727698</v>
+        <v>0.001445803955727697</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001489257160498463</v>
+        <v>0.001489257160498466</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001380867015038802</v>
+        <v>0.001380867015038804</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001346899218748519</v>
+        <v>0.001346899218748517</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001575657573199438</v>
+        <v>0.001575657573199435</v>
       </c>
       <c r="K5" t="n">
         <v>0.001600438370873733</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001843003585826099</v>
+        <v>0.001843003585826098</v>
       </c>
       <c r="M5" t="n">
-        <v>0.00133512101997564</v>
+        <v>0.001335121019975641</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001521316262528358</v>
+        <v>0.001521316262528355</v>
       </c>
       <c r="O5" t="n">
         <v>0.001922931491527599</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001592489562043316</v>
+        <v>0.001592489562043312</v>
       </c>
       <c r="Q5" t="n">
         <v>0.001196243311070963</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002053525937607409</v>
+        <v>0.00205352593760741</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001653407698070256</v>
+        <v>0.001653407698070254</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001456300055564587</v>
+        <v>0.001456300055564588</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001685616390700755</v>
+        <v>0.001685616390700753</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001625771670794303</v>
+        <v>0.001625771670794306</v>
       </c>
       <c r="W5" t="n">
         <v>0.002284007563489572</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004705809812623167</v>
+        <v>0.00470580981262316</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003150505812037323</v>
+        <v>0.003150505812037321</v>
       </c>
       <c r="Z5" t="n">
         <v>0.001440434536252637</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002872570755820396</v>
+        <v>0.002872570755820399</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001122012386696068</v>
+        <v>0.001122012386696071</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009409192612360648</v>
+        <v>0.000835502141525661</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009541003560569867</v>
+        <v>0.0008486832363465835</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0009580376042315755</v>
+        <v>0.0009580376042315772</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0009497261967199497</v>
+        <v>0.0008443090770095463</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009667489620534524</v>
+        <v>0.0008613318423430489</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0008699980659950228</v>
+        <v>0.0009754151857054267</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0008559221107713381</v>
+        <v>0.0009613392304817423</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008555384747369436</v>
+        <v>0.0009609555944473486</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0008723782013055851</v>
+        <v>0.0009777953210159903</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000979577111312367</v>
+        <v>0.0008741599916019637</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008906076207606002</v>
+        <v>0.0009960247404710049</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0008551359251412961</v>
+        <v>0.0009605530448517015</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001521316262528358</v>
+        <v>0.001521316262528355</v>
       </c>
       <c r="O6" t="n">
         <v>0.001008920124170177</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0008690323412562671</v>
+        <v>0.0009843225700198815</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0009546079098922855</v>
+        <v>0.0009546079098922861</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0008921799839175943</v>
+        <v>0.0009975971036279986</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0008800471845018985</v>
+        <v>0.000985464304212303</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0009668196177774926</v>
+        <v>0.000861402498067089</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0008817904029894941</v>
+        <v>0.000987207522699898</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0008765266039437598</v>
+        <v>0.0009819437236541638</v>
       </c>
       <c r="W6" t="n">
-        <v>0.000920203825520116</v>
+        <v>0.0009202038255201165</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001052315023890024</v>
+        <v>0.001052315023890025</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0009670841657964651</v>
+        <v>0.0009670841657964691</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0009737382916865197</v>
+        <v>0.0008683211719761164</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0009421968038070753</v>
+        <v>0.0009421968038070762</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0008423432348574504</v>
+        <v>0.0008423432348574509</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007796929687944608</v>
+        <v>0.0007796929687944614</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007928740636153834</v>
+        <v>0.000792874063615383</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007968113117899717</v>
+        <v>0.0007968113117899719</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0007884999042783457</v>
+        <v>0.0007884999042783461</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008055226696118489</v>
+        <v>0.0008055226696118492</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000814188893263823</v>
+        <v>0.0008141888932638238</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008001129380401386</v>
+        <v>0.0008001129380401387</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007997293020057442</v>
+        <v>0.0007997293020057441</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008165690285743858</v>
+        <v>0.0008165690285743861</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008183508188707634</v>
+        <v>0.0008183508188707639</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008347984480294</v>
+        <v>0.0008347984480294006</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0007993267524100963</v>
+        <v>0.000799326752410097</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001521316262528358</v>
+        <v>0.001521316262528355</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0008423670461264472</v>
+        <v>0.0008423670461264476</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0008208100103878345</v>
+        <v>0.0008208100103878352</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0007933816174506819</v>
+        <v>0.0007933816174506821</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0008363708111863943</v>
+        <v>0.0008363708111863948</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0008242380117706985</v>
+        <v>0.0008242380117706987</v>
       </c>
       <c r="T7" t="n">
         <v>0.0008055933253358888</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0008258780003642823</v>
+        <v>0.000825878000364283</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0008207174312125599</v>
+        <v>0.00082071743121256</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0008546642795107584</v>
+        <v>0.0008546642795107587</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0009965058511588244</v>
+        <v>0.0009965058511588246</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0009012327725958303</v>
+        <v>0.0009012327725958304</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008125119992449163</v>
+        <v>0.0008125119992449165</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0008863876310758758</v>
+        <v>0.0008863876310758765</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0007865411117451407</v>
+        <v>0.0007865411117451414</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000845050191704852</v>
+        <v>0.0008450501917048533</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009761992009624711</v>
+        <v>0.000976199200962472</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009801364491370593</v>
+        <v>0.0009801364491370613</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009718250416254335</v>
+        <v>0.0009090106070266974</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008892579148694369</v>
+        <v>0.0008892579148694377</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009975140306109111</v>
+        <v>0.001021975446157777</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009834380753872256</v>
+        <v>0.0009834380753872272</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009830544393528314</v>
+        <v>0.0009830544393528331</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0009998941659214739</v>
+        <v>0.0009998941659214746</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001001675956217851</v>
+        <v>0.001001675956217853</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001018123585376488</v>
+        <v>0.001018123585376489</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0009826518897571843</v>
+        <v>0.0009826518897571759</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001521316262528358</v>
+        <v>0.001521316262528355</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0009593860419094386</v>
+        <v>0.0009593860419094395</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0009316690741662145</v>
+        <v>0.0009316690741662159</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.00083555545269199</v>
+        <v>0.0008355554526919909</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001019695948533482</v>
+        <v>0.001019695948533483</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001007563149117787</v>
+        <v>0.001007563149117788</v>
       </c>
       <c r="T8" t="n">
-        <v>0.000988918462682976</v>
+        <v>0.0009889184626829777</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0009366464005260118</v>
+        <v>0.0009516546870395446</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001004042568559647</v>
+        <v>0.0009717195139637266</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001038012600917922</v>
+        <v>0.001038012600917923</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001049491680154781</v>
+        <v>0.001049491680154782</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001201725641902071</v>
+        <v>0.001201725641902073</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0009958371365920034</v>
+        <v>0.0008756779075809953</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001069712768422963</v>
+        <v>0.001069712768422964</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001093093600023916</v>
+        <v>0.001093093600023917</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0008712674781590662</v>
+        <v>0.0008712674781590663</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009430450061666584</v>
+        <v>0.0009430450061666591</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0009469822543412465</v>
+        <v>0.0009469822543412471</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0009386708468296212</v>
+        <v>0.0009251470635835439</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009556936121631245</v>
+        <v>0.0008206127826010683</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0009643598358150985</v>
+        <v>0.0009643598806965687</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0009502838805914135</v>
+        <v>0.000950283880591414</v>
       </c>
       <c r="I9" t="n">
-        <v>0.000949900244557019</v>
+        <v>0.0009499002445570194</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0009667399711256618</v>
+        <v>0.0009667399711256623</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009685217614220388</v>
+        <v>0.0009685217614220393</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009849693905806757</v>
+        <v>0.0009849693905806755</v>
       </c>
       <c r="M9" t="n">
         <v>0.0009494976949613719</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001521316262528358</v>
+        <v>0.001521316262528355</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001011965713319514</v>
+        <v>0.001011965713319516</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0009946319325632731</v>
+        <v>0.0009946319325632735</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.000943552604883428</v>
+        <v>0.0009435526048834292</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0009865417537376696</v>
+        <v>0.0009865417537376694</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0009744089543219741</v>
+        <v>0.0009744089543219743</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0009557642678871638</v>
+        <v>0.0009557642678871642</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0009761521728095693</v>
+        <v>0.0009761521728095694</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0009708883737638349</v>
+        <v>0.001038507444214693</v>
       </c>
       <c r="W9" t="n">
         <v>0.001004835222062034</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0011466767937101</v>
+        <v>0.001146676793710101</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001051403715147105</v>
+        <v>0.001051403715147106</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0009626829417961904</v>
+        <v>0.0009273545210047222</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001036558573627151</v>
+        <v>0.001036558573627152</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0009367120542964163</v>
+        <v>0.0009367120542964161</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008299818571598539</v>
+        <v>0.0008299818571598548</v>
       </c>
       <c r="C2" t="n">
         <v>0.0008837515420322504</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008263771317753115</v>
+        <v>0.0008263771317753124</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008147910354858701</v>
+        <v>0.0008147910354858702</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008168770000632062</v>
+        <v>0.0008168770000632072</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008431905497778996</v>
+        <v>0.0008431905497779007</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008143163118185334</v>
+        <v>0.0008143163118185344</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008205005147818738</v>
+        <v>0.0008205005147818745</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008315449214297054</v>
+        <v>0.0008315449214297058</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008394778718434495</v>
+        <v>0.0008394778718434487</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008437686154278506</v>
+        <v>0.0008437686154278516</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008415413562622606</v>
+        <v>0.0008415413562622604</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008256215602332466</v>
+        <v>0.0008256215602332475</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001168891191514715</v>
+        <v>0.001168891191514714</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008437507977245111</v>
+        <v>0.000843750797724512</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0008177515484964941</v>
+        <v>0.0008177515484964952</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0008143156404626814</v>
+        <v>0.0008143156404626822</v>
       </c>
       <c r="S2" t="n">
-        <v>0.000831156475328635</v>
+        <v>0.0008311564753286358</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008244824337954485</v>
+        <v>0.0008244824337954495</v>
       </c>
       <c r="U2" t="n">
         <v>0.001056344852031129</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008138284905075665</v>
+        <v>0.0008138284905075675</v>
       </c>
       <c r="W2" t="n">
         <v>0.001004534402706849</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008320604874540065</v>
+        <v>0.0008320604874540074</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.000830014481816022</v>
+        <v>0.0008300144818160237</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.000968968582575748</v>
+        <v>0.00096896858257575</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008280733385529711</v>
+        <v>0.0008280733385529731</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008581586645517163</v>
+        <v>0.0008581586645517154</v>
       </c>
     </row>
     <row r="3">
@@ -2394,82 +2394,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0009310909893303447</v>
+        <v>0.0009310909893303467</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009160718038637991</v>
+        <v>0.0009160718038637989</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009065455913845629</v>
+        <v>0.0009065455913845645</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000823325836208455</v>
+        <v>0.000823325836208456</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008385632889733961</v>
+        <v>0.0008385632889733965</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001025296315436484</v>
+        <v>0.001025296315436486</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008203586238371811</v>
+        <v>0.000820358623837182</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008645510137441638</v>
+        <v>0.0008645510137441656</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000942728893212102</v>
+        <v>0.0009427288932121023</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009993339324951632</v>
+        <v>0.0009993339324951655</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001030162364206047</v>
+        <v>0.001030162364206048</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001015863275536969</v>
+        <v>0.00101586327553697</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0009008881475225627</v>
+        <v>0.0009008881475225641</v>
       </c>
       <c r="O3" t="n">
         <v>0.001479253074249687</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001029211761561769</v>
+        <v>0.001029211761561771</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008446665876953482</v>
+        <v>0.0008446665876953483</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008202951536768672</v>
+        <v>0.0008202951536768681</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009396971535272638</v>
+        <v>0.0009396971535272649</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008929749488024875</v>
+        <v>0.0008929749488024888</v>
       </c>
       <c r="U3" t="n">
         <v>0.001354254864011655</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008162770651031516</v>
+        <v>0.0008162770651031538</v>
       </c>
       <c r="W3" t="n">
         <v>0.001202669550253593</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0009470331819616377</v>
+        <v>0.0009470331819616388</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009320141187875296</v>
+        <v>0.0009320141187875309</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001097290321700495</v>
+        <v>0.001097290321700496</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0009182345443465253</v>
+        <v>0.0009182345443465256</v>
       </c>
       <c r="AB3" t="n">
         <v>0.001132765995929639</v>
@@ -2488,22 +2488,22 @@
         <v>0.000819044002734952</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000993828915270304</v>
+        <v>0.0009938289152703044</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008629586278134497</v>
+        <v>0.0008629586278134499</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008865205573055718</v>
+        <v>0.0008865205573055717</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001183744206163951</v>
+        <v>0.001183744206163949</v>
       </c>
       <c r="H4" t="n">
         <v>0.0008575964056072054</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0009274498229520467</v>
+        <v>0.0009274498229520469</v>
       </c>
       <c r="J4" t="n">
         <v>0.001051775682302364</v>
@@ -2518,31 +2518,31 @@
         <v>0.001166300990921084</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0009852943871226029</v>
+        <v>0.0009852943871226027</v>
       </c>
       <c r="O4" t="n">
         <v>0.001011622383091521</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001190072464447721</v>
+        <v>0.001190072464447722</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0008963989841717169</v>
+        <v>0.000896398984171717</v>
       </c>
       <c r="R4" t="n">
-        <v>0.000857588822334014</v>
+        <v>0.0008575888223340143</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001047813799311751</v>
+        <v>0.001047813799311752</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0009724274299836282</v>
+        <v>0.0009724274299836283</v>
       </c>
       <c r="U4" t="n">
         <v>0.001131182608177959</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0008492900463547503</v>
+        <v>0.0008492900463547504</v>
       </c>
       <c r="W4" t="n">
         <v>0.0009988819345575258</v>
@@ -2551,16 +2551,16 @@
         <v>0.001058025032133948</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001030437790195965</v>
+        <v>0.001030437790195966</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0009034058582467721</v>
+        <v>0.0009034058582467723</v>
       </c>
       <c r="AA4" t="n">
         <v>0.001012988351117651</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001348641095562809</v>
+        <v>0.001348641095562808</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005577253210873773</v>
+        <v>0.005577253210873774</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001942928386460966</v>
+        <v>0.001942928386460964</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005464588380378466</v>
+        <v>0.005464588380378456</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002695785056394034</v>
+        <v>0.002695785056394035</v>
       </c>
       <c r="F5" t="n">
         <v>0.003335844720302809</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008361700635772816</v>
+        <v>0.008361700635772825</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002828489000179756</v>
+        <v>0.002828489000179757</v>
       </c>
       <c r="I5" t="n">
         <v>0.004180095518405544</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006178853276446825</v>
+        <v>0.006178853276446831</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007866415189945491</v>
+        <v>0.007866415189945486</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008896916016892395</v>
+        <v>0.008896916016892407</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008973675386105873</v>
+        <v>0.008973675386105891</v>
       </c>
       <c r="N5" t="n">
-        <v>0.007565530860234015</v>
+        <v>0.007565530860234007</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00506845122217368</v>
+        <v>0.005068451222173682</v>
       </c>
       <c r="P5" t="n">
-        <v>0.008435154393404665</v>
+        <v>0.008435154393404675</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003445655244293353</v>
+        <v>0.003445655244293354</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002795711347412458</v>
+        <v>0.002795711347412461</v>
       </c>
       <c r="S5" t="n">
-        <v>0.005952062238157701</v>
+        <v>0.00595206223815772</v>
       </c>
       <c r="T5" t="n">
-        <v>0.005033186531850931</v>
+        <v>0.005033186531850926</v>
       </c>
       <c r="U5" t="n">
-        <v>0.007715895748337228</v>
+        <v>0.007715895748337216</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002387841501808315</v>
+        <v>0.00238784150180831</v>
       </c>
       <c r="W5" t="n">
-        <v>0.005331242630743574</v>
+        <v>0.005331242630743575</v>
       </c>
       <c r="X5" t="n">
-        <v>0.006636801000103843</v>
+        <v>0.006636801000103863</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.005968124896232924</v>
+        <v>0.005968124896232933</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.003360683249048528</v>
+        <v>0.003360683249048522</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.005594960271568014</v>
+        <v>0.005594960271568018</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01309783613492395</v>
+        <v>0.01309783613492394</v>
       </c>
     </row>
     <row r="6">
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001325444891834434</v>
+        <v>0.001181888858058407</v>
       </c>
       <c r="C6" t="n">
         <v>0.001109942947825072</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001141171826584398</v>
+        <v>0.001284727860360424</v>
       </c>
       <c r="E6" t="n">
         <v>0.001010301539127543</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001177419502395692</v>
+        <v>0.001033863468619665</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001474643151254071</v>
+        <v>0.001331087117478043</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001004939316921299</v>
+        <v>0.001148495350697325</v>
       </c>
       <c r="I6" t="n">
         <v>0.001074792734266139</v>
@@ -2685,58 +2685,58 @@
         <v>0.001342674627392483</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001289150712292207</v>
+        <v>0.001432706746068235</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00133761663491758</v>
+        <v>0.001337616634917581</v>
       </c>
       <c r="M6" t="n">
         <v>0.001313643902235177</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001133122803406845</v>
+        <v>0.001133122803406848</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001302768154975895</v>
+        <v>0.001302768154975896</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001481218638289271</v>
+        <v>0.001481218638289272</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.00104374189548581</v>
+        <v>0.001187297929261836</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001004931733648108</v>
+        <v>0.001148487767424133</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001195156710625845</v>
+        <v>0.001338712744401871</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001263326375073748</v>
+        <v>0.001119770341297721</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001426558220315943</v>
+        <v>0.001283002186539917</v>
       </c>
       <c r="V6" t="n">
-        <v>0.00114018899144487</v>
+        <v>0.001140188991444869</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001290026484665542</v>
+        <v>0.001290026484665543</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001205367943448041</v>
+        <v>0.001348923977224067</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001190747547834769</v>
+        <v>0.001190747547834772</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001050748769560866</v>
+        <v>0.001194304803336892</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.00130388729620777</v>
+        <v>0.001160331262431745</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001498872276931104</v>
+        <v>0.001498872276931103</v>
       </c>
     </row>
     <row r="7">
@@ -2749,22 +2749,22 @@
         <v>0.001137082186821867</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0009215802428125052</v>
+        <v>0.000921580242812505</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001096365155347857</v>
+        <v>0.001096365155347858</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0009654948678910029</v>
+        <v>0.0009654948678910027</v>
       </c>
       <c r="F7" t="n">
         <v>0.0009890567973831245</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001286280446241504</v>
+        <v>0.001286280446241502</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009601326456847585</v>
+        <v>0.000960132645684759</v>
       </c>
       <c r="I7" t="n">
         <v>0.001029986063029599</v>
@@ -2776,28 +2776,28 @@
         <v>0.001244344041055669</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001292809963681039</v>
+        <v>0.00129280996368104</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001268837230998638</v>
+        <v>0.001268837230998637</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001087830627200155</v>
+        <v>0.001087830627200156</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001114148833510342</v>
+        <v>0.001114148833510343</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001292598914866543</v>
+        <v>0.001292598914866544</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0009989352242492698</v>
+        <v>0.0009989352242492696</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0009601250624115671</v>
+        <v>0.0009601250624115675</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001150350039389304</v>
+        <v>0.001150350039389305</v>
       </c>
       <c r="T7" t="n">
         <v>0.001074963670061181</v>
@@ -2806,13 +2806,13 @@
         <v>0.00123806093629063</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0009518262864323035</v>
+        <v>0.0009518262864323037</v>
       </c>
       <c r="W7" t="n">
         <v>0.001101418174635079</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001160561272211502</v>
+        <v>0.001160561272211501</v>
       </c>
       <c r="Y7" t="n">
         <v>0.001137450697321383</v>
@@ -2843,19 +2843,19 @@
         <v>0.001338298970687417</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001207428683230562</v>
+        <v>0.001124874619323187</v>
       </c>
       <c r="F8" t="n">
         <v>0.001100104290674675</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001528214261581063</v>
+        <v>0.001560362752214181</v>
       </c>
       <c r="H8" t="n">
         <v>0.001202066461024318</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001271919878369159</v>
+        <v>0.001271919878369158</v>
       </c>
       <c r="J8" t="n">
         <v>0.001396245737719475</v>
@@ -2864,19 +2864,19 @@
         <v>0.001486277856395228</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0015347437790206</v>
+        <v>0.001534743779020599</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001510771046338196</v>
+        <v>0.001510771046338186</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001209582741756125</v>
+        <v>0.001209582741756124</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001268937712609097</v>
+        <v>0.001268937712609096</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001439292084378836</v>
+        <v>0.001439292084378837</v>
       </c>
       <c r="Q8" t="n">
         <v>0.001055360506572265</v>
@@ -2885,34 +2885,34 @@
         <v>0.001202058877751126</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001392283854728864</v>
+        <v>0.001392283854728865</v>
       </c>
       <c r="T8" t="n">
         <v>0.00131689748540074</v>
       </c>
       <c r="U8" t="n">
-        <v>0.00138463516722101</v>
+        <v>0.00140435981637208</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001193760101771863</v>
+        <v>0.001151278748698336</v>
       </c>
       <c r="W8" t="n">
         <v>0.001343382459694348</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001231196250585949</v>
+        <v>0.00123119625058595</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00153337151149411</v>
+        <v>0.001533371511494111</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001247875913663885</v>
+        <v>0.001089956277289711</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001357458406534764</v>
+        <v>0.001357458406534763</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001855063076024667</v>
+        <v>0.001855063076024665</v>
       </c>
     </row>
     <row r="9">
@@ -2922,25 +2922,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001388304575859563</v>
+        <v>0.001388304575859562</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001285729990101221</v>
+        <v>0.00128572999010122</v>
       </c>
       <c r="D9" t="n">
         <v>0.001460514902636574</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001329644615179719</v>
+        <v>0.001303581470041934</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001353206544671841</v>
+        <v>0.001092878114699346</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001650430193530219</v>
+        <v>0.001650430230613163</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001324282392973475</v>
+        <v>0.001324282392973474</v>
       </c>
       <c r="I9" t="n">
         <v>0.001394135810318315</v>
@@ -2949,10 +2949,10 @@
         <v>0.001518461669668632</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001608493788344385</v>
+        <v>0.001608493788344384</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001656959710969757</v>
+        <v>0.001656959710969758</v>
       </c>
       <c r="M9" t="n">
         <v>0.001632986978287353</v>
@@ -2964,13 +2964,13 @@
         <v>0.001515732398489125</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001702321555788613</v>
+        <v>0.001702321555788614</v>
       </c>
       <c r="Q9" t="n">
         <v>0.001363085008620931</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001324274809700284</v>
+        <v>0.001324274809700283</v>
       </c>
       <c r="S9" t="n">
         <v>0.00151449978667802</v>
@@ -2979,28 +2979,28 @@
         <v>0.001439113417349897</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001602345262592092</v>
+        <v>0.001602345262592093</v>
       </c>
       <c r="V9" t="n">
-        <v>0.00131597603372102</v>
+        <v>0.001446291708240324</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001465567921923796</v>
+        <v>0.001465567921923795</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001524711019500218</v>
+        <v>0.001524711019500217</v>
       </c>
       <c r="Y9" t="n">
         <v>0.0015016004446101</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001370091845613042</v>
+        <v>0.001302006705205425</v>
       </c>
       <c r="AA9" t="n">
         <v>0.00147967433848392</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001815327082929078</v>
+        <v>0.001815327082929077</v>
       </c>
     </row>
   </sheetData>
@@ -3166,58 +3166,58 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008219938637255963</v>
+        <v>0.0008219938637255958</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008812679033526254</v>
+        <v>0.0008812679033526257</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008276538286938934</v>
+        <v>0.000827653828693893</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008123545816732802</v>
+        <v>0.0008123545816732796</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000814373295772286</v>
+        <v>0.0008143732957722856</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008379686453217844</v>
+        <v>0.0008379686453217842</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008084951215199313</v>
+        <v>0.0008084951215199311</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000822560207309349</v>
+        <v>0.0008225602073093484</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008263641735173097</v>
+        <v>0.0008263641735173089</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008275440002774364</v>
+        <v>0.0008275440002774358</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008352117800626667</v>
+        <v>0.0008352117800626661</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008259031758447557</v>
+        <v>0.0008259031758447561</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008168145510657257</v>
+        <v>0.0008168145510657252</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001157489958646358</v>
+        <v>0.001157489958646357</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008405478764073797</v>
+        <v>0.0008405478764073796</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0008132397035677272</v>
+        <v>0.0008132397035677265</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0008082082247843235</v>
+        <v>0.0008082082247843238</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008265642264389329</v>
+        <v>0.0008265642264389326</v>
       </c>
       <c r="T2" t="n">
         <v>0.0008188329354924821</v>
@@ -3226,25 +3226,25 @@
         <v>0.001055223979059001</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008134254799590555</v>
+        <v>0.0008134254799590548</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001003767144784327</v>
+        <v>0.001003767144784328</v>
       </c>
       <c r="X2" t="n">
-        <v>0.000833711354678406</v>
+        <v>0.0008337113546784058</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008425943462909924</v>
+        <v>0.0008425943462909931</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009656672679840221</v>
+        <v>0.0009656672679840212</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.000826125581801188</v>
+        <v>0.0008261255818011876</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008521666949939676</v>
+        <v>0.0008521666949939678</v>
       </c>
     </row>
     <row r="3">
@@ -3254,82 +3254,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008915121581767957</v>
+        <v>0.0008915121581767953</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009110071217168099</v>
+        <v>0.0009110071217168103</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009328118747350295</v>
+        <v>0.0009328118747350297</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008231075117613336</v>
+        <v>0.0008231075117613332</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008377946654624104</v>
+        <v>0.0008377946654624102</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001005045078244952</v>
+        <v>0.001005045078244953</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007958647013974615</v>
+        <v>0.0007958647013974619</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008965064298284116</v>
+        <v>0.0008965064298284114</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009228405211513288</v>
+        <v>0.0009228405211513294</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009310128412562409</v>
+        <v>0.000931012841256241</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009862002192122404</v>
+        <v>0.00098620021921224</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0009219323139957522</v>
+        <v>0.0009219323139957524</v>
       </c>
       <c r="N3" t="n">
-        <v>0.000855146144622983</v>
+        <v>0.0008551461446229826</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001439554350616977</v>
+        <v>0.001439554350616978</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001023362089998454</v>
+        <v>0.001023362089998455</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008295303161650598</v>
+        <v>0.0008295303161650597</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00079375653453673</v>
+        <v>0.0007937565345367289</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009240488916224625</v>
+        <v>0.0009240488916224638</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000869765677087933</v>
+        <v>0.0008697656770879331</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001350578031950911</v>
+        <v>0.001350578031950912</v>
       </c>
       <c r="V3" t="n">
         <v>0.0008304263390673214</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001201484499387514</v>
+        <v>0.001201484499387513</v>
       </c>
       <c r="X3" t="n">
-        <v>0.000975977614401224</v>
+        <v>0.0009759776144012243</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001038960872899079</v>
+        <v>0.00103896087289908</v>
       </c>
       <c r="Z3" t="n">
         <v>0.001091933769082025</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0009215176745865644</v>
+        <v>0.0009215176745865638</v>
       </c>
       <c r="AB3" t="n">
         <v>0.001107303256602492</v>
@@ -3345,13 +3345,13 @@
         <v>0.0009643107298773944</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0008017956640991395</v>
+        <v>0.0008017956640991394</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001028242637906825</v>
+        <v>0.001028242637906826</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000855430604807657</v>
+        <v>0.0008554306048076571</v>
       </c>
       <c r="F4" t="n">
         <v>0.0008782329092102984</v>
@@ -3360,64 +3360,64 @@
         <v>0.001144753236768938</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008118362269361996</v>
+        <v>0.0008118362269362</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0009707078411867886</v>
+        <v>0.0009707078411867892</v>
       </c>
       <c r="J4" t="n">
         <v>0.001013290275434815</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001027002075419375</v>
+        <v>0.001027002075419376</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001113613175446519</v>
+        <v>0.00111361317544652</v>
       </c>
       <c r="M4" t="n">
         <v>0.001011155221417084</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0009058080107826161</v>
+        <v>0.0009058080107826163</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0009530586322000897</v>
+        <v>0.000953058632200091</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001173886838385655</v>
+        <v>0.001173886838385657</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0008654284637816257</v>
+        <v>0.0008654284637816261</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0008085955963284976</v>
+        <v>0.0008085955963284974</v>
       </c>
       <c r="S4" t="n">
         <v>0.001015935079195252</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0009286065913855488</v>
+        <v>0.0009286065913855495</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001113092356404268</v>
+        <v>0.001113092356404269</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0008650026869465255</v>
+        <v>0.0008650026869465256</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0009837076392890346</v>
+        <v>0.0009837076392890339</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001096665180501528</v>
+        <v>0.001096665180501529</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001193259943695914</v>
+        <v>0.001193259943695915</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0008887382591136913</v>
+        <v>0.0008887382591136916</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001010980386225421</v>
+        <v>0.001010980386225422</v>
       </c>
       <c r="AB4" t="n">
         <v>0.00130131838110648</v>
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004334821510613586</v>
+        <v>0.004334821510613591</v>
       </c>
       <c r="C5" t="n">
         <v>0.001712182514484234</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00593417493748338</v>
+        <v>0.005934174937483393</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002611924855863109</v>
+        <v>0.002611924855863113</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003160060130878426</v>
+        <v>0.003160060130878424</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007277552832416079</v>
+        <v>0.007277552832416073</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001997571138812858</v>
+        <v>0.001997571138812857</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004941444046784176</v>
+        <v>0.004941444046784182</v>
       </c>
       <c r="J5" t="n">
         <v>0.005278655149940146</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00538614086929641</v>
+        <v>0.005386140869296411</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007157447517883602</v>
+        <v>0.007157447517883607</v>
       </c>
       <c r="M5" t="n">
-        <v>0.005712295122094437</v>
+        <v>0.005712295122094442</v>
       </c>
       <c r="N5" t="n">
-        <v>0.006823043778008231</v>
+        <v>0.006823043778008257</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003985407097514077</v>
+        <v>0.003985407097514083</v>
       </c>
       <c r="P5" t="n">
-        <v>0.007745624039982689</v>
+        <v>0.007745624039982726</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002843501500483439</v>
+        <v>0.002843501500483446</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001908866082001721</v>
+        <v>0.001908866082001722</v>
       </c>
       <c r="S5" t="n">
-        <v>0.005205299196816512</v>
+        <v>0.005205299196816528</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004124766245624156</v>
+        <v>0.004124766245624168</v>
       </c>
       <c r="U5" t="n">
-        <v>0.007034070837077689</v>
+        <v>0.00703407083707772</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00265532096937315</v>
+        <v>0.00265532096937313</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004937470102256628</v>
+        <v>0.004937470102256622</v>
       </c>
       <c r="X5" t="n">
-        <v>0.007109554540671827</v>
+        <v>0.007109554540671847</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.008669075665838194</v>
+        <v>0.008669075665838209</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002982125849015302</v>
+        <v>0.002982125849015304</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.005428297164789133</v>
+        <v>0.005428297164789127</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01159882503963866</v>
+        <v>0.01159882503963865</v>
       </c>
     </row>
     <row r="6">
@@ -3518,37 +3518,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001233898902932142</v>
+        <v>0.001102602267089867</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009400872013116111</v>
+        <v>0.0009400872013116114</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001297830810961573</v>
+        <v>0.001297830810961574</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0009937221420201288</v>
+        <v>0.0009937221420201294</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00101652444642277</v>
+        <v>0.001147821082265046</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001414341409823687</v>
+        <v>0.001283044773981411</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009501277641486721</v>
+        <v>0.0009501277641486724</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001240296014241537</v>
+        <v>0.001108999378399261</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001282878448489562</v>
+        <v>0.001282878448489563</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001165293612631847</v>
+        <v>0.001296590248474124</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001383201348501268</v>
+        <v>0.001251904712658992</v>
       </c>
       <c r="M6" t="n">
         <v>0.001280743394471831</v>
@@ -3557,46 +3557,46 @@
         <v>0.001044599874158672</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001222966229210444</v>
+        <v>0.001091850495576147</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001443794284174171</v>
+        <v>0.001443794284174173</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001135016636836373</v>
+        <v>0.001135016636836374</v>
       </c>
       <c r="R6" t="n">
         <v>0.001078183769383245</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001154226616407723</v>
+        <v>0.001154226616407725</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001066898128598021</v>
+        <v>0.001066898128598022</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001386423242906832</v>
+        <v>0.001255126607064558</v>
       </c>
       <c r="V6" t="n">
         <v>0.001134590860001273</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001253614298765919</v>
+        <v>0.00113205661626433</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001234956717714</v>
+        <v>0.001234956717714001</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001343376281092505</v>
+        <v>0.001343376281092506</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001158326432168439</v>
+        <v>0.001027029796326163</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001149271923437893</v>
+        <v>0.001280568559280169</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001442080330953324</v>
+        <v>0.001442080330953325</v>
       </c>
     </row>
     <row r="7">
@@ -3609,79 +3609,79 @@
         <v>0.001057683365748858</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008951682999706022</v>
+        <v>0.0008951682999706023</v>
       </c>
       <c r="D7" t="n">
         <v>0.001121615273778289</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0009488032406791203</v>
+        <v>0.0009488032406791204</v>
       </c>
       <c r="F7" t="n">
         <v>0.0009716055450817614</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001238125872640401</v>
+        <v>0.001238125872640402</v>
       </c>
       <c r="H7" t="n">
         <v>0.0009052088628076627</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001064080477058252</v>
+        <v>0.001064080477058253</v>
       </c>
       <c r="J7" t="n">
         <v>0.001106662911306278</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001120374711290838</v>
+        <v>0.001120374711290839</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001206985811317983</v>
+        <v>0.001206985811317984</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001104527857288547</v>
+        <v>0.001104527857288546</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0009991806466540796</v>
+        <v>0.0009991806466540798</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00104642211006467</v>
+        <v>0.001046422110064671</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001267250316250234</v>
+        <v>0.001267250316250237</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0009588010996530882</v>
+        <v>0.0009588010996530887</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0009019682321999601</v>
+        <v>0.0009019682321999602</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001109307715066714</v>
+        <v>0.001109307715066715</v>
       </c>
       <c r="T7" t="n">
         <v>0.001021979227257012</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0012100855917844</v>
+        <v>0.001210085591784402</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0009583753228179893</v>
+        <v>0.0009583753228179889</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001077080275160497</v>
+        <v>0.001077080275160496</v>
       </c>
       <c r="X7" t="n">
         <v>0.001190037816372991</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001290375293015194</v>
+        <v>0.001290375293015196</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0009821108949851546</v>
+        <v>0.000982110894985155</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001104353022096884</v>
+        <v>0.001104353022096885</v>
       </c>
       <c r="AB7" t="n">
         <v>0.001394691016977943</v>
@@ -3703,13 +3703,13 @@
         <v>0.001342174052758396</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001169362019659228</v>
+        <v>0.001094044355679814</v>
       </c>
       <c r="F8" t="n">
         <v>0.001072751038307912</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001458684651620508</v>
+        <v>0.001488015118230468</v>
       </c>
       <c r="H8" t="n">
         <v>0.00112576764178777</v>
@@ -3721,22 +3721,22 @@
         <v>0.001327221690286384</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001340933490270945</v>
+        <v>0.001340933490270946</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001427544590298089</v>
+        <v>0.00142754459029809</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001325086636268654</v>
+        <v>0.001325086636268645</v>
       </c>
       <c r="N8" t="n">
         <v>0.001110092431559377</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001187474998986909</v>
+        <v>0.001187474998986911</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001400917137116637</v>
+        <v>0.001400917137116638</v>
       </c>
       <c r="Q8" t="n">
         <v>0.001010112373498418</v>
@@ -3745,16 +3745,16 @@
         <v>0.001122527011180067</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00132986649404682</v>
+        <v>0.001329866494046822</v>
       </c>
       <c r="T8" t="n">
         <v>0.001242538006237119</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001343643656139248</v>
+        <v>0.001361639353983065</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001178934101798095</v>
+        <v>0.001140177280130839</v>
       </c>
       <c r="W8" t="n">
         <v>0.001297666852991302</v>
@@ -3763,16 +3763,16 @@
         <v>0.001254313214112258</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001651424296484695</v>
+        <v>0.001651424296484697</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001202669673965262</v>
+        <v>0.00105859271947962</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001324911801076991</v>
+        <v>0.001324911801076992</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.00176300558282055</v>
+        <v>0.001763005582820551</v>
       </c>
     </row>
     <row r="9">
@@ -3788,16 +3788,16 @@
         <v>0.001194608085598271</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001421055059405956</v>
+        <v>0.001421055059405957</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001248243026306788</v>
+        <v>0.001226095607266598</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001271045330709429</v>
+        <v>0.001049828367782768</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001537565658268069</v>
+        <v>0.001537565719596442</v>
       </c>
       <c r="H9" t="n">
         <v>0.001204648648435332</v>
@@ -3806,7 +3806,7 @@
         <v>0.001363520262685921</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001406102696933946</v>
+        <v>0.001406102696933945</v>
       </c>
       <c r="K9" t="n">
         <v>0.001419814496918507</v>
@@ -3824,37 +3824,37 @@
         <v>0.00137767256957846</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001605417046507358</v>
+        <v>0.001605417046507359</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001258240946609127</v>
+        <v>0.001258240946609128</v>
       </c>
       <c r="R9" t="n">
         <v>0.001201408017827629</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001408747500694382</v>
+        <v>0.001408747500694383</v>
       </c>
       <c r="T9" t="n">
         <v>0.001321419012884681</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001509647491351215</v>
+        <v>0.001509647491351217</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001257815108445657</v>
+        <v>0.001368552337838665</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001376520060788166</v>
+        <v>0.001376520060788165</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001489477602000659</v>
+        <v>0.00148947760200066</v>
       </c>
       <c r="Y9" t="n">
         <v>0.001589815078642863</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001281550680612823</v>
+        <v>0.001223694601463372</v>
       </c>
       <c r="AA9" t="n">
         <v>0.001403792807724553</v>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.000832579570115248</v>
+        <v>0.0008325795701152473</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008807070527065591</v>
+        <v>0.0008807070527065587</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008329012844504809</v>
+        <v>0.0008329012844504812</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008225961221399736</v>
+        <v>0.0008225961221399743</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008297578666947384</v>
+        <v>0.0008297578666947391</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008470377883953015</v>
+        <v>0.0008470377883953021</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008215847881142377</v>
+        <v>0.0008215847881142373</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008350310155481393</v>
+        <v>0.0008350310155481398</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008373547964204283</v>
+        <v>0.0008373547964204277</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008450987036309524</v>
+        <v>0.0008450987036309519</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008435170948033958</v>
+        <v>0.0008435170948033963</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008358992919632452</v>
+        <v>0.000835899291963245</v>
       </c>
       <c r="N2" t="n">
-        <v>0.000825175977456707</v>
+        <v>0.0008251759774567072</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001171927533238508</v>
+        <v>0.001171927533238506</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008497478469994756</v>
+        <v>0.0008497478469994761</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0008268893102153752</v>
+        <v>0.0008268893102153756</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0008244630161710728</v>
+        <v>0.0008244630161710734</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008382144863261436</v>
+        <v>0.0008382144863261441</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008327684315594927</v>
+        <v>0.0008327684315594931</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001032984461803869</v>
+        <v>0.00103298446180387</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008331120003264364</v>
+        <v>0.0008331120003264368</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009844622554653014</v>
+        <v>0.0009844622554653021</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008484550952802505</v>
+        <v>0.0008484550952802504</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008807887823863937</v>
+        <v>0.0008807887823863938</v>
       </c>
       <c r="Z2" t="n">
         <v>0.0009773494074436966</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008413206115649048</v>
+        <v>0.0008413206115649053</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008609976088722316</v>
+        <v>0.0008609976088722312</v>
       </c>
     </row>
     <row r="3">
@@ -4114,73 +4114,73 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008878925252516275</v>
+        <v>0.0008878925252516284</v>
       </c>
       <c r="C3" t="n">
         <v>0.0009003957656849983</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008908145851681293</v>
+        <v>0.0008908145851681303</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008170362458881071</v>
+        <v>0.0008170362458881069</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000868527119960209</v>
+        <v>0.0008685271199602095</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009904705387075662</v>
+        <v>0.0009904705387075658</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008102297307899108</v>
+        <v>0.0008102297307899107</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0009063060993319523</v>
+        <v>0.0009063060993319524</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009220881558030877</v>
+        <v>0.0009220881558030879</v>
       </c>
       <c r="K3" t="n">
         <v>0.0009771336474311753</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009660488026657205</v>
+        <v>0.0009660488026657207</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0009139721064450525</v>
+        <v>0.0009139721064450523</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008357241612644197</v>
+        <v>0.0008357241612644191</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001439625503478493</v>
+        <v>0.001439625503478494</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00100967319307407</v>
+        <v>0.001009673193074071</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000847794089341444</v>
+        <v>0.0008477940893414441</v>
       </c>
       <c r="R3" t="n">
         <v>0.0008308083819140316</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009280690069805558</v>
+        <v>0.0009280690069805559</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008901894628957627</v>
+        <v>0.000890189462895763</v>
       </c>
       <c r="U3" t="n">
         <v>0.00132364991786571</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008915270691039459</v>
+        <v>0.0008915270691039456</v>
       </c>
       <c r="W3" t="n">
         <v>0.001133274845393113</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001001780054387732</v>
+        <v>0.001001780054387733</v>
       </c>
       <c r="Y3" t="n">
         <v>0.001232957984924428</v>
@@ -4189,7 +4189,7 @@
         <v>0.001096808452557737</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0009509631532759023</v>
+        <v>0.0009509631532759026</v>
       </c>
       <c r="AB3" t="n">
         <v>0.001091065688496401</v>
@@ -4202,25 +4202,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0009478833621184799</v>
+        <v>0.0009478833621184798</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0008086527933840125</v>
+        <v>0.0008086527933840124</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009515172735308518</v>
+        <v>0.0009515172735308519</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008351157246247965</v>
+        <v>0.0008351157246247964</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0009160109239361282</v>
+        <v>0.0009160109239361281</v>
       </c>
       <c r="G4" t="n">
         <v>0.0011111955887007</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008236922415674639</v>
+        <v>0.0008236922415674636</v>
       </c>
       <c r="I4" t="n">
         <v>0.0009755735660036069</v>
@@ -4229,13 +4229,13 @@
         <v>0.001001490444360919</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001089292734264308</v>
+        <v>0.001089292734264309</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001071427734981061</v>
+        <v>0.001071427734981062</v>
       </c>
       <c r="M4" t="n">
-        <v>0.000988343176553241</v>
+        <v>0.0009883431765532408</v>
       </c>
       <c r="N4" t="n">
         <v>0.0008642563772193741</v>
@@ -4247,25 +4247,25 @@
         <v>0.001141806947323408</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0008836092589005473</v>
+        <v>0.0008836092589005472</v>
       </c>
       <c r="R4" t="n">
         <v>0.0008562031515197454</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00101153233291008</v>
+        <v>0.001011532332910081</v>
       </c>
       <c r="T4" t="n">
-        <v>0.000950016639011795</v>
+        <v>0.0009500166390117948</v>
       </c>
       <c r="U4" t="n">
         <v>0.001161961285961294</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0009517396493816269</v>
+        <v>0.0009517396493816268</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0009356596648427768</v>
+        <v>0.0009356596648427767</v>
       </c>
       <c r="X4" t="n">
         <v>0.001127204721959573</v>
@@ -4277,7 +4277,7 @@
         <v>0.0008860934768102934</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001046617446370087</v>
+        <v>0.001046617446370088</v>
       </c>
       <c r="AB4" t="n">
         <v>0.001265516133789795</v>
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003773502924297456</v>
+        <v>0.00377350292429746</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001617938451135779</v>
+        <v>0.00161793845113578</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004162167055331465</v>
+        <v>0.004162167055331471</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001984282988544341</v>
+        <v>0.001984282988544344</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003610494522143168</v>
+        <v>0.003610494522143169</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006345308066325843</v>
+        <v>0.006345308066325852</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001995451081749851</v>
+        <v>0.001995451081749852</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00473871366416171</v>
+        <v>0.004738713664161717</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004786550615545534</v>
+        <v>0.004786550615545533</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006218303670558873</v>
+        <v>0.006218303670558881</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006007622642523048</v>
+        <v>0.006007622642523056</v>
       </c>
       <c r="M5" t="n">
         <v>0.004891881859238389</v>
       </c>
       <c r="N5" t="n">
-        <v>0.007109831489127623</v>
+        <v>0.007109831489127637</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00344992898675883</v>
+        <v>0.003449928986758834</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006814599649623852</v>
+        <v>0.006814599649623865</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002902679181145768</v>
+        <v>0.002902679181145771</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002589424083907308</v>
+        <v>0.002589424083907313</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004878409349511299</v>
+        <v>0.004878409349511305</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004303041155637849</v>
+        <v>0.004303041155637853</v>
       </c>
       <c r="U5" t="n">
-        <v>0.007410347917688045</v>
+        <v>0.00741034791768803</v>
       </c>
       <c r="V5" t="n">
         <v>0.003791979871366088</v>
       </c>
       <c r="W5" t="n">
-        <v>0.00387309605916936</v>
+        <v>0.003873096059169358</v>
       </c>
       <c r="X5" t="n">
-        <v>0.007247281456400484</v>
+        <v>0.007247281456400494</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01391975173141226</v>
+        <v>0.01391975173141227</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002659420587044875</v>
+        <v>0.002659420587044874</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.005874958667987452</v>
+        <v>0.005874958667987465</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01052050816483595</v>
+        <v>0.01052050816483596</v>
       </c>
     </row>
     <row r="6">
@@ -4378,76 +4378,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001105318831750054</v>
+        <v>0.00124330130670323</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009660882630155868</v>
+        <v>0.0009660882630155867</v>
       </c>
       <c r="D6" t="n">
         <v>0.001108952743162426</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0009925511942563705</v>
+        <v>0.001130533669209547</v>
       </c>
       <c r="F6" t="n">
         <v>0.001073446393567702</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001268631058332274</v>
+        <v>0.001406613533285451</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001119110186152215</v>
+        <v>0.0009811277111990374</v>
       </c>
       <c r="I6" t="n">
         <v>0.001133009035635181</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001158925913992493</v>
+        <v>0.001296908388945671</v>
       </c>
       <c r="K6" t="n">
         <v>0.001384710678849058</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001228863204612636</v>
+        <v>0.001366845679565813</v>
       </c>
       <c r="M6" t="n">
         <v>0.001145778646184815</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001022668803490768</v>
+        <v>0.001022668803490766</v>
       </c>
       <c r="O6" t="n">
-        <v>0.00108902645988234</v>
+        <v>0.001227325604119192</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001438518353633091</v>
+        <v>0.001287921932803854</v>
       </c>
       <c r="Q6" t="n">
         <v>0.001179027203485298</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001151621096104497</v>
+        <v>0.001151621096104496</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001306950277494831</v>
+        <v>0.001306950277494832</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001107452108643368</v>
+        <v>0.001245434583596545</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001460190750364534</v>
+        <v>0.001322208275411358</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001247157593966378</v>
+        <v>0.0011091751190132</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001232370726204736</v>
+        <v>0.001232370726204735</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001284640191591145</v>
+        <v>0.001284640191591146</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001659962390039698</v>
+        <v>0.001659962390039697</v>
       </c>
       <c r="Z6" t="n">
         <v>0.001181511421395044</v>
@@ -4456,7 +4456,7 @@
         <v>0.001342035390954838</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001425334602453539</v>
+        <v>0.001425334602453538</v>
       </c>
     </row>
     <row r="7">
@@ -4466,16 +4466,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001034880556508954</v>
+        <v>0.001034880556508953</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008956499877744855</v>
+        <v>0.0008956499877744852</v>
       </c>
       <c r="D7" t="n">
         <v>0.001038514467921325</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0009221129190152697</v>
+        <v>0.0009221129190152695</v>
       </c>
       <c r="F7" t="n">
         <v>0.001003008118326601</v>
@@ -4484,7 +4484,7 @@
         <v>0.001198192783091173</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000910689435957937</v>
+        <v>0.0009106894359579368</v>
       </c>
       <c r="I7" t="n">
         <v>0.00106257076039408</v>
@@ -4502,19 +4502,19 @@
         <v>0.001075340370943714</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0009512535716098474</v>
+        <v>0.000951253571609847</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001017601900378775</v>
+        <v>0.001017601900378774</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001228794814091234</v>
+        <v>0.001228794814091235</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0009706064532910205</v>
+        <v>0.0009706064532910202</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0009432003459102195</v>
+        <v>0.000943200345910219</v>
       </c>
       <c r="S7" t="n">
         <v>0.001098529527300554</v>
@@ -4526,22 +4526,22 @@
         <v>0.001251686179074977</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0010387368437721</v>
+        <v>0.001038736843772099</v>
       </c>
       <c r="W7" t="n">
         <v>0.00102265685923325</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001214201916350046</v>
+        <v>0.001214201916350045</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001579425786444873</v>
+        <v>0.001579425786444874</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0009730906712007671</v>
+        <v>0.0009730906712007665</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00113361464076056</v>
+        <v>0.001133614640760561</v>
       </c>
       <c r="AB7" t="n">
         <v>0.001352513328180269</v>
@@ -4557,40 +4557,40 @@
         <v>0.001121862086392517</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001131172683653304</v>
+        <v>0.001131172683653303</v>
       </c>
       <c r="D8" t="n">
         <v>0.001274037163800143</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001157635614894087</v>
+        <v>0.001078541825696015</v>
       </c>
       <c r="F8" t="n">
         <v>0.001113130625832228</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001433715478969991</v>
+        <v>0.001464516457393379</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001146212131836755</v>
+        <v>0.001146212131836754</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001298093456272899</v>
+        <v>0.001298093456272898</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001324010334630211</v>
+        <v>0.00132401033463021</v>
       </c>
       <c r="K8" t="n">
         <v>0.0014118126245336</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001393947625250353</v>
+        <v>0.001393947625250352</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001310863066822533</v>
+        <v>0.001310863066822527</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001071632013440985</v>
+        <v>0.001071632013440984</v>
       </c>
       <c r="O8" t="n">
         <v>0.001169632310614947</v>
@@ -4608,28 +4608,28 @@
         <v>0.001334052223179372</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001272536529281086</v>
+        <v>0.001272536529281085</v>
       </c>
       <c r="U8" t="n">
-        <v>0.00139583398852139</v>
+        <v>0.001414734004858245</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001274259539650918</v>
+        <v>0.001233597324066159</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001258208747686187</v>
+        <v>0.001258208747686186</v>
       </c>
       <c r="X8" t="n">
         <v>0.001285605809840636</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001962540822370085</v>
+        <v>0.001962540822370086</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001208613367079585</v>
+        <v>0.00105731297266633</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001369137336639379</v>
+        <v>0.001369137336639377</v>
       </c>
       <c r="AB8" t="n">
         <v>0.00174319969273218</v>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001216025180770513</v>
+        <v>0.001216025180770512</v>
       </c>
       <c r="C9" t="n">
         <v>0.001167488907058012</v>
@@ -4651,22 +4651,22 @@
         <v>0.001310353387204852</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001193951838298796</v>
+        <v>0.001173020009300823</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001274847037610127</v>
+        <v>0.001065771859491106</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001470031702374698</v>
+        <v>0.001470031760041976</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001182528355241463</v>
+        <v>0.001182528355241462</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001334409679677606</v>
+        <v>0.001334409679677604</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00136032655803492</v>
+        <v>0.001360326558034919</v>
       </c>
       <c r="K9" t="n">
         <v>0.001448128847938307</v>
@@ -4675,34 +4675,34 @@
         <v>0.00143026384865506</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00134717929022724</v>
+        <v>0.001347179290227239</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001223092490893374</v>
+        <v>0.001223092490893373</v>
       </c>
       <c r="O9" t="n">
         <v>0.001319506194679806</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001537235770483667</v>
+        <v>0.001537235770483666</v>
       </c>
       <c r="Q9" t="n">
         <v>0.001242445430241824</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001215039265193745</v>
+        <v>0.001215039265193744</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001370368446584079</v>
+        <v>0.00137036844658408</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001308852752685793</v>
+        <v>0.001308852752685794</v>
       </c>
       <c r="U9" t="n">
         <v>0.001523608919453782</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001310575763055626</v>
+        <v>0.001415235049192618</v>
       </c>
       <c r="W9" t="n">
         <v>0.001294495778516776</v>
@@ -4714,10 +4714,10 @@
         <v>0.0018512647057284</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001244929590484293</v>
+        <v>0.001190249018336484</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001405453560044084</v>
+        <v>0.001405453560044085</v>
       </c>
       <c r="AB9" t="n">
         <v>0.001624352247463792</v>
@@ -4886,43 +4886,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007787785513701685</v>
+        <v>0.0007787785513701699</v>
       </c>
       <c r="C2" t="n">
         <v>0.0008481729132373383</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007846836259811665</v>
+        <v>0.0007846836259811666</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000779405236817966</v>
+        <v>0.0007794052368179664</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007780771588451404</v>
+        <v>0.0007780771588451406</v>
       </c>
       <c r="G2" t="n">
         <v>0.0007849511438827264</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007813396452825508</v>
+        <v>0.0007813396452825512</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007818144856844692</v>
+        <v>0.0007818144856844696</v>
       </c>
       <c r="J2" t="n">
         <v>0.0007833772838637305</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007892765247887693</v>
+        <v>0.0007892765247887695</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007889423837221262</v>
+        <v>0.0007889423837221265</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007869245166844985</v>
+        <v>0.0007869245166844982</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007863600345989919</v>
+        <v>0.0007863600345989918</v>
       </c>
       <c r="O2" t="n">
         <v>0.001099441870272138</v>
@@ -4931,40 +4931,40 @@
         <v>0.0007862870328813983</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007819395678511548</v>
+        <v>0.0007819395678511555</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007805256532580313</v>
+        <v>0.0007805256532580314</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007825997077175137</v>
+        <v>0.0007825997077175142</v>
       </c>
       <c r="T2" t="n">
         <v>0.0007799049510146345</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001002831860889116</v>
+        <v>0.001002831860889117</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007779681128532734</v>
+        <v>0.0007779681128532735</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009609416731587764</v>
+        <v>0.0009609416731587777</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0007852857348755434</v>
+        <v>0.0007852857348755447</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0007792643872196395</v>
+        <v>0.0007792643872196398</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009300798205339634</v>
+        <v>0.0009300798205339631</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0007861743281358376</v>
+        <v>0.0007861743281358377</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0007878273244843492</v>
+        <v>0.000787827324484349</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007672162712071426</v>
+        <v>0.0007672162712071427</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008628515797556544</v>
+        <v>0.0008628515797556542</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008096774741613444</v>
+        <v>0.0008096774741613446</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007717665321217229</v>
+        <v>0.000771766532121723</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007624358884461326</v>
+        <v>0.000762435888446133</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008108792896203289</v>
+        <v>0.0008108792896203298</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007859165336220974</v>
+        <v>0.0007859165336220966</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007892047216253603</v>
+        <v>0.0007892047216253601</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007999214938642607</v>
+        <v>0.0007999214938642618</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0008420166414154246</v>
+        <v>0.0008420166414154262</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000839276715491817</v>
+        <v>0.0008392767154918176</v>
       </c>
       <c r="M3" t="n">
         <v>0.0008266109213693169</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008214407290483649</v>
+        <v>0.0008214407290483652</v>
       </c>
       <c r="O3" t="n">
         <v>0.001300226307886633</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008206213201300052</v>
+        <v>0.0008206213201300057</v>
       </c>
       <c r="Q3" t="n">
         <v>0.0007898759080630814</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007800413216698487</v>
+        <v>0.0007800413216698492</v>
       </c>
       <c r="S3" t="n">
-        <v>0.000794122303790086</v>
+        <v>0.0007941223037900866</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007754414939393</v>
+        <v>0.0007754414939393008</v>
       </c>
       <c r="U3" t="n">
         <v>0.00119625797023863</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007614665259706233</v>
+        <v>0.0007614665259706252</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00111825554174233</v>
+        <v>0.001118255541742332</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008139220825020804</v>
+        <v>0.0008139220825020806</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.000770826528572185</v>
+        <v>0.0007708265285721861</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001031964843351102</v>
+        <v>0.001031964843351103</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008201572914771769</v>
+        <v>0.0008201572914771774</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0008322746083587339</v>
+        <v>0.0008322746083587334</v>
       </c>
     </row>
     <row r="4">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007617857057675628</v>
+        <v>0.0007617857057675629</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007224019792678927</v>
+        <v>0.0007224019792678926</v>
       </c>
       <c r="D4" t="n">
         <v>0.0008284862399673123</v>
@@ -5080,22 +5080,22 @@
         <v>0.0008315079777297396</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007907144396693273</v>
+        <v>0.0007907144396693272</v>
       </c>
       <c r="I4" t="n">
         <v>0.0007960779804463787</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0008134036808896949</v>
+        <v>0.000813403680889695</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0008803651448370178</v>
+        <v>0.0008803651448370176</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008765908677768007</v>
+        <v>0.0008765908677768008</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0008560814554818825</v>
+        <v>0.0008560814554818828</v>
       </c>
       <c r="N4" t="n">
         <v>0.0008474220464917093</v>
@@ -5104,34 +5104,34 @@
         <v>0.0007695302287835964</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0008465974585090413</v>
+        <v>0.0008465974585090414</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0007974908410597194</v>
       </c>
       <c r="R4" t="n">
-        <v>0.000781520025297544</v>
+        <v>0.0007815200252975437</v>
       </c>
       <c r="S4" t="n">
         <v>0.0008049474245295843</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007745089079212357</v>
+        <v>0.0007745089079212358</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0008821187398207113</v>
+        <v>0.0008821187398207116</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007505036832297347</v>
+        <v>0.0007505036832297346</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0008650972941762144</v>
+        <v>0.0008650972941762145</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0008352873369130754</v>
+        <v>0.0008352873369130753</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0007653939639567985</v>
+        <v>0.0007653939639567983</v>
       </c>
       <c r="Z4" t="n">
         <v>0.0007929744407553405</v>
@@ -5140,7 +5140,7 @@
         <v>0.0008453244065611842</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0008639624839015624</v>
+        <v>0.0008639624839015623</v>
       </c>
     </row>
     <row r="5">
@@ -5150,22 +5150,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001666789030166402</v>
+        <v>0.001666789030166403</v>
       </c>
       <c r="C5" t="n">
         <v>0.001021923944555872</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003103917970724868</v>
+        <v>0.003103917970724867</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00184377628429641</v>
+        <v>0.001843776284296411</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00164239732416563</v>
+        <v>0.001642397324165634</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002767589919475813</v>
+        <v>0.002767589919475818</v>
       </c>
       <c r="H5" t="n">
         <v>0.002448248721406655</v>
@@ -5177,58 +5177,58 @@
         <v>0.002584026635106764</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003839809512317279</v>
+        <v>0.003839809512317274</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003570931443491082</v>
+        <v>0.003570931443491083</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003458574576562895</v>
+        <v>0.003458574576562893</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003857440648739449</v>
+        <v>0.003857440648739451</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001777015773977117</v>
+        <v>0.001777015773977116</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003168426623467055</v>
+        <v>0.003168426623467057</v>
       </c>
       <c r="Q5" t="n">
         <v>0.002397126822430833</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002237856684409186</v>
+        <v>0.002237856684409187</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002279473578000197</v>
+        <v>0.002279473578000196</v>
       </c>
       <c r="T5" t="n">
         <v>0.002010831536216099</v>
       </c>
       <c r="U5" t="n">
-        <v>0.003894016823294514</v>
+        <v>0.003894016823294513</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001510701889331649</v>
+        <v>0.001510701889331642</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003712388376920059</v>
+        <v>0.003712388376920058</v>
       </c>
       <c r="X5" t="n">
         <v>0.003203218335544432</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001849981842252282</v>
+        <v>0.001849981842252284</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002172697843103202</v>
+        <v>0.002172697843103201</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003333642706360176</v>
+        <v>0.003333642706360177</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003873962141540139</v>
+        <v>0.003873962141540136</v>
       </c>
     </row>
     <row r="6">
@@ -5238,82 +5238,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009047437119501362</v>
+        <v>0.0009047437119501347</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009860029249091761</v>
+        <v>0.0009860029249091759</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001092087185608596</v>
+        <v>0.0009714442461498841</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001032465351831255</v>
+        <v>0.0009118224123725434</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001017464100182142</v>
+        <v>0.001017464100182143</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009744659839123134</v>
+        <v>0.001095108923371022</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009336724458519006</v>
+        <v>0.0009336724458518993</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001059678926087662</v>
+        <v>0.0009390359866289507</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009563616870722682</v>
+        <v>0.0009563616870722668</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001143966090478301</v>
+        <v>0.001023323151019589</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001140191813418084</v>
+        <v>0.001019548873959373</v>
       </c>
       <c r="M6" t="n">
-        <v>0.000999039461664456</v>
+        <v>0.001119682401123166</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0009904974529739228</v>
+        <v>0.0009904974529739222</v>
       </c>
       <c r="O6" t="n">
         <v>0.001033828617555975</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001110895868736122</v>
+        <v>0.000978852101129</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001061091786701003</v>
+        <v>0.001061091786701002</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001045120970938827</v>
+        <v>0.0009244780314801158</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001068548370170867</v>
+        <v>0.0009479054307121562</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0009174669141038088</v>
+        <v>0.001038109853562519</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001147599166688059</v>
+        <v>0.001026956227229348</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0008934616894123086</v>
+        <v>0.001014104628871018</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001018144226066404</v>
+        <v>0.001018144226066405</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0009782453430956497</v>
+        <v>0.0009782453430956474</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0009183640033025607</v>
+        <v>0.00091836400330256</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0009359324469379133</v>
+        <v>0.001056575386396623</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0009882824127437578</v>
+        <v>0.001108925352202468</v>
       </c>
       <c r="AB6" t="n">
         <v>0.001007490846971191</v>
@@ -5326,61 +5326,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0008498188819623969</v>
+        <v>0.0008498188819623971</v>
       </c>
       <c r="C7" t="n">
         <v>0.0008104351554627269</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0009165194161621464</v>
+        <v>0.0009165194161621466</v>
       </c>
       <c r="E7" t="n">
         <v>0.0008568975823848052</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008418963307356934</v>
+        <v>0.0008418963307356931</v>
       </c>
       <c r="G7" t="n">
         <v>0.0009195411539245738</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008787476158641616</v>
+        <v>0.0008787476158641614</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008841111566412126</v>
+        <v>0.0008841111566412124</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0009014368570845288</v>
+        <v>0.0009014368570845289</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0009683983210318514</v>
+        <v>0.0009683983210318513</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009646240439716341</v>
+        <v>0.0009646240439716345</v>
       </c>
       <c r="M7" t="n">
         <v>0.0009441146316767169</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0009354552226865431</v>
+        <v>0.0009354552226865432</v>
       </c>
       <c r="O7" t="n">
         <v>0.0008575537487008178</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0009346209784262627</v>
+        <v>0.000934620978426263</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0008855240172545534</v>
+        <v>0.0008855240172545536</v>
       </c>
       <c r="R7" t="n">
-        <v>0.000869553201492378</v>
+        <v>0.0008695532014923778</v>
       </c>
       <c r="S7" t="n">
         <v>0.0008929806007244182</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0008625420841160695</v>
+        <v>0.0008625420841160697</v>
       </c>
       <c r="U7" t="n">
         <v>0.0009719352100031314</v>
@@ -5389,22 +5389,22 @@
         <v>0.0008385368594245687</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0009531304703710479</v>
+        <v>0.0009531304703710484</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0009233205131079095</v>
+        <v>0.0009233205131079094</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0008553066213776968</v>
+        <v>0.000855306621377697</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008810076169501747</v>
+        <v>0.0008810076169501748</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0009333575827560185</v>
+        <v>0.0009333575827560184</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0009519956600963963</v>
+        <v>0.000951995660096396</v>
       </c>
     </row>
     <row r="8">
@@ -5414,7 +5414,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0009240181150982753</v>
+        <v>0.0009240181150982757</v>
       </c>
       <c r="C8" t="n">
         <v>0.001018704046756973</v>
@@ -5423,13 +5423,13 @@
         <v>0.001124788307456393</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001065166473679051</v>
+        <v>0.0009937783355205394</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009369820497052131</v>
+        <v>0.0009369820497052135</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00112781004521882</v>
+        <v>0.001155610262219337</v>
       </c>
       <c r="H8" t="n">
         <v>0.001087016507158408</v>
@@ -5441,13 +5441,13 @@
         <v>0.001109705748378776</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001176667212326098</v>
+        <v>0.001176667212326097</v>
       </c>
       <c r="L8" t="n">
         <v>0.001172892935265881</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001152383522970962</v>
+        <v>0.001152383522970951</v>
       </c>
       <c r="N8" t="n">
         <v>0.001039797699538234</v>
@@ -5459,7 +5459,7 @@
         <v>0.00106053227566372</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0009333755025760438</v>
+        <v>0.0009333755025760436</v>
       </c>
       <c r="R8" t="n">
         <v>0.001077822092786624</v>
@@ -5468,25 +5468,25 @@
         <v>0.001101249492018665</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001070810975410317</v>
+        <v>0.001070810975410316</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001097737833861321</v>
+        <v>0.00111479561841562</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001046805750718816</v>
+        <v>0.001010088527085163</v>
       </c>
       <c r="W8" t="n">
         <v>0.001161425710177367</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0009834597489896014</v>
+        <v>0.0009834597489896009</v>
       </c>
       <c r="Y8" t="n">
         <v>0.001196763203079401</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001089276508244421</v>
+        <v>0.0009527164373554975</v>
       </c>
       <c r="AA8" t="n">
         <v>0.001141626474050265</v>
@@ -5508,19 +5508,19 @@
         <v>0.001076504412990861</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00118258867369028</v>
+        <v>0.001182588673690281</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00112296683991294</v>
+        <v>0.001102823158655918</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001107965588263827</v>
+        <v>0.0009067628378277217</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001185610411452707</v>
+        <v>0.001185610455357803</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001144816873392295</v>
+        <v>0.001144816873392296</v>
       </c>
       <c r="I9" t="n">
         <v>0.001150180414169347</v>
@@ -5535,19 +5535,19 @@
         <v>0.001230693301499769</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00121018388920485</v>
+        <v>0.001210183889204851</v>
       </c>
       <c r="N9" t="n">
         <v>0.001201524480214677</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001152556979040819</v>
+        <v>0.001152556979040821</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001235914741805726</v>
+        <v>0.001235914741805727</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001151593318687782</v>
+        <v>0.001151593318687783</v>
       </c>
       <c r="R9" t="n">
         <v>0.001135622459020512</v>
@@ -5562,7 +5562,7 @@
         <v>0.001238100654769744</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001104606116952703</v>
+        <v>0.001205324605998519</v>
       </c>
       <c r="W9" t="n">
         <v>0.001219199727899183</v>
@@ -5574,13 +5574,13 @@
         <v>0.001121375878905831</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001147076874478308</v>
+        <v>0.001094455212738761</v>
       </c>
       <c r="AA9" t="n">
         <v>0.001199426840284153</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.00121806491762453</v>
+        <v>0.001218064917624531</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007703963690397854</v>
+        <v>0.0007703963690397844</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008453376264006529</v>
+        <v>0.0008453376264006531</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007718351342227645</v>
+        <v>0.0007718351342227631</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007721930512813045</v>
+        <v>0.0007721930512813037</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000772481560496963</v>
+        <v>0.000772481560496962</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007725385800056506</v>
+        <v>0.0007725385800056495</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000772316358251525</v>
+        <v>0.0007723163582515239</v>
       </c>
       <c r="I2" t="n">
         <v>0.00077231684623412</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007729235242455053</v>
+        <v>0.0007729235242455056</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007713247971310683</v>
+        <v>0.0007713247971310677</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007722342561314704</v>
+        <v>0.0007722342561314688</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007701797052081782</v>
+        <v>0.0007701797052081785</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007736346419672721</v>
+        <v>0.0007736346419672715</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001092201994768032</v>
+        <v>0.001092201994768031</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007724670509331206</v>
+        <v>0.0007724670509331195</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007704778345383102</v>
+        <v>0.0007704778345383094</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007751195245541955</v>
+        <v>0.0007751195245541946</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007730086691429208</v>
+        <v>0.0007730086691429198</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007705853974459004</v>
+        <v>0.0007705853974458991</v>
       </c>
       <c r="U2" t="n">
         <v>0.0009860288252765161</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007731231160065617</v>
+        <v>0.0007731231160065607</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009538024557421648</v>
+        <v>0.0009538024557421629</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0007871554358783859</v>
+        <v>0.0007871554358783849</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0007737091283378783</v>
+        <v>0.0007737091283378778</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009221645688652989</v>
+        <v>0.0009221645688652976</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0007760873442031935</v>
+        <v>0.0007760873442031924</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.000769138034570417</v>
+        <v>0.0007691380345704172</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000745642270838113</v>
+        <v>0.0007456422708381121</v>
       </c>
       <c r="C3" t="n">
         <v>0.0008721008855947499</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007559822589143786</v>
+        <v>0.0007559822589143777</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007584553341513228</v>
+        <v>0.0007584553341513215</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007606277139824238</v>
+        <v>0.0007606277139824234</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007607766200145071</v>
+        <v>0.0007607766200145069</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007595550713460995</v>
+        <v>0.0007595550713460993</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000759475333458315</v>
+        <v>0.0007594753334583138</v>
       </c>
       <c r="J3" t="n">
         <v>0.0007636030678006974</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007523037037855091</v>
+        <v>0.0007523037037855088</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007586082125947627</v>
+        <v>0.0007586082125947613</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000745907389091889</v>
+        <v>0.0007459073890918894</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0007687673657363754</v>
+        <v>0.0007687673657363751</v>
       </c>
       <c r="O3" t="n">
         <v>0.001296248376940949</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0007603437713377651</v>
+        <v>0.0007603437713377655</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007462356625022602</v>
+        <v>0.0007462356625022593</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007795658096566169</v>
+        <v>0.0007795658096566164</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007640847639361227</v>
+        <v>0.0007640847639361222</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007470787610913013</v>
+        <v>0.0007470787610913004</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001099999582237769</v>
+        <v>0.001099999582237768</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007649646941866771</v>
+        <v>0.0007649646941866757</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001088366353731749</v>
+        <v>0.001088366353731747</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008650835335782582</v>
+        <v>0.0008650835335782577</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.000769357558267783</v>
+        <v>0.0007693575582677825</v>
       </c>
       <c r="Z3" t="n">
         <v>0.001016789006519748</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0007863250335661315</v>
+        <v>0.0007863250335661306</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.000737579078669308</v>
+        <v>0.0007375790786693076</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007203164655798307</v>
+        <v>0.0007203164655798308</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007258232183921846</v>
+        <v>0.0007258232183921842</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007365679801862708</v>
+        <v>0.0007365679801862706</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007406108180124562</v>
+        <v>0.0007406108180124556</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007438696623241159</v>
+        <v>0.0007438696623241163</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007445137239050109</v>
+        <v>0.0007445137239050104</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007420036269651115</v>
+        <v>0.0007420036269651109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007420091389530053</v>
+        <v>0.0007420091389530052</v>
       </c>
       <c r="J4" t="n">
         <v>0.0007485870232833211</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007308034879689045</v>
+        <v>0.0007308034879689036</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007410762457502507</v>
+        <v>0.0007410762457502505</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007210577547330655</v>
+        <v>0.0007210577547330649</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0007568942479749466</v>
+        <v>0.0007568942479749469</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0007606592846031264</v>
+        <v>0.0007606592846031269</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0007437057701257879</v>
+        <v>0.0007437057701257878</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0007212366558616633</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0007736666798739895</v>
+        <v>0.000773666679873989</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0007498235969621715</v>
+        <v>0.0007498235969621707</v>
       </c>
       <c r="T4" t="n">
-        <v>0.000722451628384263</v>
+        <v>0.0007224516283842626</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0007161048536374914</v>
+        <v>0.0007161048536374913</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007493372606168843</v>
+        <v>0.0007493372606168847</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0008028673154224614</v>
+        <v>0.000802867315422461</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0009096178350734693</v>
+        <v>0.0009096178350734703</v>
       </c>
       <c r="Y4" t="n">
         <v>0.000756814395433813</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0007632044594592755</v>
+        <v>0.000763204459459275</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0007845986480284474</v>
+        <v>0.0007845986480284468</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0007075867462136506</v>
+        <v>0.0007075867462136512</v>
       </c>
     </row>
     <row r="5">
@@ -6016,31 +6016,31 @@
         <v>0.001291621543906323</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001479198651358072</v>
+        <v>0.00147919865135807</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00150852115538684</v>
+        <v>0.001508521155386842</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001624861186257168</v>
+        <v>0.001624861186257166</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001502527168312647</v>
+        <v>0.001502527168312646</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001647003645571448</v>
+        <v>0.001647003645571447</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001603974142796612</v>
+        <v>0.001603974142796613</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001620138076721323</v>
+        <v>0.001620138076721322</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00135845644726589</v>
+        <v>0.001358456447265889</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001443578327392283</v>
+        <v>0.001443578327392284</v>
       </c>
       <c r="M5" t="n">
         <v>0.001208800577458499</v>
@@ -6049,7 +6049,7 @@
         <v>0.00114877863878467</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001770800025273769</v>
+        <v>0.001770800025273768</v>
       </c>
       <c r="P5" t="n">
         <v>0.001528481402227282</v>
@@ -6058,37 +6058,37 @@
         <v>0.001177214411679726</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002209297517654791</v>
+        <v>0.002209297517654795</v>
       </c>
       <c r="S5" t="n">
         <v>0.001572133351319203</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001237786029358918</v>
+        <v>0.001237786029358917</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001108910454809766</v>
+        <v>0.001108910454809767</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001625927279955699</v>
+        <v>0.001625927279955707</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002553961020709345</v>
+        <v>0.002553961020709344</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004415247183267075</v>
+        <v>0.004415247183267082</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001853847298739871</v>
+        <v>0.001853847298739872</v>
       </c>
       <c r="Z5" t="n">
         <v>0.001806644043922811</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002325870783240077</v>
+        <v>0.002325870783240074</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0009873491616634246</v>
+        <v>0.0009873491616634237</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000854127021979916</v>
+        <v>0.0008541270219799165</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009678840524601081</v>
+        <v>0.0008596337747922698</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008703785365863566</v>
+        <v>0.0008703785365863559</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0009826716520803798</v>
+        <v>0.0009826716520803796</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009859304963920402</v>
+        <v>0.0009859304963920404</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009865745579729346</v>
+        <v>0.000878324280305096</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009840644610330344</v>
+        <v>0.0008758141833651961</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008758196953530909</v>
+        <v>0.0008758196953530908</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009906478573512452</v>
+        <v>0.0008823975796834066</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008646140443689888</v>
+        <v>0.0008646140443689893</v>
       </c>
       <c r="L6" t="n">
         <v>0.0009831370798181738</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0008548683111331507</v>
+        <v>0.0009631185888009887</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0008907015465252238</v>
+        <v>0.0008907015465252259</v>
       </c>
       <c r="O6" t="n">
-        <v>0.000894466583153404</v>
+        <v>0.0008944665831534045</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0009861323955184548</v>
+        <v>0.0008674346551941295</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0009632974899295874</v>
+        <v>0.000855047212261749</v>
       </c>
       <c r="R6" t="n">
         <v>0.001015727513941913</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0009918844310300948</v>
+        <v>0.0008836341533622568</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0009645124624521867</v>
+        <v>0.0009645124624521866</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0008508366204001297</v>
+        <v>0.0008508366204001296</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0008831478170169705</v>
+        <v>0.0009913980946848081</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0009458879655079241</v>
+        <v>0.0009458879655079219</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001043428391473555</v>
+        <v>0.001043428391473556</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0008991719006815401</v>
+        <v>0.0008991719006815405</v>
       </c>
       <c r="Z6" t="n">
         <v>0.001005265293527199</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0009184092044285333</v>
+        <v>0.00102665948209637</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0008412190799401407</v>
+        <v>0.0008412190799401405</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007987269633642301</v>
+        <v>0.0007987269633642298</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008042337161765831</v>
+        <v>0.000804233716176583</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008149784779706698</v>
+        <v>0.0008149784779706696</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008190213157968548</v>
+        <v>0.000819021315796855</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000822280160108515</v>
+        <v>0.0008222801601085154</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008229242216894099</v>
+        <v>0.0008229242216894094</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008204141247495095</v>
+        <v>0.0008204141247495094</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008204196367374044</v>
+        <v>0.0008204196367374041</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008269975210677205</v>
+        <v>0.0008269975210677204</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008092139857533028</v>
+        <v>0.0008092139857533027</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008194867435346495</v>
+        <v>0.0008194867435346491</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0007994682525174641</v>
+        <v>0.0007994682525174642</v>
       </c>
       <c r="N7" t="n">
         <v>0.0008353047457593458</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0008390607632896025</v>
+        <v>0.0008390607632896019</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0008221072488122632</v>
+        <v>0.0008221072488122625</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0007996471536460626</v>
+        <v>0.0007996471536460624</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0008520771776583881</v>
+        <v>0.0008520771776583882</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0008282340947465698</v>
+        <v>0.00082823409474657</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0008008621261686618</v>
+        <v>0.0008008621261686619</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0007953580520325124</v>
+        <v>0.0007953580520325115</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0008277477584012838</v>
+        <v>0.0008277477584012834</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0008812778132068608</v>
+        <v>0.0008812778132068599</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0009880283328578686</v>
+        <v>0.0009880283328578695</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0008361461035807645</v>
+        <v>0.0008361461035807647</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008416149572436737</v>
+        <v>0.0008416149572436736</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0008630091458128464</v>
+        <v>0.0008630091458128467</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0007859972439980499</v>
+        <v>0.0007859972439980498</v>
       </c>
     </row>
     <row r="8">
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008648215824101083</v>
+        <v>0.0008648215824101088</v>
       </c>
       <c r="C8" t="n">
         <v>0.000990532748915056</v>
@@ -6283,16 +6283,16 @@
         <v>0.001001277510709142</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001005320348535328</v>
+        <v>0.0009413150440551487</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009071012219471949</v>
+        <v>0.0009071012219471954</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001009223254427882</v>
+        <v>0.001034148422664978</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001006713157487983</v>
+        <v>0.001006713157487982</v>
       </c>
       <c r="I8" t="n">
         <v>0.001006718669475877</v>
@@ -6301,43 +6301,43 @@
         <v>0.001013296553806193</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000995513018491776</v>
+        <v>0.0009955130184917756</v>
       </c>
       <c r="L8" t="n">
         <v>0.001005785776273122</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0009857672852559367</v>
+        <v>0.0009857672852559196</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0009284252481219099</v>
+        <v>0.0009284252481219094</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0009577965539458262</v>
+        <v>0.0009577965539458266</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0009345663241551618</v>
+        <v>0.0009345663241551611</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0008421188618730996</v>
+        <v>0.0008421188618730998</v>
       </c>
       <c r="R8" t="n">
-        <v>0.00103837621039686</v>
+        <v>0.001038376210396861</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001014533127485042</v>
+        <v>0.001014533127485043</v>
       </c>
       <c r="T8" t="n">
         <v>0.0009871611589071343</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0009077174894310736</v>
+        <v>0.0009230115709903852</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001014046791139757</v>
+        <v>0.0009811337135153773</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001067600469542602</v>
+        <v>0.001067600469542601</v>
       </c>
       <c r="X8" t="n">
         <v>0.001041517014440975</v>
@@ -6346,13 +6346,13 @@
         <v>0.001141869521063509</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001027913989982147</v>
+        <v>0.000905476717593168</v>
       </c>
       <c r="AA8" t="n">
         <v>0.001049308178551319</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001097859838155105</v>
+        <v>0.001097859838155104</v>
       </c>
     </row>
     <row r="9">
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000932685895149586</v>
+        <v>0.0009326858951495855</v>
       </c>
       <c r="C9" t="n">
         <v>0.001009280214071221</v>
@@ -6371,43 +6371,43 @@
         <v>0.001020024975865307</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001024067813691493</v>
+        <v>0.001007661133981716</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001027326658003154</v>
+        <v>0.0008634503476100334</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001027970719584048</v>
+        <v>0.001027970772349559</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001025460622644148</v>
+        <v>0.001025460622644147</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001025466134632043</v>
+        <v>0.001025466134632041</v>
       </c>
       <c r="J9" t="n">
         <v>0.001032044018962358</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001014260483647941</v>
+        <v>0.00101426048364794</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001024533241429288</v>
+        <v>0.001024533241429287</v>
       </c>
       <c r="M9" t="n">
         <v>0.001004514750412102</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001040351243653984</v>
+        <v>0.001040351243653983</v>
       </c>
       <c r="O9" t="n">
         <v>0.001067674676861971</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001055844697970723</v>
+        <v>0.001055844697970722</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001004693704306212</v>
+        <v>0.001004693704306211</v>
       </c>
       <c r="R9" t="n">
         <v>0.001057123675553026</v>
@@ -6419,28 +6419,28 @@
         <v>0.0010059086240633</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001000483059679081</v>
+        <v>0.00100048305967908</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001032794256295922</v>
+        <v>0.001114827835145712</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001086324311101498</v>
+        <v>0.001086324311101497</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001193074830752507</v>
+        <v>0.001193074830752506</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001041192601475403</v>
+        <v>0.001041192601475402</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001046661455138312</v>
+        <v>0.00100380199508005</v>
       </c>
       <c r="AA9" t="n">
         <v>0.001068055643707484</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.000991043741892688</v>
+        <v>0.0009910437418926871</v>
       </c>
     </row>
   </sheetData>
@@ -6606,82 +6606,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007840740348228626</v>
+        <v>0.0007840740348228633</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008447095307116182</v>
+        <v>0.000844709530711618</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007842172347065423</v>
+        <v>0.0007842172347065431</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007861657947376619</v>
+        <v>0.0007861657947376626</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007845101548467874</v>
+        <v>0.0007845101548467884</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007836235525154841</v>
+        <v>0.0007836235525154849</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007833747135241123</v>
+        <v>0.0007833747135241129</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007833755136166155</v>
+        <v>0.0007833755136166163</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007847167914611238</v>
+        <v>0.0007847167914611242</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000783022762755935</v>
+        <v>0.0007830227627559363</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007851765975089457</v>
+        <v>0.0007851765975089464</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007824853710753225</v>
+        <v>0.0007824853710753222</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007844034022943631</v>
+        <v>0.000784403402294364</v>
       </c>
       <c r="O2" t="n">
         <v>0.001111752452418982</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007860131530196689</v>
+        <v>0.0007860131530196695</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007825072952633897</v>
+        <v>0.0007825072952633901</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007883727567415127</v>
+        <v>0.000788372756741513</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007848186508161579</v>
+        <v>0.0007848186508161587</v>
       </c>
       <c r="T2" t="n">
-        <v>0.000782752278220303</v>
+        <v>0.0007827522782203032</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009588709209092565</v>
+        <v>0.000958870920909256</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007861140080532514</v>
+        <v>0.0007861140080532517</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009362071670972226</v>
+        <v>0.000936207167097222</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00080408760278773</v>
+        <v>0.0008040876027877301</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0007858069538982304</v>
+        <v>0.0007858069538982312</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009322799617867606</v>
+        <v>0.0009322799617867614</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0007892198159692328</v>
+        <v>0.000789219815969233</v>
       </c>
       <c r="AB2" t="n">
         <v>0.0007824608027955562</v>
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000767818570958082</v>
+        <v>0.0007678185709580822</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008642606253524078</v>
+        <v>0.0008642606253524074</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007689765450406061</v>
+        <v>0.0007689765450406055</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007826747698666957</v>
+        <v>0.0007826747698666955</v>
       </c>
       <c r="F3" t="n">
         <v>0.0007711129631948929</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007646057309927479</v>
+        <v>0.0007646057309927481</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007630386955805749</v>
+        <v>0.0007630386955805748</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007630011842926791</v>
+        <v>0.000763001184292679</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007724328760974861</v>
+        <v>0.0007724328760974851</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007604337188671809</v>
+        <v>0.0007604337188671807</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007756059332612366</v>
+        <v>0.0007756059332612367</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0007583877800919141</v>
+        <v>0.0007583877800919139</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0007702752480875856</v>
+        <v>0.0007702752480875857</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00132395822550344</v>
+        <v>0.001323958225503439</v>
       </c>
       <c r="P3" t="n">
-        <v>0.000781548667905976</v>
+        <v>0.0007815486679059762</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007567335677513495</v>
+        <v>0.0007567335677513493</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000798807948114895</v>
+        <v>0.0007988079481148949</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007730829904481465</v>
+        <v>0.0007730829904481467</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007585314521518429</v>
+        <v>0.0007585314521518426</v>
       </c>
       <c r="U3" t="n">
         <v>0.001049531181714214</v>
       </c>
       <c r="V3" t="n">
-        <v>0.000782290075650041</v>
+        <v>0.0007822900756500419</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001042896533776652</v>
+        <v>0.001042896533776653</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0009103430732649148</v>
+        <v>0.0009103430732649144</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0007803244413391231</v>
+        <v>0.0007803244413391229</v>
       </c>
       <c r="Z3" t="n">
         <v>0.001018908231288331</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008046683977769975</v>
+        <v>0.0008046683977769971</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0007571819129745497</v>
+        <v>0.0007571819129745496</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007476658590135169</v>
+        <v>0.0007476658590135171</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007398949438857267</v>
+        <v>0.0007398949438857269</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007492833675748806</v>
+        <v>0.0007492833675748808</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007712932495082735</v>
+        <v>0.0007712932495082738</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007525920353088685</v>
+        <v>0.000752592035308869</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007425774541195736</v>
+        <v>0.0007425774541195743</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007397667032404393</v>
+        <v>0.0007397667032404394</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007397757406533312</v>
+        <v>0.0007397757406533313</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0007546526245297352</v>
+        <v>0.0007546526245297353</v>
       </c>
       <c r="K4" t="n">
         <v>0.0007357912574085301</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007601198117567156</v>
+        <v>0.0007601198117567157</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007329525799401709</v>
+        <v>0.0007329525799401711</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0007513862161206405</v>
+        <v>0.0007513862161206407</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0007793799347423566</v>
+        <v>0.0007793799347423568</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0007695690910848846</v>
+        <v>0.0007695690910848845</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0007299688149534631</v>
+        <v>0.0007299688149534632</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0007962219005944507</v>
+        <v>0.000796221900594451</v>
       </c>
       <c r="S4" t="n">
         <v>0.0007560766391980676</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007327360101495196</v>
+        <v>0.0007327360101495197</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0007334092474129838</v>
+        <v>0.000733409247412984</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007689403180770017</v>
+        <v>0.0007689403180770016</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0007969594849011383</v>
+        <v>0.0007969594849011384</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0009737283158728064</v>
+        <v>0.0009737283158728066</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0007671260121277452</v>
+        <v>0.0007671260121277456</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0007611961525330029</v>
+        <v>0.0007611961525330034</v>
       </c>
       <c r="AA4" t="n">
         <v>0.0008057898242380376</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0007307207417938253</v>
+        <v>0.0007307207417938255</v>
       </c>
     </row>
     <row r="5">
@@ -6870,16 +6870,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001393148536899685</v>
+        <v>0.001393148536899686</v>
       </c>
       <c r="C5" t="n">
         <v>0.001321331571811517</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00149220916541299</v>
+        <v>0.001492209165412988</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001773313303767959</v>
+        <v>0.00177331330376796</v>
       </c>
       <c r="F5" t="n">
         <v>0.001574479952126483</v>
@@ -6891,19 +6891,19 @@
         <v>0.001362896065692928</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001340657413742148</v>
+        <v>0.001340657413742146</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001535234326472996</v>
+        <v>0.001535234326472997</v>
       </c>
       <c r="K5" t="n">
         <v>0.001244344006283348</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00157108732744198</v>
+        <v>0.001571087327441979</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001211634274015985</v>
+        <v>0.001211634274015984</v>
       </c>
       <c r="N5" t="n">
         <v>0.001190322074987363</v>
@@ -6912,40 +6912,40 @@
         <v>0.001872421737046018</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00172380484110261</v>
+        <v>0.001723804841102608</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00113036056000598</v>
+        <v>0.001130360560005981</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002412169306282083</v>
+        <v>0.002412169306282086</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001516025899623206</v>
+        <v>0.001516025899623205</v>
       </c>
       <c r="T5" t="n">
         <v>0.001204918209745004</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001172459071303913</v>
+        <v>0.001172459071303914</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001753379397128486</v>
+        <v>0.001753379397128488</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002271080201645627</v>
+        <v>0.002271080201645623</v>
       </c>
       <c r="X5" t="n">
-        <v>0.005229060794209353</v>
+        <v>0.005229060794209349</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001810833313505163</v>
+        <v>0.001810833313505164</v>
       </c>
       <c r="Z5" t="n">
         <v>0.001568602803745864</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002485494132863511</v>
+        <v>0.002485494132863507</v>
       </c>
       <c r="AB5" t="n">
         <v>0.001188382813628577</v>
@@ -6970,22 +6970,22 @@
         <v>0.001039239271891388</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009040070796552206</v>
+        <v>0.001020538057691983</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0008939924984659258</v>
+        <v>0.001010523476502688</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0008911817475867915</v>
+        <v>0.0008911817475867914</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001007721763036446</v>
+        <v>0.0008911907849996833</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001022598646912851</v>
+        <v>0.0009060676688760871</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008872063017548822</v>
+        <v>0.001003737279791645</v>
       </c>
       <c r="L6" t="n">
         <v>0.00102806583413983</v>
@@ -6997,7 +6997,7 @@
         <v>0.000902713091146567</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0009307068097682819</v>
+        <v>0.001047092156586041</v>
       </c>
       <c r="P6" t="n">
         <v>0.001037280709931373</v>
@@ -7006,37 +7006,37 @@
         <v>0.0009979148373365774</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001064167922977566</v>
+        <v>0.0009476369449408023</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00090749168354442</v>
+        <v>0.0009074916835444194</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001000682032532634</v>
+        <v>0.001000682032532633</v>
       </c>
       <c r="U6" t="n">
         <v>0.001001469234820306</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0009203553624233537</v>
+        <v>0.0009203553624233535</v>
       </c>
       <c r="W6" t="n">
         <v>0.001064672207231008</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001241674338255922</v>
+        <v>0.001125143360219158</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0009273900820573257</v>
+        <v>0.0009273900820573259</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001029142174916117</v>
+        <v>0.0009126111968793552</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001073735846621152</v>
+        <v>0.0009572048685843898</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0008819143281399235</v>
+        <v>0.0008819143281399236</v>
       </c>
     </row>
     <row r="7">
@@ -7046,52 +7046,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0008200981696562876</v>
+        <v>0.0008200981696562875</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008123272545284975</v>
+        <v>0.0008123272545284973</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008217156782176516</v>
+        <v>0.0008217156782176513</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008437255601510443</v>
+        <v>0.0008437255601510442</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000825024345951639</v>
+        <v>0.0008250243459516391</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008150097647623444</v>
+        <v>0.0008150097647623449</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00081219901388321</v>
+        <v>0.0008121990138832098</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008122080512961021</v>
+        <v>0.0008122080512961016</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000827084935172506</v>
+        <v>0.0008270849351725058</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008082235680513008</v>
+        <v>0.0008082235680513007</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008325521223994867</v>
+        <v>0.0008325521223994863</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0008053848905829419</v>
+        <v>0.0008053848905829417</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0008238185267634117</v>
+        <v>0.0008238185267634112</v>
       </c>
       <c r="O7" t="n">
         <v>0.0008518030465317484</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0008419922028742759</v>
+        <v>0.0008419922028742756</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0008024011255962339</v>
+        <v>0.0008024011255962337</v>
       </c>
       <c r="R7" t="n">
         <v>0.0008686542112372211</v>
@@ -7100,7 +7100,7 @@
         <v>0.0008285089498408384</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0008051683207922901</v>
+        <v>0.00080516832079229</v>
       </c>
       <c r="U7" t="n">
         <v>0.0008058784051337368</v>
@@ -7109,7 +7109,7 @@
         <v>0.0008413726287197719</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0008693917955439095</v>
+        <v>0.000869391795543909</v>
       </c>
       <c r="X7" t="n">
         <v>0.001046160626515576</v>
@@ -7118,13 +7118,13 @@
         <v>0.0008396722877947235</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008336284631757734</v>
+        <v>0.0008336284631757733</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0008782221348808088</v>
+        <v>0.0008782221348808084</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.000803153052436596</v>
+        <v>0.0008031530524365959</v>
       </c>
     </row>
     <row r="8">
@@ -7134,31 +7134,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008940565759659657</v>
+        <v>0.0008940565759659656</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001013280217756103</v>
+        <v>0.001013280217756102</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001022668641445257</v>
+        <v>0.001022668641445256</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00104467852337865</v>
+        <v>0.0009770576679274192</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009187670200105124</v>
+        <v>0.0009187670200105118</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001015962727989949</v>
+        <v>0.001042295876658586</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001013151977110815</v>
+        <v>0.001013151977110814</v>
       </c>
       <c r="I8" t="n">
         <v>0.001013161014523707</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001028037898400112</v>
+        <v>0.00102803789840011</v>
       </c>
       <c r="K8" t="n">
         <v>0.001009176531278906</v>
@@ -7167,52 +7167,52 @@
         <v>0.001033505085627091</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001006337853810547</v>
+        <v>0.001006337853810527</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0009263294626493552</v>
+        <v>0.0009263294626493546</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0009813759051356293</v>
+        <v>0.000981375905135629</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0009649337851742057</v>
+        <v>0.0009649337851742046</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0008514022029654263</v>
+        <v>0.0008514022029654262</v>
       </c>
       <c r="R8" t="n">
         <v>0.001069607174464826</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001029461913068444</v>
+        <v>0.001029461913068443</v>
       </c>
       <c r="T8" t="n">
         <v>0.001006121284019895</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0009287132242345111</v>
+        <v>0.0009448715024155303</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001042325591947377</v>
+        <v>0.001007558009128577</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001070369716827255</v>
+        <v>0.001070369716827254</v>
       </c>
       <c r="X8" t="n">
         <v>0.001106801007360199</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001166803004131368</v>
+        <v>0.001166803004131367</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001034581426403379</v>
+        <v>0.0009052278803923609</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001079175098108414</v>
+        <v>0.001079175098108413</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001136762449465195</v>
+        <v>0.001136762449465194</v>
       </c>
     </row>
     <row r="9">
@@ -7222,25 +7222,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009397716693832256</v>
+        <v>0.000939771669383226</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000999918276468688</v>
+        <v>0.0009999182764686885</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001009306700157843</v>
+        <v>0.001009306700157842</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001031316582091235</v>
+        <v>0.001015641534690377</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001012615367891829</v>
+        <v>0.0008560468753796198</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001002600786702535</v>
+        <v>0.001002600838308519</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0009997900358234013</v>
+        <v>0.0009997900358234011</v>
       </c>
       <c r="I9" t="n">
         <v>0.0009997990732362929</v>
@@ -7249,13 +7249,13 @@
         <v>0.001014675957112697</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009958145899914915</v>
+        <v>0.0009958145899914917</v>
       </c>
       <c r="L9" t="n">
         <v>0.001020143144339677</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0009929759125231327</v>
+        <v>0.0009929759125231333</v>
       </c>
       <c r="N9" t="n">
         <v>0.001011409548703603</v>
@@ -7264,43 +7264,43 @@
         <v>0.001061911113965009</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001056995329558232</v>
+        <v>0.001056995329558231</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0009899921991424097</v>
+        <v>0.0009899921991424101</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001056245233177413</v>
+        <v>0.001056245233177412</v>
       </c>
       <c r="S9" t="n">
         <v>0.001016099971781029</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0009927593427324825</v>
+        <v>0.000992759342732481</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0009935465450201537</v>
+        <v>0.0009935465450201526</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001028963650659963</v>
+        <v>0.001107339064457461</v>
       </c>
       <c r="W9" t="n">
         <v>0.0010569828174841</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001233751648455768</v>
+        <v>0.001233751648455769</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001027263309734914</v>
+        <v>0.001027263309734915</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001021219485115964</v>
+        <v>0.0009802712791752719</v>
       </c>
       <c r="AA9" t="n">
         <v>0.001065813156820999</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0009907440743767868</v>
+        <v>0.0009907440743767871</v>
       </c>
     </row>
   </sheetData>
@@ -7466,40 +7466,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008150822666598917</v>
+        <v>0.0008150822666598914</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008758108011238522</v>
+        <v>0.0008758108011238527</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008157783478089226</v>
+        <v>0.0008157783478089224</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008072371351741356</v>
+        <v>0.0008072371351741357</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008081296637574754</v>
+        <v>0.0008081296637574757</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008358830576966991</v>
+        <v>0.0008358830576966994</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008083438789158537</v>
+        <v>0.0008083438789158538</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000815169304815634</v>
+        <v>0.0008151693048156341</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008231780138924587</v>
+        <v>0.0008231780138924584</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000823587582507347</v>
+        <v>0.0008235875825073471</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008338460122547257</v>
+        <v>0.0008338460122547255</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008353765779071816</v>
+        <v>0.0008353765779071815</v>
       </c>
       <c r="N2" t="n">
         <v>0.0008243250935179575</v>
@@ -7508,40 +7508,40 @@
         <v>0.001146659074890753</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008291373495543618</v>
+        <v>0.000829137349554362</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0008102858477510477</v>
+        <v>0.0008102858477510474</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0008097616332170922</v>
+        <v>0.0008097616332170924</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008171091560864709</v>
+        <v>0.0008171091560864706</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008145518749923903</v>
+        <v>0.0008145518749923901</v>
       </c>
       <c r="U2" t="n">
         <v>0.00104504411066983</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008068580618185793</v>
+        <v>0.0008068580618185794</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009896602764660207</v>
+        <v>0.0009896602764660205</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008270987370276122</v>
+        <v>0.0008270987370276123</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008210619484081638</v>
+        <v>0.0008210619484081641</v>
       </c>
       <c r="Z2" t="n">
         <v>0.0009614728711778821</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008199945546448997</v>
+        <v>0.0008199945546449</v>
       </c>
       <c r="AB2" t="n">
         <v>0.0008455260908264419</v>
@@ -7554,34 +7554,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008609712725489822</v>
+        <v>0.0008609712725489815</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008957912254179357</v>
+        <v>0.000895791225417936</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008667603531836434</v>
+        <v>0.0008667603531836427</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008053842443447952</v>
+        <v>0.0008053842443447953</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008119946204580603</v>
+        <v>0.0008119946204580597</v>
       </c>
       <c r="G3" t="n">
         <v>0.001008595148277616</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008136820151774413</v>
+        <v>0.0008136820151774414</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008624097690895119</v>
+        <v>0.0008624097690895115</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009187022269241251</v>
+        <v>0.0009187022269241252</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009216849983941465</v>
+        <v>0.0009216849983941463</v>
       </c>
       <c r="L3" t="n">
         <v>0.0009948670915899183</v>
@@ -7590,46 +7590,46 @@
         <v>0.001006540534803458</v>
       </c>
       <c r="N3" t="n">
-        <v>0.000927631275028056</v>
+        <v>0.0009276312750280557</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001401507657642543</v>
+        <v>0.001401507657642542</v>
       </c>
       <c r="P3" t="n">
-        <v>0.000961074990367617</v>
+        <v>0.0009610749903676166</v>
       </c>
       <c r="Q3" t="n">
         <v>0.0008272413397394016</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008237939544970073</v>
+        <v>0.0008237939544970071</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008752120292364904</v>
+        <v>0.0008752120292364903</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008579706294844257</v>
+        <v>0.0008579706294844254</v>
       </c>
       <c r="U3" t="n">
         <v>0.001318010298842298</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008025377856973274</v>
+        <v>0.0008025377856973276</v>
       </c>
       <c r="W3" t="n">
         <v>0.00114309335217933</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0009475859885469431</v>
+        <v>0.0009475859885469432</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009040690287929388</v>
+        <v>0.000904069028792939</v>
       </c>
       <c r="Z3" t="n">
         <v>0.001084216260609168</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008965286992707595</v>
+        <v>0.0008965286992707591</v>
       </c>
       <c r="AB3" t="n">
         <v>0.001078609955587742</v>
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0009199767339867138</v>
+        <v>0.0009199767339867175</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007839938589227299</v>
+        <v>0.0007839938589227324</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009278392907781669</v>
+        <v>0.0009278392907781688</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008313623649163207</v>
+        <v>0.0008313623649163251</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008414438858485801</v>
+        <v>0.0008414438858485824</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001154931237584084</v>
+        <v>0.001154931237584087</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008438635446063027</v>
+        <v>0.0008438635446063049</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0009209598699953532</v>
+        <v>0.0009209598699953549</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001011001653573939</v>
+        <v>0.001011001653573942</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001016048189122323</v>
+        <v>0.001016048189122326</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00113192187222978</v>
+        <v>0.001131921872229784</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001150071516008784</v>
+        <v>0.001150071516008786</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001024378715258996</v>
+        <v>0.001024378715258997</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0009061526006957997</v>
+        <v>0.0009061526006958021</v>
       </c>
       <c r="P4" t="n">
         <v>0.001078735360937331</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0008657989759496066</v>
+        <v>0.0008657989759496095</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0008598777316379836</v>
+        <v>0.0008598777316379878</v>
       </c>
       <c r="S4" t="n">
-        <v>0.000942871382475123</v>
+        <v>0.0009428713824751276</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0009139857161100686</v>
+        <v>0.0009139857161100723</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001074964339232637</v>
+        <v>0.00107496433923264</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0008243207593167603</v>
+        <v>0.0008243207593167605</v>
       </c>
       <c r="W4" t="n">
-        <v>0.000906487066613842</v>
+        <v>0.0009064870666138434</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001055708294639592</v>
+        <v>0.001055708294639595</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0009832960462179429</v>
+        <v>0.0009832960462179457</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0008817902898860094</v>
+        <v>0.0008817902898860132</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0009754632865415023</v>
+        <v>0.0009754632865415059</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001260396658567337</v>
+        <v>0.00126039665856734</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003732152607538404</v>
+        <v>0.003732152607538407</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001453678935602251</v>
+        <v>0.001453678935602254</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004337481910528824</v>
+        <v>0.004337481910528818</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002281362964518995</v>
+        <v>0.002281362964519002</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002605657440625012</v>
+        <v>0.00260565744062501</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007711704974731931</v>
+        <v>0.007711704974731932</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002739575186876785</v>
+        <v>0.002739575186876788</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004205285376324976</v>
+        <v>0.004205285376324982</v>
       </c>
       <c r="J5" t="n">
-        <v>0.005433630563646113</v>
+        <v>0.005433630563646122</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005554703786116265</v>
+        <v>0.005554703786116258</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007727373111920836</v>
+        <v>0.007727373111920841</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008227275377284128</v>
+        <v>0.008227275377284127</v>
       </c>
       <c r="N5" t="n">
-        <v>0.006756225915410515</v>
+        <v>0.006756225915410529</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003427799426433423</v>
+        <v>0.00342779942643343</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006618205013750596</v>
+        <v>0.006618205013750602</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002987146733437471</v>
+        <v>0.002987146733437476</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003038674938249949</v>
+        <v>0.003038674938249952</v>
       </c>
       <c r="S5" t="n">
         <v>0.004039766807438374</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004055337020466362</v>
+        <v>0.004055337020466367</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00681103548328916</v>
+        <v>0.00681103548328918</v>
       </c>
       <c r="V5" t="n">
         <v>0.002119229460498285</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003755856563421868</v>
+        <v>0.003755856563421872</v>
       </c>
       <c r="X5" t="n">
-        <v>0.006772709573992355</v>
+        <v>0.006772709573992364</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.005243099108159321</v>
+        <v>0.005243099108159318</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.003092547973399253</v>
+        <v>0.003092547973399256</v>
       </c>
       <c r="AA5" t="n">
         <v>0.005058352355828796</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01141338759994694</v>
+        <v>0.01141338759994693</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001205863995841018</v>
+        <v>0.00120586399584102</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009292538404915201</v>
+        <v>0.0009292538404915243</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00121372655263247</v>
+        <v>0.001213726552632472</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001117249626770625</v>
+        <v>0.001117249626770627</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001127331147702884</v>
+        <v>0.001127331147702885</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001300191219152876</v>
+        <v>0.001300191219152879</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001129750806460605</v>
+        <v>0.001129750806460608</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001066219851564145</v>
+        <v>0.001066219851564147</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001296888915428242</v>
+        <v>0.001156261635142735</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001161308170691115</v>
+        <v>0.001161308170691118</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001277181853798572</v>
+        <v>0.001417809134084087</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001435958777863086</v>
+        <v>0.001435958777863088</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0011700730943983</v>
+        <v>0.001170073094398309</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001051846979835101</v>
+        <v>0.001051846979835115</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001365576516216002</v>
+        <v>0.001365576516216003</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001011058957518399</v>
+        <v>0.001151686237803912</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001145764993492287</v>
+        <v>0.00114576499349229</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001228758644329426</v>
+        <v>0.00122875864432943</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001199872977964372</v>
+        <v>0.001059245697678864</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001365075544991955</v>
+        <v>0.001365075544991958</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0009695807408855525</v>
+        <v>0.001110208021171063</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001062061961928421</v>
+        <v>0.001062061961928423</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001341595556493895</v>
+        <v>0.001200968276208386</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001141104005132903</v>
+        <v>0.001141104005132925</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001027050271454801</v>
+        <v>0.001027050271454805</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001261350548395807</v>
+        <v>0.001261350548395809</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001408209131435699</v>
+        <v>0.001408209131435702</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001019056686143469</v>
+        <v>0.00101905668614347</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008830738110794829</v>
+        <v>0.0008830738110794849</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001026919242934922</v>
+        <v>0.001026919242934921</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0009304423170730758</v>
+        <v>0.0009304423170730777</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0009405238380053338</v>
+        <v>0.0009405238380053348</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00125401118974084</v>
+        <v>0.001254011189740841</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009429434967630548</v>
+        <v>0.0009429434967630575</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001020039822152108</v>
+        <v>0.001020039822152107</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001110081605730697</v>
+        <v>0.001110081605730696</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001115128141279077</v>
+        <v>0.001115128141279078</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001231001824386534</v>
+        <v>0.001231001824386537</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001249151468165539</v>
+        <v>0.001249151468165538</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001123458667415749</v>
+        <v>0.00112345866741575</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001005222790862235</v>
+        <v>0.001005222790862238</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001177805551103762</v>
+        <v>0.001177805551103766</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0009648789281063616</v>
+        <v>0.0009648789281063617</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0009589576837947389</v>
+        <v>0.0009589576837947405</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001041951334631879</v>
+        <v>0.00104195133463188</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001013065668266826</v>
+        <v>0.001013065668266825</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001178128353092084</v>
+        <v>0.001178128353092087</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0009234007114735132</v>
+        <v>0.0009234007114735135</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001005567018770594</v>
+        <v>0.001005567018770596</v>
       </c>
       <c r="X7" t="n">
         <v>0.001154788246796347</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001086599942279714</v>
+        <v>0.001086599942279716</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0009808702420427647</v>
+        <v>0.0009808702420427656</v>
       </c>
       <c r="AA7" t="n">
         <v>0.001074543238698258</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001359476610724091</v>
+        <v>0.001359476610724092</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001103262370368203</v>
+        <v>0.001103262370368206</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001117726902479829</v>
+        <v>0.001117726902479832</v>
       </c>
       <c r="D8" t="n">
         <v>0.001261572334335268</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001165095408473421</v>
+        <v>0.001084986602077708</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001048167469949258</v>
+        <v>0.001048167469949262</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001488664281141184</v>
+        <v>0.001519860531091179</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001177596588163402</v>
+        <v>0.001177596588163405</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001254692913552451</v>
+        <v>0.001254692913552455</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001344734697131038</v>
+        <v>0.001344734697131042</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001349781232679421</v>
+        <v>0.001349781232679424</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00146565491578688</v>
+        <v>0.001465654915786884</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001483804559565882</v>
+        <v>0.001483804559565874</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001241489848946194</v>
+        <v>0.001241489848946196</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001155312447814925</v>
+        <v>0.001155312447814927</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001320039293990008</v>
+        <v>0.001320039293990013</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001019518263032452</v>
+        <v>0.001019518263032456</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001193610775195084</v>
+        <v>0.001193610775195087</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001276604426032224</v>
+        <v>0.001276604426032227</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001247718759667168</v>
+        <v>0.001247718759667171</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001320249138536969</v>
+        <v>0.001339389115267928</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001158053802873859</v>
+        <v>0.001116823034471499</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001240249677374819</v>
+        <v>0.001240249677374823</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001223216385519946</v>
+        <v>0.001223216385519947</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001470666958374577</v>
+        <v>0.001470666958374579</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00121552333344311</v>
+        <v>0.001062281288441132</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001309196330098604</v>
+        <v>0.001309196330098605</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001751284599106345</v>
+        <v>0.001751284599106346</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001262252867561865</v>
+        <v>0.001262252867561867</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001235722362550577</v>
+        <v>0.00123572236255058</v>
       </c>
       <c r="D9" t="n">
         <v>0.001379567794406015</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00128309086854417</v>
+        <v>0.00125782972971434</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001293172389476427</v>
+        <v>0.001040854767244164</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001606659741211934</v>
+        <v>0.001606659769462372</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00129559204823415</v>
+        <v>0.001295592048234152</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001372688373623199</v>
+        <v>0.001372688373623202</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001462730157201789</v>
+        <v>0.001462730157201791</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001467776692750169</v>
+        <v>0.001467776692750173</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001583650375857628</v>
+        <v>0.001583650375857633</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001601800019636631</v>
+        <v>0.001601800019636634</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001476107218886843</v>
+        <v>0.001476107218886845</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001394153514056573</v>
+        <v>0.001394153514056578</v>
       </c>
       <c r="P9" t="n">
-        <v>0.00157462489494085</v>
+        <v>0.001574624894940851</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001317527507827889</v>
+        <v>0.001317527507827893</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001311606235265833</v>
+        <v>0.001311606235265836</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001394599886102972</v>
+        <v>0.001394599886102974</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001365714219737916</v>
+        <v>0.00136571421973792</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001530916786765501</v>
+        <v>0.001530916786765504</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001276049262944608</v>
+        <v>0.001402354868499787</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001358215570241689</v>
+        <v>0.001358215570241691</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001507436798267438</v>
+        <v>0.001507436798267442</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001439248493750806</v>
+        <v>0.00143924849375081</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001333518793513858</v>
+        <v>0.001267528758474532</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001427191790169351</v>
+        <v>0.001427191790169354</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001712125162195188</v>
+        <v>0.001712125162195189</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007861791437478259</v>
+        <v>0.0007861791437478277</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008619432342242322</v>
+        <v>0.0008619432342242315</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007891003897988097</v>
+        <v>0.0007891003897988098</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007885170090668018</v>
+        <v>0.0007885170090668027</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007880061593972723</v>
+        <v>0.0007880061593972738</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008141002861013553</v>
+        <v>0.0008141002861013547</v>
       </c>
       <c r="H2" t="n">
         <v>0.0007888399921013024</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000788603142925729</v>
+        <v>0.0007886031429257286</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007977576061826994</v>
+        <v>0.0007977576061826983</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007912050037841083</v>
+        <v>0.0007912050037841091</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007997175417499255</v>
+        <v>0.0007997175417499265</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007892093745595929</v>
+        <v>0.0007892093745595935</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007907107089642061</v>
+        <v>0.0007907107089642066</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001111001634315324</v>
+        <v>0.001111001634315323</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008017362017893238</v>
+        <v>0.0008017362017893228</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.000790433768935934</v>
+        <v>0.0007904337689359334</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007919512472227647</v>
+        <v>0.0007919512472227643</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007910937169726595</v>
+        <v>0.0007910937169726583</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007884179524553542</v>
+        <v>0.0007884179524553557</v>
       </c>
       <c r="U2" t="n">
         <v>0.001006680096221099</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007890825394401478</v>
+        <v>0.0007890825394401488</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009724428487493959</v>
+        <v>0.0009724428487493969</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008046480227425701</v>
+        <v>0.0008046480227425698</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008110542105823988</v>
+        <v>0.0008110542105823996</v>
       </c>
       <c r="Z2" t="n">
         <v>0.0009353709294640084</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0007917858702279382</v>
+        <v>0.0007917858702279394</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008137423924482858</v>
+        <v>0.0008137423924482834</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007526039287128641</v>
+        <v>0.0007526039287128629</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008847820603057441</v>
+        <v>0.0008847820603057452</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007735447584817268</v>
+        <v>0.0007735447584817284</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007692588250756898</v>
+        <v>0.0007692588250756905</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007657352745397013</v>
+        <v>0.0007657352745397018</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009504313582951874</v>
+        <v>0.0009504313582951857</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000771805145280008</v>
+        <v>0.0007718051452800072</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007700359083547768</v>
+        <v>0.0007700359083547771</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0008347948767296393</v>
+        <v>0.0008347948767296388</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007883790454515744</v>
+        <v>0.0007883790454515751</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008487474618854475</v>
+        <v>0.0008487474618854474</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000776157181213005</v>
+        <v>0.000776157181213004</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0007850374928954324</v>
+        <v>0.000785037492895432</v>
       </c>
       <c r="O3" t="n">
         <v>0.001305339105817383</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008631171701648923</v>
+        <v>0.0008631171701648919</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007828901657790098</v>
+        <v>0.00078289016577901</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007940590768514848</v>
+        <v>0.0007940590768514862</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00078745325822733</v>
+        <v>0.0007874532582273304</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007686891221347324</v>
+        <v>0.0007686891221347313</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001140962797887641</v>
+        <v>0.001140962797887642</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007732124883046718</v>
+        <v>0.0007732124883046714</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00111396876769285</v>
+        <v>0.001113968767692853</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008844787770699098</v>
+        <v>0.0008844787770699088</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009301126521054637</v>
+        <v>0.0009301126521054632</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001015718009616299</v>
+        <v>0.001015718009616297</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0007926677802207076</v>
+        <v>0.0007926677802207089</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0009489959566137893</v>
+        <v>0.0009489959566137859</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007359971092308652</v>
+        <v>0.0007359971092308651</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007504656342037766</v>
+        <v>0.0007504656342037775</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007689939272162864</v>
+        <v>0.0007689939272162877</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007624043734798686</v>
+        <v>0.0007624043734798684</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007566340914600753</v>
+        <v>0.0007566340914600768</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001051379256474021</v>
+        <v>0.001051379256474018</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007660526154340837</v>
+        <v>0.0007660526154340807</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007633772950399708</v>
+        <v>0.0007633772950399681</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0008664064869281618</v>
+        <v>0.0008664064869281615</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007927665103505034</v>
+        <v>0.0007927665103505046</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008889195426353431</v>
+        <v>0.0008889195426353447</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007736906991549657</v>
+        <v>0.0007736906991549647</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0007871832229728574</v>
+        <v>0.0007871832229728557</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0007703694087726075</v>
+        <v>0.0007703694087726087</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0009117212364098269</v>
+        <v>0.0009117212364098255</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0007840550579547948</v>
+        <v>0.000784055057954795</v>
       </c>
       <c r="R4" t="n">
-        <v>0.000801195673279057</v>
+        <v>0.0008011956732790573</v>
       </c>
       <c r="S4" t="n">
-        <v>0.000791509474620706</v>
+        <v>0.0007915094746207036</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007612854834852848</v>
+        <v>0.0007612854834852832</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0007829905979519742</v>
+        <v>0.0007829905979519719</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007663364756151424</v>
+        <v>0.0007663364756151414</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0008468643152088959</v>
+        <v>0.0008468643152088938</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0009446115935805716</v>
+        <v>0.0009446115935805711</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00101350115363953</v>
+        <v>0.001013501153639531</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0007709833109296665</v>
+        <v>0.0007709833109296662</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0007993276640453373</v>
+        <v>0.0007993276640453358</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001045105782649273</v>
+        <v>0.001045105782649271</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001033316028591949</v>
+        <v>0.001033316028591948</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001319578345140162</v>
+        <v>0.001319578345140159</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001664466874066046</v>
+        <v>0.001664466874066047</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001484532552683847</v>
+        <v>0.00148453255268385</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00144591096959788</v>
+        <v>0.001445910969597883</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005861418125567521</v>
+        <v>0.005861418125567493</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001674040146452671</v>
+        <v>0.001674040146452668</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001585869716908051</v>
+        <v>0.001585869716908053</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003115403367576734</v>
+        <v>0.00311540336757673</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001988302299422449</v>
+        <v>0.001988302299422452</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00348889707417369</v>
+        <v>0.003488897074173691</v>
       </c>
       <c r="M5" t="n">
         <v>0.001722448550049862</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001864176199387021</v>
+        <v>0.001864176199387023</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001569251345744839</v>
+        <v>0.001569251345744846</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003872713442465797</v>
+        <v>0.003872713442465802</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001842238619887658</v>
+        <v>0.001842238619887656</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002320865877564801</v>
+        <v>0.002320865877564797</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001897908646716324</v>
+        <v>0.001897908646716327</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001535879337282041</v>
+        <v>0.001535879337282042</v>
       </c>
       <c r="U5" t="n">
         <v>0.001863454852950056</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001552275575492463</v>
+        <v>0.001552275575492465</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003021498052975732</v>
+        <v>0.003021498052975729</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004754898071369444</v>
+        <v>0.004754898071369438</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.005989422475152426</v>
+        <v>0.005989422475152432</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001575628542427173</v>
+        <v>0.00157562854242717</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00217848538928022</v>
+        <v>0.002178485389280224</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.006958441068593623</v>
+        <v>0.006958441068593611</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000991629828526969</v>
+        <v>0.0008682205419892886</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001006098353499879</v>
+        <v>0.001006098353499881</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0009012173599747095</v>
+        <v>0.0009012173599747109</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008946278062382904</v>
+        <v>0.001018037092775971</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008888575242185005</v>
+        <v>0.00101226681075618</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001307011975770124</v>
+        <v>0.001183602689232441</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0008982760481925042</v>
+        <v>0.001021685334730184</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008956007277983904</v>
+        <v>0.001019010014336071</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001122039206224268</v>
+        <v>0.0009986299196865845</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0009249899431089295</v>
+        <v>0.001048399229646608</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001144552261931444</v>
+        <v>0.001021142975393768</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0009059141319133861</v>
+        <v>0.001029323418451068</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0009195401240098901</v>
+        <v>0.0009195401240098786</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001026784745245225</v>
+        <v>0.0009027263098096371</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001033902378252596</v>
+        <v>0.001033902378252602</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0009162784907132169</v>
+        <v>0.001039687777250898</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001056828392575162</v>
+        <v>0.00105682839257516</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0009237329073791264</v>
+        <v>0.0009237329073791269</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0008935089162437054</v>
+        <v>0.0008935089162437062</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001042094595831988</v>
+        <v>0.0009186853092943107</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001021969194911246</v>
+        <v>0.001021969194911244</v>
       </c>
       <c r="W6" t="n">
-        <v>0.000988505994053224</v>
+        <v>0.0009885059940532232</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001200244312876674</v>
+        <v>0.001076835026338994</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001156596000775413</v>
+        <v>0.001156596000775415</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0009032067436880891</v>
+        <v>0.0009032067436880899</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001054960383341442</v>
+        <v>0.001054960383341439</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001178895914719134</v>
+        <v>0.00117889591471913</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0008206871051223992</v>
+        <v>0.0008206871051224034</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008351556300953142</v>
+        <v>0.0008351556300953155</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008536839231078272</v>
+        <v>0.0008536839231078258</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008470943693714116</v>
+        <v>0.0008470943693714061</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008413240873516186</v>
+        <v>0.0008413240873516147</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001136069252365556</v>
+        <v>0.001136069252365555</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008507426113256228</v>
+        <v>0.0008507426113256187</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008480672909315016</v>
+        <v>0.000848067290931506</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0009510964828197052</v>
+        <v>0.000951096482819699</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008774565062420421</v>
+        <v>0.0008774565062420426</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009736095385268834</v>
+        <v>0.0009736095385268829</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0008583806950465011</v>
+        <v>0.0008583806950465026</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0008718732188643866</v>
+        <v>0.0008718732188643936</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0008550503586140691</v>
+        <v>0.0008550503586140699</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0009964021862512887</v>
+        <v>0.0009964021862512871</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0008687450538463253</v>
+        <v>0.0008687450538463332</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0008858856691705994</v>
+        <v>0.0008858856691705953</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0008761994705122397</v>
+        <v>0.0008761994705122415</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0008459754793768219</v>
+        <v>0.000845975479376821</v>
       </c>
       <c r="U7" t="n">
-        <v>0.000871014156003405</v>
+        <v>0.0008710141560034061</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0008510264715066763</v>
+        <v>0.0008510264715066795</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0009315543111004318</v>
+        <v>0.0009315543111004325</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001029301589472105</v>
+        <v>0.001029301589472109</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001101662428114983</v>
+        <v>0.001101662428114984</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008556733068212011</v>
+        <v>0.0008556733068212046</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0008840176599368806</v>
+        <v>0.0008840176599368736</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001129795778540807</v>
+        <v>0.00112979577854081</v>
       </c>
     </row>
     <row r="8">
@@ -8854,79 +8854,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000893021044843752</v>
+        <v>0.0008930210448437511</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001037730473910578</v>
+        <v>0.001037730473910579</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001056258766923088</v>
+        <v>0.00105625876692309</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00104966921318667</v>
+        <v>0.0009803197736267548</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009339480377708598</v>
+        <v>0.0009339480377708589</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001338644096180825</v>
+        <v>0.001365650396083921</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001053317455140881</v>
+        <v>0.001053317455140883</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001050642134746765</v>
+        <v>0.00105064213474677</v>
       </c>
       <c r="J8" t="n">
         <v>0.001153671326634963</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001080031350057308</v>
+        <v>0.001080031350057307</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001176184382342145</v>
+        <v>0.001176184382342146</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001060955538861765</v>
+        <v>0.001060955538861755</v>
       </c>
       <c r="N8" t="n">
-        <v>0.000973489573173291</v>
+        <v>0.0009734895731732903</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0009844200284876016</v>
+        <v>0.0009844200284875996</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001118971065272272</v>
+        <v>0.001118971065272276</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0009154836833146605</v>
+        <v>0.0009154836833146592</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001088460512985857</v>
+        <v>0.001088460512985859</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001078774314327507</v>
+        <v>0.001078774314327505</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001048550323192082</v>
+        <v>0.001048550323192086</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0009934896130040147</v>
+        <v>0.001010058152867801</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001053601315321945</v>
+        <v>0.001017894528176666</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001134154750966149</v>
+        <v>0.00113415475096615</v>
       </c>
       <c r="X8" t="n">
         <v>0.001087977056581638</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001433562252674973</v>
+        <v>0.00143356225267497</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00105824815063647</v>
+        <v>0.0009255879548847244</v>
       </c>
       <c r="AA8" t="n">
         <v>0.001086592503752138</v>
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009981472460563049</v>
+        <v>0.0009981472460563023</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001098376702115231</v>
+        <v>0.001098376702115229</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001116904995127737</v>
+        <v>0.001116904995127739</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001110315441391319</v>
+        <v>0.001090522222432878</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00110454515937153</v>
+        <v>0.0009068427149956885</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001399290324385471</v>
+        <v>0.001399290394748908</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001113963683345536</v>
+        <v>0.001113963683345533</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001111288362951417</v>
+        <v>0.00111128836295142</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00121431755483961</v>
+        <v>0.001214317554839613</v>
       </c>
       <c r="K9" t="n">
         <v>0.001140677578261956</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001236830610546797</v>
+        <v>0.001236830610546796</v>
       </c>
       <c r="M9" t="n">
         <v>0.001121601767066417</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001135094290884306</v>
+        <v>0.001135094290884307</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001146701630633888</v>
+        <v>0.001146701630633881</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001294234556327056</v>
+        <v>0.001294234556327055</v>
       </c>
       <c r="Q9" t="n">
         <v>0.001131966196229686</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001149106741190507</v>
+        <v>0.001149106741190509</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001139420542532152</v>
+        <v>0.001139420542532156</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001109196551396734</v>
+        <v>0.001109196551396736</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001134372944447341</v>
+        <v>0.00113437294444734</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001114247543526594</v>
+        <v>0.001213213879274679</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001194775383120345</v>
+        <v>0.001194775383120347</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001292522661492025</v>
+        <v>0.001292522661492023</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001364883500134901</v>
+        <v>0.001364883500134898</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001118894378841119</v>
+        <v>0.001067188191496354</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001147238731956788</v>
+        <v>0.001147238731956787</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001393016850560721</v>
+        <v>0.001393016850560723</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia eutrophication marine results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia eutrophication marine results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008526485002888309</v>
+        <v>0.000819197759677732</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009024653104807751</v>
+        <v>0.0008751374624595906</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008456050472839616</v>
+        <v>0.0008170852271314245</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008337502026067168</v>
+        <v>0.0008044953189155438</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008393814166203795</v>
+        <v>0.000810938874918629</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008729592442491216</v>
+        <v>0.0008168374034983454</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008422652297619724</v>
+        <v>0.0008147556569441045</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00084835487016174</v>
+        <v>0.0008209869303415307</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008539364125510783</v>
+        <v>0.0008172157901638141</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008625173429668845</v>
+        <v>0.0008354634264627713</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008629694360990177</v>
+        <v>0.0008189981226827051</v>
       </c>
       <c r="M2" t="n">
-        <v>0.000874475002709096</v>
+        <v>0.0008616840143724349</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008518582131704801</v>
+        <v>0.0008251109770839523</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001201559148296635</v>
+        <v>0.001156057744657415</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008545538387561246</v>
+        <v>0.0008133788181396231</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0008380156112190542</v>
+        <v>0.0008094275612015407</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0008382077279186104</v>
+        <v>0.0008110242504805604</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008488002071268515</v>
+        <v>0.0008161261861397988</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008490949315460741</v>
+        <v>0.0008213028024916893</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001094081543554183</v>
+        <v>0.001058867916152201</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008361016529817393</v>
+        <v>0.000807692219872106</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001031752158034927</v>
+        <v>0.001001402718253393</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008473877013727463</v>
+        <v>0.0008090862376229409</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008508182674397506</v>
+        <v>0.0008115477971157746</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009932310506495276</v>
+        <v>0.0009613440882894066</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008509192366693664</v>
+        <v>0.0008240230536421572</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008765384700514183</v>
+        <v>0.0008282389230598814</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0009844044445347108</v>
+        <v>0.0009150452404215739</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009318304059817162</v>
+        <v>0.0009087317509149139</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009354703603034424</v>
+        <v>0.0009010635772151379</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008502894260445176</v>
+        <v>0.0008106875352067227</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008910898486940448</v>
+        <v>0.0008572157236151762</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001129301968239678</v>
+        <v>0.0008984719690383636</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000911919281297985</v>
+        <v>0.0008847245162734922</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0009552829669371693</v>
+        <v>0.0009291176005921998</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009941881366239708</v>
+        <v>0.00090149539812682</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001056402415188632</v>
+        <v>0.001032491640023546</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001058842332570695</v>
+        <v>0.0009142264552717236</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001142491056823972</v>
+        <v>0.001219026024529496</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0009798745113633951</v>
+        <v>0.000958160179798649</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001545369485840165</v>
+        <v>0.001460263638314887</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0009981323992155765</v>
+        <v>0.0008737729329648643</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008810038897506338</v>
+        <v>0.0008461271602403264</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000882681643943861</v>
+        <v>0.0008578335688613574</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009573454050562967</v>
+        <v>0.0008934365779818326</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0009604978911943853</v>
+        <v>0.0009312981684974663</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001423708224561261</v>
+        <v>0.001359916129174106</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008668340878038435</v>
+        <v>0.0008333025997966593</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001212941932841405</v>
+        <v>0.001186053971716122</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0009480954974041586</v>
+        <v>0.0008437320376245393</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009722424049608577</v>
+        <v>0.0008611265315227032</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001141899114380424</v>
+        <v>0.001093203324909676</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0009730281743950532</v>
+        <v>0.0009502521171842142</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001156119823705701</v>
+        <v>0.000980732466313459</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00112776772270603</v>
+        <v>0.000970396788349135</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0008480033471139881</v>
+        <v>0.000765621619887647</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001048208680867558</v>
+        <v>0.0009465347614256038</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0009143027567400838</v>
+        <v>0.000804325956483314</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0009779099095108506</v>
+        <v>0.000877108885720372</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001357186919141336</v>
+        <v>0.0009437354794854695</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001010483905564735</v>
+        <v>0.0009202211945045866</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001079269195253072</v>
+        <v>0.0009906062940559035</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001141906483674203</v>
+        <v>0.0009477139604146863</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001239240840646563</v>
+        <v>0.001154124977262552</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001244347440547114</v>
+        <v>0.0009681417966527366</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001374452612374491</v>
+        <v>0.001447291158155556</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001118841066154215</v>
+        <v>0.007480407395433476</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001097232574185378</v>
+        <v>0.000948333341007533</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00114928939719311</v>
+        <v>0.0009046691668308231</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0009624825092013475</v>
+        <v>0.0008600379020471975</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0009646525557008874</v>
+        <v>0.0008780732419670784</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001084299481139145</v>
+        <v>0.0009357019522445376</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001087628529034193</v>
+        <v>0.000994174215300316</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001204451277297961</v>
+        <v>0.001068353730234033</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0009381823934979839</v>
+        <v>0.0008385222282336113</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0009878200773720601</v>
+        <v>0.0009077532502719577</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001068344578861772</v>
+        <v>0.0008561824952103098</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00110085028942539</v>
+        <v>0.0008812589409482577</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0009731313625709377</v>
+        <v>0.0008532574958957748</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001108234894623593</v>
+        <v>0.001024900703422206</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001394339926529799</v>
+        <v>0.001071100845152271</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007143700060979638</v>
+        <v>0.005593295849191562</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002061320871580145</v>
+        <v>0.001900778295836163</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006335241335606773</v>
+        <v>0.005763927703196986</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003298507718521659</v>
+        <v>0.002590349745666967</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004942071840186399</v>
+        <v>0.004377113850467199</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01172729431084702</v>
+        <v>0.005218478556980449</v>
       </c>
       <c r="H5" t="n">
-        <v>0.005745152196399195</v>
+        <v>0.005404724885954351</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007071866976302513</v>
+        <v>0.006774685692152142</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007787982867722694</v>
+        <v>0.005496147666968338</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01031782346814856</v>
+        <v>0.01010003090329229</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009953088150898235</v>
+        <v>0.005908081320113773</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0134375544946488</v>
+        <v>0.01661638359174124</v>
       </c>
       <c r="N5" t="n">
-        <v>0.009022239518681261</v>
+        <v>0.007480407395433476</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006442904826083793</v>
+        <v>0.005081144165067257</v>
       </c>
       <c r="P5" t="n">
-        <v>0.007654044244838565</v>
+        <v>0.004422887494199616</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00443042513407502</v>
+        <v>0.003853703492926945</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004656357418873847</v>
+        <v>0.004401595158081978</v>
       </c>
       <c r="S5" t="n">
-        <v>0.006509899177198544</v>
+        <v>0.0050808327932813</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007200425714470165</v>
+        <v>0.006802656671357147</v>
       </c>
       <c r="U5" t="n">
-        <v>0.009114093841126564</v>
+        <v>0.007833283014044328</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003689391606355641</v>
+        <v>0.003195934376731544</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004841760731992534</v>
+        <v>0.004731760311372982</v>
       </c>
       <c r="X5" t="n">
-        <v>0.006682634948560339</v>
+        <v>0.003800385145922585</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.007262550275752293</v>
+        <v>0.004257021451311287</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004354486256830496</v>
+        <v>0.003481480694567356</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.007324237475524176</v>
+        <v>0.007147653053885667</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01428982117509024</v>
+        <v>0.008769263119199395</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001452390225326869</v>
+        <v>0.001128483174129544</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001172625849734828</v>
+        <v>0.001067593748001149</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001206005839435076</v>
+        <v>0.001248506889539106</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001072099915307602</v>
+        <v>0.001106298084596816</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00130253241213169</v>
+        <v>0.001035195271500781</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001681809421762176</v>
+        <v>0.001245707607598972</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001335106408185575</v>
+        <v>0.001222193322618089</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00123706635382059</v>
+        <v>0.001148692679836314</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001466528986295043</v>
+        <v>0.001105800346195095</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00139703799921408</v>
+        <v>0.001456097105376055</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001402144599114632</v>
+        <v>0.001270113924766241</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001532249770942009</v>
+        <v>0.001749263286269061</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001277427058008948</v>
+        <v>0.007480407395433476</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001422704203139344</v>
+        <v>0.001107139603506494</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001474761238914924</v>
+        <v>0.001206654082954372</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001120279667768864</v>
+        <v>0.001162010030160701</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001122449714268405</v>
+        <v>0.001180045370080581</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001408921983759985</v>
+        <v>0.001093788338024947</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001245425687601711</v>
+        <v>0.001152260601080725</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001368492547167047</v>
+        <v>0.001229168117121357</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001262804896118824</v>
+        <v>0.001140494356347114</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00131329180364717</v>
+        <v>0.001209738095581632</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001392967081482612</v>
+        <v>0.001158154623323813</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001274294120723605</v>
+        <v>0.001051702213272638</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001130928521138456</v>
+        <v>0.001011343881676185</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001266032053191111</v>
+        <v>0.001326872831535709</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001555187684752818</v>
+        <v>0.001230882190243561</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00124673421004512</v>
+        <v>0.001076583544714161</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0009669698344530793</v>
+        <v>0.0008718083762526733</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001167175168206649</v>
+        <v>0.00105272151779063</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001033269244079174</v>
+        <v>0.0009105127128483401</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001096876396849941</v>
+        <v>0.0009832956420853976</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001476153406480426</v>
+        <v>0.001049922235850496</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001129450392903825</v>
+        <v>0.001026407950869612</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001198235682592164</v>
+        <v>0.00109679305042093</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001260872971013293</v>
+        <v>0.001053900716779712</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001358207327985653</v>
+        <v>0.001260311733627578</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001363313927886205</v>
+        <v>0.001074328553017763</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001493419099713581</v>
+        <v>0.001553477914520584</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001237807553493305</v>
+        <v>0.007480407395433476</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001216188485838512</v>
+        <v>0.001054509586932446</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001268245308846243</v>
+        <v>0.001010845412755736</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001081448996540438</v>
+        <v>0.0009662246584122233</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001083619043039978</v>
+        <v>0.0009842599983321044</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001203265968478234</v>
+        <v>0.001041888708609564</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001206595016373284</v>
+        <v>0.001100360971665343</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001329505960913279</v>
+        <v>0.001177183259289406</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001057148880837075</v>
+        <v>0.0009447089845986376</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001106786564711151</v>
+        <v>0.001013940006636984</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001187311066200862</v>
+        <v>0.000962369251575336</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001226060888066048</v>
+        <v>0.0009901736984201986</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001092097849910029</v>
+        <v>0.0009594442522608012</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001227201381962683</v>
+        <v>0.001131087459787232</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001513306413868889</v>
+        <v>0.001177287601517295</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00134741002487641</v>
+        <v>0.001168753640237082</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001246956413663806</v>
+        <v>0.001125496753874912</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001447161747417377</v>
+        <v>0.001306409895412869</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001217778130599945</v>
+        <v>0.001078197369748198</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001225486733119056</v>
+        <v>0.001100628398252617</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001793321240784315</v>
+        <v>0.001337102481458292</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001409436972114553</v>
+        <v>0.001280096328491851</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001478222261802892</v>
+        <v>0.001350481428043169</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001540859550224021</v>
+        <v>0.001307589094401951</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001638193907196381</v>
+        <v>0.001514000111249817</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001643300507096933</v>
+        <v>0.001328016930640002</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001773405678924307</v>
+        <v>0.001807166292142829</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001378798292265494</v>
+        <v>0.007480407395433476</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001395387064115925</v>
+        <v>0.001217411846083058</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001438080814787722</v>
+        <v>0.001165313669830712</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001146886153609908</v>
+        <v>0.001026652725033327</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001363605622250706</v>
+        <v>0.001237948375954343</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001483252547688963</v>
+        <v>0.001295577086231803</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001486581595584012</v>
+        <v>0.001354049349287582</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001522016629853239</v>
+        <v>0.001352064042985377</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001288002891978744</v>
+        <v>0.001154188113233049</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001386808383597651</v>
+        <v>0.001267660127207995</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001269182411104945</v>
+        <v>0.00103760078967935</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001684139394192592</v>
+        <v>0.001404356969614996</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00118944287523687</v>
+        <v>0.001048614062771725</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001507187961173411</v>
+        <v>0.00138477583740947</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001980598080171027</v>
+        <v>0.001599695330711557</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001608294820492243</v>
+        <v>0.001349311679824671</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001478725079241106</v>
+        <v>0.001264772231570833</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001678930412994677</v>
+        <v>0.001445685373108791</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001510360201721816</v>
+        <v>0.001275726599861321</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001262391980437009</v>
+        <v>0.00109908343938821</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001987908679645648</v>
+        <v>0.001442886020298375</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001641205637691852</v>
+        <v>0.001419371806187773</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00170999092738019</v>
+        <v>0.00148975690573909</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00177262821580132</v>
+        <v>0.001446864572097874</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00186996257277368</v>
+        <v>0.00165327558894574</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00187506917267423</v>
+        <v>0.001467292408335925</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002005174344501608</v>
+        <v>0.001946441769838742</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001749562798281333</v>
+        <v>0.007480407395433476</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001777728649251889</v>
+        <v>0.001487329818576247</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001840610531693017</v>
+        <v>0.001452331452002317</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001593204269705657</v>
+        <v>0.001359188442860102</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001595374287828004</v>
+        <v>0.001377223853650265</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001715021213266261</v>
+        <v>0.001434852563927725</v>
       </c>
       <c r="T9" t="n">
-        <v>0.00171835026116131</v>
+        <v>0.001493324826983504</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001841417120726646</v>
+        <v>0.001570232343024137</v>
       </c>
       <c r="V9" t="n">
-        <v>0.00174222538232633</v>
+        <v>0.001476421997588035</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001618541809499178</v>
+        <v>0.001406903861955145</v>
       </c>
       <c r="X9" t="n">
-        <v>0.00169906631098889</v>
+        <v>0.001355333106893497</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001737816132854074</v>
+        <v>0.001383137553738361</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001513299097286771</v>
+        <v>0.001279916631929367</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001738956626750709</v>
+        <v>0.001524051315105393</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002025061658656916</v>
+        <v>0.001570251456835456</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.000763545599253249</v>
+        <v>0.0007650584462983489</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008197371866976492</v>
+        <v>0.0008212677122434727</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007650611057453321</v>
+        <v>0.0007665548504688234</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007643252873284722</v>
+        <v>0.0007657906768059998</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000765832332220779</v>
+        <v>0.0007673229060521725</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007665995629165216</v>
+        <v>0.0007676803384907469</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007653534024949574</v>
+        <v>0.0007668571827509974</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007653194387578786</v>
+        <v>0.0007669109217357422</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007668353206452567</v>
+        <v>0.0007682550703562016</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007669680229525512</v>
+        <v>0.000768562742527041</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007684241503812294</v>
+        <v>0.0007697120513130345</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007650341934511756</v>
+        <v>0.0007669609972165925</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007662409865791284</v>
+        <v>0.000767818995859806</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001085677255385884</v>
+        <v>0.001087413970790262</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007671865244713642</v>
+        <v>0.0007686473515066208</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007647574709812419</v>
+        <v>0.0007662413073582054</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007685633534906053</v>
+        <v>0.0007700950348917502</v>
       </c>
       <c r="S2" t="n">
-        <v>0.000767489222876068</v>
+        <v>0.0007688269938136304</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007658385874528715</v>
+        <v>0.000767463351796335</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009250609974273886</v>
+        <v>0.0009254643199282647</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007673397245664847</v>
+        <v>0.0007688109322927301</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0008969573941823841</v>
+        <v>0.0008983526122869447</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0007827402918047801</v>
+        <v>0.000784074752639968</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.000774305657148794</v>
+        <v>0.0007758022883556357</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009128364620264471</v>
+        <v>0.0009143334867103289</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0007729913997843236</v>
+        <v>0.0007744681120121976</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0007640567454095875</v>
+        <v>0.0007654045821162589</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007330122793509612</v>
+        <v>0.0007347764242136679</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008322055344252565</v>
+        <v>0.0008338671086453148</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007438837145392017</v>
+        <v>0.0007455133645951723</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007385230893343224</v>
+        <v>0.0007399560290897804</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007494149312004077</v>
+        <v>0.000751021379690753</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007546787728259983</v>
+        <v>0.0007533808571111699</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007460561097329492</v>
+        <v>0.000747756971437655</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007457612556148819</v>
+        <v>0.0007480888842244598</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007564377710794673</v>
+        <v>0.0007575456709422413</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007573809893121478</v>
+        <v>0.0007597296962222865</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007676801667393107</v>
+        <v>0.0007678488925068512</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0007452483078057126</v>
+        <v>0.0007499339097685998</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0007523196923732475</v>
+        <v>0.0007545496518240832</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001294940607402645</v>
+        <v>0.001296948921147707</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0007588408733068366</v>
+        <v>0.0007602360680386956</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007416763902396664</v>
+        <v>0.0007432348733336825</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007690262402070944</v>
+        <v>0.0007709263435973275</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007610021063782818</v>
+        <v>0.0007615243896546413</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007494774176286824</v>
+        <v>0.000752043001517196</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001021943527370769</v>
+        <v>0.001016351120805107</v>
       </c>
       <c r="V3" t="n">
-        <v>0.000759942968755582</v>
+        <v>0.0007614129056025501</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0009896699180375944</v>
+        <v>0.0009909551162335488</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008698604766982468</v>
+        <v>0.0008703544804350431</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.000809912457382025</v>
+        <v>0.0008115606474305321</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0009952180748716549</v>
+        <v>0.0009968624407448803</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008005028699367627</v>
+        <v>0.0008020087732067392</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0007373493017168913</v>
+        <v>0.0007379377400379126</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007026304120847876</v>
+        <v>0.0006901634536296589</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007158115069057097</v>
+        <v>0.0007030702747956163</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007197487550802985</v>
+        <v>0.0007070660271150924</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007114373475686728</v>
+        <v>0.0006984343340562443</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007284601129021752</v>
+        <v>0.000715741568252052</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007371263365541503</v>
+        <v>0.0007197789320727897</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007230503813304651</v>
+        <v>0.0007104810093219736</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007226667452960706</v>
+        <v>0.0007110880158758155</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0007395064718647124</v>
+        <v>0.0007259893488443287</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007412882621610904</v>
+        <v>0.0007297460915886271</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007577358913197274</v>
+        <v>0.0007427280630346043</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007222641957004234</v>
+        <v>0.0007144069414250388</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001521316262528355</v>
+        <v>0.001528723260254152</v>
       </c>
       <c r="O4" t="n">
-        <v>0.000765313373070369</v>
+        <v>0.0007525840957798045</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0007437563373317561</v>
+        <v>0.0007307017889350594</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0007163190607410083</v>
+        <v>0.0007035244134437096</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0007593082544767209</v>
+        <v>0.00074705403873735</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0007471754550610254</v>
+        <v>0.0007327309314322647</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007285307686262155</v>
+        <v>0.0007173279675405966</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0007449942585629407</v>
+        <v>0.0007210788481699773</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007436548745028868</v>
+        <v>0.0007307271454059821</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0007776017228010852</v>
+        <v>0.0007645484056148451</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0009194432944491516</v>
+        <v>0.0009049613816913571</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0008202458009004766</v>
+        <v>0.000807619344416172</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0007354494425352428</v>
+        <v>0.0007227861716098359</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0008093250743662024</v>
+        <v>0.0007964499565276623</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0007094785550354678</v>
+        <v>0.0006951571447678135</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009464040478411972</v>
+        <v>0.0009404051364150454</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001202920708125605</v>
+        <v>0.001193187771075063</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001277770909246164</v>
+        <v>0.001268908988168555</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001074256265258152</v>
+        <v>0.001062664014815809</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001445803955727697</v>
+        <v>0.001436012780400403</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001489257160498466</v>
+        <v>0.001408161688885877</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001380867015038804</v>
+        <v>0.001373796240708817</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001346899218748517</v>
+        <v>0.001357778790622339</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001575657573199435</v>
+        <v>0.001555308210601824</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001600438370873733</v>
+        <v>0.001610916980552956</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001843003585826098</v>
+        <v>0.00179726430302051</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001335121019975641</v>
+        <v>0.001412184048092071</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001521316262528355</v>
+        <v>0.001528723260254152</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001922931491527599</v>
+        <v>0.001913352905961195</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001592489562043312</v>
+        <v>0.00157730005725097</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001196243311070963</v>
+        <v>0.001185168400486493</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00205352593760741</v>
+        <v>0.002052086134409262</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001653407698070254</v>
+        <v>0.001616404641834512</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001456300055564588</v>
+        <v>0.001474048533742303</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001685616390700753</v>
+        <v>0.001501119916484234</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001625771670794306</v>
+        <v>0.001613004806120548</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002284007563489572</v>
+        <v>0.00226765050836553</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00470580981262316</v>
+        <v>0.004665733041944441</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003150505812037321</v>
+        <v>0.003141152497013654</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001440434536252637</v>
+        <v>0.00143183957056837</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002872570755820399</v>
+        <v>0.002859173773323357</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001122012386696071</v>
+        <v>0.001081589613770109</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000835502141525661</v>
+        <v>0.0008231626655111264</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008486832363465835</v>
+        <v>0.0009416401577255076</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0009580376042315772</v>
+        <v>0.0008400652389965605</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008443090770095463</v>
+        <v>0.0009370042169861351</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008613318423430489</v>
+        <v>0.0009543114511819429</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009754151857054267</v>
+        <v>0.0008527781439542578</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009613392304817423</v>
+        <v>0.0008434802212034412</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009609555944473486</v>
+        <v>0.0008440872277572835</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009777953210159903</v>
+        <v>0.0009645592317742196</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008741599916019637</v>
+        <v>0.0008627453034700947</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009960247404710049</v>
+        <v>0.000981297945964495</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0009605530448517015</v>
+        <v>0.0008474061533065068</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001521316262528355</v>
+        <v>0.001528723260254152</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001008920124170177</v>
+        <v>0.000996490813565016</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0009843225700198815</v>
+        <v>0.0008560927120303741</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0009546079098922861</v>
+        <v>0.0008365236253251777</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0009975971036279986</v>
+        <v>0.0008800532506188176</v>
       </c>
       <c r="S6" t="n">
-        <v>0.000985464304212303</v>
+        <v>0.0009713008143621556</v>
       </c>
       <c r="T6" t="n">
-        <v>0.000861402498067089</v>
+        <v>0.0008503271794220643</v>
       </c>
       <c r="U6" t="n">
-        <v>0.000987207522699898</v>
+        <v>0.0009635494787619405</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0009819437236541638</v>
+        <v>0.0008637263572874497</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0009202038255201165</v>
+        <v>0.0009072844729788594</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001052315023890025</v>
+        <v>0.001143531264621248</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0009670841657964691</v>
+        <v>0.0009545634525560792</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0008683211719761164</v>
+        <v>0.0008557853834913041</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0009421968038070762</v>
+        <v>0.001035019839457554</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0008423432348574509</v>
+        <v>0.0008281447373048895</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007796929687944614</v>
+        <v>0.0007674869591574608</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000792874063615383</v>
+        <v>0.0007803937803234177</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007968113117899719</v>
+        <v>0.0007843895326428936</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0007884999042783461</v>
+        <v>0.0007757578395840461</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008055226696118492</v>
+        <v>0.0007930650737798538</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008141888932638238</v>
+        <v>0.0007971024376005916</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008001129380401387</v>
+        <v>0.0007878045148497747</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007997293020057441</v>
+        <v>0.0007884115214036169</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008165690285743861</v>
+        <v>0.00080331285437213</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008183508188707639</v>
+        <v>0.0008070695971164287</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008347984480294006</v>
+        <v>0.0008200515685624059</v>
       </c>
       <c r="M7" t="n">
-        <v>0.000799326752410097</v>
+        <v>0.0007917304469528408</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001521316262528355</v>
+        <v>0.001528723260254152</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0008423670461264476</v>
+        <v>0.0008298987103891896</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0008208100103878352</v>
+        <v>0.000808016403544445</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0007933816174506821</v>
+        <v>0.0007808479189715112</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0008363708111863948</v>
+        <v>0.0008243775442651511</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0008242380117706987</v>
+        <v>0.0008100544369600663</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0008055933253358888</v>
+        <v>0.0007946514730683984</v>
       </c>
       <c r="U7" t="n">
-        <v>0.000825878000364283</v>
+        <v>0.0008021993715243512</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00082071743121256</v>
+        <v>0.0008080506509337838</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0008546642795107587</v>
+        <v>0.0008418719111426469</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0009965058511588246</v>
+        <v>0.0009822848872191594</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0009012327725958304</v>
+        <v>0.0008888435976060457</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008125119992449165</v>
+        <v>0.0008001096771376374</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0008863876310758765</v>
+        <v>0.000873773462055464</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0007865411117451414</v>
+        <v>0.0007724806502956153</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008450501917048533</v>
+        <v>0.0008328986957533292</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000976199200962472</v>
+        <v>0.000963936978209983</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009801364491370613</v>
+        <v>0.0009679327305294596</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009090106070266974</v>
+        <v>0.0008963995189962133</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008892579148694377</v>
+        <v>0.0008768803114114628</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001021975446157777</v>
+        <v>0.001005140963539701</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009834380753872272</v>
+        <v>0.0009713477127363402</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009830544393528331</v>
+        <v>0.0009719547192901826</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0009998941659214746</v>
+        <v>0.0009868560522586953</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001001675956217853</v>
+        <v>0.0009906127950029939</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001018123585376489</v>
+        <v>0.001003594766448971</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0009826518897571759</v>
+        <v>0.0009752736448394027</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001521316262528355</v>
+        <v>0.001528723260254152</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0009593860419094395</v>
+        <v>0.0009470438369976222</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0009316690741662159</v>
+        <v>0.000918993058220039</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0008355554526919909</v>
+        <v>0.0008230441272083769</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001019695948533483</v>
+        <v>0.001007920742151716</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001007563149117788</v>
+        <v>0.0009935976348466316</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0009889184626829777</v>
+        <v>0.0009781946709549634</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0009516546870395446</v>
+        <v>0.0009281144118322987</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0009717195139637266</v>
+        <v>0.0009592256732760679</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001038012600917923</v>
+        <v>0.001025438325232023</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001049491680154782</v>
+        <v>0.001035308078605498</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001201725641902073</v>
+        <v>0.001189716485196691</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0008756779075809953</v>
+        <v>0.0008633270611922881</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001069712768422964</v>
+        <v>0.001057316659942029</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001093093600023917</v>
+        <v>0.00107942203747952</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0008712674781590663</v>
+        <v>0.0008819411225126994</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009430450061666591</v>
+        <v>0.000959827971221612</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0009469822543412471</v>
+        <v>0.0009638237235410883</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0009251470635835439</v>
+        <v>0.0009401949384832086</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0008206127826010683</v>
+        <v>0.0008227025099361584</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0009643598806965687</v>
+        <v>0.0009765366718023501</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000950283880591414</v>
+        <v>0.0009672387057479692</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009499002445570194</v>
+        <v>0.0009678457123018108</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0009667399711256623</v>
+        <v>0.0009827470452703246</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009685217614220393</v>
+        <v>0.0009865037880146231</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009849693905806755</v>
+        <v>0.0009994857594606006</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0009494976949613719</v>
+        <v>0.0009711646378510346</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001521316262528355</v>
+        <v>0.001528723260254152</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001011965713319516</v>
+        <v>0.001030876145904243</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0009946319325632735</v>
+        <v>0.00101367718210343</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0009435526048834292</v>
+        <v>0.0009602821531732706</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0009865417537376694</v>
+        <v>0.001003811735163345</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0009744089543219743</v>
+        <v>0.000989488627858261</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0009557642678871642</v>
+        <v>0.0009740856639665934</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0009761521728095694</v>
+        <v>0.0009817372922580453</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001038507444214693</v>
+        <v>0.001062470441843618</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001004835222062034</v>
+        <v>0.001021306102040842</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001146676793710101</v>
+        <v>0.001161719078117353</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001051403715147106</v>
+        <v>0.00106827778850424</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0009273545210047222</v>
+        <v>0.0009403667068723121</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001036558573627152</v>
+        <v>0.001053207652953659</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0009367120542964161</v>
+        <v>0.0009519148411938097</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008299818571598548</v>
+        <v>0.0008057907707960663</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008837515420322504</v>
+        <v>0.0008656370131322835</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008263771317753124</v>
+        <v>0.0008041607062938205</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008147910354858702</v>
+        <v>0.0007950121825471834</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008168770000632072</v>
+        <v>0.0007963040480856688</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008431905497779007</v>
+        <v>0.0008069216457222745</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008143163118185344</v>
+        <v>0.0007959424899458532</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008205005147818745</v>
+        <v>0.0008021198779022387</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008315449214297058</v>
+        <v>0.0008074092382069745</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008394778718434487</v>
+        <v>0.0008207618758797303</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008437686154278516</v>
+        <v>0.0008075761518959716</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008415413562622604</v>
+        <v>0.0008473499417133621</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008256215602332475</v>
+        <v>0.0008072560262788536</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001168891191514714</v>
+        <v>0.001134441277833101</v>
       </c>
       <c r="P2" t="n">
-        <v>0.000843750797724512</v>
+        <v>0.0008063146938162799</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0008177515484964952</v>
+        <v>0.0007975292341677641</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0008143156404626822</v>
+        <v>0.0007963507486798182</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008311564753286358</v>
+        <v>0.000806583765240706</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008244824337954495</v>
+        <v>0.0008052894894385608</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001056344852031129</v>
+        <v>0.001028243291928681</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008138284905075675</v>
+        <v>0.0007946068651049403</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001004534402706849</v>
+        <v>0.0009831643668940502</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008320604874540074</v>
+        <v>0.0008024325156202316</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008300144818160237</v>
+        <v>0.0008012092317101756</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00096896858257575</v>
+        <v>0.000946433638248025</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008280733385529731</v>
+        <v>0.0008088421522836063</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008581586645517154</v>
+        <v>0.0008181016318124905</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0009310909893303467</v>
+        <v>0.0008746072332747473</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009160718038637989</v>
+        <v>0.0009014758789010772</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009065455913845645</v>
+        <v>0.000863885630155394</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000823325836208456</v>
+        <v>0.0007981556225865665</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008385632889733965</v>
+        <v>0.0008076649997656215</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001025296315436486</v>
+        <v>0.0008828172411817935</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000820358623837182</v>
+        <v>0.0008052019991815868</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008645510137441656</v>
+        <v>0.0008493492233467347</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009427288932121023</v>
+        <v>0.0008866594243724935</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009993339324951655</v>
+        <v>0.0009817395657193287</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001030162364206048</v>
+        <v>0.0008878668872470187</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00101586327553697</v>
+        <v>0.001171676834204575</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0009008881475225641</v>
+        <v>0.0008857973863358574</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001479253074249687</v>
+        <v>0.001404430273234074</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001029211761561771</v>
+        <v>0.0008784579812104275</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008446665876953483</v>
+        <v>0.0008163038846212</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008202951536768681</v>
+        <v>0.0008080727749934607</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009396971535272649</v>
+        <v>0.0008804358853104214</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008929749488024888</v>
+        <v>0.0008719590130334062</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001354254864011655</v>
+        <v>0.00128564329985857</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008162770651031538</v>
+        <v>0.000795109202866113</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001202669550253593</v>
+        <v>0.001181797993096367</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0009470331819616388</v>
+        <v>0.0008514045102447217</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009320141187875309</v>
+        <v>0.0008424407850902684</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001097290321700496</v>
+        <v>0.001061236420684762</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0009182345443465256</v>
+        <v>0.000896965231801249</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001132765995929639</v>
+        <v>0.0009632895314960515</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001034545946744314</v>
+        <v>0.0009014165314722461</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000819044002734952</v>
+        <v>0.0007519880201678792</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009938289152703044</v>
+        <v>0.0008830042030526609</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008629586278134499</v>
+        <v>0.0007796674188055434</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008865205573055717</v>
+        <v>0.0007942596343502485</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001183744206163949</v>
+        <v>0.0009141902839919393</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008575964056072054</v>
+        <v>0.0007901756688360688</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0009274498229520469</v>
+        <v>0.0008599521075423012</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001051775682302364</v>
+        <v>0.0009193418459304923</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001141807800978114</v>
+        <v>0.00107052205044083</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001190273723603487</v>
+        <v>0.000921583232311562</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001166300990921084</v>
+        <v>0.001367982197506244</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0009852943871226027</v>
+        <v>0.005052845882567774</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001011622383091521</v>
+        <v>0.0008754612560552371</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001190072464447722</v>
+        <v>0.0009073344830020478</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.000896398984171717</v>
+        <v>0.0008080986747609614</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0008575888223340143</v>
+        <v>0.0007947871390444934</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001047813799311752</v>
+        <v>0.000910373768519912</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0009724274299836283</v>
+        <v>0.0008957543279384129</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001131182608177959</v>
+        <v>0.0009825721426824142</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0008492900463547504</v>
+        <v>0.0007727657718363983</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0009988819345575258</v>
+        <v>0.0009298613651753004</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001058025032133948</v>
+        <v>0.0008634834943874856</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001030437790195966</v>
+        <v>0.0008411538083304245</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0009034058582467723</v>
+        <v>0.0008069700757341369</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001012988351117651</v>
+        <v>0.0009358832890788428</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001348641095562808</v>
+        <v>0.001038684642151711</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005577253210873774</v>
+        <v>0.004332495929653419</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001942928386460964</v>
+        <v>0.001843038223319835</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005464588380378456</v>
+        <v>0.004491706436884286</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002695785056394035</v>
+        <v>0.002295043065080724</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003335844720302809</v>
+        <v>0.002731828571224883</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008361700635772825</v>
+        <v>0.004651268803230905</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002828489000179757</v>
+        <v>0.002719933808068376</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004180095518405544</v>
+        <v>0.00407201650657509</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006178853276446831</v>
+        <v>0.004956494248493192</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007866415189945486</v>
+        <v>0.007687211864792332</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008896916016892407</v>
+        <v>0.005001503575174108</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008973675386105891</v>
+        <v>0.01427545077610604</v>
       </c>
       <c r="N5" t="n">
-        <v>0.007565530860234007</v>
+        <v>0.005052845882567774</v>
       </c>
       <c r="O5" t="n">
-        <v>0.005068451222173682</v>
+        <v>0.003803951754101938</v>
       </c>
       <c r="P5" t="n">
-        <v>0.008435154393404675</v>
+        <v>0.004506393636914401</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003445655244293354</v>
+        <v>0.002934916703817223</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002795711347412461</v>
+        <v>0.002783219660079233</v>
       </c>
       <c r="S5" t="n">
-        <v>0.00595206223815772</v>
+        <v>0.004595854445136513</v>
       </c>
       <c r="T5" t="n">
-        <v>0.005033186531850926</v>
+        <v>0.004742351123484614</v>
       </c>
       <c r="U5" t="n">
-        <v>0.007715895748337216</v>
+        <v>0.00619152424486619</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00238784150180831</v>
+        <v>0.002120702411608034</v>
       </c>
       <c r="W5" t="n">
-        <v>0.005331242630743575</v>
+        <v>0.005196847546406014</v>
       </c>
       <c r="X5" t="n">
-        <v>0.006636801000103863</v>
+        <v>0.00404089144284119</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.005968124896232933</v>
+        <v>0.003649998634552733</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.003360683249048522</v>
+        <v>0.002739353623832802</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.005594960271568018</v>
+        <v>0.005306834441317683</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01309783613492394</v>
+        <v>0.007923973051566301</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001181888858058407</v>
+        <v>0.001043913351185722</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001109942947825072</v>
+        <v>0.001022090686161391</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001284727860360424</v>
+        <v>0.001025501022766138</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001010301539127543</v>
+        <v>0.001049770084799055</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001033863468619665</v>
+        <v>0.0009367564540637255</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001331087117478043</v>
+        <v>0.001184292949985451</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001148495350697325</v>
+        <v>0.001060278334829581</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001074792734266139</v>
+        <v>0.001130054773535813</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001342674627392483</v>
+        <v>0.001189444511924004</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001432706746068235</v>
+        <v>0.001213018870154306</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001337616634917581</v>
+        <v>0.001191685898305073</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001313643902235177</v>
+        <v>0.001638084863499756</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001133122803406848</v>
+        <v>0.005052845882567774</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001302768154975896</v>
+        <v>0.001018279645080973</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001481218638289272</v>
+        <v>0.001179129868130295</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001187297929261836</v>
+        <v>0.0009505954944744382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001148487767424133</v>
+        <v>0.001064889805038005</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001338712744401871</v>
+        <v>0.001052870588233389</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001119770341297721</v>
+        <v>0.001038251147651889</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001283002186539917</v>
+        <v>0.001133581093950467</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001140188991444869</v>
+        <v>0.0009152625915498749</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001290026484665543</v>
+        <v>0.001083076021583813</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001348923977224067</v>
+        <v>0.001133586160380997</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001190747547834772</v>
+        <v>0.001000492817622989</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001194304803336892</v>
+        <v>0.000949466895447614</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001160331262431745</v>
+        <v>0.001205985955072354</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001498872276931103</v>
+        <v>0.001182521582190039</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001137082186821867</v>
+        <v>0.0009961771322350831</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000921580242812505</v>
+        <v>0.0008467486209307168</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001096365155347858</v>
+        <v>0.0009777648038154986</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0009654948678910027</v>
+        <v>0.0008744280195683807</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0009890567973831245</v>
+        <v>0.0008890202351130864</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001286280446241502</v>
+        <v>0.001008950884754776</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000960132645684759</v>
+        <v>0.0008849362695989067</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001029986063029599</v>
+        <v>0.0009547127083051384</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001154311922379917</v>
+        <v>0.001014102446693331</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001244344041055669</v>
+        <v>0.001165282651203668</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00129280996368104</v>
+        <v>0.001016343833074401</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001268837230998637</v>
+        <v>0.001462742798269081</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001087830627200156</v>
+        <v>0.005052845882567774</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001114148833510343</v>
+        <v>0.0009702123156648035</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001292598914866544</v>
+        <v>0.001002085542611614</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0009989352242492696</v>
+        <v>0.0009028592755237993</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0009601250624115675</v>
+        <v>0.0008895477398073308</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001150350039389305</v>
+        <v>0.00100513436928275</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001074963670061181</v>
+        <v>0.0009905149287012509</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00123806093629063</v>
+        <v>0.001085739614046274</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0009518262864323037</v>
+        <v>0.0008675263725992357</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001101418174635079</v>
+        <v>0.001024621965938138</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001160561272211501</v>
+        <v>0.0009582440951503238</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001137450697321383</v>
+        <v>0.0009444265406478368</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001005942098324325</v>
+        <v>0.0009017306764969748</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001115524591195203</v>
+        <v>0.00103064388984168</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.00145117733564036</v>
+        <v>0.001133445242914549</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001223976307707475</v>
+        <v>0.001077912226391529</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001163514058152064</v>
+        <v>0.00107249847009624</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001338298970687417</v>
+        <v>0.001203514652981022</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001124874619323187</v>
+        <v>0.001023494259865059</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001100104290674675</v>
+        <v>0.0009931911449614051</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001560362752214181</v>
+        <v>0.001264563131538982</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001202066461024318</v>
+        <v>0.00111068611876443</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001271919878369158</v>
+        <v>0.001180462557470663</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001396245737719475</v>
+        <v>0.001239852295858854</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001486277856395228</v>
+        <v>0.001391032500369191</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001534743779020599</v>
+        <v>0.001242093682239921</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001510771046338186</v>
+        <v>0.001688492647434625</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001209582741756124</v>
+        <v>0.005052845882567774</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001268937712609096</v>
+        <v>0.001115014590179016</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001439292084378837</v>
+        <v>0.001139367796934584</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001055360506572265</v>
+        <v>0.0009562921833498048</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001202058877751126</v>
+        <v>0.001115297588972855</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001392283854728865</v>
+        <v>0.001230884218448274</v>
       </c>
       <c r="T8" t="n">
-        <v>0.00131689748540074</v>
+        <v>0.001216264777866774</v>
       </c>
       <c r="U8" t="n">
-        <v>0.00140435981637208</v>
+        <v>0.001241228863881317</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001151278748698336</v>
+        <v>0.001053832998813744</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001343382459694348</v>
+        <v>0.001250400118109297</v>
       </c>
       <c r="X8" t="n">
-        <v>0.00123119625058595</v>
+        <v>0.001024876241422289</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001533371511494111</v>
+        <v>0.001313240081480577</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001089956277289711</v>
+        <v>0.0009807906226433497</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001357458406534763</v>
+        <v>0.001256393739007203</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001855063076024665</v>
+        <v>0.001509630545986565</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001388304575859562</v>
+        <v>0.001200702825573834</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00128572999010122</v>
+        <v>0.001147915674071765</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001460514902636574</v>
+        <v>0.001278931856956546</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001303581470041934</v>
+        <v>0.00115329059351618</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001092878114699346</v>
+        <v>0.0009674026586575499</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001650430230613163</v>
+        <v>0.001310117876086873</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001324282392973474</v>
+        <v>0.001186103322739955</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001394135810318315</v>
+        <v>0.001255879761446186</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001518461669668632</v>
+        <v>0.001315269499834378</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001608493788344384</v>
+        <v>0.001466449704344716</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001656959710969758</v>
+        <v>0.001317510886215447</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001632986978287353</v>
+        <v>0.001763909851410129</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001451980374488871</v>
+        <v>0.005052845882567774</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001515732398489125</v>
+        <v>0.001303415647764703</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001702321555788614</v>
+        <v>0.001342254154139895</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001363085008620931</v>
+        <v>0.001204026266855895</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001324274809700283</v>
+        <v>0.001190714792948379</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00151449978667802</v>
+        <v>0.001306301422423797</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001439113417349897</v>
+        <v>0.001291681981842298</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001602345262592093</v>
+        <v>0.001387011928140874</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001446291708240324</v>
+        <v>0.001280215233224876</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001465567921923795</v>
+        <v>0.001325789019079185</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001524711019500217</v>
+        <v>0.001259411148291372</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0015016004446101</v>
+        <v>0.001245593593788886</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001302006705205425</v>
+        <v>0.00114463155881862</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.00147967433848392</v>
+        <v>0.001331810942982729</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001815327082929077</v>
+        <v>0.001434612296055595</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008219938637255958</v>
+        <v>0.000800468749859103</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008812679033526257</v>
+        <v>0.0008640106301237231</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000827653828693893</v>
+        <v>0.000806000543588059</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008123545816732796</v>
+        <v>0.0007943203780878634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008143732957722856</v>
+        <v>0.0007942341669401843</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008379686453217842</v>
+        <v>0.0008045239112090636</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008084951215199311</v>
+        <v>0.0007917467336407743</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008225602073093484</v>
+        <v>0.0008047474005992326</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008263641735173089</v>
+        <v>0.0008050922101674485</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008275440002774358</v>
+        <v>0.0008088652220308118</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008352117800626661</v>
+        <v>0.0008026827152213981</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008259031758447561</v>
+        <v>0.0008381420285662727</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008168145510657252</v>
+        <v>0.0007991253945465107</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001157489958646357</v>
+        <v>0.001125629223877228</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008405478764073796</v>
+        <v>0.0008042720117838773</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0008132397035677265</v>
+        <v>0.0007945487120139363</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0008082082247843238</v>
+        <v>0.0007918507931827727</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008265642264389326</v>
+        <v>0.0008037109833035911</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008188329354924821</v>
+        <v>0.0008013105340732155</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001055223979059001</v>
+        <v>0.001021261480232039</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008134254799590548</v>
+        <v>0.0007950616132825854</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001003767144784328</v>
+        <v>0.0009812629823697599</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008337113546784058</v>
+        <v>0.0008051776311347217</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008425943462909931</v>
+        <v>0.0008087560481257242</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009656672679840212</v>
+        <v>0.0009448276405024504</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008261255818011876</v>
+        <v>0.000807837448513103</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008521666949939678</v>
+        <v>0.0008145753898936469</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008915121581767953</v>
+        <v>0.0008444979011382038</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009110071217168103</v>
+        <v>0.0008953426675668771</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009328118747350297</v>
+        <v>0.0008846773740586563</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008231075117613332</v>
+        <v>0.0008008938815698989</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008377946654624102</v>
+        <v>0.0008004973018508595</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001005045078244953</v>
+        <v>0.0008733008303650769</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007958647013974619</v>
+        <v>0.0007828219808720502</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008965064298284114</v>
+        <v>0.0008758414821023204</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009228405211513294</v>
+        <v>0.000877769128038605</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000931012841256241</v>
+        <v>0.0009042370579507404</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00098620021921224</v>
+        <v>0.0008605864361737232</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0009219323139957524</v>
+        <v>0.00111396529129052</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008551461446229826</v>
+        <v>0.00083538192722169</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001439554350616978</v>
+        <v>0.001370075339688327</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001023362089998455</v>
+        <v>0.0008714931147939297</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008295303161650597</v>
+        <v>0.0008026201427923697</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007937565345367289</v>
+        <v>0.0007835176261674948</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009240488916224638</v>
+        <v>0.0008675820528387811</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008697656770879331</v>
+        <v>0.0008511830515735553</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001350578031950912</v>
+        <v>0.001231918707046534</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008304263390673214</v>
+        <v>0.0008059210147954434</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001201484499387513</v>
+        <v>0.001163779896523053</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0009759776144012243</v>
+        <v>0.0008786835838161334</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00103896087289908</v>
+        <v>0.0009039710268503949</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001091933769082025</v>
+        <v>0.001058246154063977</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0009215176745865638</v>
+        <v>0.0008974843086505095</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001107303256602492</v>
+        <v>0.0009458822501397505</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0009643107298773944</v>
+        <v>0.0008514784753459021</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0008017956640991394</v>
+        <v>0.0007393457359805912</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001028242637906826</v>
+        <v>0.0009139626302652889</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008554306048076571</v>
+        <v>0.0007820297877990047</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008782329092102984</v>
+        <v>0.0007810559932268826</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001144753236768938</v>
+        <v>0.000897283388260102</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008118362269362</v>
+        <v>0.0007529592898341959</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0009707078411867892</v>
+        <v>0.0008998078037322539</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001013290275434815</v>
+        <v>0.000903378103425348</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001027002075419376</v>
+        <v>0.0009463204910933915</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00111361317544652</v>
+        <v>0.0008764862325874182</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001011155221417084</v>
+        <v>0.001275061561868026</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0009058080107826163</v>
+        <v>0.00334925367777354</v>
       </c>
       <c r="O4" t="n">
-        <v>0.000953058632200091</v>
+        <v>0.0008288224129200226</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001173886838385657</v>
+        <v>0.0008944380683731532</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0008654284637816261</v>
+        <v>0.0007846089245327956</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0008085955963284974</v>
+        <v>0.0007541346902308191</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001015935079195252</v>
+        <v>0.0008881009936024778</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0009286065913855495</v>
+        <v>0.0008609868152841764</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001113092356404269</v>
+        <v>0.0008926790367060066</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0008650026869465256</v>
+        <v>0.0007882891370468899</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0009837076392890339</v>
+        <v>0.0008936229977800765</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001096665180501529</v>
+        <v>0.0009046674555464394</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001193259943695915</v>
+        <v>0.0009391812966677549</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0008887382591136916</v>
+        <v>0.000801034914588817</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001010980386225422</v>
+        <v>0.0009347113164116962</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.00130131838110648</v>
+        <v>0.001009293911535005</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004334821510613591</v>
+        <v>0.003373222576292236</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001712182514484234</v>
+        <v>0.001578367514230629</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005934174937483393</v>
+        <v>0.004840485753270227</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002611924855863113</v>
+        <v>0.002288568250573523</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003160060130878424</v>
+        <v>0.002384687840363792</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007277552832416073</v>
+        <v>0.004111345810637576</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001997571138812857</v>
+        <v>0.00192797301782719</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004941444046784182</v>
+        <v>0.004646025870435588</v>
       </c>
       <c r="J5" t="n">
-        <v>0.005278655149940146</v>
+        <v>0.004438229671371531</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005386140869296411</v>
+        <v>0.004953812403273681</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007157447517883607</v>
+        <v>0.003964439898133739</v>
       </c>
       <c r="M5" t="n">
-        <v>0.005712295122094442</v>
+        <v>0.01172157736976084</v>
       </c>
       <c r="N5" t="n">
-        <v>0.006823043778008257</v>
+        <v>0.00334925367777354</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003985407097514083</v>
+        <v>0.002892148104115764</v>
       </c>
       <c r="P5" t="n">
-        <v>0.007745624039982726</v>
+        <v>0.004055892859051014</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002843501500483446</v>
+        <v>0.002384260905949065</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001908866082001722</v>
+        <v>0.001924388333299948</v>
       </c>
       <c r="S5" t="n">
-        <v>0.005205299196816528</v>
+        <v>0.00399201974717433</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004124766245624168</v>
+        <v>0.003892384000165508</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00703407083707772</v>
+        <v>0.004253563653242764</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00265532096937313</v>
+        <v>0.002298193566690527</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004937470102256622</v>
+        <v>0.004314412716121469</v>
       </c>
       <c r="X5" t="n">
-        <v>0.007109554540671847</v>
+        <v>0.00461357541443816</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.008669075665838209</v>
+        <v>0.005197927983704448</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002982125849015304</v>
+        <v>0.00245960931945736</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.005428297164789127</v>
+        <v>0.005050362025761129</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01159882503963865</v>
+        <v>0.006959104557866166</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001102602267089867</v>
+        <v>0.00110683493662932</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009400872013116114</v>
+        <v>0.0008761218256952766</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001297830810961574</v>
+        <v>0.001169319091548706</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0009937221420201294</v>
+        <v>0.001037386249082423</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001147821082265046</v>
+        <v>0.0009178320829415686</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001283044773981411</v>
+        <v>0.001034059477974788</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009501277641486724</v>
+        <v>0.0008897353795488821</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001108999378399261</v>
+        <v>0.001036583893446939</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001282878448489563</v>
+        <v>0.001158734564708766</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001296590248474124</v>
+        <v>0.00120167695237681</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001251904712658992</v>
+        <v>0.001131842693870835</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001280743394471831</v>
+        <v>0.001411837651582711</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001044599874158672</v>
+        <v>0.00334925367777354</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001091850495576147</v>
+        <v>0.001085141729455609</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001443794284174173</v>
+        <v>0.001150896589956944</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001135016636836374</v>
+        <v>0.001039965385816213</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001078183769383245</v>
+        <v>0.0008909107799455051</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001154226616407725</v>
+        <v>0.001143457454885896</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001066898128598022</v>
+        <v>0.0009977629049988631</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001255126607064558</v>
+        <v>0.001035361151365887</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001134590860001273</v>
+        <v>0.001043645598330307</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00113205661626433</v>
+        <v>0.001149922199231875</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001234956717714001</v>
+        <v>0.001041443545261126</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001343376281092506</v>
+        <v>0.001089942417983818</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001027029796326163</v>
+        <v>0.001056391375872234</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001280568559280169</v>
+        <v>0.001190067777695113</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001442080330953325</v>
+        <v>0.001146662925289161</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001057683365748858</v>
+        <v>0.0009387280030141772</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008951682999706023</v>
+        <v>0.0008265952636488659</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001121615273778289</v>
+        <v>0.001001212157933565</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0009488032406791204</v>
+        <v>0.0008692793154672803</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0009716055450817614</v>
+        <v>0.0008683055208951582</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001238125872640402</v>
+        <v>0.0009845329159283785</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009052088628076627</v>
+        <v>0.0008402088175024715</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001064080477058253</v>
+        <v>0.00098705733140053</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001106662911306278</v>
+        <v>0.000990627631093624</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001120374711290839</v>
+        <v>0.001033570018761667</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001206985811317984</v>
+        <v>0.0009637357602556942</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001104527857288546</v>
+        <v>0.001362311089536301</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0009991806466540798</v>
+        <v>0.00334925367777354</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001046422110064671</v>
+        <v>0.0009160629786148721</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001267250316250237</v>
+        <v>0.0009816786340680029</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0009588010996530887</v>
+        <v>0.0008718584522010711</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0009019682321999602</v>
+        <v>0.0008413842178990947</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001109307715066715</v>
+        <v>0.0009753505212707536</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001021979227257012</v>
+        <v>0.0009482363429524522</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001210085591784402</v>
+        <v>0.0009857132796730686</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0009583753228179889</v>
+        <v>0.0008755386647151652</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001077080275160496</v>
+        <v>0.000980872525448352</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001190037816372991</v>
+        <v>0.0009919169832147154</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001290375293015196</v>
+        <v>0.001032336849281223</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.000982110894985155</v>
+        <v>0.0008882844422570923</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001104353022096885</v>
+        <v>0.00102196084407997</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001394691016977943</v>
+        <v>0.00109654343920328</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001136792686547634</v>
+        <v>0.001013506123944892</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001115727078950709</v>
+        <v>0.001033761045458337</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001342174052758396</v>
+        <v>0.001208377939743036</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001094044355679814</v>
+        <v>0.001005952573054366</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001072751038307912</v>
+        <v>0.0009637080921411148</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001488015118230468</v>
+        <v>0.001219150141645171</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00112576764178777</v>
+        <v>0.001047374599311943</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00128463925603836</v>
+        <v>0.00119422311321</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001327221690286384</v>
+        <v>0.001197793412903094</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001340933490270946</v>
+        <v>0.001240735800571138</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00142754459029809</v>
+        <v>0.001170901542065164</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001325086636268645</v>
+        <v>0.001569476871345819</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001110092431559377</v>
+        <v>0.00334925367777354</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001187474998986911</v>
+        <v>0.001048816714687392</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001400917137116638</v>
+        <v>0.001107519482063212</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001010112373498418</v>
+        <v>0.0009206193761732872</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001122527011180067</v>
+        <v>0.001048549999708565</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001329866494046822</v>
+        <v>0.001182516303080225</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001242538006237119</v>
+        <v>0.001155402124761925</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001361639353983065</v>
+        <v>0.001128296654112189</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001140177280130839</v>
+        <v>0.001046424870621362</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001297666852991302</v>
+        <v>0.00118806432520717</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001254313214112258</v>
+        <v>0.001052811499352949</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001651424296484697</v>
+        <v>0.001370983723186772</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00105859271947962</v>
+        <v>0.0009606033944205657</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001324911801076992</v>
+        <v>0.001229126625889442</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001763005582820551</v>
+        <v>0.001441999202859037</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001261161896467714</v>
+        <v>0.001104491177501236</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001194608085598271</v>
+        <v>0.001075143059168851</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001421055059405957</v>
+        <v>0.001249759953453552</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001226095607266598</v>
+        <v>0.001098720725640614</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001049828367782768</v>
+        <v>0.0009260122259905833</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001537565719596442</v>
+        <v>0.001233080669217086</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001204648648435332</v>
+        <v>0.001088756613022457</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001363520262685921</v>
+        <v>0.001235605126920515</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001406102696933945</v>
+        <v>0.001239175426613609</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001419814496918507</v>
+        <v>0.001282117814281652</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001506425596945651</v>
+        <v>0.001212283555775679</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001403967642916215</v>
+        <v>0.001610858885056287</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001298620432281747</v>
+        <v>0.00334925367777354</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00137767256957846</v>
+        <v>0.0011920543948952</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001605417046507359</v>
+        <v>0.001263636627119183</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001258240946609128</v>
+        <v>0.001120406205489779</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001201408017827629</v>
+        <v>0.00108993201341908</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001408747500694383</v>
+        <v>0.001223898316790739</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001321419012884681</v>
+        <v>0.001196784138472439</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001509647491351217</v>
+        <v>0.001234382384839462</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001368552337838665</v>
+        <v>0.001219617946891271</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001376520060788165</v>
+        <v>0.001229420320968338</v>
       </c>
       <c r="X9" t="n">
-        <v>0.00148947760200066</v>
+        <v>0.001240464778734701</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001589815078642863</v>
+        <v>0.001280884644801209</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001223694601463372</v>
+        <v>0.001086920456020395</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001403792807724553</v>
+        <v>0.001270508639599957</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001694130802605611</v>
+        <v>0.001345091234723265</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008325795701152473</v>
+        <v>0.0007972491356901024</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008807070527065587</v>
+        <v>0.0008432161886572426</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008329012844504812</v>
+        <v>0.0007981259234094085</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008225961221399743</v>
+        <v>0.0007905730027217763</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008297578666947391</v>
+        <v>0.0007942311870596246</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008470377883953021</v>
+        <v>0.0008014558018470818</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008215847881142373</v>
+        <v>0.0007903077235060547</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008350310155481398</v>
+        <v>0.0008025144827506993</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008373547964204277</v>
+        <v>0.0008025095463859874</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008450987036309519</v>
+        <v>0.0008115484896244431</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008435170948033963</v>
+        <v>0.0007995951540115164</v>
       </c>
       <c r="M2" t="n">
-        <v>0.000835899291963245</v>
+        <v>0.0008281535549851667</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008251759774567072</v>
+        <v>0.000793507972978257</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001171927533238506</v>
+        <v>0.00112309387825552</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008497478469994761</v>
+        <v>0.0008009873753106406</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0008268893102153756</v>
+        <v>0.0007931966548965062</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0008244630161710734</v>
+        <v>0.0007932427060582167</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008382144863261441</v>
+        <v>0.0008013697205406092</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008327684315594931</v>
+        <v>0.0008009378974776322</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00103298446180387</v>
+        <v>0.0009637363424428461</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008331120003264368</v>
+        <v>0.0007975940654676444</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009844622554653021</v>
+        <v>0.000926097589157606</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008484550952802504</v>
+        <v>0.0008056009448597788</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008807887823863938</v>
+        <v>0.0008180446651570177</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009773494074436966</v>
+        <v>0.0009418531454546638</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008413206115649053</v>
+        <v>0.0008083632211245511</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008609976088722312</v>
+        <v>0.0008110812524751427</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008878925252516284</v>
+        <v>0.0008299072153004554</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009003957656849983</v>
+        <v>0.0008602356457646452</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008908145851681303</v>
+        <v>0.0008366300583962334</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008170362458881069</v>
+        <v>0.0007825241298356886</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008685271199602095</v>
+        <v>0.000808928860252476</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009904705387075658</v>
+        <v>0.0008597404597718036</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008102297307899107</v>
+        <v>0.0007810100146867033</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0009063060993319524</v>
+        <v>0.0008682226736091294</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009220881558030879</v>
+        <v>0.000867650084412052</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009771336474311753</v>
+        <v>0.0009317544293651636</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009660488026657207</v>
+        <v>0.0008468285702023029</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0009139721064450523</v>
+        <v>0.001050658814268765</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008357241612644191</v>
+        <v>0.0008037185648740306</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001439625503478494</v>
+        <v>0.001365380177701482</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001009673193074071</v>
+        <v>0.0008563934631076755</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008477940893414441</v>
+        <v>0.0008013628332750483</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008308083819140316</v>
+        <v>0.0008019982927585283</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009280690069805559</v>
+        <v>0.0008592872236451228</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000890189462895763</v>
+        <v>0.0008570123541995501</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00132364991786571</v>
+        <v>0.001138788634021489</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008915270691039456</v>
+        <v>0.0008322541372855147</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001133274845393113</v>
+        <v>0.001038036086545642</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001001780054387733</v>
+        <v>0.0008899479063787279</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001232957984924428</v>
+        <v>0.0009789594229103378</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001096808452557737</v>
+        <v>0.001047653852085392</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0009509631532759026</v>
+        <v>0.0009097535531803328</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001091065688496401</v>
+        <v>0.0009291881702474465</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0009478833621184798</v>
+        <v>0.0008309015354437352</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0008086527933840124</v>
+        <v>0.0007361357766238409</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009515172735308519</v>
+        <v>0.0008408052560755763</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008351157246247964</v>
+        <v>0.0007554915423935965</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0009160109239361281</v>
+        <v>0.000796812417337525</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0011111955887007</v>
+        <v>0.0008784177648488597</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008236922415674636</v>
+        <v>0.0007524950916175524</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0009755735660036069</v>
+        <v>0.000890376052672488</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001001490444360919</v>
+        <v>0.0008900226264824236</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001089292734264309</v>
+        <v>0.0009924193161599145</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001071427734981062</v>
+        <v>0.0008574008916058554</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0009883431765532408</v>
+        <v>0.00117887500751124</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0008642563772193741</v>
+        <v>0.002448361957624035</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0009306140336109476</v>
+        <v>0.0008260863547127137</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001141806947323408</v>
+        <v>0.0008731266716328976</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0008836092589005472</v>
+        <v>0.0007851269006467935</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0008562031515197454</v>
+        <v>0.0007856470697028969</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001011532332910081</v>
+        <v>0.0008774454368928979</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0009500166390117948</v>
+        <v>0.0008725677967481449</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001161961285961294</v>
+        <v>0.0008969073312390024</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0009517396493816268</v>
+        <v>0.0008328672792734352</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0009356596648427767</v>
+        <v>0.0008205961873782497</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001127204721959573</v>
+        <v>0.0009252390620372674</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00148961707223591</v>
+        <v>0.001061534915952155</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0008860934768102934</v>
+        <v>0.000787853465730917</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001046617446370088</v>
+        <v>0.0009564402431577248</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001265516133789795</v>
+        <v>0.0009856724490182229</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00377350292429746</v>
+        <v>0.002930325022197376</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00161793845113578</v>
+        <v>0.00147921794460476</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004162167055331471</v>
+        <v>0.003346548870957774</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001984282988544344</v>
+        <v>0.001733805079860408</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003610494522143169</v>
+        <v>0.002618072232862644</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006345308066325852</v>
+        <v>0.003672295521924252</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001995451081749852</v>
+        <v>0.001877316544522414</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004738713664161717</v>
+        <v>0.004363857829993274</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004786550615545533</v>
+        <v>0.004084101744440127</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006218303670558881</v>
+        <v>0.00567924908092244</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006007622642523056</v>
+        <v>0.003491101077298479</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004891881859238389</v>
+        <v>0.009492247151794498</v>
       </c>
       <c r="N5" t="n">
-        <v>0.007109831489127637</v>
+        <v>0.002448361957624035</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003449928986758834</v>
+        <v>0.002816847230637866</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006814599649623865</v>
+        <v>0.003576737753710651</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002902679181145771</v>
+        <v>0.002316808553188005</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002589424083907313</v>
+        <v>0.002484994774382481</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004878409349511305</v>
+        <v>0.00373860007255561</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004303041155637853</v>
+        <v>0.004070576249528251</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00741034791768803</v>
+        <v>0.004143635333844924</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003791979871366088</v>
+        <v>0.002937781515012772</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003873096059169358</v>
+        <v>0.002979375671548875</v>
       </c>
       <c r="X5" t="n">
-        <v>0.007247281456400494</v>
+        <v>0.004823444995874294</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01391975173141227</v>
+        <v>0.007413115443123925</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002659420587044874</v>
+        <v>0.002148380688387279</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.005874958667987465</v>
+        <v>0.00542252212655836</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01052050816483596</v>
+        <v>0.006371815050100163</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00124330130670323</v>
+        <v>0.0009692610248984594</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009660882630155867</v>
+        <v>0.000874495266078564</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001108952743162426</v>
+        <v>0.001097355646311192</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001130533669209547</v>
+        <v>0.001012041932629214</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001073446393567702</v>
+        <v>0.0009351719067922489</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001406613533285451</v>
+        <v>0.001016777254303584</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009811277111990374</v>
+        <v>0.001009045481853167</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001133009035635181</v>
+        <v>0.001028735542127211</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001296908388945671</v>
+        <v>0.00114657301671804</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001384710678849058</v>
+        <v>0.001248969706395532</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001366845679565813</v>
+        <v>0.0009957603810605796</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001145778646184815</v>
+        <v>0.001317234496965965</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001022668803490766</v>
+        <v>0.002448361957624035</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001227325604119192</v>
+        <v>0.0009829267850906525</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001287921932803854</v>
+        <v>0.001131109883370039</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001179027203485298</v>
+        <v>0.001041677290882409</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001151621096104496</v>
+        <v>0.001042197459938513</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001306950277494832</v>
+        <v>0.00101580492634762</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001245434583596545</v>
+        <v>0.001129118186983762</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001322208275411358</v>
+        <v>0.001157719412711195</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0011091751190132</v>
+        <v>0.0009712267687281582</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001232370726204735</v>
+        <v>0.0009690864898870609</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001284640191591146</v>
+        <v>0.001063598551491989</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001659962390039697</v>
+        <v>0.001214849853050879</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001181511421395044</v>
+        <v>0.00092621295518564</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001342035390954838</v>
+        <v>0.001212990633393338</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001425334602453538</v>
+        <v>0.00112530543934175</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001034880556508953</v>
+        <v>0.0009176940110564354</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008956499877744852</v>
+        <v>0.0008229282522365409</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001038514467921325</v>
+        <v>0.0009275977316882753</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0009221129190152695</v>
+        <v>0.0008422840180062964</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001003008118326601</v>
+        <v>0.0008836048929502252</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001198192783091173</v>
+        <v>0.0009652102404615608</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009106894359579368</v>
+        <v>0.0008392875672302528</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00106257076039408</v>
+        <v>0.000977168528285188</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001088487638751393</v>
+        <v>0.0009768151020951236</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001176289928654781</v>
+        <v>0.001079211791772615</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001158424929371535</v>
+        <v>0.0009441933672185552</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001075340370943714</v>
+        <v>0.001265667483123941</v>
       </c>
       <c r="N7" t="n">
-        <v>0.000951253571609847</v>
+        <v>0.002448361957624035</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001017601900378774</v>
+        <v>0.0009128697872129474</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001228794814091235</v>
+        <v>0.0009599101041331308</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0009706064532910202</v>
+        <v>0.0008719193762594934</v>
       </c>
       <c r="R7" t="n">
-        <v>0.000943200345910219</v>
+        <v>0.0008724395453155972</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001098529527300554</v>
+        <v>0.0009642379125055975</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001037013833402268</v>
+        <v>0.0009593602723608446</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001251686179074977</v>
+        <v>0.0009878556482609939</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001038736843772099</v>
+        <v>0.0009196597548861358</v>
       </c>
       <c r="W7" t="n">
-        <v>0.00102265685923325</v>
+        <v>0.0009073886629909495</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001214201916350045</v>
+        <v>0.001012031537649968</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001579425786444874</v>
+        <v>0.00115258908280143</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0009730906712007665</v>
+        <v>0.0008746459413436165</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001133614640760561</v>
+        <v>0.001043232718770424</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001352513328180269</v>
+        <v>0.001072464924630923</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001121862086392517</v>
+        <v>0.0009914406999935407</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001131172683653303</v>
+        <v>0.00102797300702439</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001274037163800143</v>
+        <v>0.001132642486476126</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001078541825696015</v>
+        <v>0.0009774164257830456</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001113130625832228</v>
+        <v>0.0009778062860316199</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001464516457393379</v>
+        <v>0.001197480504529626</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001146212131836754</v>
+        <v>0.001044332322018103</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001298093456272898</v>
+        <v>0.001182213283073036</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00132401033463021</v>
+        <v>0.001181859856882973</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0014118126245336</v>
+        <v>0.001284256546560463</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001393947625250352</v>
+        <v>0.001149238122006404</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001310863066822527</v>
+        <v>0.00147071223791186</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001071632013440984</v>
+        <v>0.002448361957624035</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001169632310614947</v>
+        <v>0.001044115087356313</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001373068848479379</v>
+        <v>0.001084299411595798</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001028396253775234</v>
+        <v>0.0009198629985297978</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001178723041789037</v>
+        <v>0.001077484300103446</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001334052223179372</v>
+        <v>0.001169282667293447</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001272536529281085</v>
+        <v>0.001164405027148694</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001414734004858245</v>
+        <v>0.001128846396511166</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001233597324066159</v>
+        <v>0.001088736020547461</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001258208747686186</v>
+        <v>0.00111245922159186</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001285605809840636</v>
+        <v>0.001072008888537138</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001962540822370086</v>
+        <v>0.001488052173692148</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00105731297266633</v>
+        <v>0.0009459537013004936</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001369137336639377</v>
+        <v>0.001248277473558274</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.00174319969273218</v>
+        <v>0.001414661488148185</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001216025180770512</v>
+        <v>0.001063187433377804</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001167488907058012</v>
+        <v>0.00104541158080377</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001310353387204852</v>
+        <v>0.001150081060255506</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001173020009300823</v>
+        <v>0.001046998365120181</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001065771859491106</v>
+        <v>0.0009286055177211761</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001470031760041976</v>
+        <v>0.001187693536361504</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001182528355241462</v>
+        <v>0.001061770895797482</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001334409679677604</v>
+        <v>0.001199651856852417</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001360326558034919</v>
+        <v>0.001199298430662353</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001448128847938307</v>
+        <v>0.001301695120339845</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00143026384865506</v>
+        <v>0.001166676695785785</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001347179290227239</v>
+        <v>0.001488150811691171</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001223092490893373</v>
+        <v>0.002448361957624035</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001319506194679806</v>
+        <v>0.001160876469520148</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001537235770483666</v>
+        <v>0.001213465718354129</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001242445430241824</v>
+        <v>0.001094402672159437</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001215039265193744</v>
+        <v>0.001094922873882825</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00137036844658408</v>
+        <v>0.001186721241072826</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001308852752685794</v>
+        <v>0.001181843600928073</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001523608919453782</v>
+        <v>0.001210444826655508</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001415235049192618</v>
+        <v>0.001230987634718715</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001294495778516776</v>
+        <v>0.001129871991558178</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001486040835633571</v>
+        <v>0.001234514866217197</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0018512647057284</v>
+        <v>0.001375072411368658</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001190249018336484</v>
+        <v>0.001050711189682375</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001405453560044085</v>
+        <v>0.001265716047337653</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001624352247463792</v>
+        <v>0.001294948253198152</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007787785513701699</v>
+        <v>0.0007725722011615624</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008481729132373383</v>
+        <v>0.0008429620276750456</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007846836259811666</v>
+        <v>0.0007787385156055924</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007794052368179664</v>
+        <v>0.0007736152769611541</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007780771588451406</v>
+        <v>0.0007720546971183344</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007849511438827264</v>
+        <v>0.000774832842058571</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007813396452825512</v>
+        <v>0.0007755802895106389</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007818144856844696</v>
+        <v>0.0007761957358639324</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007833772838637305</v>
+        <v>0.000776500162142083</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007892765247887695</v>
+        <v>0.0007836594804927332</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007889423837221265</v>
+        <v>0.0007795174190671437</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007869245166844982</v>
+        <v>0.0007886313346414327</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007863600345989918</v>
+        <v>0.0007807208629507363</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001099441870272138</v>
+        <v>0.001090933838002095</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007862870328813983</v>
+        <v>0.0007773649846047977</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007819395678511555</v>
+        <v>0.0007761103396860234</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007805256532580314</v>
+        <v>0.0007749389365460601</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007825997077175142</v>
+        <v>0.000776165982601316</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007799049510146345</v>
+        <v>0.0007742469995900148</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001002831860889117</v>
+        <v>0.0009903244651376071</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007779681128532735</v>
+        <v>0.0007721622531908456</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009609416731587777</v>
+        <v>0.0009517754362293921</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0007852857348755447</v>
+        <v>0.0007787561695028202</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0007792643872196398</v>
+        <v>0.000772897687435229</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009300798205339631</v>
+        <v>0.0009233033355739174</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0007861743281358377</v>
+        <v>0.0007802010742784014</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.000787827324484349</v>
+        <v>0.0007775958092162358</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007672162712071427</v>
+        <v>0.0007585155121464404</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008628515797556542</v>
+        <v>0.0008587857981274454</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008096774741613446</v>
+        <v>0.0008028175046452844</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000771766532121723</v>
+        <v>0.000766020125683647</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000762435888446133</v>
+        <v>0.0007550225884485513</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008108792896203298</v>
+        <v>0.0007744888520709203</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007859165336220966</v>
+        <v>0.0007803824913905398</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007892047216253601</v>
+        <v>0.0007846791135056759</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007999214938642618</v>
+        <v>0.0007864912908164288</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0008420166414154262</v>
+        <v>0.0008374978425139292</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008392767154918176</v>
+        <v>0.000807761509390328</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0008266109213693169</v>
+        <v>0.0008736124930465555</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008214407290483652</v>
+        <v>0.000816768681354333</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001300226307886633</v>
+        <v>0.001288525408963762</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008206213201300057</v>
+        <v>0.0007926082570365227</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007898759080630814</v>
+        <v>0.0007838483471351359</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007800413216698492</v>
+        <v>0.000775746214198521</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007941223037900866</v>
+        <v>0.0007838299071032847</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007754414939393008</v>
+        <v>0.000770633337339248</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00119625797023863</v>
+        <v>0.00115564482711936</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007614665259706252</v>
+        <v>0.0007556087069897246</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001118255541742332</v>
+        <v>0.001101025354135418</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008139220825020806</v>
+        <v>0.0008028869854420797</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0007708265285721861</v>
+        <v>0.0007609644755544473</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001031964843351103</v>
+        <v>0.001023060633823508</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008201572914771774</v>
+        <v>0.0008131012581991287</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0008322746083587334</v>
+        <v>0.000794994436330861</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007617857057675629</v>
+        <v>0.0007272930347540815</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007224019792678926</v>
+        <v>0.0006941301054414951</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0008284862399673123</v>
+        <v>0.0007969443930441871</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007688644061899716</v>
+        <v>0.000739075055749043</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007538631545408591</v>
+        <v>0.0007214475885222099</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008315079777297396</v>
+        <v>0.0007528280136319851</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007907144396693272</v>
+        <v>0.000761270776445907</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007960779804463787</v>
+        <v>0.0007682225261256642</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000813403680889695</v>
+        <v>0.0007713489523253061</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0008803651448370176</v>
+        <v>0.0008525289552001348</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008765908677768008</v>
+        <v>0.0008057424659557069</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0008560814554818828</v>
+        <v>0.0009098217616863864</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0008474220464917093</v>
+        <v>0.003321022224638305</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0007695302287835964</v>
+        <v>0.0007366861269527674</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0008465974585090414</v>
+        <v>0.0007814297285347357</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0007974908410597194</v>
+        <v>0.0007672579370120033</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0007815200252975437</v>
+        <v>0.0007540263996740526</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0008049474245295843</v>
+        <v>0.0007678864493372318</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007745089079212358</v>
+        <v>0.0007462106534487935</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0008821187398207116</v>
+        <v>0.0007974128641789355</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007505036832297346</v>
+        <v>0.0007206342182865256</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0008650972941762145</v>
+        <v>0.0008231450108712147</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0008352873369130753</v>
+        <v>0.0007971438019345742</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0007653939639567983</v>
+        <v>0.0007233156785690272</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0007929744407553405</v>
+        <v>0.0007600041663484789</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0008453244065611842</v>
+        <v>0.0008134646660638</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0008639624839015623</v>
+        <v>0.0007845057775460237</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001666789030166403</v>
+        <v>0.001527424924837678</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001021923944555872</v>
+        <v>0.0009888363112817604</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003103917970724867</v>
+        <v>0.003007171313472764</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001843776284296411</v>
+        <v>0.001783639440760591</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001642397324165634</v>
+        <v>0.001528424138713395</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002767589919475818</v>
+        <v>0.001920715788258593</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002448248721406655</v>
+        <v>0.002391278554093466</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00249361767655077</v>
+        <v>0.002469414830607588</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002584026635106764</v>
+        <v>0.002333611424115344</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003839809512317274</v>
+        <v>0.003812988168084707</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003570931443491083</v>
+        <v>0.002831452932715585</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003458574576562893</v>
+        <v>0.00490432047216913</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003857440648739451</v>
+        <v>0.003321022224638305</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001777015773977116</v>
+        <v>0.001667974010906906</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003168426623467057</v>
+        <v>0.002487863319454482</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002397126822430833</v>
+        <v>0.002328105767068791</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002237856684409187</v>
+        <v>0.002221540135078241</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002279473578000196</v>
+        <v>0.002108871488919294</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002010831536216099</v>
+        <v>0.001976718685524781</v>
       </c>
       <c r="U5" t="n">
-        <v>0.003894016823294513</v>
+        <v>0.002955116884542753</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001510701889331642</v>
+        <v>0.001448417294955262</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003712388376920058</v>
+        <v>0.0034206592285868</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003203218335544432</v>
+        <v>0.00297951024609624</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001849981842252284</v>
+        <v>0.001666988452766323</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002172697843103201</v>
+        <v>0.00206112437199037</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003333642706360177</v>
+        <v>0.003233553583326723</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003873962141540136</v>
+        <v>0.002815244692363438</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009047437119501347</v>
+        <v>0.0008658115562941302</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009860029249091759</v>
+        <v>0.000832648626981544</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0009714442461498841</v>
+        <v>0.001050561739175598</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0009118224123725434</v>
+        <v>0.0009926924018804541</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001017464100182143</v>
+        <v>0.0008599661100622584</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001095108923371022</v>
+        <v>0.0008913465351720342</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009336724458518993</v>
+        <v>0.001014888122577316</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009390359866289507</v>
+        <v>0.001021839872257074</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009563616870722668</v>
+        <v>0.0009098674738653547</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001023323151019589</v>
+        <v>0.001106146301331548</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001019548873959373</v>
+        <v>0.0009442609874957565</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001119682401123166</v>
+        <v>0.001163439107817794</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0009904974529739222</v>
+        <v>0.003321022224638305</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001033828617555975</v>
+        <v>0.0009927442389468901</v>
       </c>
       <c r="P6" t="n">
-        <v>0.000978852101129</v>
+        <v>0.001037666451665877</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001061091786701002</v>
+        <v>0.001020875283143412</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0009244780314801158</v>
+        <v>0.001007643745805463</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0009479054307121562</v>
+        <v>0.0009064049708772805</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001038109853562519</v>
+        <v>0.0008847291749888424</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001026956227229348</v>
+        <v>0.0009435852590961835</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001014104628871018</v>
+        <v>0.0009742515644179328</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001018144226066405</v>
+        <v>0.001079262917461091</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0009782453430956474</v>
+        <v>0.0009356623234746233</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.00091836400330256</v>
+        <v>0.0008773904618535837</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001056575386396623</v>
+        <v>0.0008985226878885276</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001108925352202468</v>
+        <v>0.001067082012195208</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001007490846971191</v>
+        <v>0.0009230989185965492</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0008498188819623971</v>
+        <v>0.000812260349985579</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008104351554627269</v>
+        <v>0.0007790974206729928</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0009165194161621466</v>
+        <v>0.0008819117082756848</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008568975823848052</v>
+        <v>0.000824042370980541</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008418963307356931</v>
+        <v>0.000806414903753708</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009195411539245738</v>
+        <v>0.0008377953288634833</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008787476158641614</v>
+        <v>0.000846238091677405</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008841111566412124</v>
+        <v>0.0008531898413571621</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0009014368570845289</v>
+        <v>0.0008563162675568043</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0009683983210318513</v>
+        <v>0.0009374962704316323</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009646240439716345</v>
+        <v>0.0008907097811872051</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0009441146316767169</v>
+        <v>0.0009947890769178851</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0009354552226865432</v>
+        <v>0.003321022224638305</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0008575537487008178</v>
+        <v>0.0008216440319251925</v>
       </c>
       <c r="P7" t="n">
-        <v>0.000934620978426263</v>
+        <v>0.0008663876335071605</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0008855240172545536</v>
+        <v>0.000852225252243501</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0008695532014923778</v>
+        <v>0.0008389937149055507</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0008929806007244182</v>
+        <v>0.0008528537645687303</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0008625420841160697</v>
+        <v>0.0008311779686802917</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0009719352100031314</v>
+        <v>0.0008899185174389606</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0008385368594245687</v>
+        <v>0.0008056015335180283</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0009531304703710484</v>
+        <v>0.0009081123261027126</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0009233205131079094</v>
+        <v>0.0008821111171660721</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.000855306621377697</v>
+        <v>0.0008159368671777246</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008810076169501748</v>
+        <v>0.0008449714815799771</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0009333575827560184</v>
+        <v>0.0008984319812952977</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.000951995660096396</v>
+        <v>0.0008694730927775209</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0009240181150982757</v>
+        <v>0.0008854060524855227</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001018704046756973</v>
+        <v>0.0009825969277390985</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001124788307456393</v>
+        <v>0.00108541121534179</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009937783355205394</v>
+        <v>0.0009581323223151606</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009369820497052135</v>
+        <v>0.0008998682055257584</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001155610262219337</v>
+        <v>0.001068324546481286</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001087016507158408</v>
+        <v>0.00104973759874351</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001092380047935459</v>
+        <v>0.001056689348423267</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001109705748378776</v>
+        <v>0.001059815774622909</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001176667212326097</v>
+        <v>0.001140995777497739</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001172892935265881</v>
+        <v>0.001094209288253311</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001152383522970951</v>
+        <v>0.001198288583983994</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001039797699538234</v>
+        <v>0.003321022224638305</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0009904657628881563</v>
+        <v>0.0009518752628699641</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00106053227566372</v>
+        <v>0.0009898121782737437</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0009333755025760436</v>
+        <v>0.0008997534569700967</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001077822092786624</v>
+        <v>0.001042493221971657</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001101249492018665</v>
+        <v>0.001056353271634835</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001070810975410316</v>
+        <v>0.001034677475746397</v>
       </c>
       <c r="U8" t="n">
-        <v>0.00111479561841562</v>
+        <v>0.001029827363308309</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001010088527085163</v>
+        <v>0.0009733826671895079</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001161425710177367</v>
+        <v>0.001111637451409429</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0009834597489896009</v>
+        <v>0.0009415865070877755</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001196763203079401</v>
+        <v>0.001148903498939355</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0009527164373554975</v>
+        <v>0.0009156957952375506</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001141626474050265</v>
+        <v>0.001101931488361403</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001300311520043888</v>
+        <v>0.001209138048705413</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001028608802251263</v>
+        <v>0.0009791132311154195</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001076504412990861</v>
+        <v>0.0010286024352332</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001182588673690281</v>
+        <v>0.001131416722835892</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001102823158655918</v>
+        <v>0.001054471625418679</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009067628378277217</v>
+        <v>0.0008653841671547745</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001185610455357803</v>
+        <v>0.001087300363108789</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001144816873392296</v>
+        <v>0.001095743106237611</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001150180414169347</v>
+        <v>0.00110269485591737</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001167506114612663</v>
+        <v>0.001105821282117012</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001234467578559985</v>
+        <v>0.00118700128499184</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001230693301499769</v>
+        <v>0.001140214795747412</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001210183889204851</v>
+        <v>0.001244294091478093</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001201524480214677</v>
+        <v>0.003321022224638305</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001152556979040821</v>
+        <v>0.001098549291748789</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001235914741805727</v>
+        <v>0.001149249925715006</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001151593318687783</v>
+        <v>0.001101730286488804</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001135622459020512</v>
+        <v>0.001088498729465758</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001159049858252552</v>
+        <v>0.001102358779128937</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001128611341644204</v>
+        <v>0.0010806829832405</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001238100654769744</v>
+        <v>0.001139539067347842</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001205324605998519</v>
+        <v>0.001150485299256193</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001219199727899183</v>
+        <v>0.001157617340662921</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001189389770636044</v>
+        <v>0.00113161613172628</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001121375878905831</v>
+        <v>0.001065441881737932</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001094455212738761</v>
+        <v>0.001044644617212895</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001199426840284153</v>
+        <v>0.001147936995855505</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001218064917624531</v>
+        <v>0.001118978107337729</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007703963690397844</v>
+        <v>0.0007673402744611901</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008453376264006531</v>
+        <v>0.0008418822732622229</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007718351342227631</v>
+        <v>0.0007685047661940352</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007721930512813037</v>
+        <v>0.0007692327690485215</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000772481560496962</v>
+        <v>0.000769343106321562</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007725385800056495</v>
+        <v>0.0007693829547438634</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007723163582515239</v>
+        <v>0.0007692268335314679</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00077231684623412</v>
+        <v>0.0007693551058604711</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007729235242455056</v>
+        <v>0.0007698220013258217</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007713247971310677</v>
+        <v>0.0007682840394491507</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007722342561314688</v>
+        <v>0.0007692424826625948</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007701797052081785</v>
+        <v>0.0007671393087493786</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007736346419672715</v>
+        <v>0.0007705650287864334</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001092201994768031</v>
+        <v>0.001087108159759422</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007724670509331195</v>
+        <v>0.0007697183470580173</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007704778345383094</v>
+        <v>0.0007673497375365339</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007751195245541946</v>
+        <v>0.0007716988671826266</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007730086691429198</v>
+        <v>0.0007697104672781054</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007705853974458991</v>
+        <v>0.0007676227905475846</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009860288252765161</v>
+        <v>0.0009797073176095986</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007731231160065607</v>
+        <v>0.0007699893225788125</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009538024557421629</v>
+        <v>0.0009471011875246723</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0007871554358783849</v>
+        <v>0.0007841476364668186</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0007737091283378778</v>
+        <v>0.00077064008821506</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009221645688652976</v>
+        <v>0.0009184486389336032</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0007760873442031924</v>
+        <v>0.0007730219819939758</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0007691380345704172</v>
+        <v>0.0007660656946012417</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007456422708381121</v>
+        <v>0.0007427209294684385</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008721008855947499</v>
+        <v>0.0008684546876589484</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007559822589143777</v>
+        <v>0.0007511063406503221</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007584553341513215</v>
+        <v>0.0007562170417127901</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007606277139824234</v>
+        <v>0.0007571180991179532</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007607766200145069</v>
+        <v>0.0007571522423287317</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007595550713460993</v>
+        <v>0.0007563935577130684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007594753334583138</v>
+        <v>0.0007572278645095512</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007636030678006974</v>
+        <v>0.0007603602619388296</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007523037037855088</v>
+        <v>0.0007494915669501622</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007586082125947613</v>
+        <v>0.0007561415988204042</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0007459073890918894</v>
+        <v>0.0007430727384282161</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0007687673657363751</v>
+        <v>0.0007657495206686142</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001296248376940949</v>
+        <v>0.001290144198037132</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0007603437713377655</v>
+        <v>0.0007596061257278106</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007462356625022593</v>
+        <v>0.0007428036696314848</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007795658096566164</v>
+        <v>0.0007740353860137759</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007640847639361222</v>
+        <v>0.0007594516664867835</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007470787610913004</v>
+        <v>0.0007448234938781027</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001099999582237768</v>
+        <v>0.001091803405303385</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007649646941866757</v>
+        <v>0.0007614927955948408</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001088366353731747</v>
+        <v>0.001078948730181453</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008650835335782577</v>
+        <v>0.0008625060952823901</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0007693575582677825</v>
+        <v>0.000766343471570271</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001016789006519748</v>
+        <v>0.001012636981288572</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0007863250335661306</v>
+        <v>0.0007833372121976404</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0007375790786693076</v>
+        <v>0.0007345285749116281</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007203164655798308</v>
+        <v>0.0007020670773126604</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007258232183921842</v>
+        <v>0.0007074400110180249</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007365679801862706</v>
+        <v>0.0007152205471278199</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007406108180124556</v>
+        <v>0.0007234436742671015</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007438696623241163</v>
+        <v>0.0007246899845237459</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007445137239050104</v>
+        <v>0.0007251400907848271</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007420036269651109</v>
+        <v>0.000723376629871509</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007420091389530052</v>
+        <v>0.0007248255248357857</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0007485870232833211</v>
+        <v>0.0007298219575344088</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007308034879689036</v>
+        <v>0.0007127273370050285</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007410762457502505</v>
+        <v>0.0007235533940065425</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007210577547330649</v>
+        <v>0.000702939092534051</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0007568942479749469</v>
+        <v>0.001787353085698113</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0007606592846031269</v>
+        <v>0.0007427852107029784</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0007437057701257878</v>
+        <v>0.0007289285012612755</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0007212366558616633</v>
+        <v>0.0007021739671019076</v>
       </c>
       <c r="R4" t="n">
-        <v>0.000773666679873989</v>
+        <v>0.0007512993871530068</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0007498235969621707</v>
+        <v>0.0007288394955222944</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007224516283842626</v>
+        <v>0.0007052582264723201</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0007161048536374913</v>
+        <v>0.0006940766197271374</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007493372606168847</v>
+        <v>0.0007301933068325025</v>
       </c>
       <c r="W4" t="n">
-        <v>0.000802867315422461</v>
+        <v>0.0007836271943039516</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0009096178350734703</v>
+        <v>0.0008919139629347566</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.000756814395433813</v>
+        <v>0.0007344009569501219</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.000763204459459275</v>
+        <v>0.0007446605300543742</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0007845986480284468</v>
+        <v>0.0007662445776100806</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0007075867462136512</v>
+        <v>0.0006891302673831818</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001154737038994662</v>
+        <v>0.001136192506225464</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001291621543906323</v>
+        <v>0.001270734669193335</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00147919865135807</v>
+        <v>0.001407376612978588</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001508521155386842</v>
+        <v>0.001508719617441099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001624861186257166</v>
+        <v>0.001589619928287611</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001502527168312646</v>
+        <v>0.001467891464797906</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001647003645571447</v>
+        <v>0.00162096184990097</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001603974142796613</v>
+        <v>0.001604518878130938</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001620138076721322</v>
+        <v>0.001593945597433014</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001358456447265889</v>
+        <v>0.001342843411797334</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001443578327392284</v>
+        <v>0.001435637095529978</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001208800577458499</v>
+        <v>0.001192550786726295</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00114877863878467</v>
+        <v>0.001787353085698113</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001770800025273768</v>
+        <v>0.001758132030233104</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001528481402227282</v>
+        <v>0.001566078232400981</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001177214411679726</v>
+        <v>0.001145960936307076</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002209297517654795</v>
+        <v>0.002114200483686507</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001572133351319203</v>
+        <v>0.001513603546029968</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001237786029358917</v>
+        <v>0.001237321322427508</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001108910454809767</v>
+        <v>0.001094188840094705</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001625927279955707</v>
+        <v>0.001593907503219966</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002553961020709344</v>
+        <v>0.002518908102200642</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004415247183267082</v>
+        <v>0.004405945782340565</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001853847298739872</v>
+        <v>0.001832533932198976</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001806644043922811</v>
+        <v>0.001783697477717933</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002325870783240074</v>
+        <v>0.002305300413537415</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0009873491616634237</v>
+        <v>0.0009649343191957613</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0008541270219799165</v>
+        <v>0.0009403054217369735</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008596337747922698</v>
+        <v>0.0008398414542916168</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008703785365863559</v>
+        <v>0.0008476219904014117</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0009826716520803796</v>
+        <v>0.0008558451175406939</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009859304963920404</v>
+        <v>0.0009629283289480587</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000878324280305096</v>
+        <v>0.0009633784352091398</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0008758141833651961</v>
+        <v>0.0009616149742958215</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008758196953530908</v>
+        <v>0.0009630638692600979</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0008823975796834066</v>
+        <v>0.0009680603019587211</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008646140443689893</v>
+        <v>0.0009509656814293411</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009831370798181738</v>
+        <v>0.0008559548372801345</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0009631185888009887</v>
+        <v>0.0009411774369583637</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0008907015465252259</v>
+        <v>0.001787353085698113</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0008944665831534045</v>
+        <v>0.0009825739848466908</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0008674346551941295</v>
+        <v>0.0008526941189917911</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.000855047212261749</v>
+        <v>0.0009404123115262205</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001015727513941913</v>
+        <v>0.000883700830426599</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0008836341533622568</v>
+        <v>0.0009670778399466075</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0009645124624521866</v>
+        <v>0.0008376596697459125</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0008508366204001296</v>
+        <v>0.0008314170977025599</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0009913980946848081</v>
+        <v>0.0008625947501060946</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0009458879655079219</v>
+        <v>0.0009256704440537859</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001043428391473556</v>
+        <v>0.00113015230735907</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0008991719006815405</v>
+        <v>0.0008794331634459506</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001005265293527199</v>
+        <v>0.0008770619733279668</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.00102665948209637</v>
+        <v>0.001004482922034393</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0008412190799401405</v>
+        <v>0.000820682407094702</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007987269633642298</v>
+        <v>0.0007791222351502801</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000804233716176583</v>
+        <v>0.0007844951688556442</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008149784779706696</v>
+        <v>0.0007922757049654392</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000819021315796855</v>
+        <v>0.0008004988321047208</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008222801601085154</v>
+        <v>0.0008017451423613654</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008229242216894094</v>
+        <v>0.0008021952486224466</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008204141247495094</v>
+        <v>0.0008004317877091285</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008204196367374041</v>
+        <v>0.0008018806826734049</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008269975210677204</v>
+        <v>0.000806877115372028</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008092139857533027</v>
+        <v>0.0007897824948426481</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008194867435346491</v>
+        <v>0.0008006085518441618</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0007994682525174642</v>
+        <v>0.0007799942503716711</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0008353047457593458</v>
+        <v>0.001787353085698113</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0008390607632896019</v>
+        <v>0.0008198315155513199</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0008221072488122625</v>
+        <v>0.000805974806109617</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0007996471536460624</v>
+        <v>0.000779229124939527</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0008520771776583882</v>
+        <v>0.0008283545449906262</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00082823409474657</v>
+        <v>0.0008058946533599144</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0008008621261686619</v>
+        <v>0.0007823133843099397</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0007953580520325115</v>
+        <v>0.0007759684317976722</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0008277477584012834</v>
+        <v>0.000807248464670122</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0008812778132068599</v>
+        <v>0.0008606823521415708</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0009880283328578695</v>
+        <v>0.0009689691207723763</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0008361461035807647</v>
+        <v>0.0008163951494895716</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008416149572436736</v>
+        <v>0.0008217156878919938</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0008630091458128467</v>
+        <v>0.0008432997354476999</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0007859972439980498</v>
+        <v>0.0007661854252208013</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008648215824101088</v>
+        <v>0.0008444348903476856</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000990532748915056</v>
+        <v>0.0009676306464907539</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001001277510709142</v>
+        <v>0.0009754111826005492</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009413150440551487</v>
+        <v>0.0009208971323505109</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009071012219471954</v>
+        <v>0.000885413216268263</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001034148422664978</v>
+        <v>0.0010097620560333</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001006713157487982</v>
+        <v>0.0009835672653442384</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001006718669475877</v>
+        <v>0.0009850161603085152</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001013296553806193</v>
+        <v>0.0009900125930071377</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0009955130184917756</v>
+        <v>0.0009729179724777581</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001005785776273122</v>
+        <v>0.0009837440294792718</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0009857672852559196</v>
+        <v>0.0009631297280067677</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0009284252481219094</v>
+        <v>0.001787353085698113</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0009577965539458266</v>
+        <v>0.0009367423836409803</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0009345663241551611</v>
+        <v>0.000916733318465254</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0008421188618730998</v>
+        <v>0.0008213869063570418</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001038376210396861</v>
+        <v>0.001011490022625736</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001014533127485043</v>
+        <v>0.000989030130995024</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0009871611589071343</v>
+        <v>0.0009654488619450498</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0009230115709903852</v>
+        <v>0.0009016260613237974</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0009811337135153773</v>
+        <v>0.0009581012433970596</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001067600469542601</v>
+        <v>0.00104384098532245</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001041517014440975</v>
+        <v>0.001021925597974809</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001141869521063509</v>
+        <v>0.001116555182890162</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.000905476717593168</v>
+        <v>0.0008848397236733734</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001049308178551319</v>
+        <v>0.00102643521308281</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001097859838155104</v>
+        <v>0.001072396693062743</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009326858951495855</v>
+        <v>0.0009111649726057849</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001009280214071221</v>
+        <v>0.0009862751974682605</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001020024975865307</v>
+        <v>0.0009940557335780555</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001007661133981716</v>
+        <v>0.0009861838202577535</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0008634503476100334</v>
+        <v>0.0008427616106664905</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001027970772349559</v>
+        <v>0.001003975331689205</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001025460622644147</v>
+        <v>0.001002211816321744</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001025466134632041</v>
+        <v>0.001003660711286021</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001032044018962358</v>
+        <v>0.001008657143984645</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00101426048364794</v>
+        <v>0.0009915625234552642</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001024533241429287</v>
+        <v>0.001002388580456778</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001004514750412102</v>
+        <v>0.0009817742789842872</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001040351243653983</v>
+        <v>0.001787353085698113</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001067674676861971</v>
+        <v>0.001044731316630147</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001055844697970722</v>
+        <v>0.001035900823814826</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001004693704306211</v>
+        <v>0.0009810092080062862</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001057123675553026</v>
+        <v>0.001030134573603243</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001033280592641208</v>
+        <v>0.001007674681972531</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0010059086240633</v>
+        <v>0.0009840934129225561</v>
       </c>
       <c r="U9" t="n">
-        <v>0.00100048305967908</v>
+        <v>0.0009778508408792037</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001114827835145712</v>
+        <v>0.00108950388873801</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001086324311101497</v>
+        <v>0.001062462380754187</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001193074830752506</v>
+        <v>0.001170749149384993</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001041192601475402</v>
+        <v>0.001018175178102188</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.00100380199508005</v>
+        <v>0.0009814503528419109</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001068055643707484</v>
+        <v>0.001045079764060316</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0009910437418926871</v>
+        <v>0.0009679654538334179</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007840740348228633</v>
+        <v>0.0007668834693289901</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000844709530711618</v>
+        <v>0.0008212251319951277</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007842172347065431</v>
+        <v>0.0007670175602022428</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007861657947376626</v>
+        <v>0.0007688332031770477</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007845101548467884</v>
+        <v>0.0007670737076480287</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007836235525154849</v>
+        <v>0.000766414344712774</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007833747135241129</v>
+        <v>0.0007661300746180672</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007833755136166163</v>
+        <v>0.0007662116251951724</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007847167914611242</v>
+        <v>0.0007675203613730136</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007830227627559363</v>
+        <v>0.0007658502563696061</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007851765975089464</v>
+        <v>0.0007678900616767651</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007824853710753222</v>
+        <v>0.0007653179158613552</v>
       </c>
       <c r="N2" t="n">
-        <v>0.000784403402294364</v>
+        <v>0.0007672092505297567</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001111752452418982</v>
+        <v>0.001091330955048135</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007860131530196695</v>
+        <v>0.0007692712031721326</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007825072952633901</v>
+        <v>0.0007653546163537931</v>
       </c>
       <c r="R2" t="n">
-        <v>0.000788372756741513</v>
+        <v>0.0007703478456294818</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007848186508161587</v>
+        <v>0.0007673428094533025</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007827522782203032</v>
+        <v>0.0007655264768406127</v>
       </c>
       <c r="U2" t="n">
-        <v>0.000958870920909256</v>
+        <v>0.0009222163954540774</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007861140080532517</v>
+        <v>0.0007688078230513301</v>
       </c>
       <c r="W2" t="n">
-        <v>0.000936207167097222</v>
+        <v>0.0008968592210335835</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008040876027877301</v>
+        <v>0.0007868839481987954</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0007858069538982312</v>
+        <v>0.0007685731298191825</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009322799617867614</v>
+        <v>0.0009144946111193314</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.000789219815969233</v>
+        <v>0.0007719574871753934</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0007824608027955562</v>
+        <v>0.0007652848345739308</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007678185709580822</v>
+        <v>0.0007501797451806329</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008642606253524074</v>
+        <v>0.0008360836319262768</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007689765450406055</v>
+        <v>0.0007512680012310986</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007826747698666955</v>
+        <v>0.0007640259901345927</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007711129631948929</v>
+        <v>0.0007517100313800247</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007646057309927481</v>
+        <v>0.000746835406870371</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007630386955805748</v>
+        <v>0.0007450046496995784</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000763001184292679</v>
+        <v>0.0007455469702919758</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007724328760974851</v>
+        <v>0.0007547488617556911</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007604337188671807</v>
+        <v>0.0007429199795876841</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007756059332612367</v>
+        <v>0.0007572883248947464</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0007583877800919139</v>
+        <v>0.0007407692791144815</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0007702752480875857</v>
+        <v>0.0007526071407741404</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001323958225503439</v>
+        <v>0.001319528145790182</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0007815486679059762</v>
+        <v>0.0007670931504436897</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007567335677513493</v>
+        <v>0.0007393620926795351</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007988079481148949</v>
+        <v>0.0007751874945046327</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007730829904481467</v>
+        <v>0.0007534210203242806</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007585314521518426</v>
+        <v>0.0007406357611776405</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001049531181714214</v>
+        <v>0.0009997819413865936</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007822900756500419</v>
+        <v>0.0007638307067498063</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001042896533776653</v>
+        <v>0.000986910740889726</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0009103430732649144</v>
+        <v>0.0008926083824315499</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0007803244413391229</v>
+        <v>0.0007623722232198469</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001018908231288331</v>
+        <v>0.0009998984280398936</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008046683977769971</v>
+        <v>0.0007865133205024212</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0007571819129745496</v>
+        <v>0.0007395460851608818</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007476658590135171</v>
+        <v>0.0007151697989475525</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007398949438857269</v>
+        <v>0.0007071155059108284</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007492833675748808</v>
+        <v>0.0007166844170458072</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007712932495082738</v>
+        <v>0.0007371929396832543</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000752592035308869</v>
+        <v>0.0007173186282750491</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007425774541195743</v>
+        <v>0.0007098708205994019</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007397667032404394</v>
+        <v>0.0007066598591089894</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007397757406533313</v>
+        <v>0.0007075810103925156</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0007546526245297353</v>
+        <v>0.0007220863932656715</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007357912574085301</v>
+        <v>0.0007034991832698655</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007601198117567157</v>
+        <v>0.000726539722571031</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007329525799401711</v>
+        <v>0.0007004604429568275</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0007513862161206407</v>
+        <v>0.001465047499305295</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0007793799347423568</v>
+        <v>0.0007853808592444026</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0007695690910848845</v>
+        <v>0.0007421403511176932</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0007299688149534632</v>
+        <v>0.0006979007012855861</v>
       </c>
       <c r="R4" t="n">
-        <v>0.000796221900594451</v>
+        <v>0.0007543015229534441</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0007560766391980676</v>
+        <v>0.0007203582569585689</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007327360101495197</v>
+        <v>0.0006998419445439508</v>
       </c>
       <c r="U4" t="n">
-        <v>0.000733409247412984</v>
+        <v>0.0006972830672885837</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007689403180770016</v>
+        <v>0.0007351115958480553</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0007969594849011384</v>
+        <v>0.0007608104529889923</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0009737283158728066</v>
+        <v>0.0009410844084568591</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0007671260121277456</v>
+        <v>0.0007304736291226024</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0007611961525330034</v>
+        <v>0.0007278865836224193</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0008057898242380376</v>
+        <v>0.0007724831646862128</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0007307207417938255</v>
+        <v>0.0006982171909896748</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001393148536899686</v>
+        <v>0.001346959844004833</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001321331571811517</v>
+        <v>0.001268014137922918</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001492209165412988</v>
+        <v>0.001441761623888941</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00177331330376796</v>
+        <v>0.00170066469536194</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001574479952126483</v>
+        <v>0.001474382945064211</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001304330515780776</v>
+        <v>0.001255222153409332</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001362896065692928</v>
+        <v>0.001301087509263098</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001340657413742146</v>
+        <v>0.001296800917901432</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001535234326472997</v>
+        <v>0.001486143015615423</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001244344006283348</v>
+        <v>0.001199792719849187</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001571087327441979</v>
+        <v>0.001508919350233445</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001211634274015984</v>
+        <v>0.001162966872469562</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001190322074987363</v>
+        <v>0.001465047499305295</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001872421737046018</v>
+        <v>0.002425989532859826</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001723804841102608</v>
+        <v>0.001757661243900986</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001130360560005981</v>
+        <v>0.001090161393807279</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002412169306282086</v>
+        <v>0.002185375681269419</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001516025899623205</v>
+        <v>0.001419521800101527</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001204918209745004</v>
+        <v>0.001148899532079924</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001172459071303914</v>
+        <v>0.001126916233336384</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001753379397128488</v>
+        <v>0.001686469765959381</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002271080201645623</v>
+        <v>0.002161395115949435</v>
       </c>
       <c r="X5" t="n">
-        <v>0.005229060794209349</v>
+        <v>0.005178988805503318</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001810833313505164</v>
+        <v>0.001753590827273077</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001568602803745864</v>
+        <v>0.001511113057268932</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002485494132863507</v>
+        <v>0.002422857792972249</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001188382813628577</v>
+        <v>0.001138159692916632</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001015611881396631</v>
+        <v>0.000955029220638199</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001007840966268841</v>
+        <v>0.000946974927601475</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001017229389957995</v>
+        <v>0.000956543838736454</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001039239271891388</v>
+        <v>0.000870662724082979</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001020538057691983</v>
+        <v>0.0009571780499656961</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001010523476502688</v>
+        <v>0.0009497302422900486</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0008911817475867914</v>
+        <v>0.0009465192807996357</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008911907849996833</v>
+        <v>0.0009474404320831619</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009060676688760871</v>
+        <v>0.0008555561776653964</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001003737279791645</v>
+        <v>0.0008369689676695904</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00102806583413983</v>
+        <v>0.0009663991442616775</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001000898602323285</v>
+        <v>0.0009403198646474742</v>
       </c>
       <c r="N6" t="n">
-        <v>0.000902713091146567</v>
+        <v>0.001465047499305295</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001047092156586041</v>
+        <v>0.0009367236802897854</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001037280709931373</v>
+        <v>0.0009831350416776023</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0009979148373365774</v>
+        <v>0.0009377601229762331</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0009476369449408023</v>
+        <v>0.0009941609446440904</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0009074916835444194</v>
+        <v>0.0009602176786492157</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001000682032532633</v>
+        <v>0.000833311728943676</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001001469234820306</v>
+        <v>0.0009409241513231297</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0009203553624233535</v>
+        <v>0.0008685813802477805</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001064672207231008</v>
+        <v>0.001001468971890324</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001125143360219158</v>
+        <v>0.001074554192856583</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0009273900820573259</v>
+        <v>0.0008775404816239235</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0009126111968793552</v>
+        <v>0.0008613563680221444</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0009572048685843898</v>
+        <v>0.001012342586376859</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0008819143281399236</v>
+        <v>0.0008314761593446256</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0008200981696562875</v>
+        <v>0.0007918947337582815</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008123272545284973</v>
+        <v>0.0007838404407215575</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008217156782176513</v>
+        <v>0.0007934093518565368</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008437255601510442</v>
+        <v>0.000813917874493983</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008250243459516391</v>
+        <v>0.0007940435630857782</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008150097647623449</v>
+        <v>0.0007865957554101309</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008121990138832098</v>
+        <v>0.0007833847939197186</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008122080512961016</v>
+        <v>0.0007843059452032446</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008270849351725058</v>
+        <v>0.0007988113280764003</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008082235680513007</v>
+        <v>0.0007802241180805946</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008325521223994863</v>
+        <v>0.0008032646573817601</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0008053848905829417</v>
+        <v>0.0007771853777675568</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0008238185267634112</v>
+        <v>0.001465047499305295</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0008518030465317484</v>
+        <v>0.0008620969042849039</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0008419922028742756</v>
+        <v>0.000818856396158195</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0008024011255962337</v>
+        <v>0.0007746256360963154</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0008686542112372211</v>
+        <v>0.0008310264577641731</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0008285089498408384</v>
+        <v>0.0007970831917692981</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00080516832079229</v>
+        <v>0.0007765668793546801</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0008058784051337368</v>
+        <v>0.0007776925179552366</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0008413726287197719</v>
+        <v>0.0008118365306587844</v>
       </c>
       <c r="W7" t="n">
-        <v>0.000869391795543909</v>
+        <v>0.0008375353877997211</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001046160626515576</v>
+        <v>0.001017809343267587</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0008396722877947235</v>
+        <v>0.0008109802262772308</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008336284631757733</v>
+        <v>0.0008046115184331484</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0008782221348808084</v>
+        <v>0.000849208099496942</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0008031530524365959</v>
+        <v>0.0007749421258004037</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008940565759659656</v>
+        <v>0.0008566921442583511</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001013280217756102</v>
+        <v>0.0009658450546365481</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001022668641445256</v>
+        <v>0.0009754139657715274</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009770576679274192</v>
+        <v>0.0009335131099894828</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009187670200105118</v>
+        <v>0.0008771004860465827</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001042295876658586</v>
+        <v>0.0009929040464861634</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001013151977110814</v>
+        <v>0.0009653894078347091</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001013161014523707</v>
+        <v>0.0009663105591182352</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00102803789840011</v>
+        <v>0.0009808159419913915</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001009176531278906</v>
+        <v>0.000962228731995585</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001033505085627091</v>
+        <v>0.0009852692712967507</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001006337853810527</v>
+        <v>0.0009591899916825305</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0009263294626493546</v>
+        <v>0.001465047499305295</v>
       </c>
       <c r="O8" t="n">
-        <v>0.000981375905135629</v>
+        <v>0.0009782230123408159</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0009649337851742046</v>
+        <v>0.0009288622942658465</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0008514022029654262</v>
+        <v>0.0008163891560050457</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001069607174464826</v>
+        <v>0.001013031071679164</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001029461913068443</v>
+        <v>0.0009790878056842884</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001006121284019895</v>
+        <v>0.0009585714932696706</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0009448715024155303</v>
+        <v>0.0009025186099203476</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001007558009128577</v>
+        <v>0.0009617312089442325</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001070369716827254</v>
+        <v>0.001019563036274596</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001106801007360199</v>
+        <v>0.001070315136255094</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001166803004131367</v>
+        <v>0.001109404287728221</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0009052278803923609</v>
+        <v>0.0008672317449565196</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001079175098108413</v>
+        <v>0.001031212713411933</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001136762449465194</v>
+        <v>0.001079379464376538</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000939771669383226</v>
+        <v>0.0009059422658464831</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009999182764686885</v>
+        <v>0.0009625231486411332</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001009306700157842</v>
+        <v>0.0009720920597761126</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001015641534690377</v>
+        <v>0.0009776830840463953</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0008560468753796198</v>
+        <v>0.0008237244880398088</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001002600838308519</v>
+        <v>0.0009652785108759171</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0009997900358234011</v>
+        <v>0.0009620675018392941</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009997990732362929</v>
+        <v>0.0009629886531228206</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001014675957112697</v>
+        <v>0.0009774940359959759</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009958145899914917</v>
+        <v>0.00095890682600017</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001020143144339677</v>
+        <v>0.000981947365301336</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0009929759125231333</v>
+        <v>0.0009558680856871323</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001011409548703603</v>
+        <v>0.001465047499305295</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001061911113965009</v>
+        <v>0.001062208577916129</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001056995329558231</v>
+        <v>0.001023626558459175</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0009899921991424101</v>
+        <v>0.0009533083915621019</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001056245233177412</v>
+        <v>0.001009709165683748</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001016099971781029</v>
+        <v>0.0009757658996888738</v>
       </c>
       <c r="T9" t="n">
-        <v>0.000992759342732481</v>
+        <v>0.0009552495872742554</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0009935465450201526</v>
+        <v>0.0009564723723627883</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001107339064457461</v>
+        <v>0.001065106895595691</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0010569828174841</v>
+        <v>0.001016218095719296</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001233751648455769</v>
+        <v>0.001196492051187163</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001027263309734915</v>
+        <v>0.0009896629341968057</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0009802712791752719</v>
+        <v>0.0009443249817905846</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001065813156820999</v>
+        <v>0.001027890807416517</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0009907440743767871</v>
+        <v>0.0009536248337199795</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008150822666598914</v>
+        <v>0.0007956216873251606</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008758108011238527</v>
+        <v>0.0008595909254418685</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008157783478089224</v>
+        <v>0.0007974059462561858</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008072371351741357</v>
+        <v>0.0007899286416906946</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008081296637574757</v>
+        <v>0.0007906690290441989</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008358830576966994</v>
+        <v>0.0008025013568275653</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008083438789158538</v>
+        <v>0.0007919788177401634</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008151693048156341</v>
+        <v>0.0007988679223302311</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008231780138924584</v>
+        <v>0.0008017231565928843</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008235875825073471</v>
+        <v>0.0008073110872557064</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008338460122547255</v>
+        <v>0.0008020260719817952</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008353765779071815</v>
+        <v>0.0008422476779577687</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008243250935179575</v>
+        <v>0.0008071331868653562</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001146659074890753</v>
+        <v>0.001121269335210141</v>
       </c>
       <c r="P2" t="n">
-        <v>0.000829137349554362</v>
+        <v>0.0008000451844818496</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0008102858477510474</v>
+        <v>0.0007931042654368681</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0008097616332170924</v>
+        <v>0.0007935584394513463</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008171091560864706</v>
+        <v>0.0007974476693927878</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008145518749923901</v>
+        <v>0.0007976871643331879</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00104504411066983</v>
+        <v>0.00101630787166001</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008068580618185794</v>
+        <v>0.0007899412304665829</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009896602764660205</v>
+        <v>0.0009684491539701103</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008270987370276123</v>
+        <v>0.0008019285559071334</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008210619484081641</v>
+        <v>0.0007962752199187075</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009614728711778821</v>
+        <v>0.0009423134966044812</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008199945546449</v>
+        <v>0.0008029063308997357</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008455260908264419</v>
+        <v>0.0008103943594896234</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008609712725489815</v>
+        <v>0.0008253015649472076</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000895791225417936</v>
+        <v>0.0008821381207610453</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008667603531836427</v>
+        <v>0.0008387046268132749</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008053842443447953</v>
+        <v>0.0007849730425102717</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008119946204580597</v>
+        <v>0.0007904689574559099</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001008595148277616</v>
+        <v>0.0008741110513054873</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008136820151774414</v>
+        <v>0.0007999919900616061</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008624097690895115</v>
+        <v>0.0008491782728763554</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009187022269241252</v>
+        <v>0.0008689022229971963</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009216849983941463</v>
+        <v>0.0009086243910706633</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009948670915899183</v>
+        <v>0.0008711239290578978</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001006540534803458</v>
+        <v>0.001156440542836971</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0009276312750280557</v>
+        <v>0.0009080388055164063</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001401507657642542</v>
+        <v>0.00136050029831469</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0009610749903676166</v>
+        <v>0.0008568609739818836</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008272413397394016</v>
+        <v>0.000807728710690077</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008237939544970071</v>
+        <v>0.0008112667226448367</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008752120292364903</v>
+        <v>0.0008381495712078039</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008579706294844254</v>
+        <v>0.0008407079151800137</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001318010298842298</v>
+        <v>0.001237867005313204</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008025377856973276</v>
+        <v>0.0007849380590076668</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00114309335217933</v>
+        <v>0.001117142619617507</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0009475859885469432</v>
+        <v>0.0008709396235038304</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.000904069028792939</v>
+        <v>0.0008303111219394232</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001084216260609168</v>
+        <v>0.001056512064647159</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008965286992707591</v>
+        <v>0.0008776836380959735</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001078609955587742</v>
+        <v>0.000931411788018104</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0009199767339867175</v>
+        <v>0.0008249268835825149</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007839938589227324</v>
+        <v>0.0007235637947406083</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009278392907781688</v>
+        <v>0.0008450809090081018</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008313623649163251</v>
+        <v>0.0007606213142108366</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008414438858485824</v>
+        <v>0.0007689843299636807</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001154931237584087</v>
+        <v>0.0009026359154165041</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008438635446063049</v>
+        <v>0.0007837789958171675</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0009209598699953549</v>
+        <v>0.0008615946013066615</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001011001653573942</v>
+        <v>0.0008934900054443211</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001016048189122326</v>
+        <v>0.0009569640331876691</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001131921872229784</v>
+        <v>0.0008972673544416923</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001150071516008786</v>
+        <v>0.001348698492089482</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001024378715258997</v>
+        <v>0.005817415591116578</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0009061526006958021</v>
+        <v>0.0008202737564312711</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001078735360937331</v>
+        <v>0.0008748923188765433</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0008657989759496095</v>
+        <v>0.000796491445282966</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0008598777316379878</v>
+        <v>0.0008016215497068671</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0009428713824751276</v>
+        <v>0.0008455521910296075</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0009139857161100723</v>
+        <v>0.0008482573965545485</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00107496433923264</v>
+        <v>0.000915551738665898</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0008243207593167605</v>
+        <v>0.0007584411200796237</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0009064870666138434</v>
+        <v>0.0008376165534403358</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001055708294639595</v>
+        <v>0.0008961658655187887</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0009832960462179457</v>
+        <v>0.0008237658941270681</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0008817902898860132</v>
+        <v>0.0008022228229744309</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0009754632865415059</v>
+        <v>0.0009072102838589387</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.00126039665856734</v>
+        <v>0.0009904412571405635</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003732152607538407</v>
+        <v>0.00303679988131916</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001453678935602254</v>
+        <v>0.001351452672876262</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004337481910528818</v>
+        <v>0.003789778694004379</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002281362964519002</v>
+        <v>0.001989446057489679</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00260565744062501</v>
+        <v>0.002265329220155776</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007711704974731932</v>
+        <v>0.004344242358446705</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002739575186876788</v>
+        <v>0.002642394989418333</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004205285376324982</v>
+        <v>0.004123958184144935</v>
       </c>
       <c r="J5" t="n">
-        <v>0.005433630563646122</v>
+        <v>0.004369681619635682</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005554703786116258</v>
+        <v>0.005474947530674523</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007727373111920841</v>
+        <v>0.004467981004751227</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008227275377284127</v>
+        <v>0.01290539338175982</v>
       </c>
       <c r="N5" t="n">
-        <v>0.006756225915410529</v>
+        <v>0.005817415591116578</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00342779942643343</v>
+        <v>0.002903083675847149</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006618205013750602</v>
+        <v>0.003975251093338831</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002987146733437476</v>
+        <v>0.002718331192949065</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003038674938249952</v>
+        <v>0.002980257318492763</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004039766807438374</v>
+        <v>0.003324383148168719</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004055337020466367</v>
+        <v>0.003847737679967689</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00681103548328918</v>
+        <v>0.00498128199510329</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002119229460498285</v>
+        <v>0.001920387686962661</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003755856563421872</v>
+        <v>0.003495929549615375</v>
       </c>
       <c r="X5" t="n">
-        <v>0.006772709573992364</v>
+        <v>0.00473172143216937</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.005243099108159318</v>
+        <v>0.003368395512531249</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.003092547973399256</v>
+        <v>0.002661183014400194</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.005058352355828796</v>
+        <v>0.004810178213112213</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01141338759994693</v>
+        <v>0.006950656887591362</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00120586399584102</v>
+        <v>0.0009654275904879315</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009292538404915243</v>
+        <v>0.0008640645016460237</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001213726552632472</v>
+        <v>0.000985581615913518</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001117249626770627</v>
+        <v>0.001026969039464501</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001127331147702885</v>
+        <v>0.0009094850368690966</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001300191219152879</v>
+        <v>0.001168983640670167</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001129750806460608</v>
+        <v>0.0009242797027225827</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001066219851564147</v>
+        <v>0.001002095308212077</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001156261635142735</v>
+        <v>0.001033990712349737</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001161308170691118</v>
+        <v>0.001223311758441333</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001417809134084087</v>
+        <v>0.001163615079695356</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001435958777863088</v>
+        <v>0.001489199198994898</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001170073094398309</v>
+        <v>0.005817415591116578</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001051846979835115</v>
+        <v>0.001089034695110062</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001365576516216003</v>
+        <v>0.001143833089905069</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001151686237803912</v>
+        <v>0.000936992152188381</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00114576499349229</v>
+        <v>0.00106796927496053</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00122875864432943</v>
+        <v>0.0009860528979350235</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001059245697678864</v>
+        <v>0.0009887581034599639</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001365075544991958</v>
+        <v>0.001190442404658971</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001110208021171063</v>
+        <v>0.0008989418269850391</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001062061961928423</v>
+        <v>0.00098827734592794</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001200968276208386</v>
+        <v>0.001162513590772452</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001141104005132925</v>
+        <v>0.0009809612551110606</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001027050271454805</v>
+        <v>0.001068570548228095</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001261350548395809</v>
+        <v>0.001173558009112601</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001408209131435702</v>
+        <v>0.001132109296153048</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00101905668614347</v>
+        <v>0.0009171789212184956</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008830738110794849</v>
+        <v>0.0008158158323765879</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001026919242934921</v>
+        <v>0.0009373329466440822</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0009304423170730777</v>
+        <v>0.0008528733518468169</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0009405238380053348</v>
+        <v>0.0008612363675996611</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001254011189740841</v>
+        <v>0.0009948879530524847</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009429434967630575</v>
+        <v>0.0008760310334531474</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001020039822152107</v>
+        <v>0.0009538466389426418</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001110081605730696</v>
+        <v>0.0009857420430803019</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001115128141279078</v>
+        <v>0.00104921607082365</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001231001824386537</v>
+        <v>0.0009895193920776732</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001249151468165538</v>
+        <v>0.001440950529725462</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00112345866741575</v>
+        <v>0.005817415591116578</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001005222790862238</v>
+        <v>0.0009125162959435891</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001177805551103766</v>
+        <v>0.0009671348583888614</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0009648789281063617</v>
+        <v>0.0008887434829189455</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0009589576837947405</v>
+        <v>0.0008938735873428476</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00104195133463188</v>
+        <v>0.0009378042286655874</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001013065668266825</v>
+        <v>0.0009405094341905284</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001178128353092087</v>
+        <v>0.001016226264530398</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0009234007114735135</v>
+        <v>0.0008506931577156035</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001005567018770596</v>
+        <v>0.000929868591076316</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001154788246796347</v>
+        <v>0.0009884179031547694</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001086599942279716</v>
+        <v>0.0009245608725024586</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0009808702420427656</v>
+        <v>0.000894474860610411</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001074543238698258</v>
+        <v>0.0009994623214949188</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001359476610724092</v>
+        <v>0.001082693294776544</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001103262370368206</v>
+        <v>0.0009969080744496035</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001117726902479832</v>
+        <v>0.001036268530338057</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001261572334335268</v>
+        <v>0.00115778564460555</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001084986602077708</v>
+        <v>0.0009983949133282224</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001048167469949262</v>
+        <v>0.0009628886044264163</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001519860531091179</v>
+        <v>0.001244520594741092</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001177596588163405</v>
+        <v>0.001096483731414615</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001254692913552455</v>
+        <v>0.00117429933690411</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001344734697131042</v>
+        <v>0.00120619474104177</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001349781232679424</v>
+        <v>0.001269668768785118</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001465654915786884</v>
+        <v>0.001209972090039141</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001483804559565874</v>
+        <v>0.001661403227686962</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001241489848946196</v>
+        <v>0.005817415591116578</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001155312447814927</v>
+        <v>0.001053871512285635</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001320039293990013</v>
+        <v>0.001101141911706361</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001019518263032456</v>
+        <v>0.0009408172477575774</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001193610775195087</v>
+        <v>0.001114326285304316</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001276604426032227</v>
+        <v>0.001158256926627056</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001247718759667171</v>
+        <v>0.001160962132151996</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001339389115267928</v>
+        <v>0.001168028144097604</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001116823034471499</v>
+        <v>0.001032589147972951</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001240249677374823</v>
+        <v>0.001150348945226351</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001223216385519947</v>
+        <v>0.001053389260477621</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001470666958374579</v>
+        <v>0.001284784689295582</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001062281288441132</v>
+        <v>0.0009715900017520843</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001309196330098605</v>
+        <v>0.001219915019456387</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001751284599106346</v>
+        <v>0.001450143502301905</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001262252867561867</v>
+        <v>0.001117448618796762</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00123572236255058</v>
+        <v>0.001110672115133556</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001379567794406015</v>
+        <v>0.001232189229401049</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00125782972971434</v>
+        <v>0.001125899388669697</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001040854767244164</v>
+        <v>0.0009380448376501527</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001606659769462372</v>
+        <v>0.001289744173554986</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001295592048234152</v>
+        <v>0.001170887316210115</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001372688373623202</v>
+        <v>0.001248702921699609</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001462730157201791</v>
+        <v>0.001280598325837269</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001467776692750173</v>
+        <v>0.001344072353580616</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001583650375857633</v>
+        <v>0.001284375674834641</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001601800019636634</v>
+        <v>0.001735806812482431</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001476107218886845</v>
+        <v>0.005817415591116578</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001394153514056578</v>
+        <v>0.001238727864416879</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001574624894940851</v>
+        <v>0.001300163611399252</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001317527507827893</v>
+        <v>0.001183599703421447</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001311606235265836</v>
+        <v>0.001188729870099815</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001394599886102974</v>
+        <v>0.001232660511422554</v>
       </c>
       <c r="T9" t="n">
-        <v>0.00136571421973792</v>
+        <v>0.001235365716947496</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001530916786765504</v>
+        <v>0.001311202999798254</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001402354868499787</v>
+        <v>0.001254700086796083</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001358215570241691</v>
+        <v>0.001224724873833283</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001507436798267442</v>
+        <v>0.001283274185911736</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.00143924849375081</v>
+        <v>0.001219417155259425</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001267528758474532</v>
+        <v>0.001132303818751407</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001427191790169354</v>
+        <v>0.001294318604251884</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001712125162195189</v>
+        <v>0.001377549577533512</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007861791437478277</v>
+        <v>0.000774741423640079</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008619432342242315</v>
+        <v>0.0008501607613112583</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007891003897988098</v>
+        <v>0.0007773062048503144</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007885170090668027</v>
+        <v>0.0007770486851438831</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007880061593972738</v>
+        <v>0.0007765087952950856</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008141002861013547</v>
+        <v>0.0007899252076781402</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007888399921013024</v>
+        <v>0.0007773888321848622</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007886031429257286</v>
+        <v>0.0007771995088419611</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007977576061826983</v>
+        <v>0.0007824645334449775</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007912050037841091</v>
+        <v>0.0007799548827753239</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007997175417499265</v>
+        <v>0.0007837606242955819</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007892093745595935</v>
+        <v>0.0007800306445760282</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007907107089642066</v>
+        <v>0.0007794436846923817</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001111001634315323</v>
+        <v>0.001094973638889425</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008017362017893228</v>
+        <v>0.0007848432881911411</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007904337689359334</v>
+        <v>0.0007787108276297867</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007919512472227643</v>
+        <v>0.0007802237444198291</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007910937169726583</v>
+        <v>0.0007792635415573769</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007884179524553557</v>
+        <v>0.000777198849131644</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001006680096221099</v>
+        <v>0.0009916737318596742</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007890825394401488</v>
+        <v>0.0007775519600676685</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009724428487493969</v>
+        <v>0.0009579047389561922</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008046480227425698</v>
+        <v>0.0007915663585622586</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008110542105823996</v>
+        <v>0.0007927445307689083</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009353709294640084</v>
+        <v>0.0009235756761960608</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0007917858702279394</v>
+        <v>0.0007803384438317571</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008137423924482834</v>
+        <v>0.0007912185628929057</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007526039287128629</v>
+        <v>0.000743334685953109</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008847820603057452</v>
+        <v>0.0008748029507174488</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007735447584817284</v>
+        <v>0.0007617274136923524</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007692588250756905</v>
+        <v>0.0007597721328491175</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007657352745397018</v>
+        <v>0.0007560380543820502</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009504313582951857</v>
+        <v>0.0008509246900903038</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007718051452800072</v>
+        <v>0.000762437462316886</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007700359083547771</v>
+        <v>0.0007610092451007096</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0008347948767296388</v>
+        <v>0.000798205692248912</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007883790454515751</v>
+        <v>0.0007804393744848859</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008487474618854474</v>
+        <v>0.0008073972166864091</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000776157181213004</v>
+        <v>0.0007825783140401188</v>
       </c>
       <c r="N3" t="n">
-        <v>0.000785037492895432</v>
+        <v>0.0007769874208331435</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001305339105817383</v>
+        <v>0.001286735934961069</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008631171701648919</v>
+        <v>0.0008150942009308519</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00078289016577901</v>
+        <v>0.0007715918803868679</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007940590768514862</v>
+        <v>0.0007827113590955355</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007874532582273304</v>
+        <v>0.0007754009869475375</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007686891221347313</v>
+        <v>0.000760981976090241</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001140962797887642</v>
+        <v>0.00111941660510517</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007732124883046714</v>
+        <v>0.0007632834390575724</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001113968767692853</v>
+        <v>0.001097182882547904</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008844787770699088</v>
+        <v>0.0008634750211209477</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009301126521054632</v>
+        <v>0.0008718162491378044</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001015718009616297</v>
+        <v>0.001004781822573527</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0007926677802207089</v>
+        <v>0.0007833286672119235</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0009489959566137859</v>
+        <v>0.0008609761546523977</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007359971092308651</v>
+        <v>0.0006979110520702899</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007504656342037775</v>
+        <v>0.0007121328837371477</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007689939272162877</v>
+        <v>0.0007268814356975533</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007624043734798684</v>
+        <v>0.0007239726321484889</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007566340914600768</v>
+        <v>0.0007178743279447244</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001051379256474018</v>
+        <v>0.0008694188776659451</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007660526154340807</v>
+        <v>0.000727814749451716</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007633772950399681</v>
+        <v>0.0007256762552006064</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0008664064869281615</v>
+        <v>0.0007848203076143629</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007927665103505046</v>
+        <v>0.0007567994713125689</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008889195426353447</v>
+        <v>0.0007997870725114808</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007736906991549647</v>
+        <v>0.0007604014653602615</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0007871832229728557</v>
+        <v>0.001978125036779732</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0007703694087726087</v>
+        <v>0.000728637091106467</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0009117212364098255</v>
+        <v>0.0008120162592618229</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.000784055057954795</v>
+        <v>0.0007427472961501008</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0008011956732790573</v>
+        <v>0.0007598363872697267</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0007915094746207036</v>
+        <v>0.0007489904542231938</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007612854834852832</v>
+        <v>0.0007256688034690912</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0007829905979519719</v>
+        <v>0.0007291500528209317</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007663364756151414</v>
+        <v>0.0007275262562159505</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0008468643152088938</v>
+        <v>0.0008038420434789167</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0009446115935805711</v>
+        <v>0.0008879564318687706</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001013501153639531</v>
+        <v>0.0008952677345499991</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0007709833109296662</v>
+        <v>0.000730661590506329</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0007993276640453358</v>
+        <v>0.0007611319698917925</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001045105782649271</v>
+        <v>0.0008830596795341609</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001033316028591948</v>
+        <v>0.0009907959528928443</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001319578345140159</v>
+        <v>0.001271775425048392</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001664466874066047</v>
+        <v>0.0015486625152754</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00148453255268385</v>
+        <v>0.001436401930907799</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001445910969597883</v>
+        <v>0.001390285837260459</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005861418125567493</v>
+        <v>0.003621316897273135</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001674040146452668</v>
+        <v>0.001627529352628574</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001585869716908053</v>
+        <v>0.001549799583901969</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00311540336757673</v>
+        <v>0.002404234590882197</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001988302299422452</v>
+        <v>0.00197842431298992</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003488897074173691</v>
+        <v>0.002633052136311427</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001722448550049862</v>
+        <v>0.002097137021188358</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001864176199387023</v>
+        <v>0.001978125036779732</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001569251345744846</v>
+        <v>0.001469601290281302</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003872713442465802</v>
+        <v>0.002833777003324759</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001842238619887656</v>
+        <v>0.00174615521786707</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002320865877564797</v>
+        <v>0.002215125245016382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001897908646716327</v>
+        <v>0.001786283622534743</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001535879337282042</v>
+        <v>0.001537976315085601</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001863454852950056</v>
+        <v>0.001607280982871513</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001552275575492465</v>
+        <v>0.001493049749824281</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003021498052975729</v>
+        <v>0.002891003602879061</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004754898071369438</v>
+        <v>0.004383122342449674</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.005989422475152432</v>
+        <v>0.00458354417511336</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00157562854242717</v>
+        <v>0.001498295008728734</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002178485389280224</v>
+        <v>0.002133717348515392</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.006958441068593611</v>
+        <v>0.004560515898366022</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0008682205419892886</v>
+        <v>0.000943415833384906</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001006098353499881</v>
+        <v>0.0009576376650517634</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0009012173599747109</v>
+        <v>0.0009723862170121696</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001018037092775971</v>
+        <v>0.0008559397719258075</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00101226681075618</v>
+        <v>0.0008498414677220422</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001183602689232441</v>
+        <v>0.001001386017443264</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001021685334730184</v>
+        <v>0.0008597818892290339</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001019010014336071</v>
+        <v>0.0009711810365152229</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009986299196865845</v>
+        <v>0.00103032508892898</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001048399229646608</v>
+        <v>0.0008887666110898873</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001021142975393768</v>
+        <v>0.001045291853826097</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001029323418451068</v>
+        <v>0.0008923686051375797</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0009195401240098786</v>
+        <v>0.001978125036779732</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0009027263098096371</v>
+        <v>0.0009756422534502374</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001033902378252602</v>
+        <v>0.0009353777616978442</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001039687777250898</v>
+        <v>0.0008747144359274194</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00105682839257516</v>
+        <v>0.001005341168584343</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0009237329073791269</v>
+        <v>0.0008809575940005118</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0008935089162437062</v>
+        <v>0.0008576359432464095</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0009186853092943107</v>
+        <v>0.0009806515285144157</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001021969194911244</v>
+        <v>0.0008594933959932689</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0009885059940532232</v>
+        <v>0.0009456186775155749</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001076835026338994</v>
+        <v>0.001133461213183387</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001156596000775415</v>
+        <v>0.001040856261244292</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0009032067436880899</v>
+        <v>0.0009761663718209449</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001054960383341439</v>
+        <v>0.0008930991096691107</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00117889591471913</v>
+        <v>0.001015245187786513</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0008206871051224034</v>
+        <v>0.0007781398320658402</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008351556300953155</v>
+        <v>0.000792361663732698</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008536839231078258</v>
+        <v>0.0008071102156931034</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008470943693714061</v>
+        <v>0.0008042014121440395</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008413240873516147</v>
+        <v>0.0007981031079402748</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001136069252365555</v>
+        <v>0.0009496476576614957</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008507426113256187</v>
+        <v>0.0008080435294472666</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000848067290931506</v>
+        <v>0.0008059050351961565</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000951096482819699</v>
+        <v>0.0008650490876099137</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008774565062420426</v>
+        <v>0.0008370282513081191</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009736095385268829</v>
+        <v>0.0008800158525070313</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0008583806950465026</v>
+        <v>0.0008406302453558118</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0008718732188643936</v>
+        <v>0.001978125036779732</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0008550503586140699</v>
+        <v>0.0008088569893186842</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0009964021862512871</v>
+        <v>0.0008922361574740399</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0008687450538463332</v>
+        <v>0.0008229760761456514</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0008858856691705953</v>
+        <v>0.000840065167265277</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0008761994705122415</v>
+        <v>0.0008292192342187441</v>
       </c>
       <c r="T7" t="n">
-        <v>0.000845975479376821</v>
+        <v>0.0008058975834646414</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0008710141560034061</v>
+        <v>0.0008152452669410665</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0008510264715066795</v>
+        <v>0.0008077550362115009</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0009315543111004325</v>
+        <v>0.0008840708234744667</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001029301589472109</v>
+        <v>0.000968185211864321</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001101662428114984</v>
+        <v>0.0009814932089244172</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008556733068212046</v>
+        <v>0.0008108903705018795</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0008840176599368736</v>
+        <v>0.000841360749887343</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.00112979577854081</v>
+        <v>0.0009632884595297109</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008930210448437511</v>
+        <v>0.0008469936118189542</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001037730473910579</v>
+        <v>0.0009843464256894946</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00105625876692309</v>
+        <v>0.0009990949776498997</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009803197736267548</v>
+        <v>0.0009306225582175934</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009339480377708589</v>
+        <v>0.0008861392556563822</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001365650396083921</v>
+        <v>0.001167164430900819</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001053317455140883</v>
+        <v>0.001000028291404063</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00105064213474677</v>
+        <v>0.0009978897971529533</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001153671326634963</v>
+        <v>0.00105703384956671</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001080031350057307</v>
+        <v>0.001029013013264915</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001176184382342146</v>
+        <v>0.001072000614463828</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001060955538861755</v>
+        <v>0.001032615007312606</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0009734895731732903</v>
+        <v>0.001978125036779732</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0009844200284875996</v>
+        <v>0.0009316332172129107</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001118971065272276</v>
+        <v>0.001008582853392344</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0009154836833146592</v>
+        <v>0.0008676318075727783</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001088460512985859</v>
+        <v>0.001032049929222074</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001078774314327505</v>
+        <v>0.001021203996175541</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001048550323192086</v>
+        <v>0.0009978823454214383</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001010058152867801</v>
+        <v>0.0009471676348035991</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001017894528176666</v>
+        <v>0.0009659824928193603</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00113415475096615</v>
+        <v>0.001076079784179958</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001087977056581638</v>
+        <v>0.001024126142464795</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00143356225267497</v>
+        <v>0.001295743385418515</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0009255879548847244</v>
+        <v>0.0008774569290463679</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001086592503752138</v>
+        <v>0.001033345511844139</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001468418137231923</v>
+        <v>0.001283893828427596</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009981472460563023</v>
+        <v>0.0009306620245184832</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001098376702115229</v>
+        <v>0.001021615927814316</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001116904995127739</v>
+        <v>0.001036364479774721</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001090522222432878</v>
+        <v>0.001015746266059335</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009068427149956885</v>
+        <v>0.000850468938599612</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001399290394748908</v>
+        <v>0.001178901972420599</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001113963683345533</v>
+        <v>0.001037297793528883</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00111128836295142</v>
+        <v>0.001035159299277774</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001214317554839613</v>
+        <v>0.00109430335169153</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001140677578261956</v>
+        <v>0.001066282515389737</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001236830610546796</v>
+        <v>0.001109270116588648</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001121601767066417</v>
+        <v>0.001069884509437429</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001135094290884307</v>
+        <v>0.001978125036779732</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001146701630633881</v>
+        <v>0.001063549110721821</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001294234556327055</v>
+        <v>0.001152458633747096</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001131966196229686</v>
+        <v>0.001052230390904753</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001149106741190509</v>
+        <v>0.001069319431346895</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001139420542532156</v>
+        <v>0.001058473498300361</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001109196551396736</v>
+        <v>0.001035151847546259</v>
       </c>
       <c r="U9" t="n">
-        <v>0.00113437294444734</v>
+        <v>0.001044629791276966</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001213213879274679</v>
+        <v>0.001125556501873968</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001194775383120347</v>
+        <v>0.001113325087556084</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001292522661492023</v>
+        <v>0.001197439475945937</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001364883500134898</v>
+        <v>0.001210747473006034</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001067188191496354</v>
+        <v>0.0009938820387967436</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001147238731956787</v>
+        <v>0.001070615013968961</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001393016850560723</v>
+        <v>0.001192542723611328</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia eutrophication marine results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia eutrophication marine results.xlsx
@@ -798,7 +798,7 @@
         <v>0.001447291158155556</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007480407395433476</v>
+        <v>0.001037189299166789</v>
       </c>
       <c r="O4" t="n">
         <v>0.000948333341007533</v>
@@ -974,7 +974,7 @@
         <v>0.001749263286269061</v>
       </c>
       <c r="N6" t="n">
-        <v>0.007480407395433476</v>
+        <v>0.001195995877767603</v>
       </c>
       <c r="O6" t="n">
         <v>0.001107139603506494</v>
@@ -1062,7 +1062,7 @@
         <v>0.001553477914520584</v>
       </c>
       <c r="N7" t="n">
-        <v>0.007480407395433476</v>
+        <v>0.001143376055531815</v>
       </c>
       <c r="O7" t="n">
         <v>0.001054509586932446</v>
@@ -1150,7 +1150,7 @@
         <v>0.001807166292142829</v>
       </c>
       <c r="N8" t="n">
-        <v>0.007480407395433476</v>
+        <v>0.001271860743101422</v>
       </c>
       <c r="O8" t="n">
         <v>0.001217411846083058</v>
@@ -1238,7 +1238,7 @@
         <v>0.001946441769838742</v>
       </c>
       <c r="N9" t="n">
-        <v>0.007480407395433476</v>
+        <v>0.001536339910849976</v>
       </c>
       <c r="O9" t="n">
         <v>0.001487329818576247</v>
@@ -1658,7 +1658,7 @@
         <v>0.0007144069414250388</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001528723260254152</v>
+        <v>0.0007213451308418551</v>
       </c>
       <c r="O4" t="n">
         <v>0.0007525840957798045</v>
@@ -1670,7 +1670,7 @@
         <v>0.0007035244134437096</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00074705403873735</v>
+        <v>0.0007470540387373498</v>
       </c>
       <c r="S4" t="n">
         <v>0.0007327309314322647</v>
@@ -1834,7 +1834,7 @@
         <v>0.0008474061533065068</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001528723260254152</v>
+        <v>0.0008551244634595856</v>
       </c>
       <c r="O6" t="n">
         <v>0.000996490813565016</v>
@@ -1922,7 +1922,7 @@
         <v>0.0007917304469528408</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001528723260254152</v>
+        <v>0.0007986686363696562</v>
       </c>
       <c r="O7" t="n">
         <v>0.0008298987103891896</v>
@@ -2010,7 +2010,7 @@
         <v>0.0009752736448394027</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001528723260254152</v>
+        <v>0.0008906401887892271</v>
       </c>
       <c r="O8" t="n">
         <v>0.0009470438369976222</v>
@@ -2098,7 +2098,7 @@
         <v>0.0009711646378510346</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001528723260254152</v>
+        <v>0.000978102827267851</v>
       </c>
       <c r="O9" t="n">
         <v>0.001030876145904243</v>
@@ -2518,7 +2518,7 @@
         <v>0.001367982197506244</v>
       </c>
       <c r="N4" t="n">
-        <v>0.005052845882567774</v>
+        <v>0.0009179672662011485</v>
       </c>
       <c r="O4" t="n">
         <v>0.0008754612560552371</v>
@@ -2694,7 +2694,7 @@
         <v>0.001638084863499756</v>
       </c>
       <c r="N6" t="n">
-        <v>0.005052845882567774</v>
+        <v>0.001061050841017942</v>
       </c>
       <c r="O6" t="n">
         <v>0.001018279645080973</v>
@@ -2782,7 +2782,7 @@
         <v>0.001462742798269081</v>
       </c>
       <c r="N7" t="n">
-        <v>0.005052845882567774</v>
+        <v>0.001012727866963986</v>
       </c>
       <c r="O7" t="n">
         <v>0.0009702123156648035</v>
@@ -2870,7 +2870,7 @@
         <v>0.001688492647434625</v>
       </c>
       <c r="N8" t="n">
-        <v>0.005052845882567774</v>
+        <v>0.001126842187848515</v>
       </c>
       <c r="O8" t="n">
         <v>0.001115014590179016</v>
@@ -2958,7 +2958,7 @@
         <v>0.001763909851410129</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005052845882567774</v>
+        <v>0.001313894920105034</v>
       </c>
       <c r="O9" t="n">
         <v>0.001303415647764703</v>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.000800468749859103</v>
+        <v>0.0008004687498591041</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008640106301237231</v>
+        <v>0.0008640106301237237</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000806000543588059</v>
+        <v>0.0008060005435880585</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007943203780878634</v>
+        <v>0.0007943203780878646</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007942341669401843</v>
+        <v>0.0007942341669401854</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008045239112090636</v>
+        <v>0.0008045239112090647</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007917467336407743</v>
+        <v>0.000791746733640775</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008047474005992326</v>
+        <v>0.0008047474005992339</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008050922101674485</v>
+        <v>0.0008050922101674498</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008088652220308118</v>
+        <v>0.000808865222030813</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008026827152213981</v>
+        <v>0.0008026827152213994</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008381420285662727</v>
+        <v>0.0008381420285662731</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007991253945465107</v>
+        <v>0.0007991253945465109</v>
       </c>
       <c r="O2" t="n">
         <v>0.001125629223877228</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008042720117838773</v>
+        <v>0.000804272011783878</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007945487120139363</v>
+        <v>0.0007945487120139375</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007918507931827727</v>
+        <v>0.000791850793182774</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008037109833035911</v>
+        <v>0.0008037109833035931</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008013105340732155</v>
+        <v>0.0008013105340732162</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001021261480232039</v>
+        <v>0.00102126148023204</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007950616132825854</v>
+        <v>0.0007950616132825866</v>
       </c>
       <c r="W2" t="n">
         <v>0.0009812629823697599</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008051776311347217</v>
+        <v>0.0008051776311347237</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008087560481257242</v>
+        <v>0.0008087560481257251</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009448276405024504</v>
+        <v>0.0009448276405024519</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.000807837448513103</v>
+        <v>0.0008078374485131043</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008145753898936469</v>
+        <v>0.0008145753898936471</v>
       </c>
     </row>
     <row r="3">
@@ -3254,82 +3254,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008444979011382038</v>
+        <v>0.0008444979011382033</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008953426675668771</v>
+        <v>0.0008953426675668774</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008846773740586563</v>
+        <v>0.0008846773740586562</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008008938815698989</v>
+        <v>0.0008008938815698988</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008004973018508595</v>
+        <v>0.000800497301850859</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008733008303650769</v>
+        <v>0.0008733008303650766</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007828219808720502</v>
+        <v>0.0007828219808720501</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008758414821023204</v>
+        <v>0.0008758414821023202</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000877769128038605</v>
+        <v>0.0008777691280386047</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009042370579507404</v>
+        <v>0.0009042370579507399</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008605864361737232</v>
+        <v>0.0008605864361737219</v>
       </c>
       <c r="M3" t="n">
         <v>0.00111396529129052</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00083538192722169</v>
+        <v>0.0008353819272216895</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001370075339688327</v>
+        <v>0.001370075339688328</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008714931147939297</v>
+        <v>0.00087149311479393</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008026201427923697</v>
+        <v>0.0008026201427923693</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007835176261674948</v>
+        <v>0.000783517626167495</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008675820528387811</v>
+        <v>0.0008675820528387808</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008511830515735553</v>
+        <v>0.0008511830515735546</v>
       </c>
       <c r="U3" t="n">
         <v>0.001231918707046534</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008059210147954434</v>
+        <v>0.0008059210147954429</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001163779896523053</v>
+        <v>0.001163779896523052</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008786835838161334</v>
+        <v>0.0008786835838161336</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009039710268503949</v>
+        <v>0.0009039710268503959</v>
       </c>
       <c r="Z3" t="n">
         <v>0.001058246154063977</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008974843086505095</v>
+        <v>0.0008974843086505093</v>
       </c>
       <c r="AB3" t="n">
         <v>0.0009458822501397505</v>
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0008514784753459021</v>
+        <v>0.0008514784753459014</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007393457359805912</v>
+        <v>0.0007393457359805906</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009139626302652889</v>
+        <v>0.0009139626302652882</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007820297877990047</v>
+        <v>0.0007820297877990041</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007810559932268826</v>
+        <v>0.0007810559932268819</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000897283388260102</v>
+        <v>0.0008972833882601015</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007529592898341959</v>
+        <v>0.0007529592898341955</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008998078037322539</v>
+        <v>0.0008998078037322533</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000903378103425348</v>
+        <v>0.0009033781034253472</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0009463204910933915</v>
+        <v>0.0009463204910933909</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008764862325874182</v>
+        <v>0.0008764862325874155</v>
       </c>
       <c r="M4" t="n">
         <v>0.001275061561868026</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00334925367777354</v>
+        <v>0.0008363046591161951</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0008288224129200226</v>
+        <v>0.0008288224129200219</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0008944380683731532</v>
+        <v>0.0008944380683731531</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0007846089245327956</v>
+        <v>0.0007846089245327949</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0007541346902308191</v>
+        <v>0.0007541346902308185</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0008881009936024778</v>
+        <v>0.0008881009936024771</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0008609868152841764</v>
+        <v>0.0008609868152841761</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0008926790367060066</v>
+        <v>0.0008926790367060069</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007882891370468899</v>
+        <v>0.0007882891370468896</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0008936229977800765</v>
+        <v>0.0008936229977800759</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0009046674555464394</v>
+        <v>0.0009046674555464384</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0009391812966677549</v>
+        <v>0.0009391812966677548</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.000801034914588817</v>
+        <v>0.0008010349145888157</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0009347113164116962</v>
+        <v>0.000934711316411695</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001009293911535005</v>
+        <v>0.001009293911535004</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003373222576292236</v>
+        <v>0.003373222576292227</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001578367514230629</v>
+        <v>0.001578367514230627</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004840485753270227</v>
+        <v>0.004840485753270224</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002288568250573523</v>
+        <v>0.002288568250573522</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002384687840363792</v>
+        <v>0.00238468784036379</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004111345810637576</v>
+        <v>0.004111345810637581</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00192797301782719</v>
+        <v>0.001927973017827195</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004646025870435588</v>
+        <v>0.004646025870435585</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004438229671371531</v>
+        <v>0.004438229671371525</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004953812403273681</v>
+        <v>0.004953812403273678</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003964439898133739</v>
+        <v>0.003964439898133718</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01172157736976084</v>
+        <v>0.01172157736976081</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00334925367777354</v>
+        <v>0.003349253677773539</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002892148104115764</v>
+        <v>0.002892148104115769</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004055892859051014</v>
+        <v>0.00405589285905102</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002384260905949065</v>
+        <v>0.002384260905949062</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001924388333299948</v>
+        <v>0.001924388333299947</v>
       </c>
       <c r="S5" t="n">
-        <v>0.00399201974717433</v>
+        <v>0.003992019747174327</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003892384000165508</v>
+        <v>0.003892384000165507</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004253563653242764</v>
+        <v>0.004253563653242803</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002298193566690527</v>
+        <v>0.002298193566690533</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004314412716121469</v>
+        <v>0.00431441271612146</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00461357541443816</v>
+        <v>0.004613575414438181</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.005197927983704448</v>
+        <v>0.005197927983704445</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00245960931945736</v>
+        <v>0.00245960931945735</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.005050362025761129</v>
+        <v>0.005050362025761126</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.006959104557866166</v>
+        <v>0.006959104557866155</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00110683493662932</v>
+        <v>0.001106834936629319</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008761218256952766</v>
+        <v>0.000876121825695276</v>
       </c>
       <c r="D6" t="n">
         <v>0.001169319091548706</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001037386249082423</v>
+        <v>0.001037386249082422</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009178320829415686</v>
+        <v>0.0009178320829415682</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001034059477974788</v>
+        <v>0.001034059477974787</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0008897353795488821</v>
+        <v>0.0008897353795488815</v>
       </c>
       <c r="I6" t="n">
         <v>0.001036583893446939</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001158734564708766</v>
+        <v>0.001158734564708765</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00120167695237681</v>
+        <v>0.001201676952376809</v>
       </c>
       <c r="L6" t="n">
         <v>0.001131842693870835</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001411837651582711</v>
+        <v>0.00141183765158271</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00334925367777354</v>
+        <v>0.0009737745876848058</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001085141729455609</v>
+        <v>0.001085141729455608</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001150896589956944</v>
+        <v>0.001150896589956943</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001039965385816213</v>
+        <v>0.001039965385816212</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0008909107799455051</v>
+        <v>0.0008909107799455045</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001143457454885896</v>
+        <v>0.001143457454885895</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0009977629049988631</v>
+        <v>0.0009977629049988624</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001035361151365887</v>
+        <v>0.001035361151365888</v>
       </c>
       <c r="V6" t="n">
         <v>0.001043645598330307</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001149922199231875</v>
+        <v>0.001149922199231874</v>
       </c>
       <c r="X6" t="n">
         <v>0.001041443545261126</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001089942417983818</v>
+        <v>0.00108994241798382</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001056391375872234</v>
+        <v>0.001056391375872233</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001190067777695113</v>
+        <v>0.001190067777695112</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001146662925289161</v>
+        <v>0.00114666292528916</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0009387280030141772</v>
+        <v>0.0009387280030141764</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008265952636488659</v>
+        <v>0.0008265952636488658</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001001212157933565</v>
+        <v>0.001001212157933564</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008692793154672803</v>
+        <v>0.0008692793154672798</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008683055208951582</v>
+        <v>0.0008683055208951578</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009845329159283785</v>
+        <v>0.0009845329159283774</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008402088175024715</v>
+        <v>0.0008402088175024713</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00098705733140053</v>
+        <v>0.0009870573314005287</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000990627631093624</v>
+        <v>0.0009906276310936229</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001033570018761667</v>
+        <v>0.001033570018761666</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009637357602556942</v>
+        <v>0.000963735760255693</v>
       </c>
       <c r="M7" t="n">
         <v>0.001362311089536301</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00334925367777354</v>
+        <v>0.0009235541867844702</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0009160629786148721</v>
+        <v>0.0009160629786148718</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0009816786340680029</v>
+        <v>0.0009816786340680025</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0008718584522010711</v>
+        <v>0.0008718584522010701</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0008413842178990947</v>
+        <v>0.0008413842178990942</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0009753505212707536</v>
+        <v>0.0009753505212707526</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0009482363429524522</v>
+        <v>0.0009482363429524521</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0009857132796730686</v>
+        <v>0.000985713279673071</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0008755386647151652</v>
+        <v>0.0008755386647151649</v>
       </c>
       <c r="W7" t="n">
-        <v>0.000980872525448352</v>
+        <v>0.0009808725254483511</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0009919169832147154</v>
+        <v>0.0009919169832147145</v>
       </c>
       <c r="Y7" t="n">
         <v>0.001032336849281223</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008882844422570923</v>
+        <v>0.0008882844422570907</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00102196084407997</v>
+        <v>0.001021960844079969</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.00109654343920328</v>
+        <v>0.001096543439203279</v>
       </c>
     </row>
     <row r="8">
@@ -3703,13 +3703,13 @@
         <v>0.001208377939743036</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001005952573054366</v>
+        <v>0.001005952573054365</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009637080921411148</v>
+        <v>0.0009637080921411146</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001219150141645171</v>
+        <v>0.00121915014164517</v>
       </c>
       <c r="H8" t="n">
         <v>0.001047374599311943</v>
@@ -3727,19 +3727,19 @@
         <v>0.001170901542065164</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001569476871345819</v>
+        <v>0.00156947687134582</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00334925367777354</v>
+        <v>0.001028097383434659</v>
       </c>
       <c r="O8" t="n">
         <v>0.001048816714687392</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001107519482063212</v>
+        <v>0.001107519482063211</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0009206193761732872</v>
+        <v>0.0009206193761732863</v>
       </c>
       <c r="R8" t="n">
         <v>0.001048549999708565</v>
@@ -3748,31 +3748,31 @@
         <v>0.001182516303080225</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001155402124761925</v>
+        <v>0.001155402124761924</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001128296654112189</v>
+        <v>0.001128296654112188</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001046424870621362</v>
+        <v>0.001046424870621364</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00118806432520717</v>
+        <v>0.001188064325207169</v>
       </c>
       <c r="X8" t="n">
         <v>0.001052811499352949</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001370983723186772</v>
+        <v>0.001370983723186771</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0009606033944205657</v>
+        <v>0.0009606033944205656</v>
       </c>
       <c r="AA8" t="n">
         <v>0.001229126625889442</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001441999202859037</v>
+        <v>0.001441999202859036</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001104491177501236</v>
+        <v>0.001104491177501235</v>
       </c>
       <c r="C9" t="n">
         <v>0.001075143059168851</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001249759953453552</v>
+        <v>0.001249759953453551</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001098720725640614</v>
+        <v>0.001098720725640613</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009260122259905833</v>
+        <v>0.0009260122259905827</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001233080669217086</v>
+        <v>0.001233080669217085</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001088756613022457</v>
+        <v>0.001088756613022455</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001235605126920515</v>
+        <v>0.001235605126920514</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001239175426613609</v>
+        <v>0.001239175426613608</v>
       </c>
       <c r="K9" t="n">
         <v>0.001282117814281652</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001212283555775679</v>
+        <v>0.001212283555775677</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001610858885056287</v>
+        <v>0.001610858885056285</v>
       </c>
       <c r="N9" t="n">
-        <v>0.00334925367777354</v>
+        <v>0.001172101982304456</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0011920543948952</v>
+        <v>0.001192054394895201</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001263636627119183</v>
+        <v>0.001263636627119182</v>
       </c>
       <c r="Q9" t="n">
         <v>0.001120406205489779</v>
       </c>
       <c r="R9" t="n">
-        <v>0.00108993201341908</v>
+        <v>0.001089932013419079</v>
       </c>
       <c r="S9" t="n">
         <v>0.001223898316790739</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001196784138472439</v>
+        <v>0.001196784138472438</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001234382384839462</v>
+        <v>0.001234382384839464</v>
       </c>
       <c r="V9" t="n">
         <v>0.001219617946891271</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001229420320968338</v>
+        <v>0.001229420320968337</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001240464778734701</v>
+        <v>0.0012404647787347</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001280884644801209</v>
+        <v>0.001280884644801208</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001086920456020395</v>
+        <v>0.001086920456020393</v>
       </c>
       <c r="AA9" t="n">
         <v>0.001270508639599957</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001345091234723265</v>
+        <v>0.001345091234723264</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007972491356901024</v>
+        <v>0.0007972491356901023</v>
       </c>
       <c r="C2" t="n">
         <v>0.0008432161886572426</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007981259234094085</v>
+        <v>0.0007981259234094088</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007905730027217763</v>
+        <v>0.0007905730027217767</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007942311870596246</v>
+        <v>0.0007942311870596249</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008014558018470818</v>
+        <v>0.0008014558018470822</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007903077235060547</v>
+        <v>0.0007903077235060553</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008025144827506993</v>
+        <v>0.0008025144827506997</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008025095463859874</v>
+        <v>0.0008025095463859873</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008115484896244431</v>
+        <v>0.0008115484896244435</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007995951540115164</v>
+        <v>0.0007995951540115169</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008281535549851667</v>
+        <v>0.0008281535549851663</v>
       </c>
       <c r="N2" t="n">
-        <v>0.000793507972978257</v>
+        <v>0.0007935079729782571</v>
       </c>
       <c r="O2" t="n">
         <v>0.00112309387825552</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008009873753106406</v>
+        <v>0.0008009873753106408</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007931966548965062</v>
+        <v>0.0007931966548965064</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007932427060582167</v>
+        <v>0.0007932427060582166</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008013697205406092</v>
+        <v>0.0008013697205406095</v>
       </c>
       <c r="T2" t="n">
         <v>0.0008009378974776322</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009637363424428461</v>
+        <v>0.0009637363424428453</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007975940654676444</v>
+        <v>0.0007975940654676445</v>
       </c>
       <c r="W2" t="n">
-        <v>0.000926097589157606</v>
+        <v>0.0009260975891576062</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008056009448597788</v>
+        <v>0.000805600944859779</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008180446651570177</v>
+        <v>0.0008180446651570173</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009418531454546638</v>
+        <v>0.0009418531454546636</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008083632211245511</v>
+        <v>0.0008083632211245515</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008110812524751427</v>
+        <v>0.0008110812524751425</v>
       </c>
     </row>
     <row r="3">
@@ -4117,82 +4117,82 @@
         <v>0.0008299072153004554</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008602356457646452</v>
+        <v>0.0008602356457646451</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008366300583962334</v>
+        <v>0.0008366300583962322</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007825241298356886</v>
+        <v>0.000782524129835688</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000808928860252476</v>
+        <v>0.0008089288602524756</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008597404597718036</v>
+        <v>0.0008597404597718038</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007810100146867033</v>
+        <v>0.0007810100146867029</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008682226736091294</v>
+        <v>0.0008682226736091289</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000867650084412052</v>
+        <v>0.0008676500844120515</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009317544293651636</v>
+        <v>0.0009317544293651633</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008468285702023029</v>
+        <v>0.0008468285702023027</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001050658814268765</v>
+        <v>0.001050658814268764</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008037185648740306</v>
+        <v>0.0008037185648740301</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001365380177701482</v>
+        <v>0.001365380177701481</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008563934631076755</v>
+        <v>0.000856393463107675</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008013628332750483</v>
+        <v>0.0008013628332750485</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008019982927585283</v>
+        <v>0.0008019982927585281</v>
       </c>
       <c r="S3" t="n">
         <v>0.0008592872236451228</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008570123541995501</v>
+        <v>0.0008570123541995505</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001138788634021489</v>
+        <v>0.00113878863402149</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008322541372855147</v>
+        <v>0.0008322541372855156</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001038036086545642</v>
+        <v>0.001038036086545643</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008899479063787279</v>
+        <v>0.0008899479063787276</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009789594229103378</v>
+        <v>0.0009789594229103363</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001047653852085392</v>
+        <v>0.001047653852085391</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0009097535531803328</v>
+        <v>0.000909753553180332</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0009291881702474465</v>
+        <v>0.000929188170247446</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0008309015354437352</v>
+        <v>0.0008309015354437362</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007361357766238409</v>
+        <v>0.0007361357766238414</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0008408052560755763</v>
+        <v>0.0008408052560755766</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007554915423935965</v>
+        <v>0.0007554915423935971</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000796812417337525</v>
+        <v>0.0007968124173375264</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008784177648488597</v>
+        <v>0.0008784177648488602</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007524950916175524</v>
+        <v>0.0007524950916175531</v>
       </c>
       <c r="I4" t="n">
-        <v>0.000890376052672488</v>
+        <v>0.0008903760526724889</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0008900226264824236</v>
+        <v>0.0008900226264824234</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0009924193161599145</v>
+        <v>0.0009924193161599153</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008574008916058554</v>
+        <v>0.0008574008916058561</v>
       </c>
       <c r="M4" t="n">
         <v>0.00117887500751124</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002448361957624035</v>
+        <v>0.0007886433815935679</v>
       </c>
       <c r="O4" t="n">
         <v>0.0008260863547127137</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0008731266716328976</v>
+        <v>0.0008731266716328977</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0007851269006467935</v>
+        <v>0.0007851269006467937</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0007856470697028969</v>
+        <v>0.000785647069702897</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0008774454368928979</v>
+        <v>0.0008774454368928981</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0008725677967481449</v>
+        <v>0.0008725677967481454</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0008969073312390024</v>
+        <v>0.0008969073312390033</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0008328672792734352</v>
+        <v>0.0008328672792734335</v>
       </c>
       <c r="W4" t="n">
         <v>0.0008205961873782497</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0009252390620372674</v>
+        <v>0.0009252390620372677</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001061534915952155</v>
+        <v>0.001061534915952156</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.000787853465730917</v>
+        <v>0.0007878534657309174</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0009564402431577248</v>
+        <v>0.0009564402431577247</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0009856724490182229</v>
+        <v>0.0009856724490182238</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002930325022197376</v>
+        <v>0.002930325022197382</v>
       </c>
       <c r="C5" t="n">
         <v>0.00147921794460476</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003346548870957774</v>
+        <v>0.003346548870957757</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001733805079860408</v>
+        <v>0.001733805079860409</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002618072232862644</v>
+        <v>0.002618072232862637</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003672295521924252</v>
+        <v>0.003672295521924239</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001877316544522414</v>
+        <v>0.001877316544522416</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004363857829993274</v>
+        <v>0.004363857829993273</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004084101744440127</v>
+        <v>0.004084101744440119</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00567924908092244</v>
+        <v>0.005679249080922448</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003491101077298479</v>
+        <v>0.003491101077298482</v>
       </c>
       <c r="M5" t="n">
         <v>0.009492247151794498</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002448361957624035</v>
+        <v>0.002448361957624032</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002816847230637866</v>
+        <v>0.002816847230637859</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003576737753710651</v>
+        <v>0.003576737753710633</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002316808553188005</v>
+        <v>0.002316808553188002</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002484994774382481</v>
+        <v>0.002484994774382478</v>
       </c>
       <c r="S5" t="n">
-        <v>0.00373860007255561</v>
+        <v>0.003738600072555609</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004070576249528251</v>
+        <v>0.004070576249528255</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004143635333844924</v>
+        <v>0.004143635333844928</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002937781515012772</v>
+        <v>0.00293778151501277</v>
       </c>
       <c r="W5" t="n">
         <v>0.002979375671548875</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004823444995874294</v>
+        <v>0.00482344499587428</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.007413115443123925</v>
+        <v>0.00741311544312392</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002148380688387279</v>
+        <v>0.00214838068838728</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00542252212655836</v>
+        <v>0.005422522126558357</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.006371815050100163</v>
+        <v>0.006371815050100156</v>
       </c>
     </row>
     <row r="6">
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009692610248984594</v>
+        <v>0.0009692610248984576</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000874495266078564</v>
+        <v>0.0008744952660785629</v>
       </c>
       <c r="D6" t="n">
         <v>0.001097355646311192</v>
@@ -4390,73 +4390,73 @@
         <v>0.001012041932629214</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009351719067922489</v>
+        <v>0.0009351719067922467</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001016777254303584</v>
+        <v>0.001016777254303581</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001009045481853167</v>
+        <v>0.00100904548185317</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001028735542127211</v>
+        <v>0.00102873554212721</v>
       </c>
       <c r="J6" t="n">
         <v>0.00114657301671804</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001248969706395532</v>
+        <v>0.001248969706395533</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009957603810605796</v>
+        <v>0.0009957603810605772</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001317234496965965</v>
+        <v>0.001317234496965963</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002448361957624035</v>
+        <v>0.0009281476995760493</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0009829267850906525</v>
+        <v>0.0009829267850906553</v>
       </c>
       <c r="P6" t="n">
         <v>0.001131109883370039</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001041677290882409</v>
+        <v>0.001041677290882411</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001042197459938513</v>
+        <v>0.001042197459938514</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00101580492634762</v>
+        <v>0.001015804926347619</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001129118186983762</v>
+        <v>0.001129118186983761</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001157719412711195</v>
+        <v>0.001157719412711196</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0009712267687281582</v>
+        <v>0.0009712267687281541</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0009690864898870609</v>
+        <v>0.0009690864898870616</v>
       </c>
       <c r="X6" t="n">
         <v>0.001063598551491989</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001214849853050879</v>
+        <v>0.001214849853050876</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.00092621295518564</v>
+        <v>0.0009262129551856389</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001212990633393338</v>
+        <v>0.00121299063339334</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00112530543934175</v>
+        <v>0.001125305439341751</v>
       </c>
     </row>
     <row r="7">
@@ -4466,82 +4466,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0009176940110564354</v>
+        <v>0.0009176940110564356</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008229282522365409</v>
+        <v>0.0008229282522365413</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0009275977316882753</v>
+        <v>0.0009275977316882755</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008422840180062964</v>
+        <v>0.0008422840180062969</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008836048929502252</v>
+        <v>0.0008836048929502263</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009652102404615608</v>
+        <v>0.0009652102404615604</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008392875672302528</v>
+        <v>0.0008392875672302524</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000977168528285188</v>
+        <v>0.0009771685282851884</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0009768151020951236</v>
+        <v>0.000976815102095123</v>
       </c>
       <c r="K7" t="n">
         <v>0.001079211791772615</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009441933672185552</v>
+        <v>0.0009441933672185561</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001265667483123941</v>
+        <v>0.00126566748312394</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002448361957624035</v>
+        <v>0.0008754358572062681</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0009128697872129474</v>
+        <v>0.0009128697872129472</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0009599101041331308</v>
+        <v>0.00095991010413313</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0008719193762594934</v>
+        <v>0.0008719193762594935</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0008724395453155972</v>
+        <v>0.0008724395453155967</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0009642379125055975</v>
+        <v>0.0009642379125055974</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0009593602723608446</v>
+        <v>0.0009593602723608448</v>
       </c>
       <c r="U7" t="n">
         <v>0.0009878556482609939</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0009196597548861358</v>
+        <v>0.0009196597548861335</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0009073886629909495</v>
+        <v>0.00090738866299095</v>
       </c>
       <c r="X7" t="n">
         <v>0.001012031537649968</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.00115258908280143</v>
+        <v>0.001152589082801429</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008746459413436165</v>
+        <v>0.0008746459413436166</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001043232718770424</v>
+        <v>0.001043232718770423</v>
       </c>
       <c r="AB7" t="n">
         <v>0.001072464924630923</v>
@@ -4554,31 +4554,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0009914406999935407</v>
+        <v>0.0009914406999935405</v>
       </c>
       <c r="C8" t="n">
         <v>0.00102797300702439</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001132642486476126</v>
+        <v>0.001132642486476125</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009774164257830456</v>
+        <v>0.0009774164257830454</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009778062860316199</v>
+        <v>0.0009778062860316197</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001197480504529626</v>
+        <v>0.001197480504529624</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001044332322018103</v>
+        <v>0.001044332322018102</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001182213283073036</v>
+        <v>0.001182213283073037</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001181859856882973</v>
+        <v>0.001181859856882972</v>
       </c>
       <c r="K8" t="n">
         <v>0.001284256546560463</v>
@@ -4590,16 +4590,16 @@
         <v>0.00147071223791186</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002448361957624035</v>
+        <v>0.0009787026452669047</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001044115087356313</v>
+        <v>0.001044115087356312</v>
       </c>
       <c r="P8" t="n">
         <v>0.001084299411595798</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0009198629985297978</v>
+        <v>0.0009198629985297986</v>
       </c>
       <c r="R8" t="n">
         <v>0.001077484300103446</v>
@@ -4608,28 +4608,28 @@
         <v>0.001169282667293447</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001164405027148694</v>
+        <v>0.001164405027148695</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001128846396511166</v>
+        <v>0.001128846396511165</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001088736020547461</v>
+        <v>0.001088736020547462</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00111245922159186</v>
+        <v>0.001112459221591861</v>
       </c>
       <c r="X8" t="n">
         <v>0.001072008888537138</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001488052173692148</v>
+        <v>0.001488052173692145</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0009459537013004936</v>
+        <v>0.0009459537013004943</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001248277473558274</v>
+        <v>0.001248277473558273</v>
       </c>
       <c r="AB8" t="n">
         <v>0.001414661488148185</v>
@@ -4645,19 +4645,19 @@
         <v>0.001063187433377804</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00104541158080377</v>
+        <v>0.001045411580803769</v>
       </c>
       <c r="D9" t="n">
         <v>0.001150081060255506</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001046998365120181</v>
+        <v>0.00104699836512018</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009286055177211761</v>
+        <v>0.0009286055177211766</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001187693536361504</v>
+        <v>0.001187693536361505</v>
       </c>
       <c r="H9" t="n">
         <v>0.001061770895797482</v>
@@ -4666,22 +4666,22 @@
         <v>0.001199651856852417</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001199298430662353</v>
+        <v>0.001199298430662352</v>
       </c>
       <c r="K9" t="n">
         <v>0.001301695120339845</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001166676695785785</v>
+        <v>0.001166676695785784</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001488150811691171</v>
+        <v>0.00148815081169117</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002448361957624035</v>
+        <v>0.001097919185773498</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001160876469520148</v>
+        <v>0.001160876469520147</v>
       </c>
       <c r="P9" t="n">
         <v>0.001213465718354129</v>
@@ -4693,34 +4693,34 @@
         <v>0.001094922873882825</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001186721241072826</v>
+        <v>0.001186721241072827</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001181843600928073</v>
+        <v>0.001181843600928075</v>
       </c>
       <c r="U9" t="n">
         <v>0.001210444826655508</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001230987634718715</v>
+        <v>0.001230987634718713</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001129871991558178</v>
+        <v>0.001129871991558179</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001234514866217197</v>
+        <v>0.001234514866217196</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001375072411368658</v>
+        <v>0.00137507241136866</v>
       </c>
       <c r="Z9" t="n">
         <v>0.001050711189682375</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001265716047337653</v>
+        <v>0.001265716047337654</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001294948253198152</v>
+        <v>0.001294948253198153</v>
       </c>
     </row>
   </sheetData>
@@ -5098,7 +5098,7 @@
         <v>0.0009098217616863864</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003321022224638305</v>
+        <v>0.0008193359182324242</v>
       </c>
       <c r="O4" t="n">
         <v>0.0007366861269527674</v>
@@ -5274,7 +5274,7 @@
         <v>0.001163439107817794</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003321022224638305</v>
+        <v>0.0009581199321041863</v>
       </c>
       <c r="O6" t="n">
         <v>0.0009927442389468901</v>
@@ -5362,7 +5362,7 @@
         <v>0.0009947890769178851</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003321022224638305</v>
+        <v>0.0009043032334639213</v>
       </c>
       <c r="O7" t="n">
         <v>0.0008216440319251925</v>
@@ -5450,7 +5450,7 @@
         <v>0.001198288583983994</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003321022224638305</v>
+        <v>0.001006756734270286</v>
       </c>
       <c r="O8" t="n">
         <v>0.0009518752628699641</v>
@@ -5538,7 +5538,7 @@
         <v>0.001244294091478093</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003321022224638305</v>
+        <v>0.00115380824802413</v>
       </c>
       <c r="O9" t="n">
         <v>0.001098549291748789</v>
@@ -5761,7 +5761,7 @@
         <v>0.000769343106321562</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007693829547438634</v>
+        <v>0.0007693829547438633</v>
       </c>
       <c r="H2" t="n">
         <v>0.0007692268335314679</v>
@@ -5958,7 +5958,7 @@
         <v>0.000702939092534051</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001787353085698113</v>
+        <v>0.000738492160876575</v>
       </c>
       <c r="O4" t="n">
         <v>0.0007427852107029784</v>
@@ -6134,7 +6134,7 @@
         <v>0.0009411774369583637</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001787353085698113</v>
+        <v>0.0008713223667171156</v>
       </c>
       <c r="O6" t="n">
         <v>0.0009825739848466908</v>
@@ -6158,7 +6158,7 @@
         <v>0.0008314170977025599</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0008625947501060946</v>
+        <v>0.0008625947501060947</v>
       </c>
       <c r="W6" t="n">
         <v>0.0009256704440537859</v>
@@ -6222,7 +6222,7 @@
         <v>0.0007799942503716711</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001787353085698113</v>
+        <v>0.0008155473187141944</v>
       </c>
       <c r="O7" t="n">
         <v>0.0008198315155513199</v>
@@ -6246,7 +6246,7 @@
         <v>0.0007759684317976722</v>
       </c>
       <c r="V7" t="n">
-        <v>0.000807248464670122</v>
+        <v>0.0008072484646701219</v>
       </c>
       <c r="W7" t="n">
         <v>0.0008606823521415708</v>
@@ -6310,7 +6310,7 @@
         <v>0.0009631297280067677</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001787353085698113</v>
+        <v>0.0009073503976273567</v>
       </c>
       <c r="O8" t="n">
         <v>0.0009367423836409803</v>
@@ -6398,7 +6398,7 @@
         <v>0.0009817742789842872</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001787353085698113</v>
+        <v>0.001017327347326811</v>
       </c>
       <c r="O9" t="n">
         <v>0.001044731316630147</v>
@@ -6818,7 +6818,7 @@
         <v>0.0007004604429568275</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001465047499305295</v>
+        <v>0.000718849647476971</v>
       </c>
       <c r="O4" t="n">
         <v>0.0007853808592444026</v>
@@ -6994,7 +6994,7 @@
         <v>0.0009403198646474742</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001465047499305295</v>
+        <v>0.0008528508142667276</v>
       </c>
       <c r="O6" t="n">
         <v>0.0009367236802897854</v>
@@ -7082,7 +7082,7 @@
         <v>0.0007771853777675568</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001465047499305295</v>
+        <v>0.0007955745822877</v>
       </c>
       <c r="O7" t="n">
         <v>0.0008620969042849039</v>
@@ -7170,7 +7170,7 @@
         <v>0.0009591899916825305</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001465047499305295</v>
+        <v>0.0008867240052144428</v>
       </c>
       <c r="O8" t="n">
         <v>0.0009782230123408159</v>
@@ -7258,7 +7258,7 @@
         <v>0.0009558680856871323</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001465047499305295</v>
+        <v>0.0009742572902072753</v>
       </c>
       <c r="O9" t="n">
         <v>0.001062208577916129</v>
@@ -7678,7 +7678,7 @@
         <v>0.001348698492089482</v>
       </c>
       <c r="N4" t="n">
-        <v>0.005817415591116578</v>
+        <v>0.0009549545664404369</v>
       </c>
       <c r="O4" t="n">
         <v>0.0008202737564312711</v>
@@ -7854,7 +7854,7 @@
         <v>0.001489199198994898</v>
       </c>
       <c r="N6" t="n">
-        <v>0.005817415591116578</v>
+        <v>0.00109598257071428</v>
       </c>
       <c r="O6" t="n">
         <v>0.001089034695110062</v>
@@ -7942,7 +7942,7 @@
         <v>0.001440950529725462</v>
       </c>
       <c r="N7" t="n">
-        <v>0.005817415591116578</v>
+        <v>0.001047206604076417</v>
       </c>
       <c r="O7" t="n">
         <v>0.0009125162959435891</v>
@@ -8030,7 +8030,7 @@
         <v>0.001661403227686962</v>
       </c>
       <c r="N8" t="n">
-        <v>0.005817415591116578</v>
+        <v>0.001158575012330406</v>
       </c>
       <c r="O8" t="n">
         <v>0.001053871512285635</v>
@@ -8118,7 +8118,7 @@
         <v>0.001735806812482431</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005817415591116578</v>
+        <v>0.001342062886833384</v>
       </c>
       <c r="O9" t="n">
         <v>0.001238727864416879</v>
@@ -8538,7 +8538,7 @@
         <v>0.0007604014653602615</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001978125036779732</v>
+        <v>0.0007510252538030145</v>
       </c>
       <c r="O4" t="n">
         <v>0.000728637091106467</v>
@@ -8714,7 +8714,7 @@
         <v>0.0008923686051375797</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001978125036779732</v>
+        <v>0.0008835191130204683</v>
       </c>
       <c r="O6" t="n">
         <v>0.0009756422534502374</v>
@@ -8802,7 +8802,7 @@
         <v>0.0008406302453558118</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001978125036779732</v>
+        <v>0.0008312540337985655</v>
       </c>
       <c r="O7" t="n">
         <v>0.0008088569893186842</v>
@@ -8890,7 +8890,7 @@
         <v>0.001032615007312606</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001978125036779732</v>
+        <v>0.0009277916851783683</v>
       </c>
       <c r="O8" t="n">
         <v>0.0009316332172129107</v>
@@ -8978,7 +8978,7 @@
         <v>0.001069884509437429</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001978125036779732</v>
+        <v>0.001060508297880182</v>
       </c>
       <c r="O9" t="n">
         <v>0.001063549110721821</v>

--- a/Results/Phase 2/Ammonia/ammonia eutrophication marine results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia eutrophication marine results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.000819197759677732</v>
+        <v>0.0008191977596777324</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008751374624595906</v>
+        <v>0.0008751374624595909</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008170852271314245</v>
+        <v>0.0008170852271314248</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008044953189155438</v>
+        <v>0.0008044953189155442</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000810938874918629</v>
+        <v>0.0008109388749186292</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008168374034983454</v>
+        <v>0.0008168374034983456</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008147556569441045</v>
+        <v>0.0008147556569441047</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008209869303415307</v>
+        <v>0.0008209869303415309</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008172157901638141</v>
+        <v>0.0008172157901638148</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008354634264627713</v>
+        <v>0.0008354634264627715</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008189981226827051</v>
+        <v>0.0008189981226827053</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008616840143724349</v>
+        <v>0.000861684014372435</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008251109770839523</v>
+        <v>0.0008251109770839524</v>
       </c>
       <c r="O2" t="n">
         <v>0.001156057744657415</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008133788181396231</v>
+        <v>0.0008133788181396233</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0008094275612015407</v>
+        <v>0.0008094275612015409</v>
       </c>
       <c r="R2" t="n">
         <v>0.0008110242504805604</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008161261861397988</v>
+        <v>0.0008161261861397992</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008213028024916893</v>
+        <v>0.0008213028024916895</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001058867916152201</v>
+        <v>0.001058867916152202</v>
       </c>
       <c r="V2" t="n">
-        <v>0.000807692219872106</v>
+        <v>0.0008076922198721062</v>
       </c>
       <c r="W2" t="n">
         <v>0.001001402718253393</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008090862376229409</v>
+        <v>0.0008090862376229412</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008115477971157746</v>
+        <v>0.0008115477971157748</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009613440882894066</v>
+        <v>0.0009613440882894068</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008240230536421572</v>
+        <v>0.0008240230536421575</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008282389230598814</v>
+        <v>0.0008282389230598815</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0009150452404215739</v>
+        <v>0.0009212637020316259</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009087317509149139</v>
+        <v>0.0009104356566953058</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009010635772151379</v>
+        <v>0.0009068361550331185</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008106875352067227</v>
+        <v>0.0008132311758948594</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008572157236151762</v>
+        <v>0.0008614460531016692</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008984719690383636</v>
+        <v>0.0009041031701030413</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008847245162734922</v>
+        <v>0.0008899377881923513</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0009291176005921998</v>
+        <v>0.0009358928503200681</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00090149539812682</v>
+        <v>0.0009072574929282517</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001032491640023546</v>
+        <v>0.00104291698105681</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009142264552717236</v>
+        <v>0.0009204312455586219</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001219026024529496</v>
+        <v>0.001236119584539504</v>
       </c>
       <c r="N3" t="n">
-        <v>0.000958160179798649</v>
+        <v>0.0009659397098853837</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001460263638314887</v>
+        <v>0.00146598795592489</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008737729329648643</v>
+        <v>0.0008785279456440019</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008461271602403264</v>
+        <v>0.0008499464928059981</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008578335688613574</v>
+        <v>0.0008620820789664485</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008934365779818326</v>
+        <v>0.0008989026136993323</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0009312981684974663</v>
+        <v>0.0009381458267478689</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001359916129174106</v>
+        <v>0.001368405855272026</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008333025997966593</v>
+        <v>0.0008366490670676729</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001186053971716122</v>
+        <v>0.001190921013616459</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008437320376245393</v>
+        <v>0.0008474701791115744</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0008611265315227032</v>
+        <v>0.0008654696150445619</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001093203324909676</v>
+        <v>0.001096832433195249</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0009502521171842142</v>
+        <v>0.0009577387108142287</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.000980732466313459</v>
+        <v>0.0009893073324317894</v>
       </c>
     </row>
     <row r="4">
@@ -762,79 +762,79 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.000970396788349135</v>
+        <v>0.0009703967883491348</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000765621619887647</v>
+        <v>0.0007656216198876468</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009465347614256038</v>
+        <v>0.0009465347614256035</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000804325956483314</v>
+        <v>0.0008043259564833136</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000877108885720372</v>
+        <v>0.0008771088857203715</v>
       </c>
       <c r="G4" t="n">
         <v>0.0009437354794854695</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0009202211945045866</v>
+        <v>0.0009202211945045863</v>
       </c>
       <c r="I4" t="n">
         <v>0.0009906062940559035</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0009477139604146863</v>
+        <v>0.0009477139604146865</v>
       </c>
       <c r="K4" t="n">
         <v>0.001154124977262552</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0009681417966527366</v>
+        <v>0.000968141796652738</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001447291158155556</v>
+        <v>0.001447291158155555</v>
       </c>
       <c r="N4" t="n">
         <v>0.001037189299166789</v>
       </c>
       <c r="O4" t="n">
-        <v>0.000948333341007533</v>
+        <v>0.0009483333410075322</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0009046691668308231</v>
+        <v>0.0009046691668308221</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0008600379020471975</v>
+        <v>0.0008600379020471963</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0008780732419670784</v>
+        <v>0.000878073241967078</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0009357019522445376</v>
+        <v>0.0009357019522445373</v>
       </c>
       <c r="T4" t="n">
         <v>0.000994174215300316</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001068353730234033</v>
+        <v>0.001068353730234032</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0008385222282336113</v>
+        <v>0.0008385222282336114</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0009077532502719577</v>
+        <v>0.0009077532502719568</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0008561824952103098</v>
+        <v>0.0008561824952103095</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0008812589409482577</v>
+        <v>0.0008812589409482567</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0008532574958957748</v>
+        <v>0.0008532574958957742</v>
       </c>
       <c r="AA4" t="n">
         <v>0.001024900703422206</v>
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005593295849191562</v>
+        <v>0.005593295849191529</v>
       </c>
       <c r="C5" t="n">
         <v>0.001900778295836163</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005763927703196986</v>
+        <v>0.005763927703196966</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002590349745666967</v>
+        <v>0.002590349745666968</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004377113850467199</v>
+        <v>0.004377113850467202</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005218478556980449</v>
+        <v>0.005218478556980457</v>
       </c>
       <c r="H5" t="n">
-        <v>0.005404724885954351</v>
+        <v>0.005404724885954347</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006774685692152142</v>
+        <v>0.006774685692152149</v>
       </c>
       <c r="J5" t="n">
         <v>0.005496147666968338</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01010003090329229</v>
+        <v>0.01010003090329228</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005908081320113773</v>
+        <v>0.005908081320113759</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01661638359174124</v>
+        <v>0.01661638359174123</v>
       </c>
       <c r="N5" t="n">
-        <v>0.007480407395433476</v>
+        <v>0.007480407395433468</v>
       </c>
       <c r="O5" t="n">
-        <v>0.005081144165067257</v>
+        <v>0.005081144165067241</v>
       </c>
       <c r="P5" t="n">
         <v>0.004422887494199616</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003853703492926945</v>
+        <v>0.003853703492926947</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004401595158081978</v>
+        <v>0.004401595158081975</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0050808327932813</v>
+        <v>0.005080832793281307</v>
       </c>
       <c r="T5" t="n">
-        <v>0.006802656671357147</v>
+        <v>0.006802656671357144</v>
       </c>
       <c r="U5" t="n">
-        <v>0.007833283014044328</v>
+        <v>0.007833283014044319</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003195934376731544</v>
+        <v>0.003195934376731545</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004731760311372982</v>
+        <v>0.004731760311372978</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003800385145922585</v>
+        <v>0.003800385145922579</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004257021451311287</v>
+        <v>0.004257021451311278</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.003481480694567356</v>
+        <v>0.003481480694567354</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.007147653053885667</v>
+        <v>0.007147653053885681</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.008769263119199395</v>
+        <v>0.008769263119199405</v>
       </c>
     </row>
     <row r="6">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001128483174129544</v>
+        <v>0.001128483174129543</v>
       </c>
       <c r="C6" t="n">
         <v>0.001067593748001149</v>
@@ -950,46 +950,46 @@
         <v>0.001106298084596816</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001035195271500781</v>
+        <v>0.00103519527150078</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001245707607598972</v>
+        <v>0.001245707607598974</v>
       </c>
       <c r="H6" t="n">
         <v>0.001222193322618089</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001148692679836314</v>
+        <v>0.001148692679836313</v>
       </c>
       <c r="J6" t="n">
         <v>0.001105800346195095</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001456097105376055</v>
+        <v>0.001456097105376057</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001270113924766241</v>
+        <v>0.001270113924766242</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001749263286269061</v>
+        <v>0.00174926328626906</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001195995877767603</v>
+        <v>0.0011959958777676</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001107139603506494</v>
+        <v>0.001107139603506492</v>
       </c>
       <c r="P6" t="n">
         <v>0.001206654082954372</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001162010030160701</v>
+        <v>0.0011620100301607</v>
       </c>
       <c r="R6" t="n">
         <v>0.001180045370080581</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001093788338024947</v>
+        <v>0.001093788338024946</v>
       </c>
       <c r="T6" t="n">
         <v>0.001152260601080725</v>
@@ -1007,13 +1007,13 @@
         <v>0.001158154623323813</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001051702213272638</v>
+        <v>0.001051702213272639</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001011343881676185</v>
+        <v>0.001011343881676184</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001326872831535709</v>
+        <v>0.001326872831535708</v>
       </c>
       <c r="AB6" t="n">
         <v>0.001230882190243561</v>
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001076583544714161</v>
+        <v>0.00107658354471416</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008718083762526733</v>
+        <v>0.0008718083762526727</v>
       </c>
       <c r="D7" t="n">
         <v>0.00105272151779063</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0009105127128483401</v>
+        <v>0.0009105127128483394</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0009832956420853976</v>
+        <v>0.0009832956420853974</v>
       </c>
       <c r="G7" t="n">
         <v>0.001049922235850496</v>
@@ -1047,7 +1047,7 @@
         <v>0.001026407950869612</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00109679305042093</v>
+        <v>0.001096793050420929</v>
       </c>
       <c r="J7" t="n">
         <v>0.001053900716779712</v>
@@ -1059,28 +1059,28 @@
         <v>0.001074328553017763</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001553477914520584</v>
+        <v>0.001553477914520582</v>
       </c>
       <c r="N7" t="n">
         <v>0.001143376055531815</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001054509586932446</v>
+        <v>0.001054509586932444</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001010845412755736</v>
+        <v>0.001010845412755735</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0009662246584122233</v>
+        <v>0.0009662246584122241</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0009842599983321044</v>
+        <v>0.0009842599983321033</v>
       </c>
       <c r="S7" t="n">
         <v>0.001041888708609564</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001100360971665343</v>
+        <v>0.001100360971665342</v>
       </c>
       <c r="U7" t="n">
         <v>0.001177183259289406</v>
@@ -1089,22 +1089,22 @@
         <v>0.0009447089845986376</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001013940006636984</v>
+        <v>0.001013940006636983</v>
       </c>
       <c r="X7" t="n">
-        <v>0.000962369251575336</v>
+        <v>0.0009623692515753352</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0009901736984201986</v>
+        <v>0.000990173698420198</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0009594442522608012</v>
+        <v>0.0009594442522608003</v>
       </c>
       <c r="AA7" t="n">
         <v>0.001131087459787232</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001177287601517295</v>
+        <v>0.001177287601517294</v>
       </c>
     </row>
     <row r="8">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001168753640237082</v>
+        <v>0.001168753640237081</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001125496753874912</v>
+        <v>0.001125496753874913</v>
       </c>
       <c r="D8" t="n">
         <v>0.001306409895412869</v>
@@ -1126,40 +1126,40 @@
         <v>0.001078197369748198</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001100628398252617</v>
+        <v>0.001100628398252618</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001337102481458292</v>
+        <v>0.001337102481458293</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001280096328491851</v>
+        <v>0.001280096328491852</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001350481428043169</v>
+        <v>0.001350481428043171</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001307589094401951</v>
+        <v>0.001307589094401952</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001514000111249817</v>
+        <v>0.001514000111249819</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001328016930640002</v>
+        <v>0.001328016930640003</v>
       </c>
       <c r="M8" t="n">
         <v>0.001807166292142829</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001271860743101422</v>
+        <v>0.001271860743101423</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001217411846083058</v>
+        <v>0.001217411846083057</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001165313669830712</v>
+        <v>0.00116531366983071</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001026652725033327</v>
+        <v>0.001026652725033328</v>
       </c>
       <c r="R8" t="n">
         <v>0.001237948375954343</v>
@@ -1171,13 +1171,13 @@
         <v>0.001354049349287582</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001352064042985377</v>
+        <v>0.001352064042985378</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001154188113233049</v>
+        <v>0.00115418811323305</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001267660127207995</v>
+        <v>0.001267660127207994</v>
       </c>
       <c r="X8" t="n">
         <v>0.00103760078967935</v>
@@ -1192,7 +1192,7 @@
         <v>0.00138477583740947</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001599695330711557</v>
+        <v>0.001599695330711558</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001349311679824671</v>
+        <v>0.001349311679824673</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001264772231570833</v>
+        <v>0.001264772231570836</v>
       </c>
       <c r="D9" t="n">
         <v>0.001445685373108791</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001275726599861321</v>
+        <v>0.001275726599861323</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00109908343938821</v>
+        <v>0.001099083439388211</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001442886020298375</v>
+        <v>0.001442886020298377</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001419371806187773</v>
+        <v>0.001419371806187775</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00148975690573909</v>
+        <v>0.001489756905739093</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001446864572097874</v>
+        <v>0.001446864572097875</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00165327558894574</v>
+        <v>0.001653275588945742</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001467292408335925</v>
+        <v>0.001467292408335926</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001946441769838742</v>
+        <v>0.001946441769838744</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001536339910849976</v>
+        <v>0.001536339910849979</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001487329818576247</v>
+        <v>0.001487329818576248</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001452331452002317</v>
+        <v>0.001452331452002319</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001359188442860102</v>
+        <v>0.001359188442860104</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001377223853650265</v>
+        <v>0.001377223853650266</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001434852563927725</v>
+        <v>0.001434852563927727</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001493324826983504</v>
+        <v>0.001493324826983505</v>
       </c>
       <c r="U9" t="n">
         <v>0.001570232343024137</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001476421997588035</v>
+        <v>0.001476421997588037</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001406903861955145</v>
+        <v>0.001406903861955146</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001355333106893497</v>
+        <v>0.001355333106893499</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001383137553738361</v>
+        <v>0.001383137553738362</v>
       </c>
       <c r="Z9" t="n">
         <v>0.001279916631929367</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001524051315105393</v>
+        <v>0.001524051315105395</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001570251456835456</v>
+        <v>0.001570251456835457</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007650584462983489</v>
+        <v>0.0007650584462983505</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008212677122434727</v>
+        <v>0.0008212677122434725</v>
       </c>
       <c r="D2" t="n">
         <v>0.0007665548504688234</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007657906768059998</v>
+        <v>0.0007657906768060011</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007673229060521725</v>
+        <v>0.0007673229060521733</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007676803384907469</v>
+        <v>0.000767680338490748</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007668571827509974</v>
+        <v>0.0007668571827509976</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007669109217357422</v>
+        <v>0.0007669109217357425</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007682550703562016</v>
+        <v>0.0007682550703562017</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000768562742527041</v>
+        <v>0.0007685627425270394</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007697120513130345</v>
+        <v>0.0007697120513130351</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007669609972165925</v>
+        <v>0.0007669609972165924</v>
       </c>
       <c r="N2" t="n">
-        <v>0.000767818995859806</v>
+        <v>0.0007678189958598063</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001087413970790262</v>
+        <v>0.001087413970790261</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007686473515066208</v>
+        <v>0.000768647351506621</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007662413073582054</v>
+        <v>0.0007662413073582058</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007700950348917502</v>
+        <v>0.0007700950348917506</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007688269938136304</v>
+        <v>0.0007688269938136311</v>
       </c>
       <c r="T2" t="n">
-        <v>0.000767463351796335</v>
+        <v>0.0007674633517963361</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009254643199282647</v>
+        <v>0.0009254643199282656</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007688109322927301</v>
+        <v>0.0007688109322927302</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0008983526122869447</v>
+        <v>0.0008983526122869453</v>
       </c>
       <c r="X2" t="n">
-        <v>0.000784074752639968</v>
+        <v>0.0007840747526399693</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0007758022883556357</v>
+        <v>0.0007758022883556361</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009143334867103289</v>
+        <v>0.0009143334867103303</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0007744681120121976</v>
+        <v>0.0007744681120121977</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0007654045821162589</v>
+        <v>0.0007654045821162592</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007347764242136679</v>
+        <v>0.000735502760100028</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008338671086453148</v>
+        <v>0.0008348883529252178</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007455133645951723</v>
+        <v>0.0007466251880055342</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007399560290897804</v>
+        <v>0.0007408575152715443</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000751021379690753</v>
+        <v>0.0007523328109567584</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007533808571111699</v>
+        <v>0.0007547632968566051</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000747756971437655</v>
+        <v>0.0007489510926245393</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007480888842244598</v>
+        <v>0.0007492926788306196</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007575456709422413</v>
+        <v>0.00075907952044912</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007597296962222865</v>
+        <v>0.0007613496366452267</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007678488925068512</v>
+        <v>0.000769748319828876</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0007499339097685998</v>
+        <v>0.0007512142022795119</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0007545496518240832</v>
+        <v>0.0007559780353729457</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001296948921147707</v>
+        <v>0.001299055063451302</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0007602360680386956</v>
+        <v>0.0007618572620989967</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007432348733336825</v>
+        <v>0.0007442654002772907</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007709263435973275</v>
+        <v>0.0007729436267637233</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007615243896546413</v>
+        <v>0.0007631969692557949</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000752043001517196</v>
+        <v>0.0007533861431689836</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001016351120805107</v>
+        <v>0.001017854076092355</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007614129056025501</v>
+        <v>0.0007630795029825316</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0009909551162335488</v>
+        <v>0.000993343950124397</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008703544804350431</v>
+        <v>0.0008759102986573581</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0008115606474305321</v>
+        <v>0.0008150024742575361</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0009968624407448803</v>
+        <v>0.0009983120764017401</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008020087732067392</v>
+        <v>0.0008051116178504638</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0007379377400379126</v>
+        <v>0.0007387819386989313</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0006901634536296589</v>
+        <v>0.0006901634536296592</v>
       </c>
       <c r="C4" t="n">
         <v>0.0007030702747956163</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007070660271150924</v>
+        <v>0.0007070660271150923</v>
       </c>
       <c r="E4" t="n">
         <v>0.0006984343340562443</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000715741568252052</v>
+        <v>0.0007157415682520521</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007197789320727897</v>
+        <v>0.000719778932072789</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007104810093219736</v>
+        <v>0.0007104810093219734</v>
       </c>
       <c r="I4" t="n">
         <v>0.0007110880158758155</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0007259893488443287</v>
+        <v>0.000725989348844328</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007297460915886271</v>
+        <v>0.0007297460915886268</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007427280630346043</v>
+        <v>0.0007427280630346041</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007144069414250388</v>
+        <v>0.0007144069414250387</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0007213451308418551</v>
+        <v>0.0007213451308418554</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0007525840957798045</v>
+        <v>0.0007525840957798048</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0007307017889350594</v>
+        <v>0.0007307017889350596</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0007035244134437096</v>
+        <v>0.0007035244134437098</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0007470540387373498</v>
+        <v>0.0007470540387373501</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0007327309314322647</v>
+        <v>0.000732730931432265</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007173279675405966</v>
+        <v>0.0007173279675405967</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0007210788481699773</v>
+        <v>0.0007210788481699767</v>
       </c>
       <c r="V4" t="n">
         <v>0.0007307271454059821</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0007645484056148451</v>
+        <v>0.0007645484056148454</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0009049613816913571</v>
+        <v>0.0009049613816913575</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.000807619344416172</v>
+        <v>0.0008076193444161719</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0007227861716098359</v>
+        <v>0.0007227861716098362</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0007964499565276623</v>
+        <v>0.0007964499565276629</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0006951571447678135</v>
+        <v>0.0006951571447678136</v>
       </c>
     </row>
     <row r="5">
@@ -1710,13 +1710,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009404051364150454</v>
+        <v>0.0009404051364150449</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001193187771075063</v>
+        <v>0.001193187771075065</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001268908988168555</v>
+        <v>0.001268908988168556</v>
       </c>
       <c r="E5" t="n">
         <v>0.001062664014815809</v>
@@ -1725,34 +1725,34 @@
         <v>0.001436012780400403</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001408161688885877</v>
+        <v>0.001408161688885888</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001373796240708817</v>
+        <v>0.001373796240708816</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001357778790622339</v>
+        <v>0.001357778790622338</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001555308210601824</v>
+        <v>0.001555308210601826</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001610916980552956</v>
+        <v>0.001610916980552955</v>
       </c>
       <c r="L5" t="n">
         <v>0.00179726430302051</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001412184048092071</v>
+        <v>0.00141218404809207</v>
       </c>
       <c r="N5" t="n">
         <v>0.001528723260254152</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001913352905961195</v>
+        <v>0.001913352905961194</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00157730005725097</v>
+        <v>0.001577300057250969</v>
       </c>
       <c r="Q5" t="n">
         <v>0.001185168400486493</v>
@@ -1761,34 +1761,34 @@
         <v>0.002052086134409262</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001616404641834512</v>
+        <v>0.001616404641834511</v>
       </c>
       <c r="T5" t="n">
         <v>0.001474048533742303</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001501119916484234</v>
+        <v>0.001501119916484235</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001613004806120548</v>
+        <v>0.001613004806120547</v>
       </c>
       <c r="W5" t="n">
-        <v>0.00226765050836553</v>
+        <v>0.002267650508365523</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004665733041944441</v>
+        <v>0.004665733041944446</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003141152497013654</v>
+        <v>0.003141152497013659</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00143183957056837</v>
+        <v>0.001431839570568371</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002859173773323357</v>
+        <v>0.002859173773323364</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001081589613770109</v>
+        <v>0.00108158961377011</v>
       </c>
     </row>
     <row r="6">
@@ -1801,76 +1801,76 @@
         <v>0.0008231626655111264</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009416401577255076</v>
+        <v>0.0009416401577255073</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008400652389965605</v>
+        <v>0.00084006523899656</v>
       </c>
       <c r="E6" t="n">
         <v>0.0009370042169861351</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009543114511819429</v>
+        <v>0.000954311451181943</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0008527781439542578</v>
+        <v>0.0008527781439542566</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0008434802212034412</v>
+        <v>0.0008434802212034411</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008440872277572835</v>
+        <v>0.0008440872277572829</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009645592317742196</v>
+        <v>0.0009645592317742194</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008627453034700947</v>
+        <v>0.0008627453034700944</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000981297945964495</v>
+        <v>0.0009812979459644954</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0008474061533065068</v>
+        <v>0.0008474061533065061</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0008551244634595856</v>
+        <v>0.0008551244634595851</v>
       </c>
       <c r="O6" t="n">
-        <v>0.000996490813565016</v>
+        <v>0.0009964908135650162</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0008560927120303741</v>
+        <v>0.0008560927120303739</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0008365236253251777</v>
+        <v>0.0008365236253251771</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0008800532506188176</v>
+        <v>0.0008800532506188166</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0009713008143621556</v>
+        <v>0.000971300814362155</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0008503271794220643</v>
+        <v>0.0008503271794220645</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0009635494787619405</v>
+        <v>0.0009635494787619403</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0008637263572874497</v>
+        <v>0.0008637263572874492</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0009072844729788594</v>
+        <v>0.0009072844729788549</v>
       </c>
       <c r="X6" t="n">
         <v>0.001143531264621248</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0009545634525560792</v>
+        <v>0.0009545634525560784</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0008557853834913041</v>
+        <v>0.0008557853834913036</v>
       </c>
       <c r="AA6" t="n">
         <v>0.001035019839457554</v>
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007674869591574608</v>
+        <v>0.0007674869591574604</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007803937803234177</v>
+        <v>0.0007803937803234176</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007843895326428936</v>
+        <v>0.0007843895326428935</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0007757578395840461</v>
+        <v>0.0007757578395840459</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0007930650737798538</v>
+        <v>0.0007930650737798536</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007971024376005916</v>
+        <v>0.0007971024376005911</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0007878045148497747</v>
+        <v>0.000787804514849775</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007884115214036169</v>
+        <v>0.0007884115214036168</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00080331285437213</v>
+        <v>0.0008033128543721298</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008070695971164287</v>
+        <v>0.0008070695971164286</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008200515685624059</v>
+        <v>0.0008200515685624056</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0007917304469528408</v>
+        <v>0.0007917304469528402</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0007986686363696562</v>
+        <v>0.0007986686363696564</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0008298987103891896</v>
+        <v>0.0008298987103891893</v>
       </c>
       <c r="P7" t="n">
-        <v>0.000808016403544445</v>
+        <v>0.0008080164035444452</v>
       </c>
       <c r="Q7" t="n">
         <v>0.0007808479189715112</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0008243775442651511</v>
+        <v>0.000824377544265151</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0008100544369600663</v>
+        <v>0.0008100544369600661</v>
       </c>
       <c r="T7" t="n">
         <v>0.0007946514730683984</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0008021993715243512</v>
+        <v>0.0008021993715243507</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0008080506509337838</v>
+        <v>0.0008080506509337836</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0008418719111426469</v>
+        <v>0.0008418719111426463</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0009822848872191594</v>
+        <v>0.000982284887219159</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0008888435976060457</v>
+        <v>0.0008888435976060453</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008001096771376374</v>
+        <v>0.0008001096771376376</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.000873773462055464</v>
+        <v>0.0008737734620554641</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0007724806502956153</v>
+        <v>0.000772480650295615</v>
       </c>
     </row>
     <row r="8">
@@ -1974,67 +1974,67 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008328986957533292</v>
+        <v>0.0008328986957533294</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000963936978209983</v>
+        <v>0.0009639369782099826</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009679327305294596</v>
+        <v>0.0009679327305294597</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0008963995189962133</v>
+        <v>0.0008963995189962136</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008768803114114628</v>
+        <v>0.000876880311411463</v>
       </c>
       <c r="G8" t="n">
         <v>0.001005140963539701</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009713477127363402</v>
+        <v>0.0009713477127363406</v>
       </c>
       <c r="I8" t="n">
         <v>0.0009719547192901826</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0009868560522586953</v>
+        <v>0.0009868560522586956</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0009906127950029939</v>
+        <v>0.0009906127950029945</v>
       </c>
       <c r="L8" t="n">
         <v>0.001003594766448971</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0009752736448394027</v>
+        <v>0.0009752736448394024</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0008906401887892271</v>
+        <v>0.0008906401887892274</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0009470438369976222</v>
+        <v>0.0009470438369976221</v>
       </c>
       <c r="P8" t="n">
-        <v>0.000918993058220039</v>
+        <v>0.0009189930582200394</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0008230441272083769</v>
+        <v>0.000823044127208377</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001007920742151716</v>
+        <v>0.001007920742151717</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0009935976348466316</v>
+        <v>0.0009935976348466322</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0009781946709549634</v>
+        <v>0.0009781946709549632</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0009281144118322987</v>
+        <v>0.000928114411832299</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0009592256732760679</v>
+        <v>0.0009592256732760682</v>
       </c>
       <c r="W8" t="n">
         <v>0.001025438325232023</v>
@@ -2043,16 +2043,16 @@
         <v>0.001035308078605498</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001189716485196691</v>
+        <v>0.001189716485196692</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0008633270611922881</v>
+        <v>0.0008633270611922885</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001057316659942029</v>
+        <v>0.00105731665994203</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.00107942203747952</v>
+        <v>0.001079422037479521</v>
       </c>
     </row>
     <row r="9">
@@ -2062,70 +2062,70 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0008819411225126994</v>
+        <v>0.0008819411225126997</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000959827971221612</v>
+        <v>0.0009598279712216119</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0009638237235410883</v>
+        <v>0.0009638237235410884</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0009401949384832086</v>
+        <v>0.0009401949384832079</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0008227025099361584</v>
+        <v>0.0008227025099361585</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0009765366718023501</v>
+        <v>0.0009765366718023495</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0009672387057479692</v>
+        <v>0.0009672387057479688</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009678457123018108</v>
+        <v>0.0009678457123018112</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0009827470452703246</v>
+        <v>0.0009827470452703239</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009865037880146231</v>
+        <v>0.0009865037880146229</v>
       </c>
       <c r="L9" t="n">
         <v>0.0009994857594606006</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0009711646378510346</v>
+        <v>0.0009711646378510351</v>
       </c>
       <c r="N9" t="n">
-        <v>0.000978102827267851</v>
+        <v>0.0009781028272678508</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001030876145904243</v>
+        <v>0.001030876145904242</v>
       </c>
       <c r="P9" t="n">
         <v>0.00101367718210343</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0009602821531732706</v>
+        <v>0.0009602821531732694</v>
       </c>
       <c r="R9" t="n">
         <v>0.001003811735163345</v>
       </c>
       <c r="S9" t="n">
-        <v>0.000989488627858261</v>
+        <v>0.0009894886278582606</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0009740856639665934</v>
+        <v>0.0009740856639665932</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0009817372922580453</v>
+        <v>0.0009817372922580456</v>
       </c>
       <c r="V9" t="n">
         <v>0.001062470441843618</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001021306102040842</v>
+        <v>0.001021306102040841</v>
       </c>
       <c r="X9" t="n">
         <v>0.001161719078117353</v>
@@ -2134,13 +2134,13 @@
         <v>0.00106827778850424</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0009403667068723121</v>
+        <v>0.0009403667068723119</v>
       </c>
       <c r="AA9" t="n">
         <v>0.001053207652953659</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0009519148411938097</v>
+        <v>0.00095191484119381</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008057907707960663</v>
+        <v>0.0008057907707960665</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008656370131322835</v>
+        <v>0.0008656370131322807</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008041607062938205</v>
+        <v>0.0008041607062938196</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007950121825471834</v>
+        <v>0.0007950121825471822</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007963040480856688</v>
+        <v>0.0007963040480856683</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008069216457222745</v>
+        <v>0.0008069216457222738</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007959424899458532</v>
+        <v>0.0007959424899458524</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008021198779022387</v>
+        <v>0.000802119877902238</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008074092382069745</v>
+        <v>0.0008074092382069735</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008207618758797303</v>
+        <v>0.0008207618758797308</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008075761518959716</v>
+        <v>0.0008075761518959727</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008473499417133621</v>
+        <v>0.0008473499417133625</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008072560262788536</v>
+        <v>0.0008072560262788527</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001134441277833101</v>
+        <v>0.001134441277833102</v>
       </c>
       <c r="P2" t="n">
         <v>0.0008063146938162799</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007975292341677641</v>
+        <v>0.0007975292341677648</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007963507486798182</v>
+        <v>0.0007963507486798173</v>
       </c>
       <c r="S2" t="n">
-        <v>0.000806583765240706</v>
+        <v>0.0008065837652407063</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008052894894385608</v>
+        <v>0.0008052894894385599</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001028243291928681</v>
+        <v>0.001028243291928682</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007946068651049403</v>
+        <v>0.0007946068651049402</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009831643668940502</v>
+        <v>0.0009831643668940506</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008024325156202316</v>
+        <v>0.0008024325156202308</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008012092317101756</v>
+        <v>0.0008012092317101748</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.000946433638248025</v>
+        <v>0.0009464336382480256</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008088421522836063</v>
+        <v>0.0008088421522836057</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008181016318124905</v>
+        <v>0.0008181016318124944</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008746072332747473</v>
+        <v>0.0008795649211714319</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009014758789010772</v>
+        <v>0.0009031449064900383</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000863885630155394</v>
+        <v>0.000868501636566818</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007981556225865665</v>
+        <v>0.0008004185885922731</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008076649997656215</v>
+        <v>0.0008102970859054323</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008828172411817935</v>
+        <v>0.000888060404654515</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008052019991815868</v>
+        <v>0.0008077459520852917</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008493492233467347</v>
+        <v>0.0008534540332745317</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0008866594243724935</v>
+        <v>0.0008920634128114449</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009817395657193287</v>
+        <v>0.000990559227540826</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008878668872470187</v>
+        <v>0.000893302953187096</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001171676834204575</v>
+        <v>0.001187253687248487</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008857973863358574</v>
+        <v>0.0008911780858503719</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001404430273234074</v>
+        <v>0.001408809037900622</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008784579812104275</v>
+        <v>0.0008835372872098748</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008163038846212</v>
+        <v>0.0008192292913347516</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008080727749934607</v>
+        <v>0.0008107146042352679</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008804358853104214</v>
+        <v>0.0008856067602830352</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008719590130334062</v>
+        <v>0.0008768645603935506</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00128564329985857</v>
+        <v>0.001292620871397599</v>
       </c>
       <c r="V3" t="n">
-        <v>0.000795109202866113</v>
+        <v>0.000797273480108328</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001181797993096367</v>
+        <v>0.001187427280117722</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008514045102447217</v>
+        <v>0.0008555779727788552</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0008424407850902684</v>
+        <v>0.0008462863990786351</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001061236420684762</v>
+        <v>0.001064106323852458</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.000896965231801249</v>
+        <v>0.0009027332938415931</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0009632895314960515</v>
+        <v>0.000971407239028599</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0009014165314722461</v>
+        <v>0.0009014165314722453</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007519880201678792</v>
+        <v>0.000751988020167879</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0008830042030526609</v>
+        <v>0.0008830042030526607</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007796674188055434</v>
+        <v>0.000779667418805543</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007942596343502485</v>
+        <v>0.0007942596343502482</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0009141902839919393</v>
+        <v>0.000914190283991939</v>
       </c>
       <c r="H4" t="n">
         <v>0.0007901756688360688</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008599521075423012</v>
+        <v>0.0008599521075423009</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0009193418459304923</v>
+        <v>0.0009193418459304932</v>
       </c>
       <c r="K4" t="n">
         <v>0.00107052205044083</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000921583232311562</v>
+        <v>0.0009215832323115667</v>
       </c>
       <c r="M4" t="n">
         <v>0.001367982197506244</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0009179672662011485</v>
+        <v>0.0009179672662011477</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0008754612560552371</v>
+        <v>0.0008754612560552362</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0009073344830020478</v>
+        <v>0.0009073344830020476</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0008080986747609614</v>
+        <v>0.0008080986747609618</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0007947871390444934</v>
+        <v>0.0007947871390444932</v>
       </c>
       <c r="S4" t="n">
-        <v>0.000910373768519912</v>
+        <v>0.0009103737685199107</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0008957543279384129</v>
+        <v>0.000895754327938413</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0009825721426824142</v>
+        <v>0.0009825721426824131</v>
       </c>
       <c r="V4" t="n">
         <v>0.0007727657718363983</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0009298613651753004</v>
+        <v>0.0009298613651752996</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0008634834943874856</v>
+        <v>0.0008634834943874873</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0008411538083304245</v>
+        <v>0.0008411538083304238</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0008069700757341369</v>
+        <v>0.0008069700757341367</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0009358832890788428</v>
+        <v>0.0009358832890788431</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001038684642151711</v>
+        <v>0.00103868464215171</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004332495929653419</v>
+        <v>0.004332495929653517</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001843038223319835</v>
+        <v>0.001843038223319833</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004491706436884286</v>
+        <v>0.004491706436884273</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002295043065080724</v>
+        <v>0.002295043065080746</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002731828571224883</v>
+        <v>0.002731828571224884</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004651268803230905</v>
+        <v>0.0046512688032309</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002719933808068376</v>
+        <v>0.002719933808068374</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00407201650657509</v>
+        <v>0.004072016506575099</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004956494248493192</v>
+        <v>0.004956494248493205</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007687211864792332</v>
+        <v>0.007687211864792328</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005001503575174108</v>
+        <v>0.005001503575174248</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01427545077610604</v>
+        <v>0.01427545077610602</v>
       </c>
       <c r="N5" t="n">
-        <v>0.005052845882567774</v>
+        <v>0.005052845882567772</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003803951754101938</v>
+        <v>0.003803951754101926</v>
       </c>
       <c r="P5" t="n">
         <v>0.004506393636914401</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002934916703817223</v>
+        <v>0.002934916703817229</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002783219660079233</v>
+        <v>0.002783219660079232</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004595854445136513</v>
+        <v>0.004595854445136485</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004742351123484614</v>
+        <v>0.004742351123484609</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00619152424486619</v>
+        <v>0.006191524244866181</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002120702411608034</v>
+        <v>0.002120702411608035</v>
       </c>
       <c r="W5" t="n">
-        <v>0.005196847546406014</v>
+        <v>0.005196847546406017</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00404089144284119</v>
+        <v>0.004040891442841209</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003649998634552733</v>
+        <v>0.003649998634552732</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002739353623832802</v>
+        <v>0.00273935362383284</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.005306834441317683</v>
+        <v>0.005306834441317692</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.007923973051566301</v>
+        <v>0.007923973051566285</v>
       </c>
     </row>
     <row r="6">
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001043913351185722</v>
+        <v>0.001043913351185723</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001022090686161391</v>
+        <v>0.00102209068616139</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001025501022766138</v>
+        <v>0.001025501022766137</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001049770084799055</v>
+        <v>0.001049770084799056</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009367564540637255</v>
+        <v>0.0009367564540637251</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001184292949985451</v>
+        <v>0.001184292949985449</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001060278334829581</v>
+        <v>0.00106027833482958</v>
       </c>
       <c r="I6" t="n">
         <v>0.001130054773535813</v>
@@ -2691,34 +2691,34 @@
         <v>0.001191685898305073</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001638084863499756</v>
+        <v>0.001638084863499754</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001061050841017942</v>
+        <v>0.001061050841017939</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001018279645080973</v>
+        <v>0.001018279645080962</v>
       </c>
       <c r="P6" t="n">
         <v>0.001179129868130295</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0009505954944744382</v>
+        <v>0.0009505954944744393</v>
       </c>
       <c r="R6" t="n">
         <v>0.001064889805038005</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001052870588233389</v>
+        <v>0.001052870588233388</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001038251147651889</v>
+        <v>0.00103825114765189</v>
       </c>
       <c r="U6" t="n">
         <v>0.001133581093950467</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0009152625915498749</v>
+        <v>0.000915262591549875</v>
       </c>
       <c r="W6" t="n">
         <v>0.001083076021583813</v>
@@ -2727,10 +2727,10 @@
         <v>0.001133586160380997</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001000492817622989</v>
+        <v>0.001000492817622982</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.000949466895447614</v>
+        <v>0.0009494668954476139</v>
       </c>
       <c r="AA6" t="n">
         <v>0.001205985955072354</v>
@@ -2746,19 +2746,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0009961771322350831</v>
+        <v>0.0009961771322350829</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008467486209307168</v>
+        <v>0.0008467486209307165</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0009777648038154986</v>
+        <v>0.0009777648038154978</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008744280195683807</v>
+        <v>0.0008744280195683818</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008890202351130864</v>
+        <v>0.000889020235113086</v>
       </c>
       <c r="G7" t="n">
         <v>0.001008950884754776</v>
@@ -2767,7 +2767,7 @@
         <v>0.0008849362695989067</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0009547127083051384</v>
+        <v>0.0009547127083051383</v>
       </c>
       <c r="J7" t="n">
         <v>0.001014102446693331</v>
@@ -2776,46 +2776,46 @@
         <v>0.001165282651203668</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001016343833074401</v>
+        <v>0.001016343833074396</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001462742798269081</v>
+        <v>0.00146274279826908</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001012727866963986</v>
+        <v>0.001012727866963985</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0009702123156648035</v>
+        <v>0.0009702123156648019</v>
       </c>
       <c r="P7" t="n">
         <v>0.001002085542611614</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0009028592755237993</v>
+        <v>0.0009028592755237989</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0008895477398073308</v>
+        <v>0.0008895477398073307</v>
       </c>
       <c r="S7" t="n">
         <v>0.00100513436928275</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0009905149287012509</v>
+        <v>0.0009905149287012496</v>
       </c>
       <c r="U7" t="n">
         <v>0.001085739614046274</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0008675263725992357</v>
+        <v>0.0008675263725992366</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001024621965938138</v>
+        <v>0.001024621965938137</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0009582440951503238</v>
+        <v>0.0009582440951503249</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0009444265406478368</v>
+        <v>0.0009444265406478363</v>
       </c>
       <c r="Z7" t="n">
         <v>0.0009017306764969748</v>
@@ -2834,22 +2834,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001077912226391529</v>
+        <v>0.00107791222639153</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00107249847009624</v>
+        <v>0.001072498470096241</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001203514652981022</v>
+        <v>0.001203514652981021</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001023494259865059</v>
+        <v>0.00102349425986506</v>
       </c>
       <c r="F8" t="n">
         <v>0.0009931911449614051</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001264563131538982</v>
+        <v>0.001264563131538983</v>
       </c>
       <c r="H8" t="n">
         <v>0.00111068611876443</v>
@@ -2858,16 +2858,16 @@
         <v>0.001180462557470663</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001239852295858854</v>
+        <v>0.001239852295858855</v>
       </c>
       <c r="K8" t="n">
         <v>0.001391032500369191</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001242093682239921</v>
+        <v>0.001242093682239924</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001688492647434625</v>
+        <v>0.001688492647434626</v>
       </c>
       <c r="N8" t="n">
         <v>0.001126842187848515</v>
@@ -2879,10 +2879,10 @@
         <v>0.001139367796934584</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0009562921833498048</v>
+        <v>0.0009562921833498053</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001115297588972855</v>
+        <v>0.001115297588972854</v>
       </c>
       <c r="S8" t="n">
         <v>0.001230884218448274</v>
@@ -2894,19 +2894,19 @@
         <v>0.001241228863881317</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001053832998813744</v>
+        <v>0.001053832998813745</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001250400118109297</v>
+        <v>0.001250400118109298</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001024876241422289</v>
+        <v>0.00102487624142229</v>
       </c>
       <c r="Y8" t="n">
         <v>0.001313240081480577</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0009807906226433497</v>
+        <v>0.0009807906226433501</v>
       </c>
       <c r="AA8" t="n">
         <v>0.001256393739007203</v>
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001200702825573834</v>
+        <v>0.001200702825573836</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001147915674071765</v>
+        <v>0.001147915674071766</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001278931856956546</v>
+        <v>0.001278931856956547</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00115329059351618</v>
+        <v>0.001153290593516183</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009674026586575499</v>
+        <v>0.0009674026586575502</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001310117876086873</v>
+        <v>0.001310117876086874</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001186103322739955</v>
+        <v>0.001186103322739957</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001255879761446186</v>
+        <v>0.001255879761446189</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001315269499834378</v>
+        <v>0.00131526949983438</v>
       </c>
       <c r="K9" t="n">
         <v>0.001466449704344716</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001317510886215447</v>
+        <v>0.001317510886215449</v>
       </c>
       <c r="M9" t="n">
         <v>0.001763909851410129</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001313894920105034</v>
+        <v>0.001313894920105035</v>
       </c>
       <c r="O9" t="n">
         <v>0.001303415647764703</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001342254154139895</v>
+        <v>0.001342254154139896</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001204026266855895</v>
+        <v>0.001204026266855896</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001190714792948379</v>
+        <v>0.00119071479294838</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001306301422423797</v>
+        <v>0.0013063014224238</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001291681981842298</v>
+        <v>0.0012916819818423</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001387011928140874</v>
+        <v>0.001387011928140876</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001280215233224876</v>
+        <v>0.001280215233224877</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001325789019079185</v>
+        <v>0.001325789019079186</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001259411148291372</v>
+        <v>0.001259411148291375</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001245593593788886</v>
+        <v>0.001245593593788887</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.00114463155881862</v>
+        <v>0.001144631558818622</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001331810942982729</v>
+        <v>0.00133181094298273</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001434612296055595</v>
+        <v>0.001434612296055596</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008004687498591041</v>
+        <v>0.0008004687498591019</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008640106301237237</v>
+        <v>0.0008640106301237235</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008060005435880585</v>
+        <v>0.0008060005435880564</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007943203780878646</v>
+        <v>0.0007943203780878632</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007942341669401854</v>
+        <v>0.0007942341669401835</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008045239112090647</v>
+        <v>0.0008045239112090634</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000791746733640775</v>
+        <v>0.0007917467336407731</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008047474005992339</v>
+        <v>0.0008047474005992315</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008050922101674498</v>
+        <v>0.0008050922101674474</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000808865222030813</v>
+        <v>0.0008088652220308104</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008026827152213994</v>
+        <v>0.0008026827152213981</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008381420285662731</v>
+        <v>0.0008381420285662729</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007991253945465109</v>
+        <v>0.0007991253945465088</v>
       </c>
       <c r="O2" t="n">
         <v>0.001125629223877228</v>
       </c>
       <c r="P2" t="n">
-        <v>0.000804272011783878</v>
+        <v>0.0008042720117838759</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007945487120139375</v>
+        <v>0.0007945487120139351</v>
       </c>
       <c r="R2" t="n">
-        <v>0.000791850793182774</v>
+        <v>0.0007918507931827716</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008037109833035931</v>
+        <v>0.0008037109833035905</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008013105340732162</v>
+        <v>0.0008013105340732138</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00102126148023204</v>
+        <v>0.001021261480232038</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007950616132825866</v>
+        <v>0.0007950616132825846</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009812629823697599</v>
+        <v>0.0009812629823697592</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008051776311347237</v>
+        <v>0.0008051776311347215</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008087560481257251</v>
+        <v>0.0008087560481257226</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009448276405024519</v>
+        <v>0.0009448276405024504</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008078374485131043</v>
+        <v>0.0008078374485131026</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008145753898936471</v>
+        <v>0.0008145753898936469</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008444979011382033</v>
+        <v>0.0008484484179083852</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008953426675668774</v>
+        <v>0.0008968270062930664</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008846773740586562</v>
+        <v>0.0008900886506699309</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008008938815698988</v>
+        <v>0.0008033082501763928</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000800497301850859</v>
+        <v>0.0008029307124530497</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008733008303650766</v>
+        <v>0.0008782678026517432</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007828219808720501</v>
+        <v>0.0007846233216364795</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008758414821023202</v>
+        <v>0.0008809433957856862</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0008777691280386047</v>
+        <v>0.0008829182451874926</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009042370579507399</v>
+        <v>0.00091036761980103</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008605864361737219</v>
+        <v>0.0008651166136240171</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00111396529129052</v>
+        <v>0.001127544735370631</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008353819272216895</v>
+        <v>0.0008390334535043182</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001370075339688328</v>
+        <v>0.001373521010883106</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00087149311479393</v>
+        <v>0.0008763856021247134</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008026201427923693</v>
+        <v>0.0008051179151747157</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000783517626167495</v>
+        <v>0.0007853414649751011</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008675820528387808</v>
+        <v>0.0008723568158933307</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008511830515735546</v>
+        <v>0.0008554058002231456</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001231918707046534</v>
+        <v>0.001236936494629655</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008059210147954429</v>
+        <v>0.0008085231670953755</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001163779896523052</v>
+        <v>0.001168699385880438</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008786835838161336</v>
+        <v>0.0008838812453735876</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009039710268503959</v>
+        <v>0.0009100480141615032</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001058246154063977</v>
+        <v>0.001061082827257235</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008974843086505093</v>
+        <v>0.000903325015310772</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0009458822501397505</v>
+        <v>0.0009534383544470025</v>
       </c>
     </row>
     <row r="4">
@@ -3342,82 +3342,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0008514784753459014</v>
+        <v>0.0008514784753459018</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007393457359805906</v>
+        <v>0.0007393457359805907</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009139626302652882</v>
+        <v>0.0009139626302652888</v>
       </c>
       <c r="E4" t="n">
         <v>0.0007820297877990041</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007810559932268819</v>
+        <v>0.0007810559932268817</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008972833882601015</v>
+        <v>0.0008972833882601019</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007529592898341955</v>
+        <v>0.0007529592898341956</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008998078037322533</v>
+        <v>0.0008998078037322535</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0009033781034253472</v>
+        <v>0.000903378103425347</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0009463204910933909</v>
+        <v>0.0009463204910933908</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008764862325874155</v>
+        <v>0.0008764862325874177</v>
       </c>
       <c r="M4" t="n">
         <v>0.001275061561868026</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0008363046591161951</v>
+        <v>0.0008363046591161948</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0008288224129200219</v>
+        <v>0.0008288224129200216</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0008944380683731531</v>
+        <v>0.0008944380683731526</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0007846089245327949</v>
+        <v>0.0007846089245327951</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0007541346902308185</v>
+        <v>0.0007541346902308188</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0008881009936024771</v>
+        <v>0.000888100993602478</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0008609868152841761</v>
+        <v>0.0008609868152841763</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0008926790367060069</v>
+        <v>0.0008926790367060068</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007882891370468896</v>
+        <v>0.0007882891370468892</v>
       </c>
       <c r="W4" t="n">
         <v>0.0008936229977800759</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0009046674555464384</v>
+        <v>0.0009046674555464391</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0009391812966677548</v>
+        <v>0.0009391812966677551</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0008010349145888157</v>
+        <v>0.0008010349145888168</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.000934711316411695</v>
+        <v>0.0009347113164116953</v>
       </c>
       <c r="AB4" t="n">
         <v>0.001009293911535004</v>
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003373222576292227</v>
+        <v>0.003373222576292234</v>
       </c>
       <c r="C5" t="n">
         <v>0.001578367514230627</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004840485753270224</v>
+        <v>0.004840485753270229</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002288568250573522</v>
+        <v>0.002288568250573519</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00238468784036379</v>
+        <v>0.002384687840363788</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004111345810637581</v>
+        <v>0.00411134581063756</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001927973017827195</v>
+        <v>0.001927973017827191</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004646025870435585</v>
+        <v>0.004646025870435588</v>
       </c>
       <c r="J5" t="n">
         <v>0.004438229671371525</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004953812403273678</v>
+        <v>0.00495381240327368</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003964439898133718</v>
+        <v>0.003964439898133731</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01172157736976081</v>
+        <v>0.01172157736976082</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003349253677773539</v>
+        <v>0.00334925367777354</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002892148104115769</v>
+        <v>0.002892148104115763</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00405589285905102</v>
+        <v>0.004055892859051017</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002384260905949062</v>
+        <v>0.00238426090594906</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001924388333299947</v>
+        <v>0.001924388333299946</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003992019747174327</v>
+        <v>0.003992019747174323</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003892384000165507</v>
+        <v>0.003892384000165511</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004253563653242803</v>
+        <v>0.004253563653242769</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002298193566690533</v>
+        <v>0.002298193566690526</v>
       </c>
       <c r="W5" t="n">
-        <v>0.00431441271612146</v>
+        <v>0.004314412716121467</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004613575414438181</v>
+        <v>0.004613575414438163</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.005197927983704445</v>
+        <v>0.005197927983704454</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00245960931945735</v>
+        <v>0.00245960931945736</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.005050362025761126</v>
+        <v>0.005050362025761129</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.006959104557866155</v>
+        <v>0.006959104557866158</v>
       </c>
     </row>
     <row r="6">
@@ -3521,7 +3521,7 @@
         <v>0.001106834936629319</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000876121825695276</v>
+        <v>0.0008761218256952761</v>
       </c>
       <c r="D6" t="n">
         <v>0.001169319091548706</v>
@@ -3536,7 +3536,7 @@
         <v>0.001034059477974787</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0008897353795488815</v>
+        <v>0.0008897353795488816</v>
       </c>
       <c r="I6" t="n">
         <v>0.001036583893446939</v>
@@ -3554,7 +3554,7 @@
         <v>0.00141183765158271</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0009737745876848058</v>
+        <v>0.0009737745876848045</v>
       </c>
       <c r="O6" t="n">
         <v>0.001085141729455608</v>
@@ -3563,19 +3563,19 @@
         <v>0.001150896589956943</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001039965385816212</v>
+        <v>0.001039965385816213</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0008909107799455045</v>
+        <v>0.0008909107799455047</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001143457454885895</v>
+        <v>0.001143457454885896</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0009977629049988624</v>
+        <v>0.0009977629049988629</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001035361151365888</v>
+        <v>0.001035361151365887</v>
       </c>
       <c r="V6" t="n">
         <v>0.001043645598330307</v>
@@ -3587,16 +3587,16 @@
         <v>0.001041443545261126</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.00108994241798382</v>
+        <v>0.001089942417983817</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001056391375872233</v>
+        <v>0.001056391375872234</v>
       </c>
       <c r="AA6" t="n">
         <v>0.001190067777695112</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00114666292528916</v>
+        <v>0.001146662925289161</v>
       </c>
     </row>
     <row r="7">
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0009387280030141764</v>
+        <v>0.0009387280030141771</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008265952636488658</v>
+        <v>0.000826595263648866</v>
       </c>
       <c r="D7" t="n">
         <v>0.001001212157933564</v>
@@ -3618,73 +3618,73 @@
         <v>0.0008692793154672798</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008683055208951578</v>
+        <v>0.0008683055208951582</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009845329159283774</v>
+        <v>0.0009845329159283778</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008402088175024713</v>
+        <v>0.0008402088175024714</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0009870573314005287</v>
+        <v>0.0009870573314005294</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0009906276310936229</v>
+        <v>0.0009906276310936235</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001033570018761666</v>
+        <v>0.001033570018761667</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000963735760255693</v>
+        <v>0.0009637357602556935</v>
       </c>
       <c r="M7" t="n">
         <v>0.001362311089536301</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0009235541867844702</v>
+        <v>0.0009235541867844709</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0009160629786148718</v>
+        <v>0.0009160629786148719</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0009816786340680025</v>
+        <v>0.0009816786340680027</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0008718584522010701</v>
+        <v>0.0008718584522010707</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0008413842178990942</v>
+        <v>0.000841384217899095</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0009753505212707526</v>
+        <v>0.0009753505212707532</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0009482363429524521</v>
+        <v>0.000948236342952452</v>
       </c>
       <c r="U7" t="n">
-        <v>0.000985713279673071</v>
+        <v>0.000985713279673069</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0008755386647151649</v>
+        <v>0.0008755386647151648</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0009808725254483511</v>
+        <v>0.0009808725254483515</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0009919169832147145</v>
+        <v>0.0009919169832147147</v>
       </c>
       <c r="Y7" t="n">
         <v>0.001032336849281223</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008882844422570907</v>
+        <v>0.0008882844422570919</v>
       </c>
       <c r="AA7" t="n">
         <v>0.001021960844079969</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001096543439203279</v>
+        <v>0.00109654343920328</v>
       </c>
     </row>
     <row r="8">
@@ -3697,7 +3697,7 @@
         <v>0.001013506123944892</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001033761045458337</v>
+        <v>0.001033761045458338</v>
       </c>
       <c r="D8" t="n">
         <v>0.001208377939743036</v>
@@ -3706,10 +3706,10 @@
         <v>0.001005952573054365</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009637080921411146</v>
+        <v>0.0009637080921411145</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00121915014164517</v>
+        <v>0.001219150141645169</v>
       </c>
       <c r="H8" t="n">
         <v>0.001047374599311943</v>
@@ -3736,10 +3736,10 @@
         <v>0.001048816714687392</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001107519482063211</v>
+        <v>0.001107519482063212</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0009206193761732863</v>
+        <v>0.0009206193761732869</v>
       </c>
       <c r="R8" t="n">
         <v>0.001048549999708565</v>
@@ -3754,25 +3754,25 @@
         <v>0.001128296654112188</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001046424870621364</v>
+        <v>0.001046424870621362</v>
       </c>
       <c r="W8" t="n">
         <v>0.001188064325207169</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001052811499352949</v>
+        <v>0.001052811499352948</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001370983723186771</v>
+        <v>0.001370983723186772</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0009606033944205656</v>
+        <v>0.0009606033944205662</v>
       </c>
       <c r="AA8" t="n">
         <v>0.001229126625889442</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001441999202859036</v>
+        <v>0.001441999202859037</v>
       </c>
     </row>
     <row r="9">
@@ -3791,16 +3791,16 @@
         <v>0.001249759953453551</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001098720725640613</v>
+        <v>0.001098720725640614</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009260122259905827</v>
+        <v>0.0009260122259905831</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001233080669217085</v>
+        <v>0.001233080669217084</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001088756613022455</v>
+        <v>0.001088756613022456</v>
       </c>
       <c r="I9" t="n">
         <v>0.001235605126920514</v>
@@ -3809,52 +3809,52 @@
         <v>0.001239175426613608</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001282117814281652</v>
+        <v>0.001282117814281651</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001212283555775677</v>
+        <v>0.001212283555775678</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001610858885056285</v>
+        <v>0.001610858885056286</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001172101982304456</v>
+        <v>0.001172101982304455</v>
       </c>
       <c r="O9" t="n">
         <v>0.001192054394895201</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001263636627119182</v>
+        <v>0.001263636627119183</v>
       </c>
       <c r="Q9" t="n">
         <v>0.001120406205489779</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001089932013419079</v>
+        <v>0.00108993201341908</v>
       </c>
       <c r="S9" t="n">
         <v>0.001223898316790739</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001196784138472438</v>
+        <v>0.001196784138472439</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001234382384839464</v>
+        <v>0.001234382384839462</v>
       </c>
       <c r="V9" t="n">
         <v>0.001219617946891271</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001229420320968337</v>
+        <v>0.001229420320968338</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0012404647787347</v>
+        <v>0.001240464778734701</v>
       </c>
       <c r="Y9" t="n">
         <v>0.001280884644801208</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001086920456020393</v>
+        <v>0.001086920456020395</v>
       </c>
       <c r="AA9" t="n">
         <v>0.001270508639599957</v>
@@ -4029,82 +4029,82 @@
         <v>0.0007972491356901023</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008432161886572426</v>
+        <v>0.0008432161886572423</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007981259234094088</v>
+        <v>0.0007981259234094082</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007905730027217767</v>
+        <v>0.0007905730027217763</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007942311870596249</v>
+        <v>0.0007942311870596243</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008014558018470822</v>
+        <v>0.0008014558018470816</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007903077235060553</v>
+        <v>0.0007903077235060544</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008025144827506997</v>
+        <v>0.0008025144827506991</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008025095463859873</v>
+        <v>0.000802509546385987</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008115484896244435</v>
+        <v>0.000811548489624443</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007995951540115169</v>
+        <v>0.0007995951540115166</v>
       </c>
       <c r="M2" t="n">
         <v>0.0008281535549851663</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007935079729782571</v>
+        <v>0.0007935079729782568</v>
       </c>
       <c r="O2" t="n">
         <v>0.00112309387825552</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008009873753106408</v>
+        <v>0.0008009873753106402</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007931966548965064</v>
+        <v>0.0007931966548965061</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007932427060582166</v>
+        <v>0.0007932427060582167</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008013697205406095</v>
+        <v>0.0008013697205406089</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008009378974776322</v>
+        <v>0.0008009378974776321</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009637363424428453</v>
+        <v>0.0009637363424428451</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007975940654676445</v>
+        <v>0.0007975940654676444</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009260975891576062</v>
+        <v>0.0009260975891576052</v>
       </c>
       <c r="X2" t="n">
-        <v>0.000805600944859779</v>
+        <v>0.0008056009448597788</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008180446651570173</v>
+        <v>0.0008180446651570172</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009418531454546636</v>
+        <v>0.0009418531454546633</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008083632211245515</v>
+        <v>0.0008083632211245509</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008110812524751425</v>
+        <v>0.0008110812524751423</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008299072153004554</v>
+        <v>0.0008333682523211424</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008602356457646451</v>
+        <v>0.000861613138743769</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008366300583962322</v>
+        <v>0.0008403618227973137</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000782524129835688</v>
+        <v>0.0007843129836621449</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008089288602524756</v>
+        <v>0.0008116831478390809</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008597404597718038</v>
+        <v>0.0008642555711397705</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007810100146867029</v>
+        <v>0.0007827656605633106</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008682226736091289</v>
+        <v>0.0008730772235875805</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0008676500844120515</v>
+        <v>0.0008724691883753462</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009317544293651633</v>
+        <v>0.0009388851426242315</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008468285702023027</v>
+        <v>0.0008508992855220178</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001050658814268764</v>
+        <v>0.001062032575728649</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008037185648740301</v>
+        <v>0.0008062685073623932</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001365380177701481</v>
+        <v>0.001368731403011378</v>
       </c>
       <c r="P3" t="n">
-        <v>0.000856393463107675</v>
+        <v>0.0008607812482870042</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008013628332750485</v>
+        <v>0.0008038375302834565</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008019982927585281</v>
+        <v>0.0008044983416919013</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008592872236451228</v>
+        <v>0.000863791225509848</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008570123541995505</v>
+        <v>0.0008614607655396426</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00113878863402149</v>
+        <v>0.001143829637467483</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008322541372855156</v>
+        <v>0.0008358065453479243</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001038036086545643</v>
+        <v>0.001041291763030706</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008899479063787276</v>
+        <v>0.0008955728282683712</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009789594229103363</v>
+        <v>0.0009876995435463584</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001047653852085391</v>
+        <v>0.001050164364226604</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.000909753553180332</v>
+        <v>0.0009160450057562372</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.000929188170247446</v>
+        <v>0.0009361782692046615</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0008309015354437362</v>
+        <v>0.0008309015354437358</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007361357766238414</v>
+        <v>0.0007361357766238408</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0008408052560755766</v>
+        <v>0.0008408052560755754</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007554915423935971</v>
+        <v>0.0007554915423935969</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007968124173375264</v>
+        <v>0.0007968124173375256</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008784177648488602</v>
+        <v>0.0008784177648488595</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007524950916175531</v>
+        <v>0.0007524950916175527</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008903760526724889</v>
+        <v>0.0008903760526724882</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0008900226264824234</v>
+        <v>0.0008900226264824229</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0009924193161599153</v>
+        <v>0.0009924193161599151</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008574008916058561</v>
+        <v>0.0008574008916058557</v>
       </c>
       <c r="M4" t="n">
         <v>0.00117887500751124</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0007886433815935679</v>
+        <v>0.0007886433815935683</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0008260863547127137</v>
+        <v>0.0008260863547127133</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0008731266716328977</v>
+        <v>0.0008731266716328973</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0007851269006467937</v>
+        <v>0.0007851269006467935</v>
       </c>
       <c r="R4" t="n">
-        <v>0.000785647069702897</v>
+        <v>0.0007856470697028971</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0008774454368928981</v>
+        <v>0.0008774454368928974</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0008725677967481454</v>
+        <v>0.0008725677967481452</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0008969073312390033</v>
+        <v>0.0008969073312390024</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0008328672792734335</v>
+        <v>0.0008328672792734332</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0008205961873782497</v>
+        <v>0.0008205961873782502</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0009252390620372677</v>
+        <v>0.0009252390620372673</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001061534915952156</v>
+        <v>0.001061534915952155</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0007878534657309174</v>
+        <v>0.0007878534657309173</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0009564402431577247</v>
+        <v>0.0009564402431577241</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0009856724490182238</v>
+        <v>0.0009856724490182229</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002930325022197382</v>
+        <v>0.002930325022197383</v>
       </c>
       <c r="C5" t="n">
         <v>0.00147921794460476</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003346548870957757</v>
+        <v>0.003346548870957756</v>
       </c>
       <c r="E5" t="n">
         <v>0.001733805079860409</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002618072232862637</v>
+        <v>0.002618072232862641</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003672295521924239</v>
+        <v>0.003672295521924235</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001877316544522416</v>
+        <v>0.001877316544522418</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004363857829993273</v>
+        <v>0.004363857829993272</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004084101744440119</v>
+        <v>0.004084101744440121</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005679249080922448</v>
+        <v>0.005679249080922435</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003491101077298482</v>
+        <v>0.003491101077298483</v>
       </c>
       <c r="M5" t="n">
-        <v>0.009492247151794498</v>
+        <v>0.009492247151794505</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002448361957624032</v>
+        <v>0.002448361957624031</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002816847230637859</v>
+        <v>0.002816847230637858</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003576737753710633</v>
+        <v>0.003576737753710654</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002316808553188002</v>
+        <v>0.002316808553188007</v>
       </c>
       <c r="R5" t="n">
         <v>0.002484994774382478</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003738600072555609</v>
+        <v>0.003738600072555606</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004070576249528255</v>
+        <v>0.004070576249528248</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004143635333844928</v>
+        <v>0.004143635333844922</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00293778151501277</v>
+        <v>0.002937781515012766</v>
       </c>
       <c r="W5" t="n">
         <v>0.002979375671548875</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00482344499587428</v>
+        <v>0.004823444995874286</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.00741311544312392</v>
+        <v>0.007413115443123921</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00214838068838728</v>
+        <v>0.002148380688387279</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.005422522126558357</v>
+        <v>0.005422522126558362</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.006371815050100156</v>
+        <v>0.006371815050100159</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009692610248984576</v>
+        <v>0.0009692610248984568</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008744952660785629</v>
+        <v>0.0008744952660785618</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001097355646311192</v>
+        <v>0.001097355646311191</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001012041932629214</v>
+        <v>0.001012041932629213</v>
       </c>
       <c r="F6" t="n">
         <v>0.0009351719067922467</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001016777254303581</v>
+        <v>0.00101677725430358</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00100904548185317</v>
+        <v>0.001009045481853169</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00102873554212721</v>
+        <v>0.001028735542127209</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00114657301671804</v>
+        <v>0.001146573016718039</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001248969706395533</v>
+        <v>0.001248969706395531</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009957603810605772</v>
+        <v>0.0009957603810605766</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001317234496965963</v>
+        <v>0.001317234496965962</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0009281476995760493</v>
+        <v>0.0009281476995760558</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0009829267850906553</v>
+        <v>0.0009829267850906586</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001131109883370039</v>
+        <v>0.001131109883370038</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001041677290882411</v>
+        <v>0.00104167729088241</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001042197459938514</v>
+        <v>0.001042197459938513</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001015804926347619</v>
+        <v>0.001015804926347618</v>
       </c>
       <c r="T6" t="n">
         <v>0.001129118186983761</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001157719412711196</v>
+        <v>0.001157719412711195</v>
       </c>
       <c r="V6" t="n">
         <v>0.0009712267687281541</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0009690864898870616</v>
+        <v>0.0009690864898870604</v>
       </c>
       <c r="X6" t="n">
         <v>0.001063598551491989</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001214849853050876</v>
+        <v>0.001214849853050878</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0009262129551856389</v>
+        <v>0.0009262129551856383</v>
       </c>
       <c r="AA6" t="n">
         <v>0.00121299063339334</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001125305439341751</v>
+        <v>0.00112530543934175</v>
       </c>
     </row>
     <row r="7">
@@ -4466,28 +4466,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0009176940110564356</v>
+        <v>0.0009176940110564352</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008229282522365413</v>
+        <v>0.0008229282522365405</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0009275977316882755</v>
+        <v>0.0009275977316882747</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008422840180062969</v>
+        <v>0.0008422840180062968</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008836048929502263</v>
+        <v>0.0008836048929502258</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009652102404615604</v>
+        <v>0.0009652102404615599</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008392875672302524</v>
+        <v>0.0008392875672302521</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0009771685282851884</v>
+        <v>0.0009771685282851878</v>
       </c>
       <c r="J7" t="n">
         <v>0.000976815102095123</v>
@@ -4496,16 +4496,16 @@
         <v>0.001079211791772615</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009441933672185561</v>
+        <v>0.0009441933672185558</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00126566748312394</v>
+        <v>0.001265667483123941</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0008754358572062681</v>
+        <v>0.0008754358572062677</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0009128697872129472</v>
+        <v>0.0009128697872129458</v>
       </c>
       <c r="P7" t="n">
         <v>0.00095991010413313</v>
@@ -4514,31 +4514,31 @@
         <v>0.0008719193762594935</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0008724395453155967</v>
+        <v>0.0008724395453155969</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0009642379125055974</v>
+        <v>0.0009642379125055969</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0009593602723608448</v>
+        <v>0.0009593602723608447</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0009878556482609939</v>
+        <v>0.0009878556482609932</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0009196597548861335</v>
+        <v>0.0009196597548861331</v>
       </c>
       <c r="W7" t="n">
-        <v>0.00090738866299095</v>
+        <v>0.000907388662990949</v>
       </c>
       <c r="X7" t="n">
         <v>0.001012031537649968</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001152589082801429</v>
+        <v>0.00115258908280143</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008746459413436166</v>
+        <v>0.0008746459413436162</v>
       </c>
       <c r="AA7" t="n">
         <v>0.001043232718770423</v>
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0009914406999935405</v>
+        <v>0.0009914406999935402</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00102797300702439</v>
+        <v>0.001027973007024389</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001132642486476125</v>
+        <v>0.001132642486476124</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009774164257830454</v>
+        <v>0.0009774164257830447</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009778062860316197</v>
+        <v>0.0009778062860316191</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001197480504529624</v>
+        <v>0.001197480504529623</v>
       </c>
       <c r="H8" t="n">
         <v>0.001044332322018102</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001182213283073037</v>
+        <v>0.001182213283073036</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001181859856882972</v>
+        <v>0.001181859856882971</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001284256546560463</v>
+        <v>0.001284256546560462</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001149238122006404</v>
+        <v>0.001149238122006403</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00147071223791186</v>
+        <v>0.001470712237911859</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0009787026452669047</v>
+        <v>0.0009787026452669036</v>
       </c>
       <c r="O8" t="n">
         <v>0.001044115087356312</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001084299411595798</v>
+        <v>0.001084299411595797</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0009198629985297986</v>
+        <v>0.0009198629985297973</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001077484300103446</v>
+        <v>0.001077484300103445</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001169282667293447</v>
+        <v>0.001169282667293446</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001164405027148695</v>
+        <v>0.001164405027148694</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001128846396511165</v>
+        <v>0.001128846396511164</v>
       </c>
       <c r="V8" t="n">
         <v>0.001088736020547462</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001112459221591861</v>
+        <v>0.00111245922159186</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001072008888537138</v>
+        <v>0.001072008888537137</v>
       </c>
       <c r="Y8" t="n">
         <v>0.001488052173692145</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0009459537013004943</v>
+        <v>0.0009459537013004933</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001248277473558273</v>
+        <v>0.001248277473558272</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001414661488148185</v>
+        <v>0.001414661488148184</v>
       </c>
     </row>
     <row r="9">
@@ -4648,79 +4648,79 @@
         <v>0.001045411580803769</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001150081060255506</v>
+        <v>0.001150081060255503</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00104699836512018</v>
+        <v>0.001046998365120179</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009286055177211766</v>
+        <v>0.0009286055177211759</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001187693536361505</v>
+        <v>0.001187693536361503</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001061770895797482</v>
+        <v>0.001061770895797481</v>
       </c>
       <c r="I9" t="n">
         <v>0.001199651856852417</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001199298430662352</v>
+        <v>0.001199298430662351</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001301695120339845</v>
+        <v>0.001301695120339844</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001166676695785784</v>
+        <v>0.001166676695785783</v>
       </c>
       <c r="M9" t="n">
         <v>0.00148815081169117</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001097919185773498</v>
+        <v>0.001097919185773497</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001160876469520147</v>
+        <v>0.001160876469520146</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001213465718354129</v>
+        <v>0.001213465718354128</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001094402672159437</v>
+        <v>0.001094402672159436</v>
       </c>
       <c r="R9" t="n">
         <v>0.001094922873882825</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001186721241072827</v>
+        <v>0.001186721241072825</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001181843600928075</v>
+        <v>0.001181843600928073</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001210444826655508</v>
+        <v>0.001210444826655507</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001230987634718713</v>
+        <v>0.001230987634718712</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001129871991558179</v>
+        <v>0.001129871991558178</v>
       </c>
       <c r="X9" t="n">
         <v>0.001234514866217196</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.00137507241136866</v>
+        <v>0.001375072411368657</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001050711189682375</v>
+        <v>0.001050711189682374</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001265716047337654</v>
+        <v>0.001265716047337653</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001294948253198153</v>
+        <v>0.001294948253198151</v>
       </c>
     </row>
   </sheetData>
@@ -4886,40 +4886,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007725722011615624</v>
+        <v>0.0007725722011615625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008429620276750456</v>
+        <v>0.0008429620276750457</v>
       </c>
       <c r="D2" t="n">
         <v>0.0007787385156055924</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007736152769611541</v>
+        <v>0.0007736152769611539</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007720546971183344</v>
+        <v>0.0007720546971183342</v>
       </c>
       <c r="G2" t="n">
         <v>0.000774832842058571</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007755802895106389</v>
+        <v>0.0007755802895106388</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007761957358639324</v>
+        <v>0.0007761957358639325</v>
       </c>
       <c r="J2" t="n">
         <v>0.000776500162142083</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007836594804927332</v>
+        <v>0.0007836594804927331</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007795174190671437</v>
+        <v>0.0007795174190671436</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007886313346414327</v>
+        <v>0.0007886313346414329</v>
       </c>
       <c r="N2" t="n">
         <v>0.0007807208629507363</v>
@@ -4931,7 +4931,7 @@
         <v>0.0007773649846047977</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007761103396860234</v>
+        <v>0.0007761103396860236</v>
       </c>
       <c r="R2" t="n">
         <v>0.0007749389365460601</v>
@@ -4940,31 +4940,31 @@
         <v>0.000776165982601316</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007742469995900148</v>
+        <v>0.000774246999590015</v>
       </c>
       <c r="U2" t="n">
         <v>0.0009903244651376071</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007721622531908456</v>
+        <v>0.0007721622531908455</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009517754362293921</v>
+        <v>0.0009517754362293922</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0007787561695028202</v>
+        <v>0.0007787561695028204</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.000772897687435229</v>
+        <v>0.0007728976874352294</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009233033355739174</v>
+        <v>0.0009233033355739171</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0007802010742784014</v>
+        <v>0.0007802010742784015</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0007775958092162358</v>
+        <v>0.000777595809216236</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007585155121464404</v>
+        <v>0.0007599182805735774</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008587857981274454</v>
+        <v>0.0008594594270958824</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008028175046452844</v>
+        <v>0.0008058029507746906</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000766020125683647</v>
+        <v>0.0007676807580522522</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007550225884485513</v>
+        <v>0.0007563154630841407</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007744888520709203</v>
+        <v>0.0007764577540077805</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007803824913905398</v>
+        <v>0.0007825785400176052</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007846791135056759</v>
+        <v>0.0007870226222117621</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007864912908164288</v>
+        <v>0.00078889224268014</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0008374978425139292</v>
+        <v>0.0008417273808249621</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000807761509390328</v>
+        <v>0.0008109185217019027</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0008736124930465555</v>
+        <v>0.0008791553785345023</v>
       </c>
       <c r="N3" t="n">
-        <v>0.000816768681354333</v>
+        <v>0.0008202442067970049</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001288525408963762</v>
+        <v>0.001290134699778449</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0007926082570365227</v>
+        <v>0.0007952048628454573</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007838483471351359</v>
+        <v>0.0007861613225181014</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000775746214198521</v>
+        <v>0.0007777734956414798</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007838299071032847</v>
+        <v>0.0007861373284518336</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000770633337339248</v>
+        <v>0.0007724791778432698</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00115564482711936</v>
+        <v>0.001158783981419124</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007556087069897246</v>
+        <v>0.0007569104546261494</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001101025354135418</v>
+        <v>0.001104575382794177</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008028869854420797</v>
+        <v>0.0008058743555185487</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0007609644755544473</v>
+        <v>0.0007624597530881691</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001023060633823508</v>
+        <v>0.001025189463612781</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008131012581991287</v>
+        <v>0.0008164377428548991</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.000794994436330861</v>
+        <v>0.0007977007848667775</v>
       </c>
     </row>
     <row r="4">
@@ -5065,82 +5065,82 @@
         <v>0.0007272930347540815</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0006941301054414951</v>
+        <v>0.0006941301054414952</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007969443930441871</v>
+        <v>0.0007969443930441872</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000739075055749043</v>
+        <v>0.0007390750557490432</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007214475885222099</v>
+        <v>0.0007214475885222101</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007528280136319851</v>
+        <v>0.0007528280136319855</v>
       </c>
       <c r="H4" t="n">
         <v>0.000761270776445907</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007682225261256642</v>
+        <v>0.0007682225261256645</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0007713489523253061</v>
+        <v>0.000771348952325308</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0008525289552001348</v>
+        <v>0.0008525289552001347</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008057424659557069</v>
+        <v>0.0008057424659557079</v>
       </c>
       <c r="M4" t="n">
         <v>0.0009098217616863864</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0008193359182324242</v>
+        <v>0.000819335918232424</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0007366861269527674</v>
+        <v>0.0007366861269527671</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0007814297285347357</v>
+        <v>0.0007814297285347355</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0007672579370120033</v>
+        <v>0.0007672579370120031</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0007540263996740526</v>
+        <v>0.0007540263996740527</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0007678864493372318</v>
+        <v>0.0007678864493372322</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007462106534487935</v>
+        <v>0.0007462106534487941</v>
       </c>
       <c r="U4" t="n">
         <v>0.0007974128641789355</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007206342182865256</v>
+        <v>0.0007206342182865308</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0008231450108712147</v>
+        <v>0.0008231450108712145</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0007971438019345742</v>
+        <v>0.000797143801934574</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0007233156785690272</v>
+        <v>0.0007233156785690274</v>
       </c>
       <c r="Z4" t="n">
         <v>0.0007600041663484789</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0008134646660638</v>
+        <v>0.0008134646660638001</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0007845057775460237</v>
+        <v>0.0007845057775460235</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001527424924837678</v>
+        <v>0.001527424924837679</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009888363112817604</v>
+        <v>0.0009888363112817609</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003007171313472764</v>
+        <v>0.003007171313472757</v>
       </c>
       <c r="E5" t="n">
         <v>0.001783639440760591</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001528424138713395</v>
+        <v>0.001528424138713393</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001920715788258593</v>
+        <v>0.001920715788258603</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002391278554093466</v>
+        <v>0.002391278554093464</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002469414830607588</v>
+        <v>0.002469414830607586</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002333611424115344</v>
+        <v>0.002333611424115348</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003812988168084707</v>
+        <v>0.00381298816808471</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002831452932715585</v>
+        <v>0.00283145293271559</v>
       </c>
       <c r="M5" t="n">
         <v>0.00490432047216913</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003321022224638305</v>
+        <v>0.003321022224638312</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001667974010906906</v>
+        <v>0.001667974010906903</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002487863319454482</v>
+        <v>0.002487863319454484</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002328105767068791</v>
+        <v>0.00232810576706879</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002221540135078241</v>
+        <v>0.002221540135078245</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002108871488919294</v>
+        <v>0.002108871488919295</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001976718685524781</v>
+        <v>0.001976718685524783</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002955116884542753</v>
+        <v>0.002955116884542747</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001448417294955262</v>
+        <v>0.001448417294955265</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0034206592285868</v>
+        <v>0.003420659228586807</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00297951024609624</v>
+        <v>0.002979510246096244</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001666988452766323</v>
+        <v>0.001666988452766321</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00206112437199037</v>
+        <v>0.002061124371990369</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003233553583326723</v>
+        <v>0.003233553583326721</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002815244692363438</v>
+        <v>0.002815244692363439</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0008658115562941302</v>
+        <v>0.0008658115562941299</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000832648626981544</v>
+        <v>0.0008326486269815437</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001050561739175598</v>
+        <v>0.001050561739175599</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0009926924018804541</v>
+        <v>0.0009926924018804546</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008599661100622584</v>
+        <v>0.0008599661100622587</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0008913465351720342</v>
+        <v>0.0008913465351720343</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001014888122577316</v>
+        <v>0.001014888122577319</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001021839872257074</v>
+        <v>0.001021839872257076</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009098674738653547</v>
+        <v>0.0009098674738653562</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001106146301331548</v>
+        <v>0.001106146301331546</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009442609874957565</v>
+        <v>0.0009442609874957564</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001163439107817794</v>
+        <v>0.001163439107817798</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0009581199321041863</v>
+        <v>0.0009581199321041887</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0009927442389468901</v>
+        <v>0.0009927442389468944</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001037666451665877</v>
+        <v>0.001037666451665878</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001020875283143412</v>
+        <v>0.001020875283143415</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001007643745805463</v>
+        <v>0.001007643745805464</v>
       </c>
       <c r="S6" t="n">
         <v>0.0009064049708772805</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0008847291749888424</v>
+        <v>0.0008847291749888423</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0009435852590961835</v>
+        <v>0.0009435852590961838</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0009742515644179328</v>
+        <v>0.0009742515644179421</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001079262917461091</v>
+        <v>0.001079262917461089</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0009356623234746233</v>
+        <v>0.0009356623234746225</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0008773904618535837</v>
+        <v>0.0008773904618535835</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0008985226878885276</v>
+        <v>0.0008985226878885275</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001067082012195208</v>
+        <v>0.00106708201219521</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0009230989185965492</v>
+        <v>0.0009230989185965493</v>
       </c>
     </row>
     <row r="7">
@@ -5326,70 +5326,70 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.000812260349985579</v>
+        <v>0.0008122603499855792</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007790974206729928</v>
+        <v>0.0007790974206729927</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008819117082756848</v>
+        <v>0.0008819117082756844</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000824042370980541</v>
+        <v>0.0008240423709805408</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000806414903753708</v>
+        <v>0.0008064149037537076</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008377953288634833</v>
+        <v>0.0008377953288634832</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000846238091677405</v>
+        <v>0.0008462380916774046</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008531898413571621</v>
+        <v>0.0008531898413571617</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008563162675568043</v>
+        <v>0.0008563162675568054</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0009374962704316323</v>
+        <v>0.0009374962704316321</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008907097811872051</v>
+        <v>0.0008907097811872056</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0009947890769178851</v>
+        <v>0.0009947890769178847</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0009043032334639213</v>
+        <v>0.0009043032334639211</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0008216440319251925</v>
+        <v>0.0008216440319251924</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0008663876335071605</v>
+        <v>0.0008663876335071607</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.000852225252243501</v>
+        <v>0.0008522252522435009</v>
       </c>
       <c r="R7" t="n">
         <v>0.0008389937149055507</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0008528537645687303</v>
+        <v>0.0008528537645687301</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0008311779686802917</v>
+        <v>0.0008311779686802915</v>
       </c>
       <c r="U7" t="n">
         <v>0.0008899185174389606</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0008056015335180283</v>
+        <v>0.0008056015335180287</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0009081123261027126</v>
+        <v>0.0009081123261027123</v>
       </c>
       <c r="X7" t="n">
         <v>0.0008821111171660721</v>
@@ -5398,10 +5398,10 @@
         <v>0.0008159368671777246</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008449714815799771</v>
+        <v>0.0008449714815799764</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0008984319812952977</v>
+        <v>0.0008984319812952975</v>
       </c>
       <c r="AB7" t="n">
         <v>0.0008694730927775209</v>
@@ -5414,82 +5414,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008854060524855227</v>
+        <v>0.0008854060524855233</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009825969277390985</v>
+        <v>0.0009825969277390987</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00108541121534179</v>
+        <v>0.001085411215341791</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009581323223151606</v>
+        <v>0.0009581323223151611</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008998682055257584</v>
+        <v>0.0008998682055257592</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001068324546481286</v>
+        <v>0.001068324546481287</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00104973759874351</v>
+        <v>0.001049737598743511</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001056689348423267</v>
+        <v>0.001056689348423268</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001059815774622909</v>
+        <v>0.001059815774622912</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001140995777497739</v>
+        <v>0.001140995777497738</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001094209288253311</v>
+        <v>0.001094209288253312</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001198288583983994</v>
+        <v>0.001198288583983995</v>
       </c>
       <c r="N8" t="n">
         <v>0.001006756734270286</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0009518752628699641</v>
+        <v>0.0009518752628699644</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0009898121782737437</v>
+        <v>0.0009898121782737444</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0008997534569700967</v>
+        <v>0.000899753456970097</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001042493221971657</v>
+        <v>0.001042493221971656</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001056353271634835</v>
+        <v>0.001056353271634836</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001034677475746397</v>
+        <v>0.001034677475746398</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001029827363308309</v>
+        <v>0.00102982736330831</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0009733826671895079</v>
+        <v>0.0009733826671895124</v>
       </c>
       <c r="W8" t="n">
         <v>0.001111637451409429</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0009415865070877755</v>
+        <v>0.0009415865070877756</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001148903498939355</v>
+        <v>0.001148903498939357</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0009156957952375506</v>
+        <v>0.0009156957952375503</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001101931488361403</v>
+        <v>0.001101931488361404</v>
       </c>
       <c r="AB8" t="n">
         <v>0.001209138048705413</v>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009791132311154195</v>
+        <v>0.0009791132311154202</v>
       </c>
       <c r="C9" t="n">
         <v>0.0010286024352332</v>
@@ -5514,37 +5514,37 @@
         <v>0.001054471625418679</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0008653841671547745</v>
+        <v>0.0008653841671547738</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001087300363108789</v>
+        <v>0.001087300363108787</v>
       </c>
       <c r="H9" t="n">
         <v>0.001095743106237611</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00110269485591737</v>
+        <v>0.001102694855917369</v>
       </c>
       <c r="J9" t="n">
         <v>0.001105821282117012</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00118700128499184</v>
+        <v>0.001187001284991839</v>
       </c>
       <c r="L9" t="n">
         <v>0.001140214795747412</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001244294091478093</v>
+        <v>0.001244294091478091</v>
       </c>
       <c r="N9" t="n">
-        <v>0.00115380824802413</v>
+        <v>0.001153808248024129</v>
       </c>
       <c r="O9" t="n">
         <v>0.001098549291748789</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001149249925715006</v>
+        <v>0.001149249925715003</v>
       </c>
       <c r="Q9" t="n">
         <v>0.001101730286488804</v>
@@ -5556,31 +5556,31 @@
         <v>0.001102358779128937</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0010806829832405</v>
+        <v>0.001080682983240498</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001139539067347842</v>
+        <v>0.00113953906734784</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001150485299256193</v>
+        <v>0.001150485299256196</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001157617340662921</v>
+        <v>0.00115761734066292</v>
       </c>
       <c r="X9" t="n">
-        <v>0.00113161613172628</v>
+        <v>0.001131616131726279</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001065441881737932</v>
+        <v>0.001065441881737931</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001044644617212895</v>
+        <v>0.001044644617212893</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001147936995855505</v>
+        <v>0.001147936995855504</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001118978107337729</v>
+        <v>0.001118978107337728</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007673402744611901</v>
+        <v>0.00076734027446119</v>
       </c>
       <c r="C2" t="n">
         <v>0.0008418822732622229</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007685047661940352</v>
+        <v>0.0007685047661940351</v>
       </c>
       <c r="E2" t="n">
         <v>0.0007692327690485215</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000769343106321562</v>
+        <v>0.0007693431063215619</v>
       </c>
       <c r="G2" t="n">
         <v>0.0007693829547438633</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007692268335314679</v>
+        <v>0.0007692268335314678</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007693551058604711</v>
+        <v>0.0007693551058604707</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007698220013258217</v>
+        <v>0.0007698220013258214</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007682840394491507</v>
+        <v>0.0007682840394491505</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007692424826625948</v>
+        <v>0.0007692424826625942</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007671393087493786</v>
+        <v>0.0007671393087493785</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007705650287864334</v>
+        <v>0.0007705650287864329</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001087108159759422</v>
+        <v>0.001087108159759421</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007697183470580173</v>
+        <v>0.0007697183470580171</v>
       </c>
       <c r="Q2" t="n">
         <v>0.0007673497375365339</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007716988671826266</v>
+        <v>0.0007716988671826264</v>
       </c>
       <c r="S2" t="n">
         <v>0.0007697104672781054</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007676227905475846</v>
+        <v>0.0007676227905475843</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009797073176095986</v>
+        <v>0.0009797073176095981</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007699893225788125</v>
+        <v>0.0007699893225788123</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009471011875246723</v>
+        <v>0.0009471011875246722</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0007841476364668186</v>
+        <v>0.0007841476364668185</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00077064008821506</v>
+        <v>0.0007706400882150597</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009184486389336032</v>
+        <v>0.000918448638933603</v>
       </c>
       <c r="AA2" t="n">
         <v>0.0007730219819939758</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0007660656946012417</v>
+        <v>0.0007660656946012418</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007427209294684385</v>
+        <v>0.0007436926478131379</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008684546876589484</v>
+        <v>0.0008695559575998038</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007511063406503221</v>
+        <v>0.0007523833916632658</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007562170417127901</v>
+        <v>0.000757657586856746</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007571180991179532</v>
+        <v>0.0007586135950458459</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007571522423287317</v>
+        <v>0.0007586353122641697</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007563935577130684</v>
+        <v>0.0007578614653773734</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007572278645095512</v>
+        <v>0.000758722980758244</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007603602619388296</v>
+        <v>0.0007619598057862938</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007494915669501622</v>
+        <v>0.0007507113435167595</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007561415988204042</v>
+        <v>0.0007575958082834137</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0007430727384282161</v>
+        <v>0.0007440761386358766</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0007657495206686142</v>
+        <v>0.0007675436704569484</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001290144198037132</v>
+        <v>0.001292015569458184</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0007596061257278106</v>
+        <v>0.0007611700379652506</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007428036696314848</v>
+        <v>0.0007437858145727024</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007740353860137759</v>
+        <v>0.0007761303924976772</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007594516664867835</v>
+        <v>0.0007610197370937366</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007448234938781027</v>
+        <v>0.0007458770198329487</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001091803405303385</v>
+        <v>0.001092710488267443</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007614927955948408</v>
+        <v>0.0007631288496169653</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001078948730181453</v>
+        <v>0.001081745151458598</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008625060952823901</v>
+        <v>0.0008677507716540736</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.000766343471570271</v>
+        <v>0.000768154096597992</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001012636981288572</v>
+        <v>0.001014553240838523</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0007833372121976404</v>
+        <v>0.0007857474590681469</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0007345285749116281</v>
+        <v>0.0007352191515629757</v>
       </c>
     </row>
     <row r="4">
@@ -5922,70 +5922,70 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007020670773126604</v>
+        <v>0.0007020670773126607</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007074400110180249</v>
+        <v>0.0007074400110180251</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007152205471278199</v>
+        <v>0.0007152205471278195</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007234436742671015</v>
+        <v>0.0007234436742671018</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007246899845237459</v>
+        <v>0.0007246899845237461</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007251400907848271</v>
+        <v>0.0007251400907848272</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000723376629871509</v>
+        <v>0.0007233766298715089</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007248255248357857</v>
+        <v>0.0007248255248357854</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0007298219575344088</v>
+        <v>0.0007298219575344087</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007127273370050285</v>
+        <v>0.0007127273370050286</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007235533940065425</v>
+        <v>0.0007235533940065423</v>
       </c>
       <c r="M4" t="n">
-        <v>0.000702939092534051</v>
+        <v>0.0007029390925340512</v>
       </c>
       <c r="N4" t="n">
-        <v>0.000738492160876575</v>
+        <v>0.0007384921608765745</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0007427852107029784</v>
+        <v>0.0007427852107029786</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0007289285012612755</v>
+        <v>0.0007289285012612756</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0007021739671019076</v>
+        <v>0.0007021739671019078</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0007512993871530068</v>
+        <v>0.0007512993871530066</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0007288394955222944</v>
+        <v>0.0007288394955222949</v>
       </c>
       <c r="T4" t="n">
         <v>0.0007052582264723201</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0006940766197271374</v>
+        <v>0.0006940766197271375</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007301933068325025</v>
+        <v>0.0007301933068325022</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0007836271943039516</v>
+        <v>0.0007836271943039515</v>
       </c>
       <c r="X4" t="n">
         <v>0.0008919139629347566</v>
@@ -5994,13 +5994,13 @@
         <v>0.0007344009569501219</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0007446605300543742</v>
+        <v>0.0007446605300543745</v>
       </c>
       <c r="AA4" t="n">
         <v>0.0007662445776100806</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0006891302673831818</v>
+        <v>0.0006891302673831819</v>
       </c>
     </row>
     <row r="5">
@@ -6010,34 +6010,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001136192506225464</v>
+        <v>0.001136192506225465</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001270734669193335</v>
+        <v>0.001270734669193338</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001407376612978588</v>
+        <v>0.001407376612978587</v>
       </c>
       <c r="E5" t="n">
         <v>0.001508719617441099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001589619928287611</v>
+        <v>0.001589619928287613</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001467891464797906</v>
+        <v>0.00146789146479791</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00162096184990097</v>
+        <v>0.001620961849900972</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001604518878130938</v>
+        <v>0.00160451887813094</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001593945597433014</v>
+        <v>0.001593945597433015</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001342843411797334</v>
+        <v>0.001342843411797335</v>
       </c>
       <c r="L5" t="n">
         <v>0.001435637095529978</v>
@@ -6046,19 +6046,19 @@
         <v>0.001192550786726295</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001787353085698113</v>
+        <v>0.001787353085698116</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001758132030233104</v>
+        <v>0.001758132030233107</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001566078232400981</v>
+        <v>0.001566078232400983</v>
       </c>
       <c r="Q5" t="n">
         <v>0.001145960936307076</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002114200483686507</v>
+        <v>0.002114200483686508</v>
       </c>
       <c r="S5" t="n">
         <v>0.001513603546029968</v>
@@ -6070,25 +6070,25 @@
         <v>0.001094188840094705</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001593907503219966</v>
+        <v>0.001593907503219968</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002518908102200642</v>
+        <v>0.002518908102200641</v>
       </c>
       <c r="X5" t="n">
         <v>0.004405945782340565</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001832533932198976</v>
+        <v>0.001832533932198977</v>
       </c>
       <c r="Z5" t="n">
         <v>0.001783697477717933</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002305300413537415</v>
+        <v>0.002305300413537412</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0009649343191957613</v>
+        <v>0.0009649343191957612</v>
       </c>
     </row>
     <row r="6">
@@ -6098,67 +6098,67 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009403054217369735</v>
+        <v>0.0009403054217369736</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008398414542916168</v>
+        <v>0.000839841454291617</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008476219904014117</v>
+        <v>0.0008476219904014119</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008558451175406939</v>
+        <v>0.000855845117540694</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009629283289480587</v>
+        <v>0.0009629283289480589</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009633784352091398</v>
+        <v>0.0009633784352091402</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009616149742958215</v>
+        <v>0.0009616149742958216</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009630638692600979</v>
+        <v>0.0009630638692600983</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009680603019587211</v>
+        <v>0.0009680603019587215</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0009509656814293411</v>
+        <v>0.0009509656814293417</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008559548372801345</v>
+        <v>0.0008559548372801347</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0009411774369583637</v>
+        <v>0.0009411774369583642</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0008713223667171156</v>
+        <v>0.0008713223667171157</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0009825739848466908</v>
+        <v>0.0009825739848466901</v>
       </c>
       <c r="P6" t="n">
         <v>0.0008526941189917911</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0009404123115262205</v>
+        <v>0.0009404123115262207</v>
       </c>
       <c r="R6" t="n">
-        <v>0.000883700830426599</v>
+        <v>0.0008837008304265992</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0009670778399466075</v>
+        <v>0.0009670778399466078</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0008376596697459125</v>
+        <v>0.0008376596697459126</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0008314170977025599</v>
+        <v>0.0008314170977025601</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0008625947501060947</v>
+        <v>0.0008625947501060944</v>
       </c>
       <c r="W6" t="n">
         <v>0.0009256704440537859</v>
@@ -6170,13 +6170,13 @@
         <v>0.0008794331634459506</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0008770619733279668</v>
+        <v>0.0008770619733279669</v>
       </c>
       <c r="AA6" t="n">
         <v>0.001004482922034393</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.000820682407094702</v>
+        <v>0.0008206824070947019</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007791222351502801</v>
+        <v>0.0007791222351502805</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007844951688556442</v>
+        <v>0.0007844951688556445</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007922757049654392</v>
+        <v>0.0007922757049654395</v>
       </c>
       <c r="E7" t="n">
         <v>0.0008004988321047208</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008017451423613654</v>
+        <v>0.0008017451423613656</v>
       </c>
       <c r="G7" t="n">
         <v>0.0008021952486224466</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008004317877091285</v>
+        <v>0.0008004317877091287</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008018806826734049</v>
+        <v>0.0008018806826734053</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000806877115372028</v>
+        <v>0.0008068771153720283</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007897824948426481</v>
+        <v>0.0007897824948426478</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008006085518441618</v>
+        <v>0.0008006085518441617</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0007799942503716711</v>
+        <v>0.0007799942503716712</v>
       </c>
       <c r="N7" t="n">
         <v>0.0008155473187141944</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0008198315155513199</v>
+        <v>0.0008198315155513202</v>
       </c>
       <c r="P7" t="n">
         <v>0.000805974806109617</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.000779229124939527</v>
+        <v>0.0007792291249395272</v>
       </c>
       <c r="R7" t="n">
         <v>0.0008283545449906262</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0008058946533599144</v>
+        <v>0.0008058946533599147</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0007823133843099397</v>
+        <v>0.00078231338430994</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0007759684317976722</v>
+        <v>0.0007759684317976723</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0008072484646701219</v>
+        <v>0.0008072484646701223</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0008606823521415708</v>
+        <v>0.0008606823521415711</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0009689691207723763</v>
+        <v>0.0009689691207723766</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0008163951494895716</v>
+        <v>0.000816395149489572</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008217156878919938</v>
+        <v>0.0008217156878919941</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0008432997354476999</v>
+        <v>0.0008432997354477</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0007661854252208013</v>
+        <v>0.0007661854252208015</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008444348903476856</v>
+        <v>0.0008444348903476859</v>
       </c>
       <c r="C8" t="n">
         <v>0.0009676306464907539</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009754111826005492</v>
+        <v>0.0009754111826005488</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009208971323505109</v>
+        <v>0.0009208971323505108</v>
       </c>
       <c r="F8" t="n">
-        <v>0.000885413216268263</v>
+        <v>0.0008854132162682631</v>
       </c>
       <c r="G8" t="n">
         <v>0.0010097620560333</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009835672653442384</v>
+        <v>0.0009835672653442382</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009850161603085152</v>
+        <v>0.0009850161603085145</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0009900125930071377</v>
+        <v>0.0009900125930071379</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0009729179724777581</v>
+        <v>0.0009729179724777579</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0009837440294792718</v>
+        <v>0.0009837440294792712</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0009631297280067677</v>
+        <v>0.0009631297280067674</v>
       </c>
       <c r="N8" t="n">
         <v>0.0009073503976273567</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0009367423836409803</v>
+        <v>0.0009367423836409804</v>
       </c>
       <c r="P8" t="n">
         <v>0.000916733318465254</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0008213869063570418</v>
+        <v>0.0008213869063570423</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001011490022625736</v>
+        <v>0.001011490022625735</v>
       </c>
       <c r="S8" t="n">
-        <v>0.000989030130995024</v>
+        <v>0.0009890301309950242</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0009654488619450498</v>
+        <v>0.0009654488619450495</v>
       </c>
       <c r="U8" t="n">
         <v>0.0009016260613237974</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0009581012433970596</v>
+        <v>0.0009581012433970591</v>
       </c>
       <c r="W8" t="n">
         <v>0.00104384098532245</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001021925597974809</v>
+        <v>0.001021925597974808</v>
       </c>
       <c r="Y8" t="n">
         <v>0.001116555182890162</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0008848397236733734</v>
+        <v>0.0008848397236733732</v>
       </c>
       <c r="AA8" t="n">
         <v>0.00102643521308281</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001072396693062743</v>
+        <v>0.001072396693062742</v>
       </c>
     </row>
     <row r="9">
@@ -6362,40 +6362,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009111649726057849</v>
+        <v>0.0009111649726057853</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009862751974682605</v>
+        <v>0.0009862751974682607</v>
       </c>
       <c r="D9" t="n">
         <v>0.0009940557335780555</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0009861838202577535</v>
+        <v>0.0009861838202577533</v>
       </c>
       <c r="F9" t="n">
         <v>0.0008427616106664905</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001003975331689205</v>
+        <v>0.001003975331689206</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001002211816321744</v>
+        <v>0.001002211816321745</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001003660711286021</v>
+        <v>0.001003660711286022</v>
       </c>
       <c r="J9" t="n">
         <v>0.001008657143984645</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009915625234552642</v>
+        <v>0.0009915625234552645</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001002388580456778</v>
+        <v>0.001002388580456779</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0009817742789842872</v>
+        <v>0.0009817742789842874</v>
       </c>
       <c r="N9" t="n">
         <v>0.001017327347326811</v>
@@ -6404,10 +6404,10 @@
         <v>0.001044731316630147</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001035900823814826</v>
+        <v>0.001035900823814827</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0009810092080062862</v>
+        <v>0.0009810092080062864</v>
       </c>
       <c r="R9" t="n">
         <v>0.001030134573603243</v>
@@ -6416,31 +6416,31 @@
         <v>0.001007674681972531</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0009840934129225561</v>
+        <v>0.0009840934129225567</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0009778508408792037</v>
+        <v>0.0009778508408792039</v>
       </c>
       <c r="V9" t="n">
-        <v>0.00108950388873801</v>
+        <v>0.001089503888738011</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001062462380754187</v>
+        <v>0.001062462380754188</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001170749149384993</v>
+        <v>0.001170749149384992</v>
       </c>
       <c r="Y9" t="n">
         <v>0.001018175178102188</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0009814503528419109</v>
+        <v>0.0009814503528419111</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001045079764060316</v>
+        <v>0.001045079764060317</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0009679654538334179</v>
+        <v>0.0009679654538334181</v>
       </c>
     </row>
   </sheetData>
@@ -6606,34 +6606,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007668834693289901</v>
+        <v>0.0007668834693289894</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008212251319951277</v>
+        <v>0.0008212251319951278</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007670175602022428</v>
+        <v>0.0007670175602022437</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007688332031770477</v>
+        <v>0.0007688332031770476</v>
       </c>
       <c r="F2" t="n">
         <v>0.0007670737076480287</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000766414344712774</v>
+        <v>0.0007664143447127734</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007661300746180672</v>
+        <v>0.0007661300746180671</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007662116251951724</v>
+        <v>0.0007662116251951725</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007675203613730136</v>
+        <v>0.0007675203613730139</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007658502563696061</v>
+        <v>0.0007658502563696056</v>
       </c>
       <c r="L2" t="n">
         <v>0.0007678900616767651</v>
@@ -6642,22 +6642,22 @@
         <v>0.0007653179158613552</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007672092505297567</v>
+        <v>0.0007672092505297562</v>
       </c>
       <c r="O2" t="n">
         <v>0.001091330955048135</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007692712031721326</v>
+        <v>0.0007692712031721327</v>
       </c>
       <c r="Q2" t="n">
         <v>0.0007653546163537931</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007703478456294818</v>
+        <v>0.0007703478456294825</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007673428094533025</v>
+        <v>0.0007673428094533031</v>
       </c>
       <c r="T2" t="n">
         <v>0.0007655264768406127</v>
@@ -6666,25 +6666,25 @@
         <v>0.0009222163954540774</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007688078230513301</v>
+        <v>0.0007688078230513296</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0008968592210335835</v>
+        <v>0.0008968592210335831</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0007868839481987954</v>
+        <v>0.0007868839481987959</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0007685731298191825</v>
+        <v>0.0007685731298191819</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009144946111193314</v>
+        <v>0.0009144946111193319</v>
       </c>
       <c r="AA2" t="n">
         <v>0.0007719574871753934</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0007652848345739308</v>
+        <v>0.0007652848345739306</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007501797451806329</v>
+        <v>0.0007514602994837358</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008360836319262768</v>
+        <v>0.0008371964527647977</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007512680012310986</v>
+        <v>0.0007525968026705308</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007640259901345927</v>
+        <v>0.000765791724150181</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007517100313800247</v>
+        <v>0.0007530578474676003</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000746835406870371</v>
+        <v>0.000747999107205418</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007450046496995784</v>
+        <v>0.0007461130442235675</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007455469702919758</v>
+        <v>0.0007466725221146464</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007547488617556911</v>
+        <v>0.0007561960662937034</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007429199795876841</v>
+        <v>0.0007439514245566514</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007572883248947464</v>
+        <v>0.0007588278740156366</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0007407692791144815</v>
+        <v>0.0007417355925873298</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0007526071407741404</v>
+        <v>0.0007539803889999606</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001319528145790182</v>
+        <v>0.001322360156055503</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0007670931504436897</v>
+        <v>0.0007689677323489149</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007393620926795351</v>
+        <v>0.0007402672479163478</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007751874945046327</v>
+        <v>0.0007773691100008235</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007534210203242806</v>
+        <v>0.0007548195878961002</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007406357611776405</v>
+        <v>0.0007415862856897171</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0009997819413865936</v>
+        <v>0.001000753438933638</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007638307067498063</v>
+        <v>0.0007655945956168094</v>
       </c>
       <c r="W3" t="n">
-        <v>0.000986910740889726</v>
+        <v>0.0009892168939630989</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008926083824315499</v>
+        <v>0.0008989762587293464</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0007623722232198469</v>
+        <v>0.0007640880408088149</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0009998984280398936</v>
+        <v>0.001001461789217024</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0007865133205024212</v>
+        <v>0.0007890817020832511</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0007395460851608818</v>
+        <v>0.0007404598369812539</v>
       </c>
     </row>
     <row r="4">
@@ -6785,82 +6785,82 @@
         <v>0.0007151697989475525</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007071155059108284</v>
+        <v>0.0007071155059108287</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007166844170458072</v>
+        <v>0.0007166844170458077</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007371929396832543</v>
+        <v>0.0007371929396832541</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007173186282750491</v>
+        <v>0.0007173186282750495</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007098708205994019</v>
+        <v>0.0007098708205994018</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007066598591089894</v>
+        <v>0.0007066598591089896</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007075810103925156</v>
+        <v>0.0007075810103925159</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0007220863932656715</v>
+        <v>0.0007220863932656717</v>
       </c>
       <c r="K4" t="n">
         <v>0.0007034991832698655</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000726539722571031</v>
+        <v>0.0007265397225710313</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007004604429568275</v>
+        <v>0.0007004604429568281</v>
       </c>
       <c r="N4" t="n">
-        <v>0.000718849647476971</v>
+        <v>0.0007188496474769715</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0007853808592444026</v>
+        <v>0.0007853808592444024</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0007421403511176932</v>
+        <v>0.000742140351117693</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0006979007012855861</v>
+        <v>0.0006979007012855866</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0007543015229534441</v>
+        <v>0.0007543015229534442</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0007203582569585689</v>
+        <v>0.0007203582569585693</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0006998419445439508</v>
+        <v>0.0006998419445439514</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0006972830672885837</v>
+        <v>0.0006972830672885838</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007351115958480553</v>
+        <v>0.0007351115958480557</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0007608104529889923</v>
+        <v>0.0007608104529889922</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0009410844084568591</v>
+        <v>0.0009410844084568588</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0007304736291226024</v>
+        <v>0.0007304736291226026</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0007278865836224193</v>
+        <v>0.0007278865836224196</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0007724831646862128</v>
+        <v>0.0007724831646862136</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0006982171909896748</v>
+        <v>0.0006982171909896747</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001346959844004833</v>
+        <v>0.001346959844004834</v>
       </c>
       <c r="C5" t="n">
         <v>0.001268014137922918</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001441761623888941</v>
+        <v>0.00144176162388894</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00170066469536194</v>
+        <v>0.001700664695361938</v>
       </c>
       <c r="F5" t="n">
         <v>0.001474382945064211</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001255222153409332</v>
+        <v>0.001255222153409333</v>
       </c>
       <c r="H5" t="n">
         <v>0.001301087509263098</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001296800917901432</v>
+        <v>0.001296800917901433</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001486143015615423</v>
+        <v>0.001486143015615424</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001199792719849187</v>
+        <v>0.001199792719849189</v>
       </c>
       <c r="L5" t="n">
         <v>0.001508919350233445</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001162966872469562</v>
+        <v>0.001162966872469563</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001465047499305295</v>
+        <v>0.001465047499305296</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002425989532859826</v>
+        <v>0.002425989532859829</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001757661243900986</v>
+        <v>0.001757661243900991</v>
       </c>
       <c r="Q5" t="n">
         <v>0.001090161393807279</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002185375681269419</v>
+        <v>0.002185375681269421</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001419521800101527</v>
+        <v>0.001419521800101528</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001148899532079924</v>
+        <v>0.001148899532079926</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001126916233336384</v>
+        <v>0.001126916233336386</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001686469765959381</v>
+        <v>0.00168646976595938</v>
       </c>
       <c r="W5" t="n">
         <v>0.002161395115949435</v>
       </c>
       <c r="X5" t="n">
-        <v>0.005178988805503318</v>
+        <v>0.005178988805503317</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001753590827273077</v>
+        <v>0.001753590827273075</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001511113057268932</v>
+        <v>0.001511113057268934</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002422857792972249</v>
+        <v>0.002422857792972257</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001138159692916632</v>
+        <v>0.001138159692916631</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000955029220638199</v>
+        <v>0.0009550292206381998</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000946974927601475</v>
+        <v>0.0009469749276014754</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000956543838736454</v>
+        <v>0.0009565438387364544</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000870662724082979</v>
+        <v>0.0008706627240829793</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009571780499656961</v>
+        <v>0.0009571780499656962</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009497302422900486</v>
+        <v>0.000949730242290049</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009465192807996357</v>
+        <v>0.0009465192807996362</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009474404320831619</v>
+        <v>0.0009474404320831628</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0008555561776653964</v>
+        <v>0.0008555561776653965</v>
       </c>
       <c r="K6" t="n">
         <v>0.0008369689676695904</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009663991442616775</v>
+        <v>0.0009663991442616779</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0009403198646474742</v>
+        <v>0.0009403198646474747</v>
       </c>
       <c r="N6" t="n">
         <v>0.0008528508142667276</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0009367236802897854</v>
+        <v>0.0009367236802897856</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0009831350416776023</v>
+        <v>0.0009831350416776039</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0009377601229762331</v>
+        <v>0.0009377601229762336</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0009941609446440904</v>
+        <v>0.0009941609446440913</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0009602176786492157</v>
+        <v>0.0009602176786492162</v>
       </c>
       <c r="T6" t="n">
-        <v>0.000833311728943676</v>
+        <v>0.0008333117289436764</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0009409241513231297</v>
+        <v>0.0009409241513231299</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0008685813802477805</v>
+        <v>0.0008685813802477806</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001001468971890324</v>
+        <v>0.001001468971890325</v>
       </c>
       <c r="X6" t="n">
         <v>0.001074554192856583</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0008775404816239235</v>
+        <v>0.000877540481623922</v>
       </c>
       <c r="Z6" t="n">
         <v>0.0008613563680221444</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001012342586376859</v>
+        <v>0.001012342586376861</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0008314761593446256</v>
+        <v>0.0008314761593446259</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007918947337582815</v>
+        <v>0.0007918947337582814</v>
       </c>
       <c r="C7" t="n">
         <v>0.0007838404407215575</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007934093518565368</v>
+        <v>0.0007934093518565367</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000813917874493983</v>
+        <v>0.0008139178744939837</v>
       </c>
       <c r="F7" t="n">
         <v>0.0007940435630857782</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007865957554101309</v>
+        <v>0.0007865957554101312</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0007833847939197186</v>
+        <v>0.0007833847939197188</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007843059452032446</v>
+        <v>0.0007843059452032447</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0007988113280764003</v>
+        <v>0.0007988113280764006</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007802241180805946</v>
+        <v>0.0007802241180805949</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008032646573817601</v>
+        <v>0.00080326465738176</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0007771853777675568</v>
+        <v>0.000777185377767557</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0007955745822877</v>
+        <v>0.0007955745822877004</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0008620969042849039</v>
+        <v>0.0008620969042849045</v>
       </c>
       <c r="P7" t="n">
-        <v>0.000818856396158195</v>
+        <v>0.0008188563961581951</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0007746256360963154</v>
+        <v>0.0007746256360963156</v>
       </c>
       <c r="R7" t="n">
         <v>0.0008310264577641731</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0007970831917692981</v>
+        <v>0.0007970831917692979</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0007765668793546801</v>
+        <v>0.0007765668793546805</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0007776925179552366</v>
+        <v>0.0007776925179552372</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0008118365306587844</v>
+        <v>0.0008118365306587847</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0008375353877997211</v>
+        <v>0.0008375353877997212</v>
       </c>
       <c r="X7" t="n">
         <v>0.001017809343267587</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0008109802262772308</v>
+        <v>0.0008109802262772311</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008046115184331484</v>
+        <v>0.0008046115184331483</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.000849208099496942</v>
+        <v>0.0008492080994969426</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0007749421258004037</v>
+        <v>0.0007749421258004035</v>
       </c>
     </row>
     <row r="8">
@@ -7134,49 +7134,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008566921442583511</v>
+        <v>0.0008566921442583513</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009658450546365481</v>
+        <v>0.0009658450546365488</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009754139657715274</v>
+        <v>0.0009754139657715278</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009335131099894828</v>
+        <v>0.0009335131099894831</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008771004860465827</v>
+        <v>0.0008771004860465829</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009929040464861634</v>
+        <v>0.0009929040464861641</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009653894078347091</v>
+        <v>0.0009653894078347099</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009663105591182352</v>
+        <v>0.0009663105591182363</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0009808159419913915</v>
+        <v>0.0009808159419913919</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000962228731995585</v>
+        <v>0.0009622287319955854</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0009852692712967507</v>
+        <v>0.0009852692712967509</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0009591899916825305</v>
+        <v>0.0009591899916825312</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0008867240052144428</v>
+        <v>0.0008867240052144432</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0009782230123408159</v>
+        <v>0.0009782230123408166</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0009288622942658465</v>
+        <v>0.0009288622942658466</v>
       </c>
       <c r="Q8" t="n">
         <v>0.0008163891560050457</v>
@@ -7185,19 +7185,19 @@
         <v>0.001013031071679164</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0009790878056842884</v>
+        <v>0.000979087805684289</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0009585714932696706</v>
+        <v>0.0009585714932696711</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0009025186099203476</v>
+        <v>0.0009025186099203479</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0009617312089442325</v>
+        <v>0.0009617312089442329</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001019563036274596</v>
+        <v>0.001019563036274597</v>
       </c>
       <c r="X8" t="n">
         <v>0.001070315136255094</v>
@@ -7206,10 +7206,10 @@
         <v>0.001109404287728221</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0008672317449565196</v>
+        <v>0.0008672317449565201</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001031212713411933</v>
+        <v>0.001031212713411934</v>
       </c>
       <c r="AB8" t="n">
         <v>0.001079379464376538</v>
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009059422658464831</v>
+        <v>0.0009059422658464835</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009625231486411332</v>
+        <v>0.000962523148641134</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0009720920597761126</v>
+        <v>0.0009720920597761127</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0009776830840463953</v>
+        <v>0.0009776830840463962</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0008237244880398088</v>
+        <v>0.0008237244880398092</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0009652785108759171</v>
+        <v>0.0009652785108759176</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0009620675018392941</v>
+        <v>0.0009620675018392948</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009629886531228206</v>
+        <v>0.000962988653122821</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0009774940359959759</v>
+        <v>0.0009774940359959764</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00095890682600017</v>
+        <v>0.0009589068260001711</v>
       </c>
       <c r="L9" t="n">
-        <v>0.000981947365301336</v>
+        <v>0.0009819473653013364</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0009558680856871323</v>
+        <v>0.0009558680856871326</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0009742572902072753</v>
+        <v>0.0009742572902072764</v>
       </c>
       <c r="O9" t="n">
         <v>0.001062208577916129</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001023626558459175</v>
+        <v>0.001023626558459176</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0009533083915621019</v>
+        <v>0.0009533083915621028</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001009709165683748</v>
+        <v>0.001009709165683749</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0009757658996888738</v>
+        <v>0.0009757658996888743</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0009552495872742554</v>
+        <v>0.0009552495872742563</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0009564723723627883</v>
+        <v>0.0009564723723627887</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001065106895595691</v>
+        <v>0.001065106895595693</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001016218095719296</v>
+        <v>0.001016218095719297</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001196492051187163</v>
+        <v>0.001196492051187164</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0009896629341968057</v>
+        <v>0.0009896629341968064</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0009443249817905846</v>
+        <v>0.0009443249817905849</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001027890807416517</v>
+        <v>0.001027890807416518</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0009536248337199795</v>
+        <v>0.0009536248337199801</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007956216873251606</v>
+        <v>0.0007956216873251604</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008595909254418685</v>
+        <v>0.0008595909254418683</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007974059462561858</v>
+        <v>0.0007974059462561849</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007899286416906946</v>
+        <v>0.0007899286416906935</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007906690290441989</v>
+        <v>0.0007906690290441985</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008025013568275653</v>
+        <v>0.0008025013568275646</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007919788177401634</v>
+        <v>0.0007919788177401623</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007988679223302311</v>
+        <v>0.0007988679223302302</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008017231565928843</v>
+        <v>0.0008017231565928833</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008073110872557064</v>
+        <v>0.0008073110872557057</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008020260719817952</v>
+        <v>0.0008020260719817927</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008422476779577687</v>
+        <v>0.0008422476779577688</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008071331868653562</v>
+        <v>0.0008071331868653557</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001121269335210141</v>
+        <v>0.00112126933521014</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008000451844818496</v>
+        <v>0.0008000451844818494</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007931042654368681</v>
+        <v>0.0007931042654368672</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007935584394513463</v>
+        <v>0.0007935584394513455</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007974476693927878</v>
+        <v>0.0007974476693927869</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007976871643331879</v>
+        <v>0.0007976871643331873</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00101630787166001</v>
+        <v>0.001016307871660008</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007899412304665829</v>
+        <v>0.0007899412304665823</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009684491539701103</v>
+        <v>0.0009684491539701098</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008019285559071334</v>
+        <v>0.0008019285559071321</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0007962752199187075</v>
+        <v>0.0007962752199187069</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009423134966044812</v>
+        <v>0.0009423134966044806</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008029063308997357</v>
+        <v>0.0008029063308997351</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008103943594896234</v>
+        <v>0.0008103943594896233</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008253015649472076</v>
+        <v>0.0008286273335690988</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008821381207610453</v>
+        <v>0.000883230998663636</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008387046268132749</v>
+        <v>0.0008425302663898392</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007849730425102717</v>
+        <v>0.0007868734267275458</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007904689574559099</v>
+        <v>0.0007925925582700518</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008741110513054873</v>
+        <v>0.0008791595426191751</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007999919900616061</v>
+        <v>0.0008024538111388086</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008491782728763554</v>
+        <v>0.0008533824058531398</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0008689022229971963</v>
+        <v>0.0008737904271143803</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009086243910706633</v>
+        <v>0.0009149568270533234</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008711239290578978</v>
+        <v>0.0008760799606974693</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001156440542836971</v>
+        <v>0.001171644673514121</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0009080388055164063</v>
+        <v>0.0009143094588370561</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00136050029831469</v>
+        <v>0.001363719928676655</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008568609739818836</v>
+        <v>0.0008612846491744086</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000807728710690077</v>
+        <v>0.0008104558724023185</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008112667226448367</v>
+        <v>0.0008141252722347991</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008381495712078039</v>
+        <v>0.0008419425584049535</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008407079151800137</v>
+        <v>0.0008446072295797921</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001237867005313204</v>
+        <v>0.001243415410621724</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007849380590076668</v>
+        <v>0.0007868460159398571</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001117142619617507</v>
+        <v>0.001120775433095181</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008709396235038304</v>
+        <v>0.0008759092693592639</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0008303111219394232</v>
+        <v>0.0008338306498468855</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001056512064647159</v>
+        <v>0.001059338033820548</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008776836380959735</v>
+        <v>0.0008828731851693448</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.000931411788018104</v>
+        <v>0.0009385068849394466</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0008249268835825149</v>
+        <v>0.0008249268835825107</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007235637947406083</v>
+        <v>0.0007235637947406084</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0008450809090081018</v>
+        <v>0.0008450809090081019</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007606213142108366</v>
+        <v>0.0007606213142108358</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007689843299636807</v>
+        <v>0.000768984329963681</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0009026359154165041</v>
+        <v>0.0009026359154165048</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007837789958171675</v>
+        <v>0.0007837789958171664</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008615946013066615</v>
+        <v>0.0008615946013066617</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0008934900054443211</v>
+        <v>0.0008934900054443202</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0009569640331876691</v>
+        <v>0.0009569640331876692</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008972673544416923</v>
+        <v>0.0008972673544416826</v>
       </c>
       <c r="M4" t="n">
         <v>0.001348698492089482</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0009549545664404369</v>
+        <v>0.0009549545664404372</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0008202737564312711</v>
+        <v>0.0008202737564312714</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0008748923188765433</v>
+        <v>0.0008748923188765431</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.000796491445282966</v>
+        <v>0.0007964914452829651</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0008016215497068671</v>
+        <v>0.0008016215497068677</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0008455521910296075</v>
+        <v>0.0008455521910296071</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0008482573965545485</v>
+        <v>0.0008482573965545481</v>
       </c>
       <c r="U4" t="n">
-        <v>0.000915551738665898</v>
+        <v>0.0009155517386658977</v>
       </c>
       <c r="V4" t="n">
         <v>0.0007584411200796237</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0008376165534403358</v>
+        <v>0.0008376165534403357</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0008961658655187887</v>
+        <v>0.0008961658655187855</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0008237658941270681</v>
+        <v>0.0008237658941270677</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0008022228229744309</v>
+        <v>0.0008022228229744298</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0009072102838589387</v>
+        <v>0.0009072102838589383</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0009904412571405635</v>
+        <v>0.0009904412571405639</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00303679988131916</v>
+        <v>0.00303679988131912</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001351452672876262</v>
+        <v>0.001351452672876264</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003789778694004379</v>
+        <v>0.003789778694004378</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001989446057489679</v>
+        <v>0.001989446057489669</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002265329220155776</v>
+        <v>0.002265329220155775</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004344242358446705</v>
+        <v>0.004344242358446706</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002642394989418333</v>
+        <v>0.002642394989418337</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004123958184144935</v>
+        <v>0.004123958184144936</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004369681619635682</v>
+        <v>0.004369681619635675</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005474947530674523</v>
+        <v>0.005474947530674522</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004467981004751227</v>
+        <v>0.004467981004751075</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01290539338175982</v>
+        <v>0.01290539338175983</v>
       </c>
       <c r="N5" t="n">
-        <v>0.005817415591116578</v>
+        <v>0.005817415591116585</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002903083675847149</v>
+        <v>0.00290308367584715</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003975251093338831</v>
+        <v>0.003975251093338826</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002718331192949065</v>
+        <v>0.00271833119294905</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002980257318492763</v>
+        <v>0.002980257318492772</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003324383148168719</v>
+        <v>0.003324383148168699</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003847737679967689</v>
+        <v>0.003847737679967679</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00498128199510329</v>
+        <v>0.004981281995103286</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001920387686962661</v>
+        <v>0.001920387686962664</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003495929549615375</v>
+        <v>0.003495929549615364</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00473172143216937</v>
+        <v>0.004731721432169358</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003368395512531249</v>
+        <v>0.003368395512531243</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002661183014400194</v>
+        <v>0.002661183014400157</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.004810178213112213</v>
+        <v>0.004810178213112208</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.006950656887591362</v>
+        <v>0.006950656887591352</v>
       </c>
     </row>
     <row r="6">
@@ -7818,25 +7818,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009654275904879315</v>
+        <v>0.000965427590487929</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008640645016460237</v>
+        <v>0.0008640645016460243</v>
       </c>
       <c r="D6" t="n">
         <v>0.000985581615913518</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001026969039464501</v>
+        <v>0.001026969039464499</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009094850368690966</v>
+        <v>0.0009094850368690974</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001168983640670167</v>
+        <v>0.001168983640670168</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009242797027225827</v>
+        <v>0.0009242797027225828</v>
       </c>
       <c r="I6" t="n">
         <v>0.001002095308212077</v>
@@ -7845,34 +7845,34 @@
         <v>0.001033990712349737</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001223311758441333</v>
+        <v>0.001223311758441332</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001163615079695356</v>
+        <v>0.001163615079695341</v>
       </c>
       <c r="M6" t="n">
         <v>0.001489199198994898</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00109598257071428</v>
+        <v>0.001095982570714277</v>
       </c>
       <c r="O6" t="n">
         <v>0.001089034695110062</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001143833089905069</v>
+        <v>0.001143833089905068</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.000936992152188381</v>
+        <v>0.0009369921521883799</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00106796927496053</v>
+        <v>0.001067969274960531</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0009860528979350235</v>
+        <v>0.0009860528979350228</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0009887581034599639</v>
+        <v>0.0009887581034599647</v>
       </c>
       <c r="U6" t="n">
         <v>0.001190442404658971</v>
@@ -7881,19 +7881,19 @@
         <v>0.0008989418269850391</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00098827734592794</v>
+        <v>0.0009882773459279392</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001162513590772452</v>
+        <v>0.001162513590772448</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0009809612551110606</v>
+        <v>0.0009809612551110621</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001068570548228095</v>
+        <v>0.001068570548228093</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001173558009112601</v>
+        <v>0.0011735580091126</v>
       </c>
       <c r="AB6" t="n">
         <v>0.001132109296153048</v>
@@ -7906,37 +7906,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0009171789212184956</v>
+        <v>0.0009171789212184923</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008158158323765879</v>
+        <v>0.0008158158323765885</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0009373329466440822</v>
+        <v>0.0009373329466440826</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008528733518468169</v>
+        <v>0.0008528733518468158</v>
       </c>
       <c r="F7" t="n">
         <v>0.0008612363675996611</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009948879530524847</v>
+        <v>0.0009948879530524849</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008760310334531474</v>
+        <v>0.0008760310334531466</v>
       </c>
       <c r="I7" t="n">
         <v>0.0009538466389426418</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0009857420430803019</v>
+        <v>0.0009857420430803008</v>
       </c>
       <c r="K7" t="n">
         <v>0.00104921607082365</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009895193920776732</v>
+        <v>0.0009895193920776582</v>
       </c>
       <c r="M7" t="n">
         <v>0.001440950529725462</v>
@@ -7945,22 +7945,22 @@
         <v>0.001047206604076417</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0009125162959435891</v>
+        <v>0.0009125162959435892</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0009671348583888614</v>
+        <v>0.0009671348583888599</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0008887434829189455</v>
+        <v>0.0008887434829189444</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0008938735873428476</v>
+        <v>0.0008938735873428481</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0009378042286655874</v>
+        <v>0.0009378042286655871</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0009405094341905284</v>
+        <v>0.0009405094341905282</v>
       </c>
       <c r="U7" t="n">
         <v>0.001016226264530398</v>
@@ -7969,19 +7969,19 @@
         <v>0.0008506931577156035</v>
       </c>
       <c r="W7" t="n">
-        <v>0.000929868591076316</v>
+        <v>0.0009298685910763159</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0009884179031547694</v>
+        <v>0.0009884179031547664</v>
       </c>
       <c r="Y7" t="n">
         <v>0.0009245608725024586</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.000894474860610411</v>
+        <v>0.0008944748606104103</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0009994623214949188</v>
+        <v>0.0009994623214949182</v>
       </c>
       <c r="AB7" t="n">
         <v>0.001082693294776544</v>
@@ -7994,22 +7994,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0009969080744496035</v>
+        <v>0.0009969080744496003</v>
       </c>
       <c r="C8" t="n">
         <v>0.001036268530338057</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00115778564460555</v>
+        <v>0.001157785644605551</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009983949133282224</v>
+        <v>0.0009983949133282213</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009628886044264163</v>
+        <v>0.0009628886044264159</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001244520594741092</v>
+        <v>0.001244520594741093</v>
       </c>
       <c r="H8" t="n">
         <v>0.001096483731414615</v>
@@ -8024,7 +8024,7 @@
         <v>0.001269668768785118</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001209972090039141</v>
+        <v>0.001209972090039133</v>
       </c>
       <c r="M8" t="n">
         <v>0.001661403227686962</v>
@@ -8033,10 +8033,10 @@
         <v>0.001158575012330406</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001053871512285635</v>
+        <v>0.001053871512285634</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001101141911706361</v>
+        <v>0.001101141911706362</v>
       </c>
       <c r="Q8" t="n">
         <v>0.0009408172477575774</v>
@@ -8045,7 +8045,7 @@
         <v>0.001114326285304316</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001158256926627056</v>
+        <v>0.001158256926627055</v>
       </c>
       <c r="T8" t="n">
         <v>0.001160962132151996</v>
@@ -8060,19 +8060,19 @@
         <v>0.001150348945226351</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001053389260477621</v>
+        <v>0.001053389260477619</v>
       </c>
       <c r="Y8" t="n">
         <v>0.001284784689295582</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0009715900017520843</v>
+        <v>0.0009715900017520826</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001219915019456387</v>
+        <v>0.001219915019456386</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001450143502301905</v>
+        <v>0.001450143502301904</v>
       </c>
     </row>
     <row r="9">
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001117448618796762</v>
+        <v>0.001117448618796757</v>
       </c>
       <c r="C9" t="n">
         <v>0.001110672115133556</v>
@@ -8091,10 +8091,10 @@
         <v>0.001232189229401049</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001125899388669697</v>
+        <v>0.001125899388669695</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009380448376501527</v>
+        <v>0.0009380448376501521</v>
       </c>
       <c r="G9" t="n">
         <v>0.001289744173554986</v>
@@ -8106,16 +8106,16 @@
         <v>0.001248702921699609</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001280598325837269</v>
+        <v>0.001280598325837268</v>
       </c>
       <c r="K9" t="n">
         <v>0.001344072353580616</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001284375674834641</v>
+        <v>0.001284375674834624</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001735806812482431</v>
+        <v>0.00173580681248243</v>
       </c>
       <c r="N9" t="n">
         <v>0.001342062886833384</v>
@@ -8124,19 +8124,19 @@
         <v>0.001238727864416879</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001300163611399252</v>
+        <v>0.001300163611399251</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001183599703421447</v>
+        <v>0.001183599703421445</v>
       </c>
       <c r="R9" t="n">
         <v>0.001188729870099815</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001232660511422554</v>
+        <v>0.001232660511422553</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001235365716947496</v>
+        <v>0.001235365716947495</v>
       </c>
       <c r="U9" t="n">
         <v>0.001311202999798254</v>
@@ -8148,13 +8148,13 @@
         <v>0.001224724873833283</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001283274185911736</v>
+        <v>0.001283274185911732</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001219417155259425</v>
+        <v>0.001219417155259426</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001132303818751407</v>
+        <v>0.001132303818751405</v>
       </c>
       <c r="AA9" t="n">
         <v>0.001294318604251884</v>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.000774741423640079</v>
+        <v>0.0007747414236400788</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008501607613112583</v>
+        <v>0.0008501607613112577</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007773062048503144</v>
+        <v>0.000777306204850314</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007770486851438831</v>
+        <v>0.0007770486851438821</v>
       </c>
       <c r="F2" t="n">
         <v>0.0007765087952950856</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007899252076781402</v>
+        <v>0.0007899252076781394</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007773888321848622</v>
+        <v>0.0007773888321848618</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007771995088419611</v>
+        <v>0.0007771995088419598</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007824645334449775</v>
+        <v>0.0007824645334449774</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007799548827753239</v>
+        <v>0.0007799548827753238</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007837606242955819</v>
+        <v>0.0007837606242955805</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007800306445760282</v>
+        <v>0.0007800306445760284</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007794436846923817</v>
+        <v>0.0007794436846923815</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001094973638889425</v>
+        <v>0.001094973638889427</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007848432881911411</v>
+        <v>0.0007848432881911408</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007787108276297867</v>
+        <v>0.0007787108276297853</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007802237444198291</v>
+        <v>0.0007802237444198302</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007792635415573769</v>
+        <v>0.0007792635415573766</v>
       </c>
       <c r="T2" t="n">
-        <v>0.000777198849131644</v>
+        <v>0.0007771988491316435</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009916737318596742</v>
+        <v>0.0009916737318596757</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007775519600676685</v>
+        <v>0.0007775519600676678</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009579047389561922</v>
+        <v>0.0009579047389561932</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0007915663585622586</v>
+        <v>0.0007915663585622582</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0007927445307689083</v>
+        <v>0.0007927445307689073</v>
       </c>
       <c r="Z2" t="n">
         <v>0.0009235756761960608</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0007803384438317571</v>
+        <v>0.0007803384438317583</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0007912185628929057</v>
+        <v>0.0007912185628929058</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000743334685953109</v>
+        <v>0.0007441065181712041</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008748029507174488</v>
+        <v>0.0008759000830571057</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007617274136923524</v>
+        <v>0.00076315696834869</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007597721328491175</v>
+        <v>0.0007611155839075286</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007560380543820502</v>
+        <v>0.0007572693627875085</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008509246900903038</v>
+        <v>0.0008554952173259469</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000762437462316886</v>
+        <v>0.0007638953974932091</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007610092451007096</v>
+        <v>0.0007624136584457357</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000798205692248912</v>
+        <v>0.0008009199685062806</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007804393744848859</v>
+        <v>0.0007825390662506966</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008073972166864091</v>
+        <v>0.000810440926357243</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0007825783140401188</v>
+        <v>0.0007847683891107711</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0007769874208331435</v>
+        <v>0.0007789529766278952</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001286735934961069</v>
+        <v>0.00128818670645607</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008150942009308519</v>
+        <v>0.0008183859737129371</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007715918803868679</v>
+        <v>0.0007733744880705349</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007827113590955355</v>
+        <v>0.0007848889472258063</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007754009869475375</v>
+        <v>0.0007773082439143721</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000760981976090241</v>
+        <v>0.0007623849305994696</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00111941660510517</v>
+        <v>0.001121019215069843</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007632834390575724</v>
+        <v>0.0007647597058738236</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001097182882547904</v>
+        <v>0.001100321550570466</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008634750211209477</v>
+        <v>0.0008685212712432422</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0008718162491378044</v>
+        <v>0.000877136631749002</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001004781822573527</v>
+        <v>0.00100627985314797</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0007833286672119235</v>
+        <v>0.0007855158650224032</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0008609761546523977</v>
+        <v>0.0008659178710414188</v>
       </c>
     </row>
     <row r="4">
@@ -8505,22 +8505,22 @@
         <v>0.0006979110520702899</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007121328837371477</v>
+        <v>0.0007121328837371479</v>
       </c>
       <c r="D4" t="n">
         <v>0.0007268814356975533</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007239726321484889</v>
+        <v>0.0007239726321484891</v>
       </c>
       <c r="F4" t="n">
         <v>0.0007178743279447244</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008694188776659451</v>
+        <v>0.0008694188776659448</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000727814749451716</v>
+        <v>0.0007278147494517161</v>
       </c>
       <c r="I4" t="n">
         <v>0.0007256762552006064</v>
@@ -8529,58 +8529,58 @@
         <v>0.0007848203076143629</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007567994713125689</v>
+        <v>0.0007567994713125691</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007997870725114808</v>
+        <v>0.0007997870725114806</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007604014653602615</v>
+        <v>0.0007604014653602614</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0007510252538030145</v>
+        <v>0.0007510252538030146</v>
       </c>
       <c r="O4" t="n">
-        <v>0.000728637091106467</v>
+        <v>0.0007286370911064676</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0008120162592618229</v>
+        <v>0.0008120162592618231</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0007427472961501008</v>
+        <v>0.0007427472961501013</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0007598363872697267</v>
+        <v>0.0007598363872697265</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0007489904542231938</v>
+        <v>0.0007489904542231936</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007256688034690912</v>
+        <v>0.0007256688034690914</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0007291500528209317</v>
+        <v>0.0007291500528209318</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007275262562159505</v>
+        <v>0.0007275262562159506</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0008038420434789167</v>
+        <v>0.0008038420434789165</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0008879564318687706</v>
+        <v>0.0008879564318687713</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0008952677345499991</v>
+        <v>0.000895267734549999</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.000730661590506329</v>
+        <v>0.0007306615905063289</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0007611319698917925</v>
+        <v>0.0007611319698917924</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0008830596795341609</v>
+        <v>0.0008830596795341612</v>
       </c>
     </row>
     <row r="5">
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009907959528928443</v>
+        <v>0.0009907959528928441</v>
       </c>
       <c r="C5" t="n">
         <v>0.001271775425048392</v>
@@ -8602,73 +8602,73 @@
         <v>0.001436401930907799</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001390285837260459</v>
+        <v>0.001390285837260458</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003621316897273135</v>
+        <v>0.003621316897273122</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001627529352628574</v>
+        <v>0.001627529352628573</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001549799583901969</v>
+        <v>0.001549799583901968</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002404234590882197</v>
+        <v>0.002404234590882191</v>
       </c>
       <c r="K5" t="n">
         <v>0.00197842431298992</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002633052136311427</v>
+        <v>0.002633052136311429</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002097137021188358</v>
+        <v>0.002097137021188359</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001978125036779732</v>
+        <v>0.001978125036779729</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001469601290281302</v>
+        <v>0.001469601290281303</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002833777003324759</v>
+        <v>0.002833777003324758</v>
       </c>
       <c r="Q5" t="n">
         <v>0.00174615521786707</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002215125245016382</v>
+        <v>0.002215125245016384</v>
       </c>
       <c r="S5" t="n">
         <v>0.001786283622534743</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001537976315085601</v>
+        <v>0.001537976315085606</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001607280982871513</v>
+        <v>0.001607280982871516</v>
       </c>
       <c r="V5" t="n">
         <v>0.001493049749824281</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002891003602879061</v>
+        <v>0.002891003602879057</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004383122342449674</v>
+        <v>0.004383122342449672</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.00458354417511336</v>
+        <v>0.004583544175113355</v>
       </c>
       <c r="Z5" t="n">
         <v>0.001498295008728734</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002133717348515392</v>
+        <v>0.002133717348515389</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004560515898366022</v>
+        <v>0.004560515898366029</v>
       </c>
     </row>
     <row r="6">
@@ -8678,25 +8678,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000943415833384906</v>
+        <v>0.0009434158333849064</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009576376650517634</v>
+        <v>0.0009576376650517638</v>
       </c>
       <c r="D6" t="n">
         <v>0.0009723862170121696</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008559397719258075</v>
+        <v>0.0008559397719258072</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008498414677220422</v>
+        <v>0.0008498414677220425</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001001386017443264</v>
+        <v>0.001001386017443263</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0008597818892290339</v>
+        <v>0.000859781889229034</v>
       </c>
       <c r="I6" t="n">
         <v>0.0009711810365152229</v>
@@ -8711,25 +8711,25 @@
         <v>0.001045291853826097</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0008923686051375797</v>
+        <v>0.0008923686051375798</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0008835191130204683</v>
+        <v>0.0008835191130204685</v>
       </c>
       <c r="O6" t="n">
         <v>0.0009756422534502374</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0009353777616978442</v>
+        <v>0.0009353777616978444</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0008747144359274194</v>
+        <v>0.0008747144359274193</v>
       </c>
       <c r="R6" t="n">
         <v>0.001005341168584343</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0008809575940005118</v>
+        <v>0.0008809575940005121</v>
       </c>
       <c r="T6" t="n">
         <v>0.0008576359432464095</v>
@@ -8738,10 +8738,10 @@
         <v>0.0009806515285144157</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0008594933959932689</v>
+        <v>0.0008594933959932688</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0009456186775155749</v>
+        <v>0.0009456186775155719</v>
       </c>
       <c r="X6" t="n">
         <v>0.001133461213183387</v>
@@ -8750,10 +8750,10 @@
         <v>0.001040856261244292</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0009761663718209449</v>
+        <v>0.0009761663718209452</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0008930991096691107</v>
+        <v>0.0008930991096691109</v>
       </c>
       <c r="AB6" t="n">
         <v>0.001015245187786513</v>
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007781398320658402</v>
+        <v>0.0007781398320658406</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000792361663732698</v>
+        <v>0.0007923616637326984</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008071102156931034</v>
+        <v>0.0008071102156931037</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008042014121440395</v>
+        <v>0.0008042014121440396</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0007981031079402748</v>
+        <v>0.0007981031079402749</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009496476576614957</v>
+        <v>0.0009496476576614948</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008080435294472666</v>
+        <v>0.0008080435294472665</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008059050351961565</v>
+        <v>0.0008059050351961566</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008650490876099137</v>
+        <v>0.0008650490876099134</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008370282513081191</v>
+        <v>0.0008370282513081196</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008800158525070313</v>
+        <v>0.0008800158525070316</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0008406302453558118</v>
+        <v>0.0008406302453558119</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0008312540337985655</v>
+        <v>0.0008312540337985656</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0008088569893186842</v>
+        <v>0.0008088569893186843</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0008922361574740399</v>
+        <v>0.0008922361574740401</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0008229760761456514</v>
+        <v>0.0008229760761456515</v>
       </c>
       <c r="R7" t="n">
-        <v>0.000840065167265277</v>
+        <v>0.0008400651672652773</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0008292192342187441</v>
+        <v>0.0008292192342187444</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0008058975834646414</v>
+        <v>0.0008058975834646419</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0008152452669410665</v>
+        <v>0.0008152452669410667</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0008077550362115009</v>
+        <v>0.000807755036211501</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0008840708234744667</v>
+        <v>0.0008840708234744668</v>
       </c>
       <c r="X7" t="n">
-        <v>0.000968185211864321</v>
+        <v>0.0009681852118643214</v>
       </c>
       <c r="Y7" t="n">
         <v>0.0009814932089244172</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008108903705018795</v>
+        <v>0.0008108903705018796</v>
       </c>
       <c r="AA7" t="n">
         <v>0.000841360749887343</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0009632884595297109</v>
+        <v>0.0009632884595297112</v>
       </c>
     </row>
     <row r="8">
@@ -8854,28 +8854,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008469936118189542</v>
+        <v>0.0008469936118189543</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009843464256894946</v>
+        <v>0.0009843464256894939</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009990949776498997</v>
+        <v>0.000999094977649899</v>
       </c>
       <c r="E8" t="n">
         <v>0.0009306225582175934</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008861392556563822</v>
+        <v>0.0008861392556563819</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001167164430900819</v>
+        <v>0.001167164430900816</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001000028291404063</v>
+        <v>0.001000028291404062</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009978897971529533</v>
+        <v>0.0009978897971529522</v>
       </c>
       <c r="J8" t="n">
         <v>0.00105703384956671</v>
@@ -8890,31 +8890,31 @@
         <v>0.001032615007312606</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0009277916851783683</v>
+        <v>0.0009277916851783687</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0009316332172129107</v>
+        <v>0.0009316332172129108</v>
       </c>
       <c r="P8" t="n">
         <v>0.001008582853392344</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0008676318075727783</v>
+        <v>0.0008676318075727782</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001032049929222074</v>
+        <v>0.001032049929222073</v>
       </c>
       <c r="S8" t="n">
         <v>0.001021203996175541</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0009978823454214383</v>
+        <v>0.0009978823454214378</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0009471676348035991</v>
+        <v>0.0009471676348035986</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0009659824928193603</v>
+        <v>0.0009659824928193605</v>
       </c>
       <c r="W8" t="n">
         <v>0.001076079784179958</v>
@@ -8929,7 +8929,7 @@
         <v>0.0008774569290463679</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001033345511844139</v>
+        <v>0.001033345511844138</v>
       </c>
       <c r="AB8" t="n">
         <v>0.001283893828427596</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009306620245184832</v>
+        <v>0.0009306620245184839</v>
       </c>
       <c r="C9" t="n">
         <v>0.001021615927814316</v>
@@ -8951,70 +8951,70 @@
         <v>0.001036364479774721</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001015746266059335</v>
+        <v>0.001015746266059336</v>
       </c>
       <c r="F9" t="n">
-        <v>0.000850468938599612</v>
+        <v>0.0008504689385996124</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001178901972420599</v>
+        <v>0.001178901972420598</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001037297793528883</v>
+        <v>0.001037297793528884</v>
       </c>
       <c r="I9" t="n">
         <v>0.001035159299277774</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00109430335169153</v>
+        <v>0.001094303351691531</v>
       </c>
       <c r="K9" t="n">
         <v>0.001066282515389737</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001109270116588648</v>
+        <v>0.001109270116588649</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001069884509437429</v>
+        <v>0.00106988450943743</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001060508297880182</v>
+        <v>0.001060508297880183</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001063549110721821</v>
+        <v>0.001063549110721822</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001152458633747096</v>
+        <v>0.001152458633747098</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001052230390904753</v>
+        <v>0.001052230390904754</v>
       </c>
       <c r="R9" t="n">
         <v>0.001069319431346895</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001058473498300361</v>
+        <v>0.001058473498300362</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001035151847546259</v>
+        <v>0.00103515184754626</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001044629791276966</v>
+        <v>0.001044629791276967</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001125556501873968</v>
+        <v>0.001125556501873969</v>
       </c>
       <c r="W9" t="n">
         <v>0.001113325087556084</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001197439475945937</v>
+        <v>0.001197439475945938</v>
       </c>
       <c r="Y9" t="n">
         <v>0.001210747473006034</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0009938820387967436</v>
+        <v>0.0009938820387967442</v>
       </c>
       <c r="AA9" t="n">
         <v>0.001070615013968961</v>

--- a/Results/Phase 2/Ammonia/ammonia eutrophication marine results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia eutrophication marine results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008191977596777323</v>
+        <v>0.0008191977596777324</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008751374624595905</v>
+        <v>0.0008751374624595904</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008170852271314246</v>
+        <v>0.0008170852271314243</v>
       </c>
       <c r="E2" t="n">
         <v>0.0008044953189155441</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008109388749186291</v>
+        <v>0.0008109388749186295</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008168374034983456</v>
+        <v>0.0008168374034983458</v>
       </c>
       <c r="H2" t="n">
         <v>0.0008147556569441047</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008209869303415306</v>
+        <v>0.0008209869303415305</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008172157901638145</v>
+        <v>0.0008172157901638144</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008354634264627713</v>
+        <v>0.0008354634264627712</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008189981226827053</v>
+        <v>0.0008189981226827052</v>
       </c>
       <c r="M2" t="n">
         <v>0.0008616840143724347</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008251109770839524</v>
+        <v>0.0008251109770839516</v>
       </c>
       <c r="O2" t="n">
         <v>0.001156057744657415</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008133788181396231</v>
+        <v>0.0008133788181396232</v>
       </c>
       <c r="Q2" t="n">
         <v>0.0008094275612015407</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0008110242504805602</v>
+        <v>0.0008110242504805612</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008161261861397989</v>
+        <v>0.0008161261861397982</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008213028024916894</v>
+        <v>0.0008213028024916889</v>
       </c>
       <c r="U2" t="n">
         <v>0.001058867916152201</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008076922198721062</v>
+        <v>0.0008076922198721065</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001001402718253393</v>
+        <v>0.001001402718253392</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008090862376229411</v>
+        <v>0.0008090862376229409</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008115477971157748</v>
+        <v>0.000811547797115775</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009613440882894062</v>
+        <v>0.0009613440882894056</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008240230536421575</v>
+        <v>0.0008240230536421578</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008282389230598815</v>
+        <v>0.0008282389230598812</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001370378606964215</v>
+        <v>0.0009845717681953214</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001028514520253634</v>
+        <v>0.0009193156356373201</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001328520217516432</v>
+        <v>0.0009761762004543136</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001137034263707991</v>
+        <v>0.0009763848755472411</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001186464202628618</v>
+        <v>0.0009271900233737826</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001316438567181745</v>
+        <v>0.0009677926605487965</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001276720151179496</v>
+        <v>0.0009597855758461187</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001420568054696552</v>
+        <v>0.001008983804871403</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001328019203835043</v>
+        <v>0.0009733370830894315</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001756482862292176</v>
+        <v>0.001125145787793697</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001368912689994283</v>
+        <v>0.0009876568430350447</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002368593494845067</v>
+        <v>0.001340986979790437</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001513374477298547</v>
+        <v>0.001038918716914487</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001663645894623588</v>
+        <v>0.001306894177120512</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001235895390236504</v>
+        <v>0.0009400193065156086</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001149009002893014</v>
+        <v>0.0009127534456536932</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001188219875371358</v>
+        <v>0.0009279323353308638</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001300968785403625</v>
+        <v>0.0009624382385951492</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001427317467918376</v>
+        <v>0.001010934703375903</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001809953524819415</v>
+        <v>0.001289361311113195</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001105841446431892</v>
+        <v>0.0008954712350326341</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001433410955900727</v>
+        <v>0.001133188739771057</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001141471073932742</v>
+        <v>0.0009103442785492167</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001197309407109772</v>
+        <v>0.0009286749582143173</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001284490776757037</v>
+        <v>0.001057384355553891</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001486690230369588</v>
+        <v>0.001029096203615573</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001586849629045399</v>
+        <v>0.001070886965371396</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005593295849191558</v>
+        <v>0.005593295849191543</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001900778295836163</v>
+        <v>0.00190077829583616</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00576392770319697</v>
+        <v>0.005763927703196971</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002590349745666967</v>
+        <v>0.002590349745666982</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0043771138504672</v>
+        <v>0.004377113850467194</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005218478556980454</v>
+        <v>0.00521847855698045</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005404724885954343</v>
+        <v>0.005404724885954345</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006774685692152147</v>
+        <v>0.006774685692152142</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005496147666968335</v>
+        <v>0.005496147666968343</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01010003090329231</v>
+        <v>0.01010003090329229</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005908081320113785</v>
+        <v>0.005908081320113712</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01661638359174124</v>
+        <v>0.01661638359174126</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007480407395433479</v>
+        <v>0.007480407395433481</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005081144165067233</v>
+        <v>0.005081144165067237</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004422887494199611</v>
+        <v>0.00442288749419961</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003853703492926948</v>
+        <v>0.003853703492926942</v>
       </c>
       <c r="R4" t="n">
-        <v>0.004401595158081978</v>
+        <v>0.004401595158081979</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005080832793281301</v>
+        <v>0.005080832793281317</v>
       </c>
       <c r="T4" t="n">
-        <v>0.006802656671357147</v>
+        <v>0.006802656671357139</v>
       </c>
       <c r="U4" t="n">
-        <v>0.007833283014044321</v>
+        <v>0.007833283014044319</v>
       </c>
       <c r="V4" t="n">
-        <v>0.003195934376731541</v>
+        <v>0.00319593437673154</v>
       </c>
       <c r="W4" t="n">
-        <v>0.004731760311372978</v>
+        <v>0.004731760311372975</v>
       </c>
       <c r="X4" t="n">
-        <v>0.003800385145922585</v>
+        <v>0.003800385145922559</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.004257021451311264</v>
+        <v>0.004257021451311265</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.003481480694567351</v>
+        <v>0.003481480694567355</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.007147653053885679</v>
+        <v>0.007147653053885665</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.008769263119199405</v>
+        <v>0.008769263119199398</v>
       </c>
     </row>
     <row r="5">
@@ -850,70 +850,70 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001168753640237081</v>
+        <v>0.001168753640237084</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001125496753874912</v>
+        <v>0.001125496753874914</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001306409895412868</v>
+        <v>0.001306409895412869</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001078197369748197</v>
+        <v>0.001078197369748198</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001100628398252617</v>
+        <v>0.001100628398252619</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001337102481458291</v>
+        <v>0.001337102481458292</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001280096328491851</v>
+        <v>0.001280096328491852</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001350481428043169</v>
+        <v>0.001350481428043171</v>
       </c>
       <c r="J5" t="n">
         <v>0.001307589094401951</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001514000111249817</v>
+        <v>0.001514000111249814</v>
       </c>
       <c r="L5" t="n">
         <v>0.001328016930640003</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001807166292142827</v>
+        <v>0.001807166292142826</v>
       </c>
       <c r="N5" t="n">
-        <v>0.007480407395433479</v>
+        <v>0.001271860743101422</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001217411846083057</v>
+        <v>0.001217411846083058</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00116531366983071</v>
+        <v>0.001165313669830714</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001026652725033327</v>
+        <v>0.001026652725033329</v>
       </c>
       <c r="R5" t="n">
         <v>0.001237948375954343</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001295577086231802</v>
+        <v>0.001295577086231803</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001354049349287582</v>
+        <v>0.001354049349287579</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001352064042985377</v>
+        <v>0.001352064042985379</v>
       </c>
       <c r="V5" t="n">
         <v>0.001154188113233049</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001267660127207994</v>
+        <v>0.001267660127207996</v>
       </c>
       <c r="X5" t="n">
         <v>0.00103760078967935</v>
@@ -922,10 +922,10 @@
         <v>0.001404356969614994</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001048614062771725</v>
+        <v>0.001048614062771727</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00138477583740947</v>
+        <v>0.001384775837409469</v>
       </c>
       <c r="AB5" t="n">
         <v>0.001599695330711556</v>
@@ -938,67 +938,67 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001349311679824672</v>
+        <v>0.001349311679824669</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001264772231570835</v>
+        <v>0.001264772231570836</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001445685373108792</v>
+        <v>0.001445685373108794</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001275726599861323</v>
+        <v>0.001275726599861321</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001099083439388211</v>
+        <v>0.001099083439388209</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001442886020298377</v>
+        <v>0.001442886020298379</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001419371806187775</v>
+        <v>0.001419371806187774</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001489756905739093</v>
+        <v>0.001489756905739091</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001446864572097875</v>
+        <v>0.001446864572097876</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001653275588945742</v>
+        <v>0.001653275588945741</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001467292408335926</v>
+        <v>0.001467292408335925</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001946441769838745</v>
+        <v>0.001946441769838744</v>
       </c>
       <c r="N6" t="n">
-        <v>0.007480407395433479</v>
+        <v>0.001536339910849978</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001487329818576248</v>
+        <v>0.001487329818576246</v>
       </c>
       <c r="P6" t="n">
         <v>0.001452331452002318</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001359188442860104</v>
+        <v>0.001359188442860105</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001377223853650267</v>
+        <v>0.001377223853650269</v>
       </c>
       <c r="S6" t="n">
         <v>0.001434852563927726</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001493324826983505</v>
+        <v>0.001493324826983506</v>
       </c>
       <c r="U6" t="n">
         <v>0.001570232343024136</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001476421997588037</v>
+        <v>0.001476421997588036</v>
       </c>
       <c r="W6" t="n">
         <v>0.001406903861955146</v>
@@ -1007,10 +1007,10 @@
         <v>0.001355333106893499</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001383137553738361</v>
+        <v>0.001383137553738365</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001279916631929368</v>
+        <v>0.001279916631929371</v>
       </c>
       <c r="AA6" t="n">
         <v>0.001524051315105395</v>
@@ -1182,85 +1182,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007650584462983491</v>
+        <v>0.000765058446298349</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008212677122434724</v>
+        <v>0.0008212677122434726</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007665548504688233</v>
+        <v>0.0007665548504688234</v>
       </c>
       <c r="E2" t="n">
         <v>0.0007657906768060003</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000767322906052173</v>
+        <v>0.0007673229060521728</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007676803384907471</v>
+        <v>0.0007676803384907469</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007668571827509981</v>
+        <v>0.0007668571827509978</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007669109217357425</v>
+        <v>0.0007669109217357431</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007682550703562031</v>
+        <v>0.0007682550703562017</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007685627425270393</v>
+        <v>0.0007685627425270397</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007697120513130353</v>
+        <v>0.0007697120513130352</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007669609972165921</v>
+        <v>0.0007669609972165924</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007678189958598069</v>
+        <v>0.0007678189958598063</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001087413970790261</v>
+        <v>0.001087413970790262</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007686473515066228</v>
+        <v>0.0007686473515066217</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007662413073582058</v>
+        <v>0.0007662413073582059</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007700950348917509</v>
+        <v>0.0007700950348917508</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00076882699381363</v>
+        <v>0.0007688269938136304</v>
       </c>
       <c r="T2" t="n">
         <v>0.0007674633517963346</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009254643199282657</v>
+        <v>0.0009254643199282647</v>
       </c>
       <c r="V2" t="n">
         <v>0.0007688109322927302</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0008983526122869454</v>
+        <v>0.0008983526122869442</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0007840747526399682</v>
+        <v>0.0007840747526399684</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0007758022883556362</v>
+        <v>0.0007758022883556359</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009143334867103295</v>
+        <v>0.0009143334867103298</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0007744681120121975</v>
+        <v>0.0007744681120121974</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0007654045821162592</v>
+        <v>0.0007654045821162595</v>
       </c>
     </row>
     <row r="3">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008345341444400532</v>
+        <v>0.0007807460311321491</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009166260094981972</v>
+        <v>0.0008453201070262033</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008698797764673824</v>
+        <v>0.000793158387650404</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0009658374988618975</v>
+        <v>0.0009012549889655571</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008881407812915465</v>
+        <v>0.0007995098225532055</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008949059567177967</v>
+        <v>0.0008008762938408598</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008774034726349528</v>
+        <v>0.0007962401505949098</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008783279964862627</v>
+        <v>0.0007962698578192289</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009087579122779573</v>
+        <v>0.0008059618040728556</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009164786186377754</v>
+        <v>0.0008083448029265583</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009423405483344516</v>
+        <v>0.0008168809305737545</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0008850577889674323</v>
+        <v>0.000798315948753137</v>
       </c>
       <c r="N3" t="n">
-        <v>0.000899070230607327</v>
+        <v>0.0008033692801490927</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001278373365735047</v>
+        <v>0.001139808617045361</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0009169422693248688</v>
+        <v>0.0008082459293284318</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008624083578735989</v>
+        <v>0.0007903373038876447</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0009530563658009485</v>
+        <v>0.0008226015943159275</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009215414558364313</v>
+        <v>0.0008097391787235462</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000891160016944934</v>
+        <v>0.0008007738053350026</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001063223723428161</v>
+        <v>0.000961902447994351</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0009210212490167546</v>
+        <v>0.0008096317323770377</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001114192948098509</v>
+        <v>0.0009602821323663119</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001278001868526698</v>
+        <v>0.0009317587117254831</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0010843573986097</v>
+        <v>0.0008674580924811164</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001047414373425415</v>
+        <v>0.0009489575315553061</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001053193801440383</v>
+        <v>0.0008565594392030977</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0008452363533800731</v>
+        <v>0.000784973120065605</v>
       </c>
     </row>
     <row r="4">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0009404051364150462</v>
+        <v>0.0009404051364150449</v>
       </c>
       <c r="C4" t="n">
         <v>0.001193187771075064</v>
@@ -1370,73 +1370,73 @@
         <v>0.001062664014815809</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001436012780400403</v>
+        <v>0.001436012780400402</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001408161688885879</v>
+        <v>0.001408161688885877</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001373796240708816</v>
+        <v>0.001373796240708817</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00135777879062234</v>
+        <v>0.001357778790622338</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001555308210601824</v>
+        <v>0.001555308210601823</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001610916980552957</v>
+        <v>0.001610916980552956</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001797264303020511</v>
+        <v>0.00179726430302051</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001412184048092073</v>
+        <v>0.001412184048092071</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001528723260254151</v>
+        <v>0.00152872326025415</v>
       </c>
       <c r="O4" t="n">
         <v>0.001913352905961197</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001577300057250971</v>
+        <v>0.00157730005725097</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001185168400486494</v>
+        <v>0.001185168400486493</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002052086134409261</v>
+        <v>0.00205208613440926</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001616404641834513</v>
+        <v>0.001616404641834511</v>
       </c>
       <c r="T4" t="n">
         <v>0.001474048533742304</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001501119916484239</v>
+        <v>0.001501119916484235</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001613004806120548</v>
+        <v>0.001613004806120544</v>
       </c>
       <c r="W4" t="n">
         <v>0.002267650508365526</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004665733041944443</v>
+        <v>0.004665733041944444</v>
       </c>
       <c r="Y4" t="n">
         <v>0.003141152497013655</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001431839570568369</v>
+        <v>0.00143183957056837</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.00285917377332336</v>
+        <v>0.002859173773323358</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.00108158961377011</v>
+        <v>0.001081589613770109</v>
       </c>
     </row>
     <row r="5">
@@ -1446,67 +1446,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0008328986957533295</v>
+        <v>0.0008328986957533291</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000963936978209982</v>
+        <v>0.0009639369782099822</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009679327305294591</v>
+        <v>0.0009679327305294587</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0008963995189962135</v>
+        <v>0.000896399518996213</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0008768803114114633</v>
+        <v>0.0008768803114114625</v>
       </c>
       <c r="G5" t="n">
         <v>0.0010051409635397</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009713477127363404</v>
+        <v>0.00097134771273634</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009719547192901828</v>
+        <v>0.0009719547192901817</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009868560522586949</v>
+        <v>0.0009868560522586938</v>
       </c>
       <c r="K5" t="n">
         <v>0.0009906127950029936</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001003594766448971</v>
+        <v>0.00100359476644897</v>
       </c>
       <c r="M5" t="n">
-        <v>0.000975273644839402</v>
+        <v>0.0009752736448394018</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001528723260254151</v>
+        <v>0.0008906401887892265</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0009470438369976221</v>
+        <v>0.0009470438369976216</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0009189930582200391</v>
+        <v>0.0009189930582200383</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0008230441272083769</v>
+        <v>0.0008230441272083765</v>
       </c>
       <c r="R5" t="n">
         <v>0.001007920742151716</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0009935976348466318</v>
+        <v>0.0009935976348466311</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0009781946709549628</v>
+        <v>0.0009781946709549625</v>
       </c>
       <c r="U5" t="n">
-        <v>0.000928114411832299</v>
+        <v>0.0009281144118322983</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0009592256732760676</v>
+        <v>0.000959225673276063</v>
       </c>
       <c r="W5" t="n">
         <v>0.001025438325232023</v>
@@ -1518,10 +1518,10 @@
         <v>0.00118971648519669</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.000863327061192289</v>
+        <v>0.0008633270611922878</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00105731665994203</v>
+        <v>0.001057316659942029</v>
       </c>
       <c r="AB5" t="n">
         <v>0.00107942203747952</v>
@@ -1534,70 +1534,70 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0008819411225126999</v>
+        <v>0.0008819411225126993</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009598279712216128</v>
+        <v>0.0009598279712216118</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000963823723541089</v>
+        <v>0.0009638237235410883</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0009401949384832082</v>
+        <v>0.0009401949384832081</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008227025099361588</v>
+        <v>0.0008227025099361584</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009765366718023501</v>
+        <v>0.00097653667180235</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009672387057479693</v>
+        <v>0.0009672387057479689</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009678457123018117</v>
+        <v>0.0009678457123018111</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009827470452703241</v>
+        <v>0.0009827470452703237</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0009865037880146233</v>
+        <v>0.0009865037880146226</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000999485759460601</v>
+        <v>0.0009994857594606001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0009711646378510353</v>
+        <v>0.0009711646378510346</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001528723260254151</v>
+        <v>0.0009781028272678508</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001030876145904243</v>
+        <v>0.001030876145904242</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001013677182103431</v>
+        <v>0.00101367718210343</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0009602821531732705</v>
+        <v>0.0009602821531732703</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001003811735163346</v>
+        <v>0.001003811735163345</v>
       </c>
       <c r="S6" t="n">
         <v>0.0009894886278582606</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0009740856639665937</v>
+        <v>0.0009740856639665928</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0009817372922580466</v>
+        <v>0.0009817372922580458</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001062470441843618</v>
+        <v>0.001062470441843615</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001021306102040842</v>
+        <v>0.001021306102040841</v>
       </c>
       <c r="X6" t="n">
         <v>0.001161719078117353</v>
@@ -1606,13 +1606,13 @@
         <v>0.00106827778850424</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0009403667068723132</v>
+        <v>0.0009403667068723123</v>
       </c>
       <c r="AA6" t="n">
         <v>0.001053207652953659</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0009519148411938105</v>
+        <v>0.0009519148411938096</v>
       </c>
     </row>
   </sheetData>
@@ -1778,85 +1778,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008057907707960666</v>
+        <v>0.000805790770796066</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008656370131322838</v>
+        <v>0.0008656370131322846</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008041607062938207</v>
+        <v>0.0008041607062938202</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007950121825471837</v>
+        <v>0.0007950121825471831</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007963040480856693</v>
+        <v>0.0007963040480856684</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008069216457222751</v>
+        <v>0.000806921645722274</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007959424899458536</v>
+        <v>0.000795942489945854</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000802119877902239</v>
+        <v>0.0008021198779022387</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000807409238206975</v>
+        <v>0.0008074092382069739</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008207618758797308</v>
+        <v>0.0008207618758797302</v>
       </c>
       <c r="L2" t="n">
         <v>0.0008075761518959719</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008473499417133624</v>
+        <v>0.0008473499417133625</v>
       </c>
       <c r="N2" t="n">
-        <v>0.000807256026278854</v>
+        <v>0.0008072560262788535</v>
       </c>
       <c r="O2" t="n">
         <v>0.001134441277833101</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008063146938162802</v>
+        <v>0.000806314693816279</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007975292341677644</v>
+        <v>0.0007975292341677637</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007963507486798184</v>
+        <v>0.0007963507486798178</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008065837652407063</v>
+        <v>0.0008065837652407066</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008052894894385611</v>
+        <v>0.0008052894894385605</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001028243291928682</v>
+        <v>0.001028243291928681</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007946068651049406</v>
+        <v>0.0007946068651049397</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009831643668940506</v>
+        <v>0.00098316436689405</v>
       </c>
       <c r="X2" t="n">
         <v>0.0008024325156202317</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.000801209231710176</v>
+        <v>0.0008012092317101751</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009464336382480251</v>
+        <v>0.0009464336382480246</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.000808842152283607</v>
+        <v>0.0008088421522836061</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008181016318124944</v>
+        <v>0.0008181016318124946</v>
       </c>
     </row>
     <row r="3">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001252793452852099</v>
+        <v>0.0009381544702715438</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00102282345687277</v>
+        <v>0.0009101396873823064</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001220727151074705</v>
+        <v>0.0009321902504346458</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001112396641996179</v>
+        <v>0.0009632309522999552</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001038096514403363</v>
+        <v>0.0008682447691017972</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001279191041897124</v>
+        <v>0.0009482564918252253</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001030037200259198</v>
+        <v>0.0008662548333918221</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001173643945750753</v>
+        <v>0.0009161001922875138</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001293511997501838</v>
+        <v>0.0009549780160626642</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0016064974115468</v>
+        <v>0.00106014963265217</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001296701960663012</v>
+        <v>0.0009564203305205935</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002227637309814598</v>
+        <v>0.001284365555723931</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001291259927218328</v>
+        <v>0.0009555428934748044</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001530394615713292</v>
+        <v>0.001250212945735299</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001264328269634097</v>
+        <v>0.0009431774707222929</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001065327106634996</v>
+        <v>0.000877212517365659</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001039112599930268</v>
+        <v>0.0008691831090012175</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001272284715680018</v>
+        <v>0.0009458050581485118</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001247276769760987</v>
+        <v>0.0009413543432837056</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001653053337572396</v>
+        <v>0.001218412400482379</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0009954771269258711</v>
+        <v>0.0008512331924122999</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001489218921839101</v>
+        <v>0.001137681128325352</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001180010843889043</v>
+        <v>0.0009172409263378117</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001150041971126246</v>
+        <v>0.0009056514357996459</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001209581795422893</v>
+        <v>0.001022980284383948</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001327029252307841</v>
+        <v>0.0009670420644664206</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001543378581109808</v>
+        <v>0.001049291425619782</v>
       </c>
     </row>
     <row r="4">
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004332495929653412</v>
+        <v>0.004332495929653428</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001843038223319833</v>
+        <v>0.001843038223319834</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004491706436884291</v>
+        <v>0.004491706436884279</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002295043065080733</v>
+        <v>0.002295043065080778</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002731828571224879</v>
+        <v>0.002731828571224883</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004651268803230904</v>
+        <v>0.004651268803230885</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002719933808068376</v>
+        <v>0.002719933808068377</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00407201650657509</v>
+        <v>0.004072016506575091</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0049564942484932</v>
+        <v>0.004956494248493201</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007687211864792335</v>
+        <v>0.007687211864792342</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005001503575174098</v>
+        <v>0.005001503575174457</v>
       </c>
       <c r="M4" t="n">
         <v>0.01427545077610602</v>
       </c>
       <c r="N4" t="n">
-        <v>0.005052845882567772</v>
+        <v>0.005052845882567773</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003803951754101939</v>
+        <v>0.003803951754101944</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004506393636914404</v>
+        <v>0.004506393636914406</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002934916703817223</v>
+        <v>0.002934916703817222</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002783219660079236</v>
+        <v>0.002783219660079233</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00459585444513651</v>
+        <v>0.004595854445136511</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004742351123484613</v>
+        <v>0.004742351123484615</v>
       </c>
       <c r="U4" t="n">
-        <v>0.006191524244866185</v>
+        <v>0.006191524244866183</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002120702411608036</v>
+        <v>0.002120702411608034</v>
       </c>
       <c r="W4" t="n">
-        <v>0.00519684754640601</v>
+        <v>0.005196847546406013</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004040891442841182</v>
+        <v>0.004040891442841188</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003649998634552733</v>
+        <v>0.003649998634552738</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002739353623832797</v>
+        <v>0.002739353623832843</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.005306834441317693</v>
+        <v>0.005306834441317701</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.007923973051566262</v>
+        <v>0.007923973051566304</v>
       </c>
     </row>
     <row r="5">
@@ -2048,10 +2048,10 @@
         <v>0.001072498470096242</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001203514652981022</v>
+        <v>0.001203514652981023</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00102349425986506</v>
+        <v>0.001023494259865063</v>
       </c>
       <c r="F5" t="n">
         <v>0.0009931911449614062</v>
@@ -2063,7 +2063,7 @@
         <v>0.001110686118764432</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001180462557470665</v>
+        <v>0.001180462557470664</v>
       </c>
       <c r="J5" t="n">
         <v>0.001239852295858855</v>
@@ -2072,22 +2072,22 @@
         <v>0.001391032500369192</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001242093682239924</v>
+        <v>0.001242093682239938</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001688492647434627</v>
+        <v>0.001688492647434626</v>
       </c>
       <c r="N5" t="n">
-        <v>0.005052845882567772</v>
+        <v>0.001126842187848516</v>
       </c>
       <c r="O5" t="n">
         <v>0.001115014590179017</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001139367796934584</v>
+        <v>0.001139367796934586</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0009562921833498051</v>
+        <v>0.0009562921833498064</v>
       </c>
       <c r="R5" t="n">
         <v>0.001115297588972856</v>
@@ -2096,7 +2096,7 @@
         <v>0.001230884218448275</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001216264777866774</v>
+        <v>0.001216264777866775</v>
       </c>
       <c r="U5" t="n">
         <v>0.001241228863881317</v>
@@ -2108,19 +2108,19 @@
         <v>0.001250400118109298</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001024876241422289</v>
+        <v>0.001024876241422291</v>
       </c>
       <c r="Y5" t="n">
         <v>0.001313240081480578</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0009807906226433508</v>
+        <v>0.0009807906226433516</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001256393739007204</v>
+        <v>0.001256393739007205</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001509630545986567</v>
+        <v>0.001509630545986568</v>
       </c>
     </row>
     <row r="6">
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001200702825573835</v>
+        <v>0.001200702825573837</v>
       </c>
       <c r="C6" t="n">
         <v>0.001147915674071766</v>
@@ -2139,10 +2139,10 @@
         <v>0.001278931856956547</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001153290593516182</v>
+        <v>0.001153290593516185</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009674026586575506</v>
+        <v>0.00096740265865755</v>
       </c>
       <c r="G6" t="n">
         <v>0.001310117876086874</v>
@@ -2157,25 +2157,25 @@
         <v>0.001315269499834379</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001466449704344717</v>
+        <v>0.001466449704344718</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001317510886215449</v>
+        <v>0.001317510886215446</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00176390985141013</v>
+        <v>0.001763909851410129</v>
       </c>
       <c r="N6" t="n">
-        <v>0.005052845882567772</v>
+        <v>0.001313894920105036</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001303415647764704</v>
+        <v>0.001303415647764703</v>
       </c>
       <c r="P6" t="n">
         <v>0.001342254154139897</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001204026266855896</v>
+        <v>0.001204026266855895</v>
       </c>
       <c r="R6" t="n">
         <v>0.00119071479294838</v>
@@ -2184,7 +2184,7 @@
         <v>0.001306301422423798</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0012916819818423</v>
+        <v>0.001291681981842301</v>
       </c>
       <c r="U6" t="n">
         <v>0.001387011928140876</v>
@@ -2196,7 +2196,7 @@
         <v>0.001325789019079186</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001259411148291373</v>
+        <v>0.001259411148291379</v>
       </c>
       <c r="Y6" t="n">
         <v>0.001245593593788887</v>
@@ -2205,10 +2205,10 @@
         <v>0.001144631558818622</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.00133181094298273</v>
+        <v>0.001331810942982731</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001434612296055597</v>
+        <v>0.001434612296055598</v>
       </c>
     </row>
   </sheetData>
@@ -2374,85 +2374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008004687498591036</v>
+        <v>0.0008004687498591045</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008640106301237233</v>
+        <v>0.0008640106301237237</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008060005435880577</v>
+        <v>0.0008060005435880586</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007943203780878639</v>
+        <v>0.0007943203780878647</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007942341669401851</v>
+        <v>0.0007942341669401857</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008045239112090644</v>
+        <v>0.0008045239112090651</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007917467336407748</v>
+        <v>0.0007917467336407756</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008047474005992332</v>
+        <v>0.000804747400599234</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008050922101674493</v>
+        <v>0.0008050922101674496</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000808865222030812</v>
+        <v>0.0008088652220308129</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008026827152213989</v>
+        <v>0.0008026827152213998</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008381420285662729</v>
+        <v>0.0008381420285662731</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007991253945465104</v>
+        <v>0.0007991253945465113</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001125629223877228</v>
+        <v>0.001125629223877229</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008042720117838774</v>
+        <v>0.000804272011783878</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007945487120139368</v>
+        <v>0.0007945487120139376</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007918507931827731</v>
+        <v>0.000791850793182774</v>
       </c>
       <c r="S2" t="n">
-        <v>0.000803710983303592</v>
+        <v>0.0008037109833035928</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008013105340732156</v>
+        <v>0.0008013105340732166</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001021261480232039</v>
+        <v>0.00102126148023204</v>
       </c>
       <c r="V2" t="n">
-        <v>0.000795061613282586</v>
+        <v>0.0007950616132825867</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009812629823697594</v>
+        <v>0.0009812629823697605</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008051776311347228</v>
+        <v>0.000805177631134724</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008087560481257245</v>
+        <v>0.0008087560481257253</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009448276405024517</v>
+        <v>0.0009448276405024522</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008078374485131037</v>
+        <v>0.0008078374485131043</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008145753898936467</v>
+        <v>0.0008145753898936471</v>
       </c>
     </row>
     <row r="3">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001156727547350053</v>
+        <v>0.000906023520790959</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001002812690696533</v>
+        <v>0.0009029517511343921</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001290372212432612</v>
+        <v>0.0009556875744848683</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001122987571049063</v>
+        <v>0.0009666450367528446</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001016409861291513</v>
+        <v>0.0008600453290987249</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001250248824205033</v>
+        <v>0.0009373766429937259</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0009584366477123884</v>
+        <v>0.0008407416812558136</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001261867678286082</v>
+        <v>0.0009465013842237253</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001266559976552361</v>
+        <v>0.0009451272620319215</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00135573787781229</v>
+        <v>0.0009718302450319025</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001209876077246003</v>
+        <v>0.0009259511233614728</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002040694551881906</v>
+        <v>0.001218911053604815</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001128805932818951</v>
+        <v>0.0008989434331157559</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001437266060053315</v>
+        <v>0.001215971099367238</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001243630346741592</v>
+        <v>0.0009352698209184813</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00102254182061552</v>
+        <v>0.0008616053246238963</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0009605427732853727</v>
+        <v>0.0008412089725009016</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001232364174670539</v>
+        <v>0.0009315312429606983</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00118112231809347</v>
+        <v>0.0009180155751781683</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001471295340910125</v>
+        <v>0.001156709379142914</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001032322227418196</v>
+        <v>0.0008629224788905028</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001422701325800095</v>
+        <v>0.001115845252547565</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001270731986732181</v>
+        <v>0.0009481781438192543</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001351899685991017</v>
+        <v>0.0009748312247021215</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001202747134707457</v>
+        <v>0.001018845659524682</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001330331466650194</v>
+        <v>0.0009680085433181912</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001488318299356492</v>
+        <v>0.001029696337687111</v>
       </c>
     </row>
     <row r="4">
@@ -2550,25 +2550,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003373222576292227</v>
+        <v>0.00337322257629224</v>
       </c>
       <c r="C4" t="n">
         <v>0.001578367514230627</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004840485753270217</v>
+        <v>0.004840485753270228</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002288568250573521</v>
+        <v>0.00228856825057352</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002384687840363789</v>
+        <v>0.002384687840363791</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004111345810637582</v>
+        <v>0.004111345810637585</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001927973017827191</v>
+        <v>0.001927973017827195</v>
       </c>
       <c r="I4" t="n">
         <v>0.004646025870435585</v>
@@ -2577,58 +2577,58 @@
         <v>0.00443822967137153</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004953812403273678</v>
+        <v>0.004953812403273688</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003964439898133741</v>
+        <v>0.003964439898133733</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01172157736976085</v>
+        <v>0.01172157736976082</v>
       </c>
       <c r="N4" t="n">
         <v>0.003349253677773541</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00289214810411576</v>
+        <v>0.002892148104115764</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004055892859051012</v>
+        <v>0.004055892859051018</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002384260905949056</v>
+        <v>0.002384260905949057</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001924388333299946</v>
+        <v>0.001924388333299945</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003992019747174318</v>
+        <v>0.003992019747174324</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003892384000165506</v>
+        <v>0.003892384000165516</v>
       </c>
       <c r="U4" t="n">
-        <v>0.004253563653242762</v>
+        <v>0.004253563653242761</v>
       </c>
       <c r="V4" t="n">
         <v>0.002298193566690523</v>
       </c>
       <c r="W4" t="n">
-        <v>0.004314412716121463</v>
+        <v>0.004314412716121457</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004613575414438154</v>
+        <v>0.004613575414438163</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00519792798370444</v>
+        <v>0.005197927983704448</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002459609319457357</v>
+        <v>0.002459609319457356</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.005050362025761128</v>
+        <v>0.005050362025761135</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.006959104557866172</v>
+        <v>0.00695910455786618</v>
       </c>
     </row>
     <row r="5">
@@ -2638,19 +2638,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001013506123944891</v>
+        <v>0.001013506123944892</v>
       </c>
       <c r="C5" t="n">
         <v>0.001033761045458337</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001208377939743034</v>
+        <v>0.001208377939743036</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001005952573054364</v>
+        <v>0.001005952573054365</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009637080921411136</v>
+        <v>0.0009637080921411146</v>
       </c>
       <c r="G5" t="n">
         <v>0.00121915014164517</v>
@@ -2659,64 +2659,64 @@
         <v>0.001047374599311943</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001194223113209999</v>
+        <v>0.00119422311321</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001197793412903093</v>
+        <v>0.001197793412903094</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001240735800571137</v>
+        <v>0.001240735800571138</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001170901542065162</v>
+        <v>0.001170901542065164</v>
       </c>
       <c r="M5" t="n">
         <v>0.001569476871345819</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003349253677773541</v>
+        <v>0.001028097383434659</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001048816714687391</v>
+        <v>0.001048816714687392</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00110751948206321</v>
+        <v>0.001107519482063211</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0009206193761732862</v>
+        <v>0.0009206193761732867</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001048549999708564</v>
+        <v>0.001048549999708565</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001182516303080224</v>
+        <v>0.001182516303080225</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001155402124761923</v>
+        <v>0.001155402124761924</v>
       </c>
       <c r="U5" t="n">
         <v>0.001128296654112188</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001046424870621362</v>
+        <v>0.001046424870621363</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001188064325207168</v>
+        <v>0.001188064325207169</v>
       </c>
       <c r="X5" t="n">
         <v>0.001052811499352948</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.00137098372318677</v>
+        <v>0.001370983723186772</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0009606033944205654</v>
+        <v>0.0009606033944205658</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001229126625889441</v>
+        <v>0.001229126625889442</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001441999202859036</v>
+        <v>0.001441999202859037</v>
       </c>
     </row>
     <row r="6">
@@ -2726,13 +2726,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001104491177501235</v>
+        <v>0.001104491177501236</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00107514305916885</v>
+        <v>0.001075143059168851</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00124975995345355</v>
+        <v>0.001249759953453551</v>
       </c>
       <c r="E6" t="n">
         <v>0.001098720725640614</v>
@@ -2741,7 +2741,7 @@
         <v>0.0009260122259905832</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001233080669217084</v>
+        <v>0.001233080669217085</v>
       </c>
       <c r="H6" t="n">
         <v>0.001088756613022456</v>
@@ -2750,25 +2750,25 @@
         <v>0.001235605126920514</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001239175426613608</v>
+        <v>0.001239175426613609</v>
       </c>
       <c r="K6" t="n">
         <v>0.001282117814281652</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001212283555775678</v>
+        <v>0.001212283555775679</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001610858885056285</v>
+        <v>0.001610858885056286</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003349253677773541</v>
+        <v>0.001172101982304455</v>
       </c>
       <c r="O6" t="n">
         <v>0.001192054394895201</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001263636627119182</v>
+        <v>0.001263636627119183</v>
       </c>
       <c r="Q6" t="n">
         <v>0.001120406205489779</v>
@@ -2777,16 +2777,16 @@
         <v>0.00108993201341908</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001223898316790737</v>
+        <v>0.001223898316790739</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001196784138472438</v>
+        <v>0.001196784138472439</v>
       </c>
       <c r="U6" t="n">
         <v>0.001234382384839462</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001219617946891271</v>
+        <v>0.001219617946891272</v>
       </c>
       <c r="W6" t="n">
         <v>0.001229420320968337</v>
@@ -2795,16 +2795,16 @@
         <v>0.001240464778734701</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001280884644801208</v>
+        <v>0.001280884644801209</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001086920456020394</v>
+        <v>0.001086920456020395</v>
       </c>
       <c r="AA6" t="n">
         <v>0.001270508639599957</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001345091234723263</v>
+        <v>0.001345091234723264</v>
       </c>
     </row>
   </sheetData>
@@ -2970,85 +2970,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007972491356901029</v>
+        <v>0.0007972491356901023</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008432161886572426</v>
+        <v>0.0008432161886572425</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007981259234094091</v>
+        <v>0.0007981259234094083</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000790573002721777</v>
+        <v>0.0007905730027217762</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007942311870596253</v>
+        <v>0.0007942311870596245</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008014558018470825</v>
+        <v>0.0008014558018470815</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007903077235060554</v>
+        <v>0.0007903077235060545</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008025144827506999</v>
+        <v>0.0008025144827506988</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008025095463859882</v>
+        <v>0.0008025095463859872</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008115484896244437</v>
+        <v>0.000811548489624443</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007995951540115175</v>
+        <v>0.0007995951540115166</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008281535549851666</v>
+        <v>0.0008281535549851667</v>
       </c>
       <c r="N2" t="n">
-        <v>0.000793507972978258</v>
+        <v>0.0007935079729782567</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001123093878255521</v>
+        <v>0.00112309387825552</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008009873753106413</v>
+        <v>0.0008009873753106404</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007931966548965067</v>
+        <v>0.0007931966548965061</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007932427060582176</v>
+        <v>0.0007932427060582169</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008013697205406096</v>
+        <v>0.000801369720540609</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008009378974776326</v>
+        <v>0.0008009378974776322</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009637363424428464</v>
+        <v>0.0009637363424428455</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007975940654676452</v>
+        <v>0.0007975940654676444</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009260975891576062</v>
+        <v>0.000926097589157606</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008056009448597795</v>
+        <v>0.0008056009448597788</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0008180446651570181</v>
+        <v>0.0008180446651570172</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009418531454546646</v>
+        <v>0.0009418531454546634</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008083632211245515</v>
+        <v>0.0008083632211245508</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008110812524751429</v>
+        <v>0.0008110812524751425</v>
       </c>
     </row>
     <row r="3">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001104090226826191</v>
+        <v>0.0008833259434829896</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009664525858206885</v>
+        <v>0.0008739655938549127</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001128363773987466</v>
+        <v>0.0008939632350876707</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001063284603075248</v>
+        <v>0.0009450265265372119</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001038416990801392</v>
+        <v>0.0008635606535198644</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001201035042405277</v>
+        <v>0.0009155005448829086</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000946819189538077</v>
+        <v>0.0008328101851854809</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001231586300660165</v>
+        <v>0.0009311466145559638</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001228546706408211</v>
+        <v>0.000926953707358193</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001440118179599841</v>
+        <v>0.0009961697142702793</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001159963932072827</v>
+        <v>0.0009034676773700312</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00182983124381436</v>
+        <v>0.001135961570419024</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001020053956919817</v>
+        <v>0.0008573722284051142</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001420254039587751</v>
+        <v>0.001205768099028394</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001189521425262652</v>
+        <v>0.000911711671985804</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001012924312360763</v>
+        <v>0.0008538671493439591</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001015258785495878</v>
+        <v>0.000856597530841878</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001199940099689641</v>
+        <v>0.0009160582596129231</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001194448992590349</v>
+        <v>0.0009188468434813884</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00140942496169512</v>
+        <v>0.001092914633280753</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001112268618535383</v>
+        <v>0.0008852144555976289</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001214853449309973</v>
+        <v>0.001009236411118488</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001302342645058992</v>
+        <v>0.000953500187011718</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001589681434077395</v>
+        <v>0.001054484113089475</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001164768631302242</v>
+        <v>0.001000983314903341</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001364428934628947</v>
+        <v>0.0009762339430190316</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001428648746671955</v>
+        <v>0.001003492268808507</v>
       </c>
     </row>
     <row r="4">
@@ -3146,85 +3146,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002930325022197382</v>
+        <v>0.002930325022197383</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00147921794460476</v>
+        <v>0.001479217944604759</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003346548870957764</v>
+        <v>0.00334654887095777</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00173380507986041</v>
+        <v>0.001733805079860408</v>
       </c>
       <c r="F4" t="n">
         <v>0.002618072232862643</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003672295521924253</v>
+        <v>0.003672295521924231</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001877316544522415</v>
+        <v>0.001877316544522418</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004363857829993273</v>
+        <v>0.004363857829993275</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004084101744440124</v>
+        <v>0.004084101744440123</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005679249080922451</v>
+        <v>0.005679249080922449</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003491101077298479</v>
+        <v>0.003491101077298484</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00949224715179451</v>
+        <v>0.009492247151794496</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002448361957624039</v>
+        <v>0.002448361957624037</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002816847230637863</v>
+        <v>0.002816847230637867</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003576737753710651</v>
+        <v>0.003576737753710654</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002316808553188004</v>
+        <v>0.002316808553188003</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002484994774382478</v>
+        <v>0.00248499477438248</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003738600072555613</v>
+        <v>0.003738600072555611</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004070576249528253</v>
+        <v>0.004070576249528254</v>
       </c>
       <c r="U4" t="n">
-        <v>0.004143635333844931</v>
+        <v>0.004143635333844923</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002937781515012772</v>
+        <v>0.002937781515012773</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002979375671548881</v>
+        <v>0.002979375671548878</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004823444995874291</v>
+        <v>0.004823444995874295</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.007413115443123936</v>
+        <v>0.007413115443123932</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002148380688387283</v>
+        <v>0.00214838068838728</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.005422522126558357</v>
+        <v>0.005422522126558363</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.006371815050100165</v>
+        <v>0.006371815050100161</v>
       </c>
     </row>
     <row r="5">
@@ -3234,31 +3234,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009914406999935441</v>
+        <v>0.0009914406999935407</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00102797300702439</v>
+        <v>0.001027973007024391</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001132642486476127</v>
+        <v>0.001132642486476126</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009774164257830458</v>
+        <v>0.000977416425783046</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009778062860316226</v>
+        <v>0.0009778062860316202</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001197480504529627</v>
+        <v>0.001197480504529625</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001044332322018102</v>
+        <v>0.001044332322018103</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001182213283073036</v>
+        <v>0.001182213283073037</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001181859856882974</v>
+        <v>0.001181859856882973</v>
       </c>
       <c r="K5" t="n">
         <v>0.001284256546560464</v>
@@ -3267,22 +3267,22 @@
         <v>0.001149238122006404</v>
       </c>
       <c r="M5" t="n">
-        <v>0.00147071223791186</v>
+        <v>0.001470712237911861</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002448361957624039</v>
+        <v>0.0009787026452669049</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001044115087356311</v>
+        <v>0.001044115087356313</v>
       </c>
       <c r="P5" t="n">
         <v>0.001084299411595798</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0009198629985297967</v>
+        <v>0.0009198629985297983</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001077484300103448</v>
+        <v>0.001077484300103446</v>
       </c>
       <c r="S5" t="n">
         <v>0.001169282667293447</v>
@@ -3291,7 +3291,7 @@
         <v>0.001164405027148695</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001128846396511169</v>
+        <v>0.001128846396511166</v>
       </c>
       <c r="V5" t="n">
         <v>0.001088736020547463</v>
@@ -3300,19 +3300,19 @@
         <v>0.001112459221591861</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00107200888853714</v>
+        <v>0.001072008888537139</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001488052173692153</v>
+        <v>0.001488052173692148</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0009459537013004945</v>
+        <v>0.0009459537013004942</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001248277473558276</v>
+        <v>0.001248277473558274</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001414661488148187</v>
+        <v>0.001414661488148186</v>
       </c>
     </row>
     <row r="6">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001063187433377803</v>
+        <v>0.001063187433377806</v>
       </c>
       <c r="C6" t="n">
         <v>0.00104541158080377</v>
@@ -3331,76 +3331,76 @@
         <v>0.001150081060255505</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001046998365120181</v>
+        <v>0.00104699836512018</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009286055177211757</v>
+        <v>0.000928605517721176</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001187693536361503</v>
+        <v>0.001187693536361505</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001061770895797482</v>
+        <v>0.001061770895797483</v>
       </c>
       <c r="I6" t="n">
         <v>0.001199651856852418</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001199298430662353</v>
+        <v>0.001199298430662352</v>
       </c>
       <c r="K6" t="n">
         <v>0.001301695120339847</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001166676695785787</v>
+        <v>0.001166676695785785</v>
       </c>
       <c r="M6" t="n">
         <v>0.001488150811691171</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002448361957624039</v>
+        <v>0.001097919185773499</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001160876469520147</v>
+        <v>0.001160876469520146</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001213465718354127</v>
+        <v>0.00121346571835413</v>
       </c>
       <c r="Q6" t="n">
         <v>0.001094402672159438</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001094922873882828</v>
+        <v>0.001094922873882826</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001186721241072831</v>
+        <v>0.001186721241072827</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001181843600928076</v>
+        <v>0.001181843600928074</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001210444826655509</v>
+        <v>0.001210444826655507</v>
       </c>
       <c r="V6" t="n">
         <v>0.001230987634718714</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00112987199155818</v>
+        <v>0.001129871991558179</v>
       </c>
       <c r="X6" t="n">
         <v>0.001234514866217198</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001375072411368662</v>
+        <v>0.00137507241136866</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001050711189682374</v>
+        <v>0.001050711189682376</v>
       </c>
       <c r="AA6" t="n">
         <v>0.001265716047337655</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00129494825319815</v>
+        <v>0.001294948253198153</v>
       </c>
     </row>
   </sheetData>
@@ -3569,82 +3569,82 @@
         <v>0.0007725722011615625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000842962027675046</v>
+        <v>0.0008429620276750458</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007787385156055924</v>
+        <v>0.0007787385156055925</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007736152769611538</v>
+        <v>0.0007736152769611539</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007720546971183343</v>
+        <v>0.0007720546971183347</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007748328420585712</v>
+        <v>0.0007748328420585711</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007755802895106389</v>
+        <v>0.000775580289510639</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007761957358639325</v>
+        <v>0.0007761957358639329</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000776500162142083</v>
+        <v>0.0007765001621420834</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007836594804927331</v>
+        <v>0.0007836594804927333</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007795174190671437</v>
+        <v>0.0007795174190671436</v>
       </c>
       <c r="M2" t="n">
         <v>0.000788631334641433</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007807208629507364</v>
+        <v>0.0007807208629507363</v>
       </c>
       <c r="O2" t="n">
         <v>0.001090933838002095</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007773649846047977</v>
+        <v>0.0007773649846047978</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007761103396860234</v>
+        <v>0.0007761103396860238</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007749389365460601</v>
+        <v>0.0007749389365460602</v>
       </c>
       <c r="S2" t="n">
-        <v>0.000776165982601316</v>
+        <v>0.0007761659826013162</v>
       </c>
       <c r="T2" t="n">
-        <v>0.000774246999590015</v>
+        <v>0.0007742469995900152</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009903244651376071</v>
+        <v>0.0009903244651376074</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007721622531908457</v>
+        <v>0.000772162253190846</v>
       </c>
       <c r="W2" t="n">
-        <v>0.000951775436229392</v>
+        <v>0.0009517754362293919</v>
       </c>
       <c r="X2" t="n">
         <v>0.0007787561695028201</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0007728976874352293</v>
+        <v>0.0007728976874352294</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009233033355739175</v>
+        <v>0.0009233033355739176</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0007802010742784015</v>
+        <v>0.0007802010742784017</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0007775958092162362</v>
+        <v>0.000777595809216236</v>
       </c>
     </row>
     <row r="3">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0009100500271177223</v>
+        <v>0.0008120472575354905</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009161919081281412</v>
+        <v>0.0008631297566321606</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001055351960661837</v>
+        <v>0.0008636265337319865</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001043452970852106</v>
+        <v>0.0009303393773509374</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008996816666256154</v>
+        <v>0.0008094718757349997</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009620654441543442</v>
+        <v>0.0008288879139776396</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0009826680651488177</v>
+        <v>0.0008391902123882687</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0009963119848841195</v>
+        <v>0.0008433675651981542</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001001665844844529</v>
+        <v>0.0008430206454548856</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001169311474630465</v>
+        <v>0.0008996137734970778</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001071074574445999</v>
+        <v>0.0008651226588197999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001289305107667965</v>
+        <v>0.0009402323986387191</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001100465698264765</v>
+        <v>0.0008779584410980464</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001246586421312364</v>
+        <v>0.001135712887952698</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001020110808394533</v>
+        <v>0.0008494779872681894</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0009934810395137183</v>
+        <v>0.0008409823614859863</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0009672368497188716</v>
+        <v>0.0008336017862088666</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009929892007517959</v>
+        <v>0.0008382259962009055</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0009505221035923891</v>
+        <v>0.0008267272754862434</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001280605174011322</v>
+        <v>0.001077378504470377</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0009007063722044863</v>
+        <v>0.0008089183001973166</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001278321697838104</v>
+        <v>0.001051734278508363</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00105552858328685</v>
+        <v>0.0008633325360253377</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009184563248527107</v>
+        <v>0.0008156270025483273</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001124630312222391</v>
+        <v>0.0009818670647635521</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001087891506793212</v>
+        <v>0.0008741129193014756</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001029736654123603</v>
+        <v>0.0008553716159187748</v>
       </c>
     </row>
     <row r="4">
@@ -3745,22 +3745,22 @@
         <v>0.001527424924837679</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0009888363112817598</v>
+        <v>0.0009888363112817609</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003007171313472759</v>
+        <v>0.00300717131347276</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00178363944076059</v>
+        <v>0.001783639440760588</v>
       </c>
       <c r="F4" t="n">
         <v>0.001528424138713394</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001920715788258595</v>
+        <v>0.001920715788258593</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002391278554093467</v>
+        <v>0.002391278554093464</v>
       </c>
       <c r="I4" t="n">
         <v>0.002469414830607585</v>
@@ -3772,55 +3772,55 @@
         <v>0.003812988168084702</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00283145293271559</v>
+        <v>0.002831452932715588</v>
       </c>
       <c r="M4" t="n">
-        <v>0.004904320472169126</v>
+        <v>0.004904320472169129</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003321022224638307</v>
+        <v>0.0033210222246383</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001667974010906904</v>
+        <v>0.001667974010906901</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002487863319454481</v>
+        <v>0.002487863319454483</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.00232810576706879</v>
+        <v>0.002328105767068786</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002221540135078241</v>
+        <v>0.00222154013507824</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002108871488919294</v>
+        <v>0.002108871488919297</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001976718685524781</v>
+        <v>0.00197671868552478</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002955116884542748</v>
+        <v>0.002955116884542757</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001448417294955264</v>
+        <v>0.001448417294955259</v>
       </c>
       <c r="W4" t="n">
-        <v>0.003420659228586801</v>
+        <v>0.003420659228586802</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002979510246096238</v>
+        <v>0.002979510246096243</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001666988452766325</v>
+        <v>0.001666988452766323</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002061124371990368</v>
+        <v>0.002061124371990369</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003233553583326723</v>
+        <v>0.003233553583326717</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002815244692363441</v>
+        <v>0.002815244692363439</v>
       </c>
     </row>
     <row r="5">
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0008854060524855227</v>
+        <v>0.0008854060524855229</v>
       </c>
       <c r="C5" t="n">
         <v>0.0009825969277390981</v>
@@ -3839,76 +3839,76 @@
         <v>0.001085411215341791</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009581323223151613</v>
+        <v>0.000958132322315161</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0008998682055257585</v>
+        <v>0.000899868205525759</v>
       </c>
       <c r="G5" t="n">
         <v>0.001068324546481286</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001049737598743511</v>
+        <v>0.001049737598743509</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001056689348423268</v>
+        <v>0.001056689348423267</v>
       </c>
       <c r="J5" t="n">
         <v>0.001059815774622911</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001140995777497738</v>
+        <v>0.001140995777497739</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001094209288253312</v>
+        <v>0.001094209288253311</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001198288583983995</v>
+        <v>0.001198288583983993</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003321022224638307</v>
+        <v>0.001006756734270285</v>
       </c>
       <c r="O5" t="n">
         <v>0.0009518752628699642</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0009898121782737428</v>
+        <v>0.0009898121782737439</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0008997534569700966</v>
+        <v>0.0008997534569700965</v>
       </c>
       <c r="R5" t="n">
         <v>0.001042493221971656</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001056353271634836</v>
+        <v>0.001056353271634835</v>
       </c>
       <c r="T5" t="n">
         <v>0.001034677475746397</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001029827363308311</v>
+        <v>0.001029827363308309</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0009733826671895117</v>
+        <v>0.0009733826671895118</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001111637451409428</v>
+        <v>0.001111637451409429</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0009415865070877751</v>
+        <v>0.0009415865070877752</v>
       </c>
       <c r="Y5" t="n">
         <v>0.001148903498939355</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0009156957952375506</v>
+        <v>0.0009156957952375504</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001101931488361404</v>
+        <v>0.001101931488361403</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001209138048705414</v>
+        <v>0.001209138048705413</v>
       </c>
     </row>
     <row r="6">
@@ -3918,67 +3918,67 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009791132311154215</v>
+        <v>0.0009791132311154202</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001028602435233199</v>
+        <v>0.0010286024352332</v>
       </c>
       <c r="D6" t="n">
         <v>0.001131416722835892</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001054471625418678</v>
+        <v>0.001054471625418679</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008653841671547745</v>
+        <v>0.000865384167154774</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001087300363108785</v>
+        <v>0.001087300363108787</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001095743106237611</v>
+        <v>0.001095743106237612</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001102694855917368</v>
+        <v>0.001102694855917369</v>
       </c>
       <c r="J6" t="n">
         <v>0.001105821282117012</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00118700128499184</v>
+        <v>0.001187001284991839</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001140214795747412</v>
+        <v>0.001140214795747413</v>
       </c>
       <c r="M6" t="n">
         <v>0.001244294091478091</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003321022224638307</v>
+        <v>0.001153808248024129</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001098549291748789</v>
+        <v>0.00109854929174879</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001149249925715002</v>
+        <v>0.001149249925715003</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001101730286488803</v>
+        <v>0.001101730286488804</v>
       </c>
       <c r="R6" t="n">
         <v>0.001088498729465757</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001102358779128936</v>
+        <v>0.001102358779128937</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001080682983240498</v>
+        <v>0.001080682983240499</v>
       </c>
       <c r="U6" t="n">
         <v>0.00113953906734784</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001150485299256196</v>
+        <v>0.001150485299256197</v>
       </c>
       <c r="W6" t="n">
         <v>0.001157617340662919</v>
@@ -3990,10 +3990,10 @@
         <v>0.001065441881737932</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001044644617212892</v>
+        <v>0.001044644617212893</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001147936995855504</v>
+        <v>0.001147936995855505</v>
       </c>
       <c r="AB6" t="n">
         <v>0.001118978107337728</v>
@@ -4162,85 +4162,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007673402744611899</v>
+        <v>0.0007673402744611895</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008418822732622229</v>
+        <v>0.0008418822732622218</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007685047661940351</v>
+        <v>0.0007685047661940348</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007692327690485216</v>
+        <v>0.0007692327690485211</v>
       </c>
       <c r="F2" t="n">
         <v>0.0007693431063215618</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007693829547438634</v>
+        <v>0.0007693829547438626</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007692268335314678</v>
+        <v>0.0007692268335314674</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007693551058604709</v>
+        <v>0.000769355105860471</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007698220013258215</v>
+        <v>0.0007698220013258217</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007682840394491505</v>
+        <v>0.00076828403944915</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007692424826625947</v>
+        <v>0.0007692424826625943</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007671393087493786</v>
+        <v>0.0007671393087493785</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007705650287864328</v>
+        <v>0.0007705650287864326</v>
       </c>
       <c r="O2" t="n">
         <v>0.001087108159759421</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007697183470580174</v>
+        <v>0.0007697183470580173</v>
       </c>
       <c r="Q2" t="n">
         <v>0.0007673497375365337</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007716988671826266</v>
+        <v>0.0007716988671826264</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007697104672781053</v>
+        <v>0.0007697104672781047</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007676227905475846</v>
+        <v>0.000767622790547584</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009797073176095988</v>
+        <v>0.0009797073176095979</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007699893225788124</v>
+        <v>0.000769989322578812</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009471011875246725</v>
+        <v>0.0009471011875246718</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0007841476364668185</v>
+        <v>0.0007841476364668183</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0007706400882150597</v>
+        <v>0.0007706400882150596</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009184486389336032</v>
+        <v>0.000918448638933603</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0007730219819939758</v>
+        <v>0.0007730219819939749</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0007660656946012419</v>
+        <v>0.0007660656946012415</v>
       </c>
     </row>
     <row r="3">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008650297590816537</v>
+        <v>0.0007952548167078379</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009508739515355693</v>
+        <v>0.0008737211814365991</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000892938910803379</v>
+        <v>0.0008051512950480842</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001017849971272485</v>
+        <v>0.000919798149675522</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000912910544954818</v>
+        <v>0.0008120826079109963</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009120142555358721</v>
+        <v>0.0008104565784239534</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0009104389584182254</v>
+        <v>0.0008119590542906006</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0009129753323525731</v>
+        <v>0.0008123572335662454</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009226794571855737</v>
+        <v>0.0008145445730632171</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0008876653909831492</v>
+        <v>0.0008030830772362954</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009092065934168283</v>
+        <v>0.0008092820723109916</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000867471653601656</v>
+        <v>0.0007962157741134752</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0009405110321057643</v>
+        <v>0.0008211547198307195</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001263989801951508</v>
+        <v>0.001138779292420187</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0009195973190187765</v>
+        <v>0.0008135913780031702</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008658258476410548</v>
+        <v>0.0007954591150400549</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0009680553413115682</v>
+        <v>0.0008317208462636531</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009197452989682788</v>
+        <v>0.0008127887106306725</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008724086964749975</v>
+        <v>0.0007981881869889952</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001071665428436576</v>
+        <v>0.001005913709554322</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0009260871665505593</v>
+        <v>0.0008154031263080338</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00120526211383229</v>
+        <v>0.001024652911870215</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001257252095591153</v>
+        <v>0.0009283966012388402</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009421396323325375</v>
+        <v>0.0008221953763235333</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001099208901872626</v>
+        <v>0.0009711740227967404</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0009973284243598359</v>
+        <v>0.000841192707875859</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0008389676694861728</v>
+        <v>0.0007868275727247367</v>
       </c>
     </row>
     <row r="4">
@@ -4338,19 +4338,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001136192506225464</v>
+        <v>0.001136192506225465</v>
       </c>
       <c r="C4" t="n">
         <v>0.001270734669193337</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001407376612978587</v>
+        <v>0.001407376612978586</v>
       </c>
       <c r="E4" t="n">
         <v>0.001508719617441099</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001589619928287612</v>
+        <v>0.001589619928287611</v>
       </c>
       <c r="G4" t="n">
         <v>0.00146789146479791</v>
@@ -4359,64 +4359,64 @@
         <v>0.00162096184990097</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001604518878130939</v>
+        <v>0.001604518878130936</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001593945597433015</v>
+        <v>0.001593945597433014</v>
       </c>
       <c r="K4" t="n">
         <v>0.001342843411797335</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001435637095529978</v>
+        <v>0.001435637095529977</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001192550786726295</v>
+        <v>0.001192550786726294</v>
       </c>
       <c r="N4" t="n">
         <v>0.001787353085698115</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001758132030233106</v>
+        <v>0.001758132030233105</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001566078232400984</v>
+        <v>0.001566078232400983</v>
       </c>
       <c r="Q4" t="n">
         <v>0.001145960936307076</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002114200483686508</v>
+        <v>0.002114200483686507</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001513603546029969</v>
+        <v>0.001513603546029968</v>
       </c>
       <c r="T4" t="n">
         <v>0.001237321322427508</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001094188840094706</v>
+        <v>0.001094188840094705</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001593907503219965</v>
+        <v>0.001593907503219964</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002518908102200641</v>
+        <v>0.00251890810220064</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004405945782340561</v>
+        <v>0.004405945782340568</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001832533932198978</v>
+        <v>0.001832533932198975</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001783697477717933</v>
+        <v>0.001783697477717931</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002305300413537411</v>
+        <v>0.00230530041353741</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0009649343191957612</v>
+        <v>0.0009649343191957611</v>
       </c>
     </row>
     <row r="5">
@@ -4426,85 +4426,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0008444348903476861</v>
+        <v>0.0008444348903476853</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009676306464907548</v>
+        <v>0.0009676306464907535</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009754111826005501</v>
+        <v>0.0009754111826005489</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009208971323505118</v>
+        <v>0.0009208971323505108</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000885413216268264</v>
+        <v>0.0008854132162682627</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001009762056033301</v>
+        <v>0.0010097620560333</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009835672653442395</v>
+        <v>0.0009835672653442375</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000985016160308516</v>
+        <v>0.0009850161603085147</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009900125930071384</v>
+        <v>0.0009900125930071375</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009729179724777591</v>
+        <v>0.0009729179724777574</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009837440294792727</v>
+        <v>0.0009837440294792714</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0009631297280067683</v>
+        <v>0.0009631297280067667</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001787353085698115</v>
+        <v>0.0009073503976273565</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0009367423836409808</v>
+        <v>0.0009367423836409798</v>
       </c>
       <c r="P5" t="n">
-        <v>0.000916733318465255</v>
+        <v>0.000916733318465254</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0008213869063570428</v>
+        <v>0.0008213869063570418</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001011490022625737</v>
+        <v>0.001011490022625735</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0009890301309950248</v>
+        <v>0.000989030130995024</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0009654488619450508</v>
+        <v>0.000965448861945049</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0009016260613237981</v>
+        <v>0.0009016260613237971</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0009581012433970599</v>
+        <v>0.0009581012433970591</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001043840985322451</v>
+        <v>0.00104384098532245</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001021925597974809</v>
+        <v>0.001021925597974808</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001116555182890164</v>
+        <v>0.001116555182890162</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0008848397236733744</v>
+        <v>0.0008848397236733731</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001026435213082811</v>
+        <v>0.001026435213082809</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001072396693062744</v>
+        <v>0.001072396693062742</v>
       </c>
     </row>
     <row r="6">
@@ -4514,64 +4514,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009111649726057853</v>
+        <v>0.0009111649726057843</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009862751974682609</v>
+        <v>0.0009862751974682601</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0009940557335780559</v>
+        <v>0.0009940557335780548</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0009861838202577531</v>
+        <v>0.0009861838202577526</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008427616106664901</v>
+        <v>0.00084276161066649</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001003975331689207</v>
+        <v>0.001003975331689205</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001002211816321745</v>
+        <v>0.001002211816321744</v>
       </c>
       <c r="I6" t="n">
         <v>0.001003660711286021</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001008657143984645</v>
+        <v>0.001008657143984644</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0009915625234552647</v>
+        <v>0.0009915625234552638</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001002388580456779</v>
+        <v>0.001002388580456778</v>
       </c>
       <c r="M6" t="n">
-        <v>0.000981774278984287</v>
+        <v>0.0009817742789842863</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001787353085698115</v>
+        <v>0.00101732734732681</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001044731316630147</v>
+        <v>0.001044731316630146</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001035900823814827</v>
+        <v>0.001035900823814826</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0009810092080062866</v>
+        <v>0.0009810092080062857</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001030134573603243</v>
+        <v>0.001030134573603242</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001007674681972531</v>
+        <v>0.00100767468197253</v>
       </c>
       <c r="T6" t="n">
         <v>0.0009840934129225559</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0009778508408792032</v>
+        <v>0.0009778508408792035</v>
       </c>
       <c r="V6" t="n">
         <v>0.00108950388873801</v>
@@ -4580,13 +4580,13 @@
         <v>0.001062462380754187</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001170749149384993</v>
+        <v>0.001170749149384992</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001018175178102189</v>
+        <v>0.001018175178102188</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0009814503528419113</v>
+        <v>0.0009814503528419105</v>
       </c>
       <c r="AA6" t="n">
         <v>0.001045079764060316</v>
@@ -4758,85 +4758,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007668834693289903</v>
+        <v>0.0007668834693289896</v>
       </c>
       <c r="C2" t="n">
         <v>0.0008212251319951278</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007670175602022443</v>
+        <v>0.0007670175602022438</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007688332031770483</v>
+        <v>0.0007688332031770477</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007670737076480298</v>
+        <v>0.000767073707648029</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007664143447127743</v>
+        <v>0.0007664143447127735</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007661300746180678</v>
+        <v>0.0007661300746180672</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007662116251951731</v>
+        <v>0.0007662116251951727</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007675203613730142</v>
+        <v>0.0007675203613730136</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007658502563696064</v>
+        <v>0.0007658502563696057</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007678900616767657</v>
+        <v>0.0007678900616767651</v>
       </c>
       <c r="M2" t="n">
         <v>0.0007653179158613556</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007672092505297563</v>
+        <v>0.0007672092505297562</v>
       </c>
       <c r="O2" t="n">
         <v>0.001091330955048135</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007692712031721321</v>
+        <v>0.0007692712031721327</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007653546163537939</v>
+        <v>0.0007653546163537932</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007703478456294831</v>
+        <v>0.0007703478456294829</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007673428094533037</v>
+        <v>0.0007673428094533031</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007655264768406136</v>
+        <v>0.0007655264768406129</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009222163954540773</v>
+        <v>0.0009222163954540775</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007688078230513292</v>
+        <v>0.0007688078230513297</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0008968592210335835</v>
+        <v>0.0008968592210335832</v>
       </c>
       <c r="X2" t="n">
-        <v>0.000786883948198797</v>
+        <v>0.0007868839481987959</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0007685731298191828</v>
+        <v>0.0007685731298191824</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009144946111193325</v>
+        <v>0.0009144946111193319</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0007719574871753942</v>
+        <v>0.0007719574871753934</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0007652848345739308</v>
+        <v>0.0007652848345739301</v>
       </c>
     </row>
     <row r="3">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008853474942097209</v>
+        <v>0.000797539804207295</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009248177121512717</v>
+        <v>0.0008478472660815635</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00088959763172972</v>
+        <v>0.0007996359218492399</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001045829833201953</v>
+        <v>0.0009283568258951487</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008912807076537068</v>
+        <v>0.0008004076003144135</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008745658990460399</v>
+        <v>0.0007938204079213518</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008693130821634495</v>
+        <v>0.0007930846030227985</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008709276768374173</v>
+        <v>0.0007934283200320894</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009005706246426729</v>
+        <v>0.0008028215182279385</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0008622870431143066</v>
+        <v>0.0007901690035977421</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000908987875884057</v>
+        <v>0.0008050199591221387</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0008560007795203254</v>
+        <v>0.000788008064332698</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008937446727647843</v>
+        <v>0.0008009414784864515</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001346371939346105</v>
+        <v>0.001163048770598489</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0009400564085680948</v>
+        <v>0.0008156418224623635</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008506754083638079</v>
+        <v>0.0007860478342799975</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0009679284698349902</v>
+        <v>0.0008274362299591778</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008961205876112251</v>
+        <v>0.0008009331570743768</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008548519051610972</v>
+        <v>0.0007877844072561436</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001013419591064084</v>
+        <v>0.0009445796398973187</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0009297637126728779</v>
+        <v>0.000812287776897273</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001105515206589488</v>
+        <v>0.0009558981720698208</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001352151467456124</v>
+        <v>0.0009551129062812477</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009253261882350928</v>
+        <v>0.0008120807583151413</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001057757880899176</v>
+        <v>0.0009521303936926332</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001003777937585236</v>
+        <v>0.0008390379870787754</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0008514104695901063</v>
+        <v>0.0007868006804319157</v>
       </c>
     </row>
     <row r="4">
@@ -4934,22 +4934,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001346959844004835</v>
+        <v>0.001346959844004834</v>
       </c>
       <c r="C4" t="n">
         <v>0.001268014137922917</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001441761623888941</v>
+        <v>0.00144176162388894</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001700664695361941</v>
+        <v>0.00170066469536194</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00147438294506421</v>
+        <v>0.001474382945064211</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001255222153409324</v>
+        <v>0.001255222153409332</v>
       </c>
       <c r="H4" t="n">
         <v>0.001301087509263099</v>
@@ -4958,13 +4958,13 @@
         <v>0.001296800917901433</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001486143015615424</v>
+        <v>0.001486143015615423</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001199792719849189</v>
+        <v>0.001199792719849188</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001508919350233446</v>
+        <v>0.001508919350233447</v>
       </c>
       <c r="M4" t="n">
         <v>0.001162966872469563</v>
@@ -4976,16 +4976,16 @@
         <v>0.002425989532859826</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001757661243900988</v>
+        <v>0.001757661243900986</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001090161393807278</v>
+        <v>0.001090161393807279</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002185375681269424</v>
+        <v>0.00218537568126942</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001419521800101527</v>
+        <v>0.001419521800101528</v>
       </c>
       <c r="T4" t="n">
         <v>0.001148899532079925</v>
@@ -4997,13 +4997,13 @@
         <v>0.00168646976595938</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002161395115949433</v>
+        <v>0.002161395115949435</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005178988805503318</v>
+        <v>0.005178988805503315</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001753590827273075</v>
+        <v>0.001753590827273076</v>
       </c>
       <c r="Z4" t="n">
         <v>0.001511113057268933</v>
@@ -5022,49 +5022,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0008566921442583513</v>
+        <v>0.0008566921442583512</v>
       </c>
       <c r="C5" t="n">
         <v>0.0009658450546365484</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009754139657715277</v>
+        <v>0.0009754139657715273</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009335131099894831</v>
+        <v>0.0009335131099894828</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000877100486046583</v>
+        <v>0.0008771004860465828</v>
       </c>
       <c r="G5" t="n">
         <v>0.0009929040464861638</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009653894078347099</v>
+        <v>0.0009653894078347097</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009663105591182361</v>
+        <v>0.0009663105591182357</v>
       </c>
       <c r="J5" t="n">
         <v>0.0009808159419913917</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009622287319955856</v>
+        <v>0.0009622287319955853</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009852692712967513</v>
+        <v>0.0009852692712967511</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0009591899916825312</v>
+        <v>0.0009591899916825313</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001465047499305295</v>
+        <v>0.0008867240052144428</v>
       </c>
       <c r="O5" t="n">
         <v>0.0009782230123408162</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0009288622942658467</v>
+        <v>0.0009288622942658464</v>
       </c>
       <c r="Q5" t="n">
         <v>0.0008163891560050457</v>
@@ -5076,16 +5076,16 @@
         <v>0.0009790878056842888</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0009585714932696708</v>
+        <v>0.0009585714932696704</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0009025186099203481</v>
+        <v>0.0009025186099203475</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0009617312089442327</v>
+        <v>0.0009617312089442334</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001019563036274597</v>
+        <v>0.001019563036274596</v>
       </c>
       <c r="X5" t="n">
         <v>0.001070315136255094</v>
@@ -5094,10 +5094,10 @@
         <v>0.001109404287728221</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0008672317449565201</v>
+        <v>0.0008672317449565195</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001031212713411933</v>
+        <v>0.001031212713411932</v>
       </c>
       <c r="AB5" t="n">
         <v>0.001079379464376538</v>
@@ -5110,70 +5110,70 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009059422658464831</v>
+        <v>0.0009059422658464826</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009625231486411342</v>
+        <v>0.0009625231486411336</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0009720920597761133</v>
+        <v>0.0009720920597761123</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0009776830840463964</v>
+        <v>0.0009776830840463957</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008237244880398094</v>
+        <v>0.0008237244880398085</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009652785108759171</v>
+        <v>0.0009652785108759174</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009620675018392952</v>
+        <v>0.0009620675018392948</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009629886531228213</v>
+        <v>0.0009629886531228208</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009774940359959766</v>
+        <v>0.0009774940359959757</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0009589068260001711</v>
+        <v>0.0009589068260001704</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009819473653013371</v>
+        <v>0.0009819473653013366</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0009558680856871334</v>
+        <v>0.000955868085687133</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001465047499305295</v>
+        <v>0.0009742572902072761</v>
       </c>
       <c r="O6" t="n">
         <v>0.001062208577916129</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001023626558459176</v>
+        <v>0.001023626558459175</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0009533083915621027</v>
+        <v>0.0009533083915621021</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001009709165683749</v>
+        <v>0.001009709165683748</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0009757658996888747</v>
+        <v>0.000975765899688874</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0009552495872742559</v>
+        <v>0.0009552495872742552</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0009564723723627889</v>
+        <v>0.0009564723723627885</v>
       </c>
       <c r="V6" t="n">
         <v>0.001065106895595692</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001016218095719297</v>
+        <v>0.001016218095719296</v>
       </c>
       <c r="X6" t="n">
         <v>0.001196492051187164</v>
@@ -5182,13 +5182,13 @@
         <v>0.0009896629341968066</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0009443249817905852</v>
+        <v>0.0009443249817905845</v>
       </c>
       <c r="AA6" t="n">
         <v>0.001027890807416518</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0009536248337199805</v>
+        <v>0.0009536248337199793</v>
       </c>
     </row>
   </sheetData>
@@ -5354,85 +5354,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.000795621687325161</v>
+        <v>0.0007956216873251599</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008595909254418651</v>
+        <v>0.0008595909254418689</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007974059462561844</v>
+        <v>0.0007974059462561852</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000789928641690695</v>
+        <v>0.0007899286416906935</v>
       </c>
       <c r="F2" t="n">
         <v>0.0007906690290441983</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008025013568275637</v>
+        <v>0.0008025013568275655</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007919788177401622</v>
+        <v>0.0007919788177401643</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007988679223302311</v>
+        <v>0.0007988679223302318</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008017231565928848</v>
+        <v>0.0008017231565928836</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000807311087255708</v>
+        <v>0.0008073110872557071</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000802026071981795</v>
+        <v>0.000802026071981797</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008422476779577706</v>
+        <v>0.000842247677957769</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008071331868653526</v>
+        <v>0.0008071331868653575</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001121269335210141</v>
+        <v>0.001121269335210142</v>
       </c>
       <c r="P2" t="n">
         <v>0.0008000451844818492</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007931042654368659</v>
+        <v>0.0007931042654368687</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007935584394513479</v>
+        <v>0.0007935584394513477</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007974476693927896</v>
+        <v>0.0007974476693927879</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007976871643331871</v>
+        <v>0.0007976871643331895</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001016307871660009</v>
+        <v>0.001016307871660012</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007899412304665824</v>
+        <v>0.0007899412304665822</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009684491539701124</v>
+        <v>0.0009684491539701115</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0008019285559071317</v>
+        <v>0.0008019285559071346</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0007962752199187094</v>
+        <v>0.0007962752199187071</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009423134966044796</v>
+        <v>0.0009423134966044812</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.000802906330899736</v>
+        <v>0.0008029063308997359</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008103943594896225</v>
+        <v>0.0008103943594896236</v>
       </c>
     </row>
     <row r="3">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001099305254501878</v>
+        <v>0.0008839724003639662</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009665408514541097</v>
+        <v>0.0008883848013344346</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001144859388963827</v>
+        <v>0.0009034187588145898</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001076271575551815</v>
+        <v>0.0009488239141627649</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000988169137188056</v>
+        <v>0.0008483743618862181</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001257791971676546</v>
+        <v>0.0009367389836814413</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001019288241364859</v>
+        <v>0.0008601943693078563</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001179506440146406</v>
+        <v>0.000915424388914086</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001242592496607869</v>
+        <v>0.000933207293411641</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001374539570450821</v>
+        <v>0.0009767263919046587</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00124908317800261</v>
+        <v>0.0009360718676571179</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002188331304678493</v>
+        <v>0.001254792923166322</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001369914581121822</v>
+        <v>0.0009804964377634431</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001415566790853836</v>
+        <v>0.001206107347415879</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001200703908028029</v>
+        <v>0.0009192263910091884</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001043816828083901</v>
+        <v>0.0008669081794404892</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00105582833645555</v>
+        <v>0.0008728284798743902</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001141960536589327</v>
+        <v>0.0008971779626759523</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001151573271580825</v>
+        <v>0.000905642744715802</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001515651245327388</v>
+        <v>0.001167041009452643</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0009686868276480786</v>
+        <v>0.0008399370063425065</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001299127880452091</v>
+        <v>0.001067703044888953</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001249999436046779</v>
+        <v>0.00093925595679921</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001116835782606245</v>
+        <v>0.0008918773561468826</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001201957361833919</v>
+        <v>0.001017350546745965</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001270590358454339</v>
+        <v>0.00094524336085473</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001446006457772302</v>
+        <v>0.001012127027486435</v>
       </c>
     </row>
     <row r="4">
@@ -5530,85 +5530,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003036799881319144</v>
+        <v>0.003036799881319165</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001351452672876264</v>
+        <v>0.001351452672876265</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003789778694004378</v>
+        <v>0.003789778694004381</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001989446057489663</v>
+        <v>0.001989446057489679</v>
       </c>
       <c r="F4" t="n">
         <v>0.002265329220155777</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004344242358446705</v>
+        <v>0.00434424235844671</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002642394989418335</v>
+        <v>0.002642394989418334</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004123958184144931</v>
+        <v>0.004123958184144933</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004369681619635673</v>
+        <v>0.004369681619635681</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005474947530674524</v>
+        <v>0.005474947530674528</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004467981004751142</v>
+        <v>0.004467981004751227</v>
       </c>
       <c r="M4" t="n">
         <v>0.01290539338175982</v>
       </c>
       <c r="N4" t="n">
-        <v>0.005817415591116591</v>
+        <v>0.005817415591116589</v>
       </c>
       <c r="O4" t="n">
         <v>0.002903083675847147</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003975251093338829</v>
+        <v>0.003975251093338831</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002718331192949071</v>
+        <v>0.002718331192949069</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002980257318492765</v>
+        <v>0.002980257318492763</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003324383148168714</v>
+        <v>0.003324383148168718</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003847737679967684</v>
+        <v>0.003847737679967688</v>
       </c>
       <c r="U4" t="n">
-        <v>0.004981281995103289</v>
+        <v>0.004981281995103328</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001920387686962665</v>
+        <v>0.001920387686962661</v>
       </c>
       <c r="W4" t="n">
-        <v>0.003495929549615374</v>
+        <v>0.003495929549615379</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004731721432169376</v>
+        <v>0.004731721432169371</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003368395512531247</v>
+        <v>0.003368395512531248</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002661183014400198</v>
+        <v>0.002661183014400191</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004810178213112214</v>
+        <v>0.004810178213112224</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.006950656887591365</v>
+        <v>0.006950656887591353</v>
       </c>
     </row>
     <row r="5">
@@ -5621,16 +5621,16 @@
         <v>0.0009969080744496044</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001036268530338057</v>
+        <v>0.001036268530338058</v>
       </c>
       <c r="D5" t="n">
         <v>0.001157785644605551</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009983949133282224</v>
+        <v>0.0009983949133282246</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009628886044264162</v>
+        <v>0.0009628886044264179</v>
       </c>
       <c r="G5" t="n">
         <v>0.001244520594741093</v>
@@ -5642,31 +5642,31 @@
         <v>0.001174299336904111</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00120619474104177</v>
+        <v>0.001206194741041771</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001269668768785118</v>
+        <v>0.00126966876878512</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001209972090039141</v>
+        <v>0.001209972090039142</v>
       </c>
       <c r="M5" t="n">
         <v>0.001661403227686961</v>
       </c>
       <c r="N5" t="n">
-        <v>0.005817415591116591</v>
+        <v>0.001158575012330406</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001053871512285633</v>
+        <v>0.001053871512285635</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001101141911706362</v>
+        <v>0.001101141911706363</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.000940817247757578</v>
+        <v>0.0009408172477575785</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001114326285304316</v>
+        <v>0.001114326285304317</v>
       </c>
       <c r="S5" t="n">
         <v>0.001158256926627056</v>
@@ -5675,7 +5675,7 @@
         <v>0.001160962132151997</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001168028144097604</v>
+        <v>0.001168028144097605</v>
       </c>
       <c r="V5" t="n">
         <v>0.001032589147972951</v>
@@ -5684,16 +5684,16 @@
         <v>0.001150348945226352</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001053389260477619</v>
+        <v>0.001053389260477621</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001284784689295582</v>
+        <v>0.001284784689295583</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0009715900017520837</v>
+        <v>0.0009715900017520852</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001219915019456387</v>
+        <v>0.001219915019456388</v>
       </c>
       <c r="AB5" t="n">
         <v>0.001450143502301905</v>
@@ -5706,64 +5706,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001117448618796761</v>
+        <v>0.001117448618796764</v>
       </c>
       <c r="C6" t="n">
         <v>0.001110672115133556</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001232189229401049</v>
+        <v>0.001232189229401048</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001125899388669697</v>
+        <v>0.001125899388669696</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009380448376501524</v>
+        <v>0.000938044837650154</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001289744173554985</v>
+        <v>0.001289744173554987</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001170887316210114</v>
+        <v>0.001170887316210116</v>
       </c>
       <c r="I6" t="n">
         <v>0.001248702921699609</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001280598325837269</v>
+        <v>0.001280598325837271</v>
       </c>
       <c r="K6" t="n">
         <v>0.001344072353580616</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00128437567483464</v>
+        <v>0.001284375674834641</v>
       </c>
       <c r="M6" t="n">
         <v>0.001735806812482431</v>
       </c>
       <c r="N6" t="n">
-        <v>0.005817415591116591</v>
+        <v>0.001342062886833384</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001238727864416879</v>
+        <v>0.00123872786441688</v>
       </c>
       <c r="P6" t="n">
         <v>0.001300163611399252</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001183599703421446</v>
+        <v>0.001183599703421447</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001188729870099815</v>
+        <v>0.001188729870099814</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001232660511422555</v>
+        <v>0.001232660511422557</v>
       </c>
       <c r="T6" t="n">
         <v>0.001235365716947496</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001311202999798254</v>
+        <v>0.001311202999798257</v>
       </c>
       <c r="V6" t="n">
         <v>0.001254700086796083</v>
@@ -5772,19 +5772,19 @@
         <v>0.001224724873833283</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001283274185911737</v>
+        <v>0.001283274185911735</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001219417155259425</v>
+        <v>0.001219417155259426</v>
       </c>
       <c r="Z6" t="n">
         <v>0.001132303818751407</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001294318604251884</v>
+        <v>0.001294318604251886</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001377549577533512</v>
+        <v>0.001377549577533513</v>
       </c>
     </row>
   </sheetData>
@@ -5950,40 +5950,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007747414236400787</v>
+        <v>0.0007747414236400788</v>
       </c>
       <c r="C2" t="n">
         <v>0.0008501607613112582</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007773062048503146</v>
+        <v>0.0007773062048503142</v>
       </c>
       <c r="E2" t="n">
         <v>0.0007770486851438829</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007765087952950856</v>
+        <v>0.0007765087952950855</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007899252076781401</v>
+        <v>0.00078992520767814</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000777388832184862</v>
+        <v>0.0007773888321848621</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007771995088419608</v>
+        <v>0.0007771995088419609</v>
       </c>
       <c r="J2" t="n">
         <v>0.0007824645334449773</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007799548827753238</v>
+        <v>0.0007799548827753239</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007837606242955819</v>
+        <v>0.0007837606242955818</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007800306445760281</v>
+        <v>0.0007800306445760279</v>
       </c>
       <c r="N2" t="n">
         <v>0.0007794436846923817</v>
@@ -5992,43 +5992,43 @@
         <v>0.001094973638889426</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007848432881911411</v>
+        <v>0.0007848432881911409</v>
       </c>
       <c r="Q2" t="n">
         <v>0.0007787108276297867</v>
       </c>
       <c r="R2" t="n">
-        <v>0.000780223744419829</v>
+        <v>0.0007802237444198291</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007792635415573771</v>
+        <v>0.0007792635415573767</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007771988491316438</v>
+        <v>0.0007771988491316439</v>
       </c>
       <c r="U2" t="n">
-        <v>0.000991673731859674</v>
+        <v>0.0009916737318596742</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0007775519600676683</v>
+        <v>0.0007775519600676682</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0009579047389561919</v>
+        <v>0.000957904738956192</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0007915663585622585</v>
+        <v>0.0007915663585622588</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0007927445307689083</v>
+        <v>0.0007927445307689084</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009235756761960606</v>
+        <v>0.0009235756761960603</v>
       </c>
       <c r="AA2" t="n">
         <v>0.0007803384438317573</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0007912185628929055</v>
+        <v>0.0007912185628929052</v>
       </c>
     </row>
     <row r="3">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000852685762276401</v>
+        <v>0.0007951881084070376</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009566553777525481</v>
+        <v>0.0008798609991468062</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009130482111871705</v>
+        <v>0.000816381508478262</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001014357446616111</v>
+        <v>0.0009222731953613876</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008947461059354325</v>
+        <v>0.0008100239848495771</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001202100802521318</v>
+        <v>0.0009106110089532708</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0009156124066727483</v>
+        <v>0.0008179720724245756</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0009107390854194246</v>
+        <v>0.000815861743172825</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00103127675758586</v>
+        <v>0.0008550287027346887</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009744674571980028</v>
+        <v>0.0008360992704062702</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001061472000101579</v>
+        <v>0.0008649475098965688</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0009824225263025577</v>
+        <v>0.0008392312805723449</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0009624379328682539</v>
+        <v>0.0008335028410967944</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001232699005454101</v>
+        <v>0.001133486892423341</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001084820507920761</v>
+        <v>0.0008733354327235025</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0009453982922946237</v>
+        <v>0.0008263866313343746</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0009817637765531266</v>
+        <v>0.0008409587409753785</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009570587655501211</v>
+        <v>0.0008297478275838787</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0009106109857638096</v>
+        <v>0.00081568231496556</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001142692646441304</v>
+        <v>0.001034560689525617</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0009174688534216646</v>
+        <v>0.0008168122806804096</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001244255377174646</v>
+        <v>0.001044351575843423</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001245338136370564</v>
+        <v>0.0009302185189231303</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001271003858157913</v>
+        <v>0.000939087842178379</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001065406578779164</v>
+        <v>0.0009632412701948043</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0009828754072752348</v>
+        <v>0.0008403096011977302</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001236203867584281</v>
+        <v>0.0009307321560412331</v>
       </c>
     </row>
     <row r="4">
@@ -6126,58 +6126,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0009907959528928441</v>
+        <v>0.0009907959528928439</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001271775425048391</v>
+        <v>0.001271775425048392</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001548662515275398</v>
+        <v>0.0015486625152754</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001436401930907797</v>
+        <v>0.001436401930907798</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001390285837260458</v>
+        <v>0.001390285837260459</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003621316897273122</v>
+        <v>0.003621316897273113</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001627529352628573</v>
+        <v>0.001627529352628574</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001549799583901967</v>
+        <v>0.001549799583901968</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002404234590882192</v>
+        <v>0.002404234590882193</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00197842431298992</v>
+        <v>0.001978424312989919</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002633052136311429</v>
+        <v>0.00263305213631143</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002097137021188358</v>
+        <v>0.002097137021188357</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00197812503677973</v>
+        <v>0.001978125036779729</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001469601290281301</v>
+        <v>0.001469601290281303</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002833777003324757</v>
+        <v>0.002833777003324758</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001746155217867069</v>
+        <v>0.001746155217867068</v>
       </c>
       <c r="R4" t="n">
         <v>0.002215125245016384</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001786283622534743</v>
+        <v>0.001786283622534742</v>
       </c>
       <c r="T4" t="n">
         <v>0.001537976315085605</v>
@@ -6189,22 +6189,22 @@
         <v>0.001493049749824281</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002891003602879057</v>
+        <v>0.002891003602879056</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004383122342449677</v>
+        <v>0.004383122342449678</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.004583544175113359</v>
+        <v>0.004583544175113353</v>
       </c>
       <c r="Z4" t="n">
         <v>0.001498295008728734</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.00213371734851539</v>
+        <v>0.002133717348515389</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.004560515898366023</v>
+        <v>0.004560515898366022</v>
       </c>
     </row>
     <row r="5">
@@ -6214,31 +6214,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0008469936118189538</v>
+        <v>0.0008469936118189543</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009843464256894935</v>
+        <v>0.0009843464256894942</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009990949776498982</v>
+        <v>0.0009990949776498993</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009306225582175931</v>
+        <v>0.0009306225582175933</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0008861392556563817</v>
+        <v>0.0008861392556563819</v>
       </c>
       <c r="G5" t="n">
         <v>0.001167164430900816</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001000028291404063</v>
+        <v>0.001000028291404062</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009978897971529522</v>
+        <v>0.0009978897971529529</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001057033849566708</v>
+        <v>0.00105703384956671</v>
       </c>
       <c r="K5" t="n">
         <v>0.001029013013264915</v>
@@ -6250,49 +6250,49 @@
         <v>0.001032615007312605</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00197812503677973</v>
+        <v>0.000927791685178368</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0009316332172129102</v>
+        <v>0.0009316332172129105</v>
       </c>
       <c r="P5" t="n">
         <v>0.001008582853392343</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0008676318075727776</v>
+        <v>0.0008676318075727782</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001032049929222072</v>
+        <v>0.001032049929222073</v>
       </c>
       <c r="S5" t="n">
-        <v>0.00102120399617554</v>
+        <v>0.001021203996175541</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0009978823454214378</v>
+        <v>0.000997882345421438</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0009471676348035985</v>
+        <v>0.0009471676348035989</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00096598249281936</v>
+        <v>0.0009659824928193605</v>
       </c>
       <c r="W5" t="n">
         <v>0.001076079784179958</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001024126142464795</v>
+        <v>0.001024126142464794</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001295743385418513</v>
+        <v>0.001295743385418515</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0008774569290463671</v>
+        <v>0.0008774569290463675</v>
       </c>
       <c r="AA5" t="n">
         <v>0.001033345511844138</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001283893828427594</v>
+        <v>0.001283893828427596</v>
       </c>
     </row>
     <row r="6">
@@ -6302,34 +6302,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000930662024518484</v>
+        <v>0.0009306620245184828</v>
       </c>
       <c r="C6" t="n">
         <v>0.001021615927814315</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001036364479774721</v>
+        <v>0.00103636447977472</v>
       </c>
       <c r="E6" t="n">
         <v>0.001015746266059335</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008504689385996115</v>
+        <v>0.0008504689385996117</v>
       </c>
       <c r="G6" t="n">
         <v>0.001178901972420597</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001037297793528882</v>
+        <v>0.001037297793528883</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001035159299277772</v>
+        <v>0.001035159299277773</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001094303351691529</v>
+        <v>0.00109430335169153</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001066282515389737</v>
+        <v>0.001066282515389736</v>
       </c>
       <c r="L6" t="n">
         <v>0.001109270116588648</v>
@@ -6338,7 +6338,7 @@
         <v>0.001069884509437428</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00197812503677973</v>
+        <v>0.001060508297880182</v>
       </c>
       <c r="O6" t="n">
         <v>0.001063549110721821</v>
@@ -6350,7 +6350,7 @@
         <v>0.001052230390904753</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001069319431346893</v>
+        <v>0.001069319431346894</v>
       </c>
       <c r="S6" t="n">
         <v>0.00105847349830036</v>
@@ -6359,25 +6359,25 @@
         <v>0.001035151847546258</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001044629791276967</v>
+        <v>0.001044629791276966</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001125556501873967</v>
+        <v>0.001125556501873968</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001113325087556084</v>
+        <v>0.001113325087556083</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001197439475945938</v>
+        <v>0.001197439475945937</v>
       </c>
       <c r="Y6" t="n">
         <v>0.001210747473006032</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0009938820387967429</v>
+        <v>0.0009938820387967436</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001070615013968959</v>
+        <v>0.00107061501396896</v>
       </c>
       <c r="AB6" t="n">
         <v>0.001192542723611327</v>

--- a/Results/Phase 2/Ammonia/ammonia eutrophication marine results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia eutrophication marine results.xlsx
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0009845717681953214</v>
+        <v>0.0009323868303152097</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009193156356373201</v>
+        <v>0.0009060316365026676</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009761762004543136</v>
+        <v>0.0009218219525411117</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0009763848755472411</v>
+        <v>0.0009558413546620558</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0009271900233737826</v>
+        <v>0.000887529414881944</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009677926605487965</v>
+        <v>0.00091949092076288</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0009597855758461187</v>
+        <v>0.0009091442467516552</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001008983804871403</v>
+        <v>0.0009438475075767923</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009733370830894315</v>
+        <v>0.0009219827031652011</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001125145787793697</v>
+        <v>0.001024743692021643</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009876568430350447</v>
+        <v>0.0009319357576259229</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001340986979790437</v>
+        <v>0.001171173852349148</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001038918716914487</v>
+        <v>0.0009664306397885028</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001306894177120512</v>
+        <v>0.001260175495166163</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0009400193065156086</v>
+        <v>0.0009001555531737448</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0009127534456536932</v>
+        <v>0.0008787403520277832</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0009279323353308638</v>
+        <v>0.0008880094277974991</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009624382385951492</v>
+        <v>0.000915582143904169</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001010934703375903</v>
+        <v>0.0009455262237472322</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001289361311113195</v>
+        <v>0.001213315418063033</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008954712350326341</v>
+        <v>0.0008685546678863983</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001133188739771057</v>
+        <v>0.001089914336361834</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0009103442785492167</v>
+        <v>0.0008768828755567546</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009286749582143173</v>
+        <v>0.0008904305294073442</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001057384355553891</v>
+        <v>0.001027447265986037</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001029096203615573</v>
+        <v>0.0009601824783114169</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001070886965371396</v>
+        <v>0.0009844017229730414</v>
       </c>
     </row>
     <row r="4">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007807460311321491</v>
+        <v>0.0007769925088891418</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008453201070262033</v>
+        <v>0.0008384980849237001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000793158387650404</v>
+        <v>0.0007854188508748894</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0009012549889655571</v>
+        <v>0.0008960433282355003</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007995098225532055</v>
+        <v>0.000789743666006636</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008008762938408598</v>
+        <v>0.0007915180555386956</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007962401505949098</v>
+        <v>0.0007872025769613831</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007962698578192289</v>
+        <v>0.0007874449448208959</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0008059618040728556</v>
+        <v>0.0007948007061496219</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0008083448029265583</v>
+        <v>0.0007965204120440165</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008168809305737545</v>
+        <v>0.0008028388440115088</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000798315948753137</v>
+        <v>0.0007888375375965821</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008033692801490927</v>
+        <v>0.000792488848847214</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001139808617045361</v>
+        <v>0.001124407599701514</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008082459293284318</v>
+        <v>0.0007968637926275722</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007903373038876447</v>
+        <v>0.0007836236752139052</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008226015943159275</v>
+        <v>0.0008053551559402139</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008097391787235462</v>
+        <v>0.0007978827716609699</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008007738053350026</v>
+        <v>0.0007905413873668983</v>
       </c>
       <c r="U3" t="n">
-        <v>0.000961902447994351</v>
+        <v>0.0009514216118429598</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008096317323770377</v>
+        <v>0.0007977931836312643</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0009602821323663119</v>
+        <v>0.0009405019754800131</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0009317587117254831</v>
+        <v>0.0008830983662988085</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0008674580924811164</v>
+        <v>0.0008371049308421491</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0009489575315553061</v>
+        <v>0.0009393348736703782</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008565594392030977</v>
+        <v>0.0008296205816295345</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.000784973120065605</v>
+        <v>0.0007794774404859155</v>
       </c>
     </row>
     <row r="4">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0009381544702715438</v>
+        <v>0.0008966592575167059</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009101396873823064</v>
+        <v>0.0008965368379304847</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009321902504346458</v>
+        <v>0.0008885778330426176</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0009632309522999552</v>
+        <v>0.0009445702858587341</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008682447691017972</v>
+        <v>0.0008445517002142696</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009482564918252253</v>
+        <v>0.0009031138721606452</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008662548333918221</v>
+        <v>0.0008426548665929309</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0009161001922875138</v>
+        <v>0.0008772155648783767</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009549780160626642</v>
+        <v>0.000906258616335172</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00106014963265217</v>
+        <v>0.0009806830119941988</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009564203305205935</v>
+        <v>0.0009071911512864549</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001284365555723931</v>
+        <v>0.001129914961736035</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0009555428934748044</v>
+        <v>0.0009056586300501259</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001250212945735299</v>
+        <v>0.001214708424132689</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0009431774707222929</v>
+        <v>0.0008996799956092077</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000877212517365659</v>
+        <v>0.0008512636627618219</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008691831090012175</v>
+        <v>0.0008448837632470162</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009458050581485118</v>
+        <v>0.0009012774674652495</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0009413543432837056</v>
+        <v>0.0008949063024912311</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001218412400482379</v>
+        <v>0.001155827003038568</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008512331924122999</v>
+        <v>0.0008345683427798678</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001137681128325352</v>
+        <v>0.001086222187028237</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0009172409263378117</v>
+        <v>0.0008787693921979367</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009056514357996459</v>
+        <v>0.0008716745122370748</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001022980284383948</v>
+        <v>0.0009993490235917699</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0009670420644664206</v>
+        <v>0.0009143438955783381</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001049291425619782</v>
+        <v>0.0009666231997800924</v>
       </c>
     </row>
     <row r="4">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000906023520790959</v>
+        <v>0.000873172634031523</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009029517511343921</v>
+        <v>0.0008916263076264164</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009556875744848683</v>
+        <v>0.0009048667049705182</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0009666450367528446</v>
+        <v>0.0009467806962929871</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008600453290987249</v>
+        <v>0.0008389389666445103</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009373766429937259</v>
+        <v>0.0008956695958690832</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008407416812558136</v>
+        <v>0.0008251182168862916</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0009465013842237253</v>
+        <v>0.0008979869833435765</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009451272620319215</v>
+        <v>0.0008993166688524791</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009718302450319025</v>
+        <v>0.0009199736199130624</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009259511233614728</v>
+        <v>0.0008858572638983172</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001218911053604815</v>
+        <v>0.001084686207899307</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008989434331157559</v>
+        <v>0.0008662050533589019</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001215971099367238</v>
+        <v>0.001188984317060103</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0009352698209184813</v>
+        <v>0.0008942357324724459</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008616053246238963</v>
+        <v>0.0008405498727522317</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008412089725009016</v>
+        <v>0.0008256463993054723</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009315312429606983</v>
+        <v>0.000891233157528906</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0009180155751781683</v>
+        <v>0.0008786451882087417</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001156709379142914</v>
+        <v>0.001113199727415765</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008629224788905028</v>
+        <v>0.0008430150808638379</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001115845252547565</v>
+        <v>0.001071493742567832</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0009481781438192543</v>
+        <v>0.000900141015153048</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009748312247021215</v>
+        <v>0.000919836089728269</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001018845659524682</v>
+        <v>0.0009970364699357754</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0009680085433181912</v>
+        <v>0.0009147683470544206</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001029696337687111</v>
+        <v>0.000952993502873243</v>
       </c>
     </row>
     <row r="4">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008833259434829896</v>
+        <v>0.0008558802925674867</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008739655938549127</v>
+        <v>0.000863870308886937</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008939632350876707</v>
+        <v>0.0008613199227743315</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0009450265265372119</v>
+        <v>0.0009319221536011649</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008635606535198644</v>
+        <v>0.0008396732820892707</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009155005448829086</v>
+        <v>0.000879171410468718</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008328101851854809</v>
+        <v>0.0008178316778321757</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0009311466145559638</v>
+        <v>0.0008861239615653893</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000926953707358193</v>
+        <v>0.0008855051830324073</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009961697142702793</v>
+        <v>0.0009356258710656825</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009034676773700312</v>
+        <v>0.0008691875400936647</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001135961570419024</v>
+        <v>0.001029026869295394</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008573722284051142</v>
+        <v>0.0008355512982028863</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001205768099028394</v>
+        <v>0.001179712464059903</v>
       </c>
       <c r="P3" t="n">
-        <v>0.000911711671985804</v>
+        <v>0.0008765372320592032</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008538671493439591</v>
+        <v>0.0008336840719790569</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000856597530841878</v>
+        <v>0.0008342696634294309</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009160582596129231</v>
+        <v>0.0008788685169969919</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0009188468434813884</v>
+        <v>0.0008773480549660831</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001092914633280753</v>
+        <v>0.001050847138271669</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008852144555976289</v>
+        <v>0.0008576985668276066</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001009236411118488</v>
+        <v>0.0009810314761923079</v>
       </c>
       <c r="X3" t="n">
-        <v>0.000953500187011718</v>
+        <v>0.0009030444476436099</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001054484113089475</v>
+        <v>0.0009726992351704134</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001000983314903341</v>
+        <v>0.0009829896510370481</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0009762339430190316</v>
+        <v>0.0009185139144920239</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001003492268808507</v>
+        <v>0.0009340027911577645</v>
       </c>
     </row>
     <row r="4">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008120472575354905</v>
+        <v>0.0008019492161206744</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008631297566321606</v>
+        <v>0.0008590562198848671</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008636265337319865</v>
+        <v>0.0008367206324145219</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0009303393773509374</v>
+        <v>0.000917327782564191</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008094718757349997</v>
+        <v>0.0007992922482669793</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008288879139776396</v>
+        <v>0.0008144063457417547</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008391902123882687</v>
+        <v>0.0008192003286829732</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008433675651981542</v>
+        <v>0.0008225291858039011</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0008430206454548856</v>
+        <v>0.0008238382630778065</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0008996137734970778</v>
+        <v>0.0008637653548352611</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008651226588197999</v>
+        <v>0.000840416131754606</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0009402323986387191</v>
+        <v>0.000892058575918722</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008779584410980464</v>
+        <v>0.0008475784416372669</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001135712887952698</v>
+        <v>0.001124051511072592</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008494779872681894</v>
+        <v>0.0008285771334972022</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008409823614859863</v>
+        <v>0.0008218168411639842</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008336017862088666</v>
+        <v>0.0008155487769966139</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008382259962009055</v>
+        <v>0.0008216811666129175</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008267272754862434</v>
+        <v>0.0008114992947805409</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001077378504470377</v>
+        <v>0.001051189890112754</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008089183001973166</v>
+        <v>0.000799682632377068</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001051734278508363</v>
+        <v>0.001020212042479554</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0008633325360253377</v>
+        <v>0.0008367587222422858</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0008156270025483273</v>
+        <v>0.0008039092335336705</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0009818670647635521</v>
+        <v>0.00096579741062792</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008741129193014756</v>
+        <v>0.0008447055333565398</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0008553716159187748</v>
+        <v>0.0008306051514389677</v>
       </c>
     </row>
     <row r="4">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007952548167078379</v>
+        <v>0.0007891505606478003</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008737211814365991</v>
+        <v>0.0008659645880438808</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008051512950480842</v>
+        <v>0.0007957463019872759</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000919798149675522</v>
+        <v>0.0009092019638624286</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008120826079109963</v>
+        <v>0.0008004674853153308</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008104565784239534</v>
+        <v>0.0008004043683981422</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008119590542906006</v>
+        <v>0.0007999262042501668</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008123572335662454</v>
+        <v>0.0008005532569155902</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0008145445730632171</v>
+        <v>0.0008029397647350109</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0008030830772362954</v>
+        <v>0.0007944717019274104</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008092820723109916</v>
+        <v>0.0007996221642324042</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0007962157741134752</v>
+        <v>0.000789401735792634</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008211547198307195</v>
+        <v>0.0008071867456435941</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001138779292420187</v>
+        <v>0.001125240031848994</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008135913780031702</v>
+        <v>0.0008023316208663754</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007954591150400549</v>
+        <v>0.0007892312682161221</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008317208462636531</v>
+        <v>0.0008137356591331384</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008127887106306725</v>
+        <v>0.0008021990729666065</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007981881869889952</v>
+        <v>0.0007908311088408054</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001005913709554322</v>
+        <v>0.001000307731962587</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008154031263080338</v>
+        <v>0.0008038035555956506</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001024652911870215</v>
+        <v>0.001001904229069991</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0009283966012388402</v>
+        <v>0.0008828940740949922</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0008221953763235333</v>
+        <v>0.000807660292636941</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0009711740227967404</v>
+        <v>0.0009573317172716187</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.000841192707875859</v>
+        <v>0.0008209541431112846</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0007868275727247367</v>
+        <v>0.0007827485692998474</v>
       </c>
     </row>
     <row r="4">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000797539804207295</v>
+        <v>0.0007889085941839908</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008478472660815635</v>
+        <v>0.0008401229015121644</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007996359218492399</v>
+        <v>0.0007898113791649107</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0009283568258951487</v>
+        <v>0.0009154827317410353</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008004076003144135</v>
+        <v>0.0007901738773924219</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007938204079213518</v>
+        <v>0.0007862949249512377</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007930846030227985</v>
+        <v>0.0007849313340717565</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007934283200320894</v>
+        <v>0.0007853416687084866</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0008028215182279385</v>
+        <v>0.0007924983494868049</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007901690035977421</v>
+        <v>0.0007832710696858175</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008050199591221387</v>
+        <v>0.0007944624018513385</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000788008064332698</v>
+        <v>0.0007815423362850347</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008009414784864515</v>
+        <v>0.0007908467597671754</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001163048770598489</v>
+        <v>0.001141512717127664</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008156418224623635</v>
+        <v>0.0008021019139121837</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007860478342799975</v>
+        <v>0.0007804806921754</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008274362299591778</v>
+        <v>0.0008085805493921095</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008009331570743768</v>
+        <v>0.0007914401028893035</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007877844072561436</v>
+        <v>0.0007814907172689876</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0009445796398973187</v>
+        <v>0.0009385828029523303</v>
       </c>
       <c r="V3" t="n">
-        <v>0.000812287776897273</v>
+        <v>0.0007995686401566229</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0009558981720698208</v>
+        <v>0.0009374325142017977</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0009551129062812477</v>
+        <v>0.0009003521543869829</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0008120807583151413</v>
+        <v>0.0007984920527169791</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0009521303936926332</v>
+        <v>0.0009415620035381613</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008390379870787754</v>
+        <v>0.0008173770071716504</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0007868006804319157</v>
+        <v>0.0007806235909410877</v>
       </c>
     </row>
     <row r="4">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008839724003639662</v>
+        <v>0.0008570176496341529</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008883848013344346</v>
+        <v>0.0008803106101395075</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009034187588145898</v>
+        <v>0.0008677289823649611</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0009488239141627649</v>
+        <v>0.0009335867689722246</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008483743618862181</v>
+        <v>0.0008299484662542597</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009367389836814413</v>
+        <v>0.0008951262226606208</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008601943693078563</v>
+        <v>0.000837450323606686</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000915424388914086</v>
+        <v>0.0008759481426797324</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000933207293411641</v>
+        <v>0.0008911822887483162</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009767263919046587</v>
+        <v>0.0009222835773453129</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009360718676571179</v>
+        <v>0.0008929201920201353</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001254792923166322</v>
+        <v>0.001116451029162624</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0009804964377634431</v>
+        <v>0.0009219475665965572</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001206107347415879</v>
+        <v>0.001180690985299839</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0009192263910091884</v>
+        <v>0.0008816811877642363</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008669081794404892</v>
+        <v>0.0008434105277922211</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008728284798743902</v>
+        <v>0.0008462699057679499</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008971779626759523</v>
+        <v>0.0008670411625913272</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000905642744715802</v>
+        <v>0.0008692999792557221</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001167041009452643</v>
+        <v>0.001118090730857551</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008399370063425065</v>
+        <v>0.0008254970265877806</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001067703044888953</v>
+        <v>0.001035426879086247</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00093925595679921</v>
+        <v>0.0008929474543311184</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0008918773561468826</v>
+        <v>0.0008610580870736346</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001017350546745965</v>
+        <v>0.0009946023983221502</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00094524336085473</v>
+        <v>0.0008981313256303685</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001012127027486435</v>
+        <v>0.0009404932895380278</v>
       </c>
     </row>
     <row r="4">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007951881084070376</v>
+        <v>0.00079086963426179</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0008798609991468062</v>
+        <v>0.000872130151863825</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000816381508478262</v>
+        <v>0.0008052973757759514</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0009222731953613876</v>
+        <v>0.00091258789449289</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008100239848495771</v>
+        <v>0.0008008505929538782</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009106110089532708</v>
+        <v>0.0008748367523363318</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008179720724245756</v>
+        <v>0.0008058910113419904</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000815861743172825</v>
+        <v>0.0008047476483371849</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0008550287027346887</v>
+        <v>0.0008337412179819951</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0008360992704062702</v>
+        <v>0.0008199003222085941</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008649475098965688</v>
+        <v>0.0008409244384231556</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0008392312805723449</v>
+        <v>0.0008215598320627244</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008335028410967944</v>
+        <v>0.000817233857257079</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001133486892423341</v>
+        <v>0.001123436572103152</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008733354327235025</v>
+        <v>0.0008469011178655327</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008263866313343746</v>
+        <v>0.0008129791216668474</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008409587409753785</v>
+        <v>0.0008217707544497695</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008297478275838787</v>
+        <v>0.0008159068566477898</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00081568231496556</v>
+        <v>0.000804719368478461</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001034560689525617</v>
+        <v>0.001022832437476097</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008168122806804096</v>
+        <v>0.0008064477970003516</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001044351575843423</v>
+        <v>0.001017080651450921</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0009302185189231303</v>
+        <v>0.0008849363532519201</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.000939087842178379</v>
+        <v>0.000891412109728192</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0009632412701948043</v>
+        <v>0.0009528497962847286</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008403096011977302</v>
+        <v>0.0008221795604915535</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0009307321560412331</v>
+        <v>0.0008831181263229237</v>
       </c>
     </row>
     <row r="4">
